--- a/excel-format/db-column-definitions_fmt-v5.0.0-ja_my-app.xlsx
+++ b/excel-format/db-column-definitions_fmt-v5.0.0-ja_my-app.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yosuke.tanaka/Desktop/development/git/ecuacion-tool-code-generator/excel-format/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DDF771A-570F-834B-890D-90434FB761DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EF66E71-AFB0-444B-94E5-7499C2C1C498}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2320" windowWidth="28800" windowHeight="14820" tabRatio="853" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="2280" windowWidth="28800" windowHeight="14820" tabRatio="853" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="dataTypeプルダウン項目" sheetId="1" state="hidden" r:id="rId1"/>
@@ -25,7 +25,7 @@
     <sheet name="テーブル一覧" sheetId="10" r:id="rId10"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="7">DB項目定義!$A$1:$Z$5</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="7">DB項目定義!$A$1:$Y$5</definedName>
     <definedName name="一般">dataTypeプルダウン項目!$A$3:$A$16</definedName>
     <definedName name="固定フォーマット">dataTypeプルダウン項目!#REF!</definedName>
     <definedName name="日時">dataTypeプルダウン項目!#REF!</definedName>
@@ -124,7 +124,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="471" uniqueCount="285">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="469" uniqueCount="284">
   <si>
     <t>DB項目定義</t>
   </si>
@@ -190,9 +190,6 @@
   </si>
   <si>
     <t>関連：参照元変数名</t>
-  </si>
-  <si>
-    <t>関連：参照元オブジェクト変数名</t>
   </si>
   <si>
     <t>関連：参照先テーブル</t>
@@ -823,6 +820,326 @@
     <t>v5.0.0</t>
   </si>
   <si>
+    <t>各種設定</t>
+  </si>
+  <si>
+    <t>※「値」、「備考」列に記入。それ以外の列には触らないこと。「備考」は任意記載（システム影響なし）。</t>
+  </si>
+  <si>
+    <t>#</t>
+  </si>
+  <si>
+    <t>分類</t>
+  </si>
+  <si>
+    <t>分類名</t>
+  </si>
+  <si>
+    <t>項目</t>
+  </si>
+  <si>
+    <t>説明</t>
+  </si>
+  <si>
+    <t>必須</t>
+  </si>
+  <si>
+    <t>値</t>
+  </si>
+  <si>
+    <t>SYSTEM_COMMON</t>
+  </si>
+  <si>
+    <t>システム共通</t>
+  </si>
+  <si>
+    <t>TEMPLATE_VERSION</t>
+  </si>
+  <si>
+    <t>本エクセルファイルのテンプレートのバージョン</t>
+  </si>
+  <si>
+    <t>◯</t>
+  </si>
+  <si>
+    <t>5.0.0</t>
+  </si>
+  <si>
+    <t>SYSTEM_NAME</t>
+  </si>
+  <si>
+    <t>システム名
+※自動生成されたソースの親フォルダ名として使用</t>
+  </si>
+  <si>
+    <t>BASE_PACKAGE</t>
+  </si>
+  <si>
+    <t>packageの共通部分</t>
+  </si>
+  <si>
+    <t>frameworkの種類
+※指定した種類により生成されるコードが異なる</t>
+  </si>
+  <si>
+    <t>CHARSET</t>
+  </si>
+  <si>
+    <t>ソースコードの文字コード("UTF-8"推奨）</t>
+  </si>
+  <si>
+    <t>LANG_DEFAULT</t>
+  </si>
+  <si>
+    <t>デフォルト言語
+※"en"などlocaleとして定義されている文字列を指定。en_US等も可能</t>
+  </si>
+  <si>
+    <t>LANG_SUPPORT_01</t>
+  </si>
+  <si>
+    <t>サポート言語1
+※サポート言語は1, 2, 3の順序で入力。1が空欄、2が入力の状態等はエラー</t>
+  </si>
+  <si>
+    <t>LANG_SUPPORT_02</t>
+  </si>
+  <si>
+    <t>サポート言語2</t>
+  </si>
+  <si>
+    <t>LANG_SUPPORT_03</t>
+  </si>
+  <si>
+    <t>サポート言語3</t>
+  </si>
+  <si>
+    <t>PROHIBITED_CHARS</t>
+  </si>
+  <si>
+    <t>禁則文字</t>
+  </si>
+  <si>
+    <t>PROHIBITED_CHARS_DESC_LANG_DEFAULT</t>
+  </si>
+  <si>
+    <t>禁則文字パターン説明（デフォルト言語）
+※「禁則文字」が空欄でない場合は必須</t>
+  </si>
+  <si>
+    <t>PROHIBITED_CHARS_DESC_LANG_SUPPORT_01</t>
+  </si>
+  <si>
+    <t>禁則文字パターン説明（追加言語1）
+※「禁則文字」が空欄でない、かつ「サポート言語1」が空欄でない場合は必須</t>
+  </si>
+  <si>
+    <t>PROHIBITED_CHARS_DESC_LANG_SUPPORT_02</t>
+  </si>
+  <si>
+    <t>禁則文字パターン説明（追加言語2）
+※「禁則文字」が空欄でない、かつ「サポート言語2」が空欄でない場合は必須</t>
+  </si>
+  <si>
+    <t>PROHIBITED_CHARS_DESC_LANG_SUPPORT_03</t>
+  </si>
+  <si>
+    <t>禁則文字パターン説明（追加言語3）
+※「禁則文字」が空欄でない、かつ「サポート言語3」が空欄でない場合は必須</t>
+  </si>
+  <si>
+    <t>LOGICAL_DELETE</t>
+  </si>
+  <si>
+    <t>論理削除</t>
+  </si>
+  <si>
+    <t>COLUMN_NAME</t>
+  </si>
+  <si>
+    <t>論理削除を表す項目名
+※論理削除項目を使用しない場合は、本項目を空欄にする。その場合、以降の分類名が「論理削除」の項目も全て空欄にする
+※この名前を持つカラムは全てグループ指定項目とみなされるため、別の用途でこのカラム名を使うことがあるのであれば、名称の変更が必要
+※実際に論理削除機能を使用するには、「DB項目定義」または「DB共通項目定義」で指定の項目名の項目を定義する必要がある</t>
+  </si>
+  <si>
+    <t>DATA_TYPE_NAME</t>
+  </si>
+  <si>
+    <t>DataType名
+※本バージョンではBOOLEAN型のDataTypeのみ選択可</t>
+  </si>
+  <si>
+    <t>DEFAULT_VALUE</t>
+  </si>
+  <si>
+    <t>初期値（論理削除前）
+※DataTypeがBOOLEAN型の場合はtrue/falseを指定</t>
+  </si>
+  <si>
+    <t>UPDATE_VALUE</t>
+  </si>
+  <si>
+    <t>更新値（論理削除後）
+※記述方法は「DEFAULT_VALUE」を参照</t>
+  </si>
+  <si>
+    <t>GROUPING</t>
+  </si>
+  <si>
+    <t>他グループを閲覧不可とする設定</t>
+  </si>
+  <si>
+    <t>カラム名
+※グループ指定を使用しない場合は、本項目を空欄にする。（その場合、以降も全て空欄にする）
+※この名前を持つカラムは全てグループ指定項目とみなされるため、別の用途でこのカラム名を使うことがあるのであれば、名称の変更が必要
+※実際に論理削除機能を使用するには、「DB項目定義」または「DB共通項目定義」で指定の項目名の項目を定義する必要がある
+※この名前とは別名で、グループ指定をする項目を指定することが可能（グループ自体を表すEntityにて使用）。DB項目定義の「グループ識別項目」にチェックを入れることで可</t>
+  </si>
+  <si>
+    <t>DataType名</t>
+  </si>
+  <si>
+    <t>TABLE_NAMES_WITHOUT_GROUPING</t>
+  </si>
+  <si>
+    <t>意図しない設定漏れを防ぐため、グループ設定なしのテーブルを明示
+※複数ある場合は"TABLE_1,TABLE_2"のようにCSVで記載。</t>
+  </si>
+  <si>
+    <t>OPTIMISTIC_LOCKING</t>
+  </si>
+  <si>
+    <t>楽観的排他制御</t>
+  </si>
+  <si>
+    <t>カラム名
+※グループ指定を使用しない場合は、本項目を空欄にする。（その場合、以降も全て空欄にする）
+※この名前を持つカラムは全て楽観的排他制御用項目とみなされるため、別の用途でこのカラム名を使うことがあるのであれば、名称の変更が必要</t>
+  </si>
+  <si>
+    <t>※DataType名のプレフィックスは「DT_」固定</t>
+  </si>
+  <si>
+    <t>共通</t>
+  </si>
+  <si>
+    <t>STRINGの場合の入力項目</t>
+  </si>
+  <si>
+    <t>数値系の場合の入力項目</t>
+  </si>
+  <si>
+    <t>Enumの
+場合</t>
+  </si>
+  <si>
+    <t>日時の
+場合</t>
+  </si>
+  <si>
+    <t>任意</t>
+  </si>
+  <si>
+    <t>長さ最小</t>
+  </si>
+  <si>
+    <t>長さ最大</t>
+  </si>
+  <si>
+    <t>データパターン（日本語）</t>
+  </si>
+  <si>
+    <t>禁則文字チェック除外</t>
+  </si>
+  <si>
+    <t>正規表現</t>
+  </si>
+  <si>
+    <t>最小値</t>
+  </si>
+  <si>
+    <t>最大値</t>
+  </si>
+  <si>
+    <t>整数部桁数</t>
+  </si>
+  <si>
+    <t>小数部桁数</t>
+  </si>
+  <si>
+    <t>コードの長さ</t>
+  </si>
+  <si>
+    <t>timezoneなし</t>
+  </si>
+  <si>
+    <t>パターン説明（デフォルト言語）</t>
+  </si>
+  <si>
+    <t>パターン説明（追加言語1）</t>
+  </si>
+  <si>
+    <t>パターン説明（追加言語2）</t>
+  </si>
+  <si>
+    <t>パターン説明（追加言語）</t>
+  </si>
+  <si>
+    <t>enum定義</t>
+  </si>
+  <si>
+    <t>※Enumクラス名は、DataType名を元に自動生成される。</t>
+  </si>
+  <si>
+    <t>　　例）DT_TRANSACTION_STATUS　→　Enumクラス名：TransactionStatusEnum</t>
+  </si>
+  <si>
+    <t>code</t>
+  </si>
+  <si>
+    <t>varName</t>
+  </si>
+  <si>
+    <t>表示名（デフォルト言語）</t>
+  </si>
+  <si>
+    <t>表示名（追加言語1）</t>
+  </si>
+  <si>
+    <t>表示名（追加言語2）</t>
+  </si>
+  <si>
+    <t>表示名（追加言語3）</t>
+  </si>
+  <si>
+    <t>DB共通項目定義</t>
+  </si>
+  <si>
+    <t>テーブル一覧</t>
+  </si>
+  <si>
+    <t>テーブル表示名（デフォルト言語）</t>
+  </si>
+  <si>
+    <t>テーブル表示名（追加言語1）</t>
+  </si>
+  <si>
+    <t>テーブル表示名（追加言語2）</t>
+  </si>
+  <si>
+    <t>テーブル表示名（追加言語3）</t>
+  </si>
+  <si>
+    <t>VERSION</t>
+  </si>
+  <si>
+    <t>UTF-8</t>
+  </si>
+  <si>
+    <t>ja</t>
+  </si>
+  <si>
     <t>■バージョン情報
 ・対応code-generator version: 15.0.0-beta.3 以降
 ・前minorバージョンからのformat移行が必要な場合：必須
@@ -832,328 +1149,7 @@
 ・ファイル名の形式変更
 ▼「DB項目定義」・「DB共通項目定義」シート
 　・「PK・UK」列を、「Surrogate key」と「natural key (unique key)」 の2つの列に分割。
-　　また、もともと「S・U」で記載していたのを、「○」で記載するよう変更
-　・「関連：参照元オブジェクト変数名」列を追加</t>
-  </si>
-  <si>
-    <t>各種設定</t>
-  </si>
-  <si>
-    <t>※「値」、「備考」列に記入。それ以外の列には触らないこと。「備考」は任意記載（システム影響なし）。</t>
-  </si>
-  <si>
-    <t>#</t>
-  </si>
-  <si>
-    <t>分類</t>
-  </si>
-  <si>
-    <t>分類名</t>
-  </si>
-  <si>
-    <t>項目</t>
-  </si>
-  <si>
-    <t>説明</t>
-  </si>
-  <si>
-    <t>必須</t>
-  </si>
-  <si>
-    <t>値</t>
-  </si>
-  <si>
-    <t>SYSTEM_COMMON</t>
-  </si>
-  <si>
-    <t>システム共通</t>
-  </si>
-  <si>
-    <t>TEMPLATE_VERSION</t>
-  </si>
-  <si>
-    <t>本エクセルファイルのテンプレートのバージョン</t>
-  </si>
-  <si>
-    <t>◯</t>
-  </si>
-  <si>
-    <t>5.0.0</t>
-  </si>
-  <si>
-    <t>SYSTEM_NAME</t>
-  </si>
-  <si>
-    <t>システム名
-※自動生成されたソースの親フォルダ名として使用</t>
-  </si>
-  <si>
-    <t>BASE_PACKAGE</t>
-  </si>
-  <si>
-    <t>packageの共通部分</t>
-  </si>
-  <si>
-    <t>frameworkの種類
-※指定した種類により生成されるコードが異なる</t>
-  </si>
-  <si>
-    <t>CHARSET</t>
-  </si>
-  <si>
-    <t>ソースコードの文字コード("UTF-8"推奨）</t>
-  </si>
-  <si>
-    <t>LANG_DEFAULT</t>
-  </si>
-  <si>
-    <t>デフォルト言語
-※"en"などlocaleとして定義されている文字列を指定。en_US等も可能</t>
-  </si>
-  <si>
-    <t>LANG_SUPPORT_01</t>
-  </si>
-  <si>
-    <t>サポート言語1
-※サポート言語は1, 2, 3の順序で入力。1が空欄、2が入力の状態等はエラー</t>
-  </si>
-  <si>
-    <t>LANG_SUPPORT_02</t>
-  </si>
-  <si>
-    <t>サポート言語2</t>
-  </si>
-  <si>
-    <t>LANG_SUPPORT_03</t>
-  </si>
-  <si>
-    <t>サポート言語3</t>
-  </si>
-  <si>
-    <t>PROHIBITED_CHARS</t>
-  </si>
-  <si>
-    <t>禁則文字</t>
-  </si>
-  <si>
-    <t>PROHIBITED_CHARS_DESC_LANG_DEFAULT</t>
-  </si>
-  <si>
-    <t>禁則文字パターン説明（デフォルト言語）
-※「禁則文字」が空欄でない場合は必須</t>
-  </si>
-  <si>
-    <t>PROHIBITED_CHARS_DESC_LANG_SUPPORT_01</t>
-  </si>
-  <si>
-    <t>禁則文字パターン説明（追加言語1）
-※「禁則文字」が空欄でない、かつ「サポート言語1」が空欄でない場合は必須</t>
-  </si>
-  <si>
-    <t>PROHIBITED_CHARS_DESC_LANG_SUPPORT_02</t>
-  </si>
-  <si>
-    <t>禁則文字パターン説明（追加言語2）
-※「禁則文字」が空欄でない、かつ「サポート言語2」が空欄でない場合は必須</t>
-  </si>
-  <si>
-    <t>PROHIBITED_CHARS_DESC_LANG_SUPPORT_03</t>
-  </si>
-  <si>
-    <t>禁則文字パターン説明（追加言語3）
-※「禁則文字」が空欄でない、かつ「サポート言語3」が空欄でない場合は必須</t>
-  </si>
-  <si>
-    <t>LOGICAL_DELETE</t>
-  </si>
-  <si>
-    <t>論理削除</t>
-  </si>
-  <si>
-    <t>COLUMN_NAME</t>
-  </si>
-  <si>
-    <t>論理削除を表す項目名
-※論理削除項目を使用しない場合は、本項目を空欄にする。その場合、以降の分類名が「論理削除」の項目も全て空欄にする
-※この名前を持つカラムは全てグループ指定項目とみなされるため、別の用途でこのカラム名を使うことがあるのであれば、名称の変更が必要
-※実際に論理削除機能を使用するには、「DB項目定義」または「DB共通項目定義」で指定の項目名の項目を定義する必要がある</t>
-  </si>
-  <si>
-    <t>DATA_TYPE_NAME</t>
-  </si>
-  <si>
-    <t>DataType名
-※本バージョンではBOOLEAN型のDataTypeのみ選択可</t>
-  </si>
-  <si>
-    <t>DEFAULT_VALUE</t>
-  </si>
-  <si>
-    <t>初期値（論理削除前）
-※DataTypeがBOOLEAN型の場合はtrue/falseを指定</t>
-  </si>
-  <si>
-    <t>UPDATE_VALUE</t>
-  </si>
-  <si>
-    <t>更新値（論理削除後）
-※記述方法は「DEFAULT_VALUE」を参照</t>
-  </si>
-  <si>
-    <t>GROUPING</t>
-  </si>
-  <si>
-    <t>他グループを閲覧不可とする設定</t>
-  </si>
-  <si>
-    <t>カラム名
-※グループ指定を使用しない場合は、本項目を空欄にする。（その場合、以降も全て空欄にする）
-※この名前を持つカラムは全てグループ指定項目とみなされるため、別の用途でこのカラム名を使うことがあるのであれば、名称の変更が必要
-※実際に論理削除機能を使用するには、「DB項目定義」または「DB共通項目定義」で指定の項目名の項目を定義する必要がある
-※この名前とは別名で、グループ指定をする項目を指定することが可能（グループ自体を表すEntityにて使用）。DB項目定義の「グループ識別項目」にチェックを入れることで可</t>
-  </si>
-  <si>
-    <t>DataType名</t>
-  </si>
-  <si>
-    <t>TABLE_NAMES_WITHOUT_GROUPING</t>
-  </si>
-  <si>
-    <t>意図しない設定漏れを防ぐため、グループ設定なしのテーブルを明示
-※複数ある場合は"TABLE_1,TABLE_2"のようにCSVで記載。</t>
-  </si>
-  <si>
-    <t>OPTIMISTIC_LOCKING</t>
-  </si>
-  <si>
-    <t>楽観的排他制御</t>
-  </si>
-  <si>
-    <t>カラム名
-※グループ指定を使用しない場合は、本項目を空欄にする。（その場合、以降も全て空欄にする）
-※この名前を持つカラムは全て楽観的排他制御用項目とみなされるため、別の用途でこのカラム名を使うことがあるのであれば、名称の変更が必要</t>
-  </si>
-  <si>
-    <t>※DataType名のプレフィックスは「DT_」固定</t>
-  </si>
-  <si>
-    <t>共通</t>
-  </si>
-  <si>
-    <t>STRINGの場合の入力項目</t>
-  </si>
-  <si>
-    <t>数値系の場合の入力項目</t>
-  </si>
-  <si>
-    <t>Enumの
-場合</t>
-  </si>
-  <si>
-    <t>日時の
-場合</t>
-  </si>
-  <si>
-    <t>任意</t>
-  </si>
-  <si>
-    <t>長さ最小</t>
-  </si>
-  <si>
-    <t>長さ最大</t>
-  </si>
-  <si>
-    <t>データパターン（日本語）</t>
-  </si>
-  <si>
-    <t>禁則文字チェック除外</t>
-  </si>
-  <si>
-    <t>正規表現</t>
-  </si>
-  <si>
-    <t>最小値</t>
-  </si>
-  <si>
-    <t>最大値</t>
-  </si>
-  <si>
-    <t>整数部桁数</t>
-  </si>
-  <si>
-    <t>小数部桁数</t>
-  </si>
-  <si>
-    <t>コードの長さ</t>
-  </si>
-  <si>
-    <t>timezoneなし</t>
-  </si>
-  <si>
-    <t>パターン説明（デフォルト言語）</t>
-  </si>
-  <si>
-    <t>パターン説明（追加言語1）</t>
-  </si>
-  <si>
-    <t>パターン説明（追加言語2）</t>
-  </si>
-  <si>
-    <t>パターン説明（追加言語）</t>
-  </si>
-  <si>
-    <t>enum定義</t>
-  </si>
-  <si>
-    <t>※Enumクラス名は、DataType名を元に自動生成される。</t>
-  </si>
-  <si>
-    <t>　　例）DT_TRANSACTION_STATUS　→　Enumクラス名：TransactionStatusEnum</t>
-  </si>
-  <si>
-    <t>code</t>
-  </si>
-  <si>
-    <t>varName</t>
-  </si>
-  <si>
-    <t>表示名（デフォルト言語）</t>
-  </si>
-  <si>
-    <t>表示名（追加言語1）</t>
-  </si>
-  <si>
-    <t>表示名（追加言語2）</t>
-  </si>
-  <si>
-    <t>表示名（追加言語3）</t>
-  </si>
-  <si>
-    <t>DB共通項目定義</t>
-  </si>
-  <si>
-    <t>テーブル一覧</t>
-  </si>
-  <si>
-    <t>テーブル表示名（デフォルト言語）</t>
-  </si>
-  <si>
-    <t>テーブル表示名（追加言語1）</t>
-  </si>
-  <si>
-    <t>テーブル表示名（追加言語2）</t>
-  </si>
-  <si>
-    <t>テーブル表示名（追加言語3）</t>
-  </si>
-  <si>
-    <t>VERSION</t>
-  </si>
-  <si>
-    <t>UTF-8</t>
-  </si>
-  <si>
-    <t>ja</t>
+　　また、もともと「S・U」で記載していたのを、「○」で記載するよう変更</t>
   </si>
 </sst>
 </file>
@@ -1928,7 +1924,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="標準 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
-  <dxfs count="124">
+  <dxfs count="122">
     <dxf>
       <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="center" vertical="center"/>
@@ -2312,22 +2308,6 @@
         <horizontal/>
       </border>
       <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="center" vertical="center"/>
-      <border>
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
     </dxf>
     <dxf>
       <numFmt numFmtId="30" formatCode="@"/>
@@ -2869,24 +2849,6 @@
         <sz val="11"/>
         <color theme="1"/>
         <name val="ＭＳ Ｐゴシック"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
       </font>
@@ -3453,114 +3415,114 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="テーブル5" displayName="テーブル5" ref="A3:D39" totalsRowShown="0" headerRowDxfId="114" dataDxfId="113">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="テーブル5" displayName="テーブル5" ref="A3:D39" totalsRowShown="0" headerRowDxfId="112" dataDxfId="111">
   <autoFilter ref="A3:D39" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="日付" dataDxfId="112"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="バージョン" dataDxfId="111"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="修正事項" dataDxfId="110"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="修正者" dataDxfId="109"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="日付" dataDxfId="110"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="バージョン" dataDxfId="109"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="修正事項" dataDxfId="108"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="修正者" dataDxfId="107"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="テーブル50" displayName="テーブル50" ref="A5:H28" totalsRowShown="0" dataDxfId="123">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="テーブル50" displayName="テーブル50" ref="A5:H28" totalsRowShown="0" dataDxfId="121">
   <autoFilter ref="A5:H28" xr:uid="{00000000-0009-0000-0100-000004000000}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="#" dataDxfId="122">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="#" dataDxfId="120">
       <calculatedColumnFormula>ROW()-5</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0300-000008000000}" name="分類" dataDxfId="121"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="分類名" dataDxfId="120"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="項目" dataDxfId="119"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="説明" dataDxfId="118"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0300-000009000000}" name="必須" dataDxfId="117"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0300-000005000000}" name="値" dataDxfId="116"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0300-000006000000}" name="備考" dataDxfId="115"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0300-000008000000}" name="分類" dataDxfId="119"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="分類名" dataDxfId="118"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="項目" dataDxfId="117"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="説明" dataDxfId="116"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0300-000009000000}" name="必須" dataDxfId="115"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0300-000005000000}" name="値" dataDxfId="114"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0300-000006000000}" name="備考" dataDxfId="113"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="テーブル2" displayName="テーブル2" ref="A7:S37" tableType="xml" totalsRowShown="0" headerRowDxfId="108" dataDxfId="107">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="テーブル2" displayName="テーブル2" ref="A7:S37" tableType="xml" totalsRowShown="0" headerRowDxfId="106" dataDxfId="105">
   <tableColumns count="19">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" uniqueName="name" name="DataType名" dataDxfId="106">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" uniqueName="name" name="DataType名" dataDxfId="104">
       <xmlColumnPr mapId="191" xpath="/root/datatype/@name" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" uniqueName="kata" name="型" dataDxfId="105">
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" uniqueName="kata" name="型" dataDxfId="103">
       <xmlColumnPr mapId="191" xpath="/root/datatype/kata" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0400-000004000000}" uniqueName="minLength" name="長さ最小" dataDxfId="104">
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0400-000004000000}" uniqueName="minLength" name="長さ最小" dataDxfId="102">
       <xmlColumnPr mapId="191" xpath="/root/datatype/minLength" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0400-00000B000000}" uniqueName="maxLength" name="長さ最大" dataDxfId="103">
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0400-00000B000000}" uniqueName="maxLength" name="長さ最大" dataDxfId="101">
       <xmlColumnPr mapId="191" xpath="/root/datatype/maxLength" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0400-00000F000000}" uniqueName="numScale" name="データパターン（日本語）" dataDxfId="102"/>
-    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0400-000018000000}" uniqueName="stringDataPtn" name="データパターン" dataDxfId="101">
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0400-00000F000000}" uniqueName="numScale" name="データパターン（日本語）" dataDxfId="100"/>
+    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0400-000018000000}" uniqueName="stringDataPtn" name="データパターン" dataDxfId="99">
       <calculatedColumnFormula>IF(テーブル2[[#This Row],[データパターン（日本語）]]="", "", VLOOKUP(テーブル2[[#This Row],[データパターン（日本語）]],dataType・データパターン一覧!A:B,2,FALSE))</calculatedColumnFormula>
       <xmlColumnPr mapId="191" xpath="/root/datatype/stringDataPtn" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0400-000012000000}" uniqueName="18" name="禁則文字チェック除外" dataDxfId="100"/>
-    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0400-000019000000}" uniqueName="stringRegEx" name="正規表現" dataDxfId="99">
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0400-000012000000}" uniqueName="18" name="禁則文字チェック除外" dataDxfId="98"/>
+    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0400-000019000000}" uniqueName="stringRegEx" name="正規表現" dataDxfId="97">
       <xmlColumnPr mapId="191" xpath="/root/datatype/stringRegEx" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0400-000009000000}" uniqueName="numMinVal" name="最小値" dataDxfId="98">
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0400-000009000000}" uniqueName="numMinVal" name="最小値" dataDxfId="96">
       <xmlColumnPr mapId="191" xpath="/root/datatype/numMinVal" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0400-00000A000000}" uniqueName="numMaxVal" name="最大値" dataDxfId="97">
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0400-00000A000000}" uniqueName="numMaxVal" name="最大値" dataDxfId="95">
       <xmlColumnPr mapId="191" xpath="/root/datatype/numMaxVal" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0400-00000C000000}" uniqueName="numDigitInteger" name="整数部桁数" dataDxfId="96">
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0400-00000C000000}" uniqueName="numDigitInteger" name="整数部桁数" dataDxfId="94">
       <xmlColumnPr mapId="191" xpath="/root/datatype/numDigitInteger" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0400-00000D000000}" uniqueName="numDigitFraction" name="小数部桁数" dataDxfId="95">
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0400-00000D000000}" uniqueName="numDigitFraction" name="小数部桁数" dataDxfId="93">
       <xmlColumnPr mapId="191" xpath="/root/datatype/numDigitFraction" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0400-000005000000}" uniqueName="enumCodeLength" name="コードの長さ" dataDxfId="94">
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0400-000005000000}" uniqueName="enumCodeLength" name="コードの長さ" dataDxfId="92">
       <xmlColumnPr mapId="191" xpath="/root/datatype/enumCodeLength" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0400-00000E000000}" uniqueName="notNeedsTimezone" name="timezoneなし" dataDxfId="93">
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0400-00000E000000}" uniqueName="notNeedsTimezone" name="timezoneなし" dataDxfId="91">
       <xmlColumnPr mapId="191" xpath="/root/datatype/notNeedsTimezone" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0400-000010000000}" uniqueName="javadoc" name="備考" dataDxfId="92">
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0400-000010000000}" uniqueName="javadoc" name="備考" dataDxfId="90">
       <xmlColumnPr mapId="191" xpath="/root/datatype/javadoc" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" uniqueName="2" name="パターン説明（デフォルト言語）" dataDxfId="91"/>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0400-000013000000}" uniqueName="19" name="パターン説明（追加言語1）" dataDxfId="90"/>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0400-000014000000}" uniqueName="20" name="パターン説明（追加言語2）" dataDxfId="89"/>
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0400-000015000000}" uniqueName="21" name="パターン説明（追加言語）" dataDxfId="88"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" uniqueName="2" name="パターン説明（デフォルト言語）" dataDxfId="89"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0400-000013000000}" uniqueName="19" name="パターン説明（追加言語1）" dataDxfId="88"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0400-000014000000}" uniqueName="20" name="パターン説明（追加言語2）" dataDxfId="87"/>
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0400-000015000000}" uniqueName="21" name="パターン説明（追加言語）" dataDxfId="86"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{00000000-000C-0000-FFFF-FFFF05000000}" name="テーブル4" displayName="テーブル4" ref="A6:I33" tableType="xml" totalsRowShown="0" headerRowDxfId="87" dataDxfId="86">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{00000000-000C-0000-FFFF-FFFF05000000}" name="テーブル4" displayName="テーブル4" ref="A6:I33" tableType="xml" totalsRowShown="0" headerRowDxfId="85" dataDxfId="84">
   <autoFilter ref="A6:I33" xr:uid="{00000000-0009-0000-0100-000006000000}"/>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0500-000001000000}" uniqueName="dataTypeName" name="DataType名" dataDxfId="85">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0500-000001000000}" uniqueName="dataTypeName" name="DataType名" dataDxfId="83">
       <xmlColumnPr mapId="132" xpath="/root/enum/dataTypeName" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0500-000008000000}" uniqueName="8" name="code" dataDxfId="84"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0500-000005000000}" uniqueName="varName" name="varName" dataDxfId="83">
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0500-000008000000}" uniqueName="8" name="code" dataDxfId="82"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0500-000005000000}" uniqueName="varName" name="varName" dataDxfId="81">
       <xmlColumnPr mapId="132" xpath="/root/enum/varName" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0500-00000A000000}" uniqueName="10" name="javaのみ" dataDxfId="82"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0500-00000C000000}" uniqueName="javadoc-value" name="備考" dataDxfId="81">
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0500-00000A000000}" uniqueName="10" name="javaのみ" dataDxfId="80"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0500-00000C000000}" uniqueName="javadoc-value" name="備考" dataDxfId="79">
       <xmlColumnPr mapId="132" xpath="/root/enum/javadoc-value" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0500-000009000000}" uniqueName="9" name="表示名（デフォルト言語）" dataDxfId="80"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0500-000004000000}" uniqueName="dispNameAddLang1" name="表示名（追加言語1）" dataDxfId="79">
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0500-000009000000}" uniqueName="9" name="表示名（デフォルト言語）" dataDxfId="78"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0500-000004000000}" uniqueName="dispNameAddLang1" name="表示名（追加言語1）" dataDxfId="77">
       <xmlColumnPr mapId="132" xpath="/root/enum/dispNameAddLang1" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0500-000006000000}" uniqueName="dispNameAddLang2" name="表示名（追加言語2）" dataDxfId="78">
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0500-000006000000}" uniqueName="dispNameAddLang2" name="表示名（追加言語2）" dataDxfId="76">
       <xmlColumnPr mapId="132" xpath="/root/enum/dispNameAddLang2" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0500-000007000000}" uniqueName="dispNameAddLang3" name="表示名（追加言語3）" dataDxfId="77">
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0500-000007000000}" uniqueName="dispNameAddLang3" name="表示名（追加言語3）" dataDxfId="75">
       <xmlColumnPr mapId="132" xpath="/root/enum/dispNameAddLang3" xmlDataType="string"/>
     </tableColumn>
   </tableColumns>
@@ -3569,82 +3531,81 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{00000000-000C-0000-FFFF-FFFF06000000}" name="テーブル7" displayName="テーブル7" ref="A5:AK119" tableType="xml" totalsRowShown="0" headerRowDxfId="76" dataDxfId="75">
-  <autoFilter ref="A5:AK119" xr:uid="{00000000-0009-0000-0100-000007000000}"/>
-  <tableColumns count="37">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0600-000001000000}" uniqueName="table" name="テーブル名" dataDxfId="74">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{00000000-000C-0000-FFFF-FFFF06000000}" name="テーブル7" displayName="テーブル7" ref="A5:AJ119" tableType="xml" totalsRowShown="0" headerRowDxfId="74" dataDxfId="73">
+  <autoFilter ref="A5:AJ119" xr:uid="{00000000-0009-0000-0100-000007000000}"/>
+  <tableColumns count="36">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0600-000001000000}" uniqueName="table" name="テーブル名" dataDxfId="72">
       <xmlColumnPr mapId="161" xpath="/root/column/table" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0600-000002000000}" uniqueName="name" name="カラム名" dataDxfId="73">
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0600-000002000000}" uniqueName="name" name="カラム名" dataDxfId="71">
       <xmlColumnPr mapId="161" xpath="/root/column/@name" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0600-00000F000000}" uniqueName="dataType" name="dataType" dataDxfId="72">
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0600-00000F000000}" uniqueName="dataType" name="dataType" dataDxfId="70">
       <xmlColumnPr mapId="161" xpath="/root/column/dataType" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0600-000010000000}" uniqueName="16" name="dataType存在確認" dataDxfId="71">
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0600-000010000000}" uniqueName="16" name="dataType存在確認" dataDxfId="69">
       <calculatedColumnFormula>IF(テーブル7[[#This Row],[dataType]]="","",IF(NOT(ISNA(VLOOKUP(テーブル7[[#This Row],[dataType]], dataType定義!A:A, 1,FALSE))), "○", "×"))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0600-00001C000000}" uniqueName="28" name="javaのみ" dataDxfId="70"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0600-000006000000}" uniqueName="pk" name="Surrogate key " dataDxfId="69">
+    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0600-00001C000000}" uniqueName="28" name="javaのみ" dataDxfId="68"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0600-000006000000}" uniqueName="pk" name="Surrogate key " dataDxfId="67">
       <xmlColumnPr mapId="161" xpath="/root/column/pk" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="29" xr3:uid="{00000000-0010-0000-0600-00001D000000}" uniqueName="29" name="natural key (unique key)" dataDxfId="68"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0600-000008000000}" uniqueName="nullable" name="nullable" dataDxfId="67">
+    <tableColumn id="29" xr3:uid="{00000000-0010-0000-0600-00001D000000}" uniqueName="29" name="natural key (unique key)" dataDxfId="66"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0600-000008000000}" uniqueName="nullable" name="nullable" dataDxfId="65">
       <xmlColumnPr mapId="161" xpath="/root/column/nullable" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0600-00000A000000}" uniqueName="autoIncrement" name="自動採番" dataDxfId="66">
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0600-00000A000000}" uniqueName="autoIncrement" name="自動採番" dataDxfId="64">
       <xmlColumnPr mapId="161" xpath="/root/column/autoIncrement" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0600-000015000000}" uniqueName="forcedIncrement" name="強制採番" dataDxfId="65">
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0600-000015000000}" uniqueName="forcedIncrement" name="強制採番" dataDxfId="63">
       <xmlColumnPr mapId="161" xpath="/root/column/forcedIncrement" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0600-00000B000000}" uniqueName="autoUpdate" name="自動更新" dataDxfId="64">
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0600-00000B000000}" uniqueName="autoUpdate" name="自動更新" dataDxfId="62">
       <xmlColumnPr mapId="161" xpath="/root/column/autoUpdate" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0600-000014000000}" uniqueName="forcedUpdate" name="強制更新" dataDxfId="63">
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0600-000014000000}" uniqueName="forcedUpdate" name="強制更新" dataDxfId="61">
       <xmlColumnPr mapId="161" xpath="/root/column/forcedUpdate" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0600-00000C000000}" uniqueName="valueChangeMethod" name="グループ識別項目" dataDxfId="62">
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0600-00000C000000}" uniqueName="valueChangeMethod" name="グループ識別項目" dataDxfId="60">
       <xmlColumnPr mapId="161" xpath="/root/column/valueChangeMethod" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0600-000012000000}" uniqueName="updatedValue" name="SPRING監査" dataDxfId="61">
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0600-000012000000}" uniqueName="updatedValue" name="SPRING監査" dataDxfId="59">
       <xmlColumnPr mapId="161" xpath="/root/column/updatedValue" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0600-000013000000}" uniqueName="optLock" name="関連：種類" dataDxfId="60">
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0600-000013000000}" uniqueName="optLock" name="関連：種類" dataDxfId="58">
       <xmlColumnPr mapId="161" xpath="/root/column/optLock" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0600-000016000000}" uniqueName="22" name="関連：direction" dataDxfId="59"/>
-    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0600-00001A000000}" uniqueName="26" name="関連：参照元変数名" dataDxfId="58"/>
-    <tableColumn id="31" xr3:uid="{00000000-0010-0000-0600-00001F000000}" uniqueName="31" name="関連：参照元オブジェクト変数名" dataDxfId="57"/>
-    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0600-000017000000}" uniqueName="23" name="関連：参照先テーブル" dataDxfId="56"/>
-    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0600-000018000000}" uniqueName="24" name="関連：参照先カラム" dataDxfId="55"/>
-    <tableColumn id="27" xr3:uid="{00000000-0010-0000-0600-00001B000000}" uniqueName="27" name="関連：参照先変数名" dataDxfId="54"/>
-    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0600-000019000000}" uniqueName="25" name="関連：eager" dataDxfId="53"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0600-000011000000}" uniqueName="index1" name="index1" dataDxfId="52">
+    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0600-000016000000}" uniqueName="22" name="関連：direction" dataDxfId="57"/>
+    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0600-00001A000000}" uniqueName="26" name="関連：参照元変数名" dataDxfId="56"/>
+    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0600-000017000000}" uniqueName="23" name="関連：参照先テーブル" dataDxfId="55"/>
+    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0600-000018000000}" uniqueName="24" name="関連：参照先カラム" dataDxfId="54"/>
+    <tableColumn id="27" xr3:uid="{00000000-0010-0000-0600-00001B000000}" uniqueName="27" name="関連：参照先変数名" dataDxfId="53"/>
+    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0600-000019000000}" uniqueName="25" name="関連：eager" dataDxfId="52"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0600-000011000000}" uniqueName="index1" name="index1" dataDxfId="51">
       <xmlColumnPr mapId="161" xpath="/root/column/index1" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0600-00000E000000}" uniqueName="index2" name="index2" dataDxfId="51">
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0600-00000E000000}" uniqueName="index2" name="index2" dataDxfId="50">
       <xmlColumnPr mapId="161" xpath="/root/column/index2" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0600-00000D000000}" uniqueName="index3" name="index3" dataDxfId="50">
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0600-00000D000000}" uniqueName="index3" name="index3" dataDxfId="49">
       <xmlColumnPr mapId="161" xpath="/root/column/index3" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="34" xr3:uid="{00000000-0010-0000-0600-000022000000}" uniqueName="34" name="index4" dataDxfId="49"/>
-    <tableColumn id="35" xr3:uid="{00000000-0010-0000-0600-000023000000}" uniqueName="35" name="index5" dataDxfId="48"/>
-    <tableColumn id="36" xr3:uid="{00000000-0010-0000-0600-000024000000}" uniqueName="36" name="index6" dataDxfId="47"/>
-    <tableColumn id="37" xr3:uid="{00000000-0010-0000-0600-000025000000}" uniqueName="37" name="index7" dataDxfId="46"/>
-    <tableColumn id="38" xr3:uid="{00000000-0010-0000-0600-000026000000}" uniqueName="38" name="index8" dataDxfId="45"/>
-    <tableColumn id="39" xr3:uid="{00000000-0010-0000-0600-000027000000}" uniqueName="39" name="index9" dataDxfId="44"/>
-    <tableColumn id="40" xr3:uid="{00000000-0010-0000-0600-000028000000}" uniqueName="40" name="index10" dataDxfId="43"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0600-000005000000}" uniqueName="dispNameAddLang1" name="備考" dataDxfId="42"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0600-000009000000}" uniqueName="9" name="カラム表示名（デフォルト言語）" dataDxfId="41"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0600-000003000000}" uniqueName="dispNameAddLang1" name="カラム表示名（追加言語1）" dataDxfId="40">
+    <tableColumn id="34" xr3:uid="{00000000-0010-0000-0600-000022000000}" uniqueName="34" name="index4" dataDxfId="48"/>
+    <tableColumn id="35" xr3:uid="{00000000-0010-0000-0600-000023000000}" uniqueName="35" name="index5" dataDxfId="47"/>
+    <tableColumn id="36" xr3:uid="{00000000-0010-0000-0600-000024000000}" uniqueName="36" name="index6" dataDxfId="46"/>
+    <tableColumn id="37" xr3:uid="{00000000-0010-0000-0600-000025000000}" uniqueName="37" name="index7" dataDxfId="45"/>
+    <tableColumn id="38" xr3:uid="{00000000-0010-0000-0600-000026000000}" uniqueName="38" name="index8" dataDxfId="44"/>
+    <tableColumn id="39" xr3:uid="{00000000-0010-0000-0600-000027000000}" uniqueName="39" name="index9" dataDxfId="43"/>
+    <tableColumn id="40" xr3:uid="{00000000-0010-0000-0600-000028000000}" uniqueName="40" name="index10" dataDxfId="42"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0600-000005000000}" uniqueName="dispNameAddLang1" name="備考" dataDxfId="41"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0600-000009000000}" uniqueName="9" name="カラム表示名（デフォルト言語）" dataDxfId="40"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0600-000003000000}" uniqueName="dispNameAddLang1" name="カラム表示名（追加言語1）" dataDxfId="39">
       <xmlColumnPr mapId="161" xpath="/root/column/dispNameAddLang1" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0600-000004000000}" uniqueName="dispNameAddLang2" name="カラム表示名（追加言語2）" dataDxfId="39">
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0600-000004000000}" uniqueName="dispNameAddLang2" name="カラム表示名（追加言語2）" dataDxfId="38">
       <xmlColumnPr mapId="161" xpath="/root/column/dispNameAddLang2" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0600-000007000000}" uniqueName="dispNameAddLang3" name="カラム表示名（追加言語3）" dataDxfId="38">
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0600-000007000000}" uniqueName="dispNameAddLang3" name="カラム表示名（追加言語3）" dataDxfId="37">
       <xmlColumnPr mapId="161" xpath="/root/column/dispNameAddLang3" xmlDataType="string"/>
     </tableColumn>
   </tableColumns>
@@ -3653,29 +3614,28 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{00000000-000C-0000-FFFF-FFFF07000000}" name="テーブル74" displayName="テーブル74" ref="A5:AK13" totalsRowShown="0" headerRowDxfId="37" dataDxfId="36">
-  <autoFilter ref="A5:AK13" xr:uid="{00000000-0009-0000-0100-000008000000}"/>
-  <tableColumns count="37">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0700-000001000000}" name="テーブル名" dataDxfId="35"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0700-000002000000}" name="カラム名" dataDxfId="34"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0700-00000F000000}" name="dataType" dataDxfId="33"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0700-000010000000}" name="dataType存在確認" dataDxfId="32">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{00000000-000C-0000-FFFF-FFFF07000000}" name="テーブル74" displayName="テーブル74" ref="A5:AJ13" totalsRowShown="0" headerRowDxfId="36" dataDxfId="35">
+  <autoFilter ref="A5:AJ13" xr:uid="{00000000-0009-0000-0100-000008000000}"/>
+  <tableColumns count="36">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0700-000001000000}" name="テーブル名" dataDxfId="34"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0700-000002000000}" name="カラム名" dataDxfId="33"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0700-00000F000000}" name="dataType" dataDxfId="32"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0700-000010000000}" name="dataType存在確認" dataDxfId="31">
       <calculatedColumnFormula>IF(C6="","",IF(テーブル74[[#This Row],[dataType]]="","",IF(NOT(ISNA(VLOOKUP(テーブル74[[#This Row],[dataType]], dataType定義!A:A, 1,FALSE))), "○", "×")))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0700-00001C000000}" name="javaのみ" dataDxfId="31"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0700-000006000000}" name="Surrogate key " dataDxfId="30"/>
+    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0700-00001C000000}" name="javaのみ" dataDxfId="30"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0700-000006000000}" name="Surrogate key " dataDxfId="29"/>
     <tableColumn id="9" xr3:uid="{00000000-0010-0000-0700-000009000000}" name="natural key (unique key)"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0700-000008000000}" name="nullable" dataDxfId="29"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0700-00000A000000}" name="自動採番" dataDxfId="28"/>
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0700-000015000000}" name="強制採番" dataDxfId="27"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0700-00000B000000}" name="自動更新" dataDxfId="26"/>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0700-000014000000}" name="強制更新" dataDxfId="25"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0700-00000C000000}" name="グループ識別項目" dataDxfId="24"/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0700-000012000000}" name="SPRING監査" dataDxfId="23"/>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0700-000013000000}" name="関連：種類" dataDxfId="22"/>
-    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0700-000016000000}" name="関連：direction" dataDxfId="21"/>
-    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0700-00001A000000}" name="関連：参照元変数名" dataDxfId="20"/>
-    <tableColumn id="29" xr3:uid="{00000000-0010-0000-0700-00001D000000}" name="関連：参照元オブジェクト変数名" dataDxfId="19"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0700-000008000000}" name="nullable" dataDxfId="28"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0700-00000A000000}" name="自動採番" dataDxfId="27"/>
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0700-000015000000}" name="強制採番" dataDxfId="26"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0700-00000B000000}" name="自動更新" dataDxfId="25"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0700-000014000000}" name="強制更新" dataDxfId="24"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0700-00000C000000}" name="グループ識別項目" dataDxfId="23"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0700-000012000000}" name="SPRING監査" dataDxfId="22"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0700-000013000000}" name="関連：種類" dataDxfId="21"/>
+    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0700-000016000000}" name="関連：direction" dataDxfId="20"/>
+    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0700-00001A000000}" name="関連：参照元変数名" dataDxfId="19"/>
     <tableColumn id="23" xr3:uid="{00000000-0010-0000-0700-000017000000}" name="関連：参照先テーブル" dataDxfId="18"/>
     <tableColumn id="24" xr3:uid="{00000000-0010-0000-0700-000018000000}" name="関連：参照先カラム" dataDxfId="17"/>
     <tableColumn id="27" xr3:uid="{00000000-0010-0000-0700-00001B000000}" name="関連：参照先変数名" dataDxfId="16"/>
@@ -3997,154 +3957,154 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="127" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B1" s="128"/>
       <c r="C1" s="129"/>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="124" t="s">
+        <v>42</v>
+      </c>
+      <c r="B2" s="124" t="s">
         <v>43</v>
       </c>
-      <c r="B2" s="124" t="s">
+      <c r="C2" s="124" t="s">
         <v>44</v>
-      </c>
-      <c r="C2" s="124" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="123" t="s">
+        <v>45</v>
+      </c>
+      <c r="B3" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="B3" s="18" t="s">
+      <c r="C3" s="19" t="s">
         <v>47</v>
-      </c>
-      <c r="C3" s="19" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="123" t="s">
+        <v>48</v>
+      </c>
+      <c r="B4" s="18" t="s">
         <v>49</v>
-      </c>
-      <c r="B4" s="18" t="s">
-        <v>50</v>
       </c>
       <c r="C4" s="19"/>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="123" t="s">
+        <v>50</v>
+      </c>
+      <c r="B5" s="18" t="s">
         <v>51</v>
-      </c>
-      <c r="B5" s="18" t="s">
-        <v>52</v>
       </c>
       <c r="C5" s="19"/>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="123" t="s">
+        <v>52</v>
+      </c>
+      <c r="B6" s="18" t="s">
         <v>53</v>
-      </c>
-      <c r="B6" s="18" t="s">
-        <v>54</v>
       </c>
       <c r="C6" s="19"/>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="123" t="s">
+        <v>54</v>
+      </c>
+      <c r="B7" s="18" t="s">
         <v>55</v>
-      </c>
-      <c r="B7" s="18" t="s">
-        <v>56</v>
       </c>
       <c r="C7" s="19"/>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="123" t="s">
+        <v>56</v>
+      </c>
+      <c r="B8" s="18" t="s">
         <v>57</v>
-      </c>
-      <c r="B8" s="18" t="s">
-        <v>58</v>
       </c>
       <c r="C8" s="19"/>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="123" t="s">
+        <v>58</v>
+      </c>
+      <c r="B9" s="18" t="s">
         <v>59</v>
-      </c>
-      <c r="B9" s="18" t="s">
-        <v>60</v>
       </c>
       <c r="C9" s="19"/>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="123" t="s">
+        <v>60</v>
+      </c>
+      <c r="B10" s="18" t="s">
         <v>61</v>
-      </c>
-      <c r="B10" s="18" t="s">
-        <v>62</v>
       </c>
       <c r="C10" s="19"/>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="123" t="s">
+        <v>62</v>
+      </c>
+      <c r="B11" s="18" t="s">
         <v>63</v>
-      </c>
-      <c r="B11" s="18" t="s">
-        <v>64</v>
       </c>
       <c r="C11" s="19"/>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="123" t="s">
+        <v>64</v>
+      </c>
+      <c r="B12" s="18" t="s">
         <v>65</v>
-      </c>
-      <c r="B12" s="18" t="s">
-        <v>66</v>
       </c>
       <c r="C12" s="19"/>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="123" t="s">
+        <v>66</v>
+      </c>
+      <c r="B13" s="18" t="s">
         <v>67</v>
-      </c>
-      <c r="B13" s="18" t="s">
-        <v>68</v>
       </c>
       <c r="C13" s="19"/>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="123" t="s">
+        <v>68</v>
+      </c>
+      <c r="B14" s="18" t="s">
         <v>69</v>
-      </c>
-      <c r="B14" s="18" t="s">
-        <v>70</v>
       </c>
       <c r="C14" s="19"/>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="123" t="s">
+        <v>70</v>
+      </c>
+      <c r="B15" s="18" t="s">
         <v>71</v>
-      </c>
-      <c r="B15" s="18" t="s">
-        <v>72</v>
       </c>
       <c r="C15" s="19"/>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="123" t="s">
+        <v>72</v>
+      </c>
+      <c r="B16" s="18" t="s">
         <v>73</v>
-      </c>
-      <c r="B16" s="18" t="s">
-        <v>74</v>
       </c>
       <c r="C16" s="19"/>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="19"/>
       <c r="B17" s="18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C17" s="19"/>
     </row>
@@ -4158,7 +4118,7 @@
     </row>
     <row r="20" spans="1:3">
       <c r="C20" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -4183,7 +4143,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="7" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="16" customHeight="1">
@@ -4223,16 +4183,16 @@
         <v>5</v>
       </c>
       <c r="B5" s="113" t="s">
+        <v>276</v>
+      </c>
+      <c r="C5" s="114" t="s">
+        <v>277</v>
+      </c>
+      <c r="D5" s="114" t="s">
         <v>278</v>
       </c>
-      <c r="C5" s="114" t="s">
+      <c r="E5" s="114" t="s">
         <v>279</v>
-      </c>
-      <c r="D5" s="114" t="s">
-        <v>280</v>
-      </c>
-      <c r="E5" s="114" t="s">
-        <v>281</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -4416,122 +4376,122 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B1" t="s">
         <v>77</v>
-      </c>
-      <c r="B1" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B10" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B12" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B13" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B14" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B15" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>
@@ -4555,71 +4515,71 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B1" t="s">
         <v>93</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>94</v>
-      </c>
-      <c r="C1" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B2" t="s">
         <v>96</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>97</v>
-      </c>
-      <c r="C2" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C3" t="s">
         <v>99</v>
-      </c>
-      <c r="B3" t="s">
-        <v>97</v>
-      </c>
-      <c r="C3" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
+        <v>100</v>
+      </c>
+      <c r="B4" t="s">
         <v>101</v>
       </c>
-      <c r="B4" t="s">
-        <v>102</v>
-      </c>
       <c r="C4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="46" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
   </sheetData>
@@ -4644,21 +4604,21 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="12" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="78" t="s">
+        <v>108</v>
+      </c>
+      <c r="B3" s="78" t="s">
         <v>109</v>
       </c>
-      <c r="B3" s="78" t="s">
+      <c r="C3" s="78" t="s">
         <v>110</v>
       </c>
-      <c r="C3" s="78" t="s">
+      <c r="D3" s="78" t="s">
         <v>111</v>
-      </c>
-      <c r="D3" s="78" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -4666,13 +4626,13 @@
         <v>41456</v>
       </c>
       <c r="B4" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="D4" s="4" t="s">
         <v>114</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -4680,13 +4640,13 @@
         <v>41484</v>
       </c>
       <c r="B5" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>117</v>
-      </c>
       <c r="D5" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -4694,13 +4654,13 @@
         <v>41486</v>
       </c>
       <c r="B6" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>119</v>
-      </c>
       <c r="D6" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="32" customHeight="1">
@@ -4708,13 +4668,13 @@
         <v>41490</v>
       </c>
       <c r="B7" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="C7" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="C7" s="15" t="s">
-        <v>121</v>
-      </c>
       <c r="D7" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -4722,13 +4682,13 @@
         <v>41506</v>
       </c>
       <c r="B8" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>123</v>
-      </c>
       <c r="D8" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="266.25" customHeight="1">
@@ -4736,13 +4696,13 @@
         <v>41973</v>
       </c>
       <c r="B9" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="C9" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="C9" s="15" t="s">
-        <v>125</v>
-      </c>
       <c r="D9" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="32" customHeight="1">
@@ -4750,13 +4710,13 @@
         <v>41993</v>
       </c>
       <c r="B10" s="14" t="s">
+        <v>125</v>
+      </c>
+      <c r="C10" s="15" t="s">
         <v>126</v>
       </c>
-      <c r="C10" s="15" t="s">
-        <v>127</v>
-      </c>
       <c r="D10" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -4764,13 +4724,13 @@
         <v>41993</v>
       </c>
       <c r="B11" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="C11" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="D11" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="48" customHeight="1">
@@ -4778,13 +4738,13 @@
         <v>42096</v>
       </c>
       <c r="B12" s="14" t="s">
+        <v>129</v>
+      </c>
+      <c r="C12" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="C12" s="15" t="s">
-        <v>131</v>
-      </c>
       <c r="D12" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="32" customHeight="1">
@@ -4792,13 +4752,13 @@
         <v>42103</v>
       </c>
       <c r="B13" s="14" t="s">
+        <v>131</v>
+      </c>
+      <c r="C13" s="15" t="s">
         <v>132</v>
       </c>
-      <c r="C13" s="15" t="s">
-        <v>133</v>
-      </c>
       <c r="D13" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="32" customHeight="1">
@@ -4806,13 +4766,13 @@
         <v>42121</v>
       </c>
       <c r="B14" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="C14" s="15" t="s">
         <v>134</v>
       </c>
-      <c r="C14" s="15" t="s">
-        <v>135</v>
-      </c>
       <c r="D14" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="48" customHeight="1">
@@ -4820,13 +4780,13 @@
         <v>42136</v>
       </c>
       <c r="B15" s="14" t="s">
+        <v>135</v>
+      </c>
+      <c r="C15" s="15" t="s">
         <v>136</v>
       </c>
-      <c r="C15" s="15" t="s">
-        <v>137</v>
-      </c>
       <c r="D15" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="80" customHeight="1">
@@ -4834,13 +4794,13 @@
         <v>42463</v>
       </c>
       <c r="B16" s="14" t="s">
+        <v>137</v>
+      </c>
+      <c r="C16" s="15" t="s">
         <v>138</v>
       </c>
-      <c r="C16" s="15" t="s">
-        <v>139</v>
-      </c>
       <c r="D16" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="80" customHeight="1">
@@ -4848,13 +4808,13 @@
         <v>43015</v>
       </c>
       <c r="B17" s="14" t="s">
+        <v>139</v>
+      </c>
+      <c r="C17" s="15" t="s">
         <v>140</v>
       </c>
-      <c r="C17" s="15" t="s">
-        <v>141</v>
-      </c>
       <c r="D17" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="32" customHeight="1">
@@ -4862,13 +4822,13 @@
         <v>43029</v>
       </c>
       <c r="B18" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="C18" s="15" t="s">
         <v>142</v>
       </c>
-      <c r="C18" s="15" t="s">
-        <v>143</v>
-      </c>
       <c r="D18" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="80" customHeight="1">
@@ -4876,13 +4836,13 @@
         <v>43060</v>
       </c>
       <c r="B19" s="14" t="s">
+        <v>143</v>
+      </c>
+      <c r="C19" s="15" t="s">
         <v>144</v>
       </c>
-      <c r="C19" s="15" t="s">
-        <v>145</v>
-      </c>
       <c r="D19" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="48" customHeight="1">
@@ -4890,13 +4850,13 @@
         <v>43182</v>
       </c>
       <c r="B20" s="14" t="s">
+        <v>145</v>
+      </c>
+      <c r="C20" s="15" t="s">
         <v>146</v>
       </c>
-      <c r="C20" s="15" t="s">
-        <v>147</v>
-      </c>
       <c r="D20" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="96" customHeight="1">
@@ -4904,13 +4864,13 @@
         <v>43856</v>
       </c>
       <c r="B21" s="14" t="s">
+        <v>147</v>
+      </c>
+      <c r="C21" s="15" t="s">
         <v>148</v>
       </c>
-      <c r="C21" s="15" t="s">
-        <v>149</v>
-      </c>
       <c r="D21" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="32" customHeight="1">
@@ -4918,13 +4878,13 @@
         <v>44962</v>
       </c>
       <c r="B22" s="14" t="s">
+        <v>149</v>
+      </c>
+      <c r="C22" s="15" t="s">
         <v>150</v>
       </c>
-      <c r="C22" s="15" t="s">
-        <v>151</v>
-      </c>
       <c r="D22" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="112" customHeight="1">
@@ -4932,13 +4892,13 @@
         <v>44962</v>
       </c>
       <c r="B23" s="14" t="s">
+        <v>151</v>
+      </c>
+      <c r="C23" s="15" t="s">
         <v>152</v>
       </c>
-      <c r="C23" s="15" t="s">
-        <v>153</v>
-      </c>
       <c r="D23" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="16" customHeight="1">
@@ -4946,13 +4906,13 @@
         <v>45017</v>
       </c>
       <c r="B24" s="14" t="s">
+        <v>153</v>
+      </c>
+      <c r="C24" s="15" t="s">
         <v>154</v>
       </c>
-      <c r="C24" s="15" t="s">
-        <v>155</v>
-      </c>
       <c r="D24" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="176" customHeight="1">
@@ -4960,13 +4920,13 @@
         <v>45050</v>
       </c>
       <c r="B25" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="C25" s="15" t="s">
         <v>156</v>
       </c>
-      <c r="C25" s="15" t="s">
-        <v>157</v>
-      </c>
       <c r="D25" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="32" customHeight="1">
@@ -4974,13 +4934,13 @@
         <v>45122</v>
       </c>
       <c r="B26" s="14" t="s">
+        <v>157</v>
+      </c>
+      <c r="C26" s="15" t="s">
         <v>158</v>
       </c>
-      <c r="C26" s="15" t="s">
-        <v>159</v>
-      </c>
       <c r="D26" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="160" customHeight="1">
@@ -4988,13 +4948,13 @@
         <v>45134</v>
       </c>
       <c r="B27" s="14" t="s">
+        <v>159</v>
+      </c>
+      <c r="C27" s="15" t="s">
         <v>160</v>
       </c>
-      <c r="C27" s="15" t="s">
-        <v>161</v>
-      </c>
       <c r="D27" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="64" customHeight="1">
@@ -5002,13 +4962,13 @@
         <v>45136</v>
       </c>
       <c r="B28" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="C28" s="15" t="s">
         <v>162</v>
       </c>
-      <c r="C28" s="15" t="s">
-        <v>163</v>
-      </c>
       <c r="D28" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="160" customHeight="1">
@@ -5016,13 +4976,13 @@
         <v>45144</v>
       </c>
       <c r="B29" s="14" t="s">
+        <v>163</v>
+      </c>
+      <c r="C29" s="15" t="s">
         <v>164</v>
       </c>
-      <c r="C29" s="15" t="s">
-        <v>165</v>
-      </c>
       <c r="D29" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="112" customHeight="1">
@@ -5030,13 +4990,13 @@
         <v>45360</v>
       </c>
       <c r="B30" s="14" t="s">
+        <v>165</v>
+      </c>
+      <c r="C30" s="15" t="s">
         <v>166</v>
       </c>
-      <c r="C30" s="15" t="s">
-        <v>167</v>
-      </c>
       <c r="D30" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="112" customHeight="1">
@@ -5044,13 +5004,13 @@
         <v>45444</v>
       </c>
       <c r="B31" s="14" t="s">
+        <v>167</v>
+      </c>
+      <c r="C31" s="15" t="s">
         <v>168</v>
       </c>
-      <c r="C31" s="15" t="s">
-        <v>169</v>
-      </c>
       <c r="D31" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="112" customHeight="1">
@@ -5058,13 +5018,13 @@
         <v>45602</v>
       </c>
       <c r="B32" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="C32" s="15" t="s">
         <v>170</v>
       </c>
-      <c r="C32" s="15" t="s">
-        <v>171</v>
-      </c>
       <c r="D32" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="192" customHeight="1">
@@ -5072,13 +5032,13 @@
         <v>45707</v>
       </c>
       <c r="B33" s="14" t="s">
+        <v>171</v>
+      </c>
+      <c r="C33" s="15" t="s">
         <v>172</v>
       </c>
-      <c r="C33" s="15" t="s">
-        <v>173</v>
-      </c>
       <c r="D33" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="240" customHeight="1">
@@ -5086,13 +5046,13 @@
         <v>45730</v>
       </c>
       <c r="B34" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="C34" s="15" t="s">
         <v>174</v>
       </c>
-      <c r="C34" s="15" t="s">
-        <v>175</v>
-      </c>
       <c r="D34" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -5100,13 +5060,13 @@
         <v>45809</v>
       </c>
       <c r="B35" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="C35" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="C35" s="1" t="s">
-        <v>177</v>
-      </c>
       <c r="D35" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="112" customHeight="1">
@@ -5114,13 +5074,13 @@
         <v>46124</v>
       </c>
       <c r="B36" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="C36" s="15" t="s">
         <v>178</v>
       </c>
-      <c r="C36" s="15" t="s">
-        <v>179</v>
-      </c>
       <c r="D36" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="409" customHeight="1">
@@ -5128,27 +5088,27 @@
         <v>46192</v>
       </c>
       <c r="B37" s="14" t="s">
+        <v>179</v>
+      </c>
+      <c r="C37" s="15" t="s">
         <v>180</v>
       </c>
-      <c r="C37" s="15" t="s">
-        <v>181</v>
-      </c>
       <c r="D37" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="224" customHeight="1">
       <c r="A38" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="B38" s="14" t="s">
+        <v>181</v>
+      </c>
+      <c r="C38" s="15" t="s">
         <v>182</v>
       </c>
-      <c r="B38" s="14" t="s">
-        <v>182</v>
-      </c>
-      <c r="C38" s="15" t="s">
-        <v>183</v>
-      </c>
       <c r="D38" s="14" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="208" customHeight="1">
@@ -5156,13 +5116,13 @@
         <v>46196</v>
       </c>
       <c r="B39" s="14" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C39" s="15" t="s">
-        <v>185</v>
+        <v>283</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>
@@ -5191,38 +5151,38 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="29" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="16" customHeight="1">
       <c r="A5" s="68" t="s">
+        <v>186</v>
+      </c>
+      <c r="B5" s="68" t="s">
+        <v>187</v>
+      </c>
+      <c r="C5" s="69" t="s">
         <v>188</v>
       </c>
-      <c r="B5" s="68" t="s">
+      <c r="D5" s="68" t="s">
         <v>189</v>
       </c>
-      <c r="C5" s="69" t="s">
+      <c r="E5" s="68" t="s">
         <v>190</v>
       </c>
-      <c r="D5" s="68" t="s">
+      <c r="F5" s="68" t="s">
         <v>191</v>
       </c>
-      <c r="E5" s="68" t="s">
+      <c r="G5" t="s">
         <v>192</v>
       </c>
-      <c r="F5" s="68" t="s">
-        <v>193</v>
-      </c>
-      <c r="G5" t="s">
-        <v>194</v>
-      </c>
       <c r="H5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="16" customHeight="1">
@@ -5231,22 +5191,22 @@
         <v>1</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="C6" s="15" t="s">
+        <v>194</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="C6" s="15" t="s">
+      <c r="E6" s="15" t="s">
         <v>196</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="F6" s="27" t="s">
         <v>197</v>
       </c>
-      <c r="E6" s="15" t="s">
+      <c r="G6" s="1" t="s">
         <v>198</v>
-      </c>
-      <c r="F6" s="27" t="s">
-        <v>199</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>200</v>
       </c>
       <c r="H6" s="1"/>
     </row>
@@ -5256,19 +5216,19 @@
         <v>2</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="F7" s="27" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
@@ -5279,19 +5239,19 @@
         <v>3</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="F8" s="27" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
@@ -5302,22 +5262,22 @@
         <v>4</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="F9" s="27" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H9" s="1"/>
     </row>
@@ -5327,22 +5287,22 @@
         <v>5</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="F10" s="27" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="H10" s="1"/>
     </row>
@@ -5352,22 +5312,22 @@
         <v>6</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="F11" s="27" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="H11" s="1"/>
     </row>
@@ -5377,16 +5337,16 @@
         <v>7</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="E12" s="15" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="F12" s="27"/>
       <c r="G12" s="1"/>
@@ -5398,16 +5358,16 @@
         <v>8</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="F13" s="4"/>
       <c r="G13" s="1"/>
@@ -5419,16 +5379,16 @@
         <v>9</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="F14" s="4"/>
       <c r="G14" s="1"/>
@@ -5440,16 +5400,16 @@
         <v>10</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="F15" s="4"/>
       <c r="G15" s="1"/>
@@ -5461,16 +5421,16 @@
         <v>11</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="E16" s="15" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="F16" s="4"/>
       <c r="G16" s="1"/>
@@ -5482,16 +5442,16 @@
         <v>12</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="E17" s="15" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="F17" s="4"/>
       <c r="G17" s="1"/>
@@ -5503,16 +5463,16 @@
         <v>13</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="E18" s="15" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="F18" s="4"/>
       <c r="G18" s="1"/>
@@ -5524,16 +5484,16 @@
         <v>14</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="E19" s="15" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="F19" s="4"/>
       <c r="G19" s="1"/>
@@ -5545,16 +5505,16 @@
         <v>15</v>
       </c>
       <c r="B20" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="C20" s="15" t="s">
+        <v>225</v>
+      </c>
+      <c r="D20" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="C20" s="15" t="s">
+      <c r="E20" s="15" t="s">
         <v>227</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="E20" s="15" t="s">
-        <v>229</v>
       </c>
       <c r="F20" s="27"/>
       <c r="G20" s="2"/>
@@ -5566,16 +5526,16 @@
         <v>16</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="E21" s="15" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="F21" s="4"/>
       <c r="G21" s="2"/>
@@ -5587,16 +5547,16 @@
         <v>17</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="E22" s="15" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="F22" s="27"/>
       <c r="G22" s="2"/>
@@ -5608,16 +5568,16 @@
         <v>18</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C23" s="15" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E23" s="15" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="F23" s="27"/>
       <c r="G23" s="2"/>
@@ -5629,16 +5589,16 @@
         <v>19</v>
       </c>
       <c r="B24" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C24" s="15" t="s">
+        <v>235</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="E24" s="15" t="s">
         <v>236</v>
-      </c>
-      <c r="C24" s="15" t="s">
-        <v>237</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="E24" s="15" t="s">
-        <v>238</v>
       </c>
       <c r="F24" s="27"/>
       <c r="G24" s="1"/>
@@ -5650,16 +5610,16 @@
         <v>20</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C25" s="15" t="s">
+        <v>235</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="E25" s="1" t="s">
         <v>237</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>239</v>
       </c>
       <c r="F25" s="4"/>
       <c r="G25" s="1"/>
@@ -5671,16 +5631,16 @@
         <v>21</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C26" s="15" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E26" s="15" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="F26" s="27"/>
       <c r="G26" s="1"/>
@@ -5692,22 +5652,22 @@
         <v>22</v>
       </c>
       <c r="B27" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="C27" s="15" t="s">
+        <v>241</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="E27" s="15" t="s">
         <v>242</v>
       </c>
-      <c r="C27" s="15" t="s">
-        <v>243</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="E27" s="15" t="s">
-        <v>244</v>
-      </c>
       <c r="F27" s="27" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="H27" s="1"/>
     </row>
@@ -5717,19 +5677,19 @@
         <v>23</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C28" s="15" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="F28" s="27" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="G28" s="1"/>
       <c r="H28" s="1"/>
@@ -5764,7 +5724,7 @@
   <sheetData>
     <row r="1" spans="1:19">
       <c r="A1" s="7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B1" s="3"/>
     </row>
@@ -5786,7 +5746,7 @@
     </row>
     <row r="3" spans="1:19">
       <c r="A3" s="79" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B3" s="3"/>
       <c r="P3" s="32" t="str">
@@ -5813,10 +5773,10 @@
     <row r="5" spans="1:19" ht="32" customHeight="1">
       <c r="A5" s="7"/>
       <c r="B5" s="28" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C5" s="132" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="D5" s="133"/>
       <c r="E5" s="133"/>
@@ -5824,22 +5784,22 @@
       <c r="G5" s="133"/>
       <c r="H5" s="133"/>
       <c r="I5" s="130" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="J5" s="131"/>
       <c r="K5" s="131"/>
       <c r="L5" s="131"/>
       <c r="M5" s="30" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="N5" s="50" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="O5" s="56" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P5" s="132" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="Q5" s="131"/>
       <c r="R5" s="131"/>
@@ -5847,117 +5807,117 @@
     </row>
     <row r="6" spans="1:19">
       <c r="B6" s="20" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C6" s="26" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D6" s="26" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E6" s="22" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="F6" s="26" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="G6" s="22" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="H6" s="22" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="I6" s="24" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="J6" s="24" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="K6" s="24" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="L6" s="24" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="M6" s="31" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="N6" s="49" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="O6" s="21" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="P6" s="22" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="Q6" s="22" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="R6" s="22" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="S6" s="22" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="7" spans="1:19" ht="32" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C7" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="E7" s="5" t="s">
         <v>252</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="F7" s="70" t="s">
+        <v>76</v>
+      </c>
+      <c r="G7" s="5" t="s">
         <v>253</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="H7" s="5" t="s">
         <v>254</v>
       </c>
-      <c r="F7" s="70" t="s">
-        <v>77</v>
-      </c>
-      <c r="G7" s="5" t="s">
+      <c r="I7" s="5" t="s">
         <v>255</v>
       </c>
-      <c r="H7" s="5" t="s">
+      <c r="J7" s="5" t="s">
         <v>256</v>
       </c>
-      <c r="I7" s="5" t="s">
+      <c r="K7" s="5" t="s">
         <v>257</v>
       </c>
-      <c r="J7" s="5" t="s">
+      <c r="L7" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="K7" s="5" t="s">
+      <c r="M7" s="5" t="s">
         <v>259</v>
       </c>
-      <c r="L7" s="5" t="s">
+      <c r="N7" s="5" t="s">
         <v>260</v>
       </c>
-      <c r="M7" s="5" t="s">
+      <c r="O7" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="P7" s="5" t="s">
         <v>261</v>
       </c>
-      <c r="N7" s="5" t="s">
+      <c r="Q7" s="5" t="s">
         <v>262</v>
       </c>
-      <c r="O7" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="P7" s="5" t="s">
+      <c r="R7" s="5" t="s">
         <v>263</v>
       </c>
-      <c r="Q7" s="5" t="s">
+      <c r="S7" s="5" t="s">
         <v>264</v>
-      </c>
-      <c r="R7" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="S7" s="5" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -6734,13 +6694,13 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="7" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="D1" s="7"/>
     </row>
     <row r="3" spans="1:9" ht="16" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="F3" s="71" t="s">
         <v>1</v>
@@ -6757,7 +6717,7 @@
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="3" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D4" s="52"/>
       <c r="F4" s="32" t="str">
@@ -6779,31 +6739,31 @@
     </row>
     <row r="6" spans="1:9" ht="16" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>9</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F6" s="77" t="s">
+        <v>270</v>
+      </c>
+      <c r="G6" s="77" t="s">
+        <v>271</v>
+      </c>
+      <c r="H6" s="77" t="s">
         <v>272</v>
       </c>
-      <c r="G6" s="77" t="s">
+      <c r="I6" s="77" t="s">
         <v>273</v>
-      </c>
-      <c r="H6" s="77" t="s">
-        <v>274</v>
-      </c>
-      <c r="I6" s="77" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -7112,7 +7072,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AR119"/>
+  <dimension ref="A1:AQ119"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="39.1640625" style="35" bestFit="1" customWidth="1"/>
@@ -7129,61 +7089,60 @@
     <col min="14" max="14" width="8.5" style="37" customWidth="1" outlineLevel="1"/>
     <col min="15" max="16" width="18.33203125" style="37" customWidth="1" outlineLevel="2"/>
     <col min="17" max="17" width="29.5" style="37" customWidth="1" outlineLevel="2"/>
-    <col min="18" max="18" width="24.33203125" style="37" customWidth="1" outlineLevel="2"/>
-    <col min="19" max="19" width="29" style="37" customWidth="1" outlineLevel="2"/>
-    <col min="20" max="21" width="18.33203125" style="37" customWidth="1" outlineLevel="2"/>
-    <col min="22" max="22" width="17.1640625" style="37" customWidth="1" outlineLevel="1"/>
-    <col min="23" max="25" width="9.1640625" style="37" customWidth="1" outlineLevel="2"/>
-    <col min="26" max="26" width="9.1640625" style="35" customWidth="1" outlineLevel="2"/>
-    <col min="27" max="32" width="9.1640625" style="38" customWidth="1" outlineLevel="2"/>
-    <col min="33" max="33" width="19.33203125" style="38" customWidth="1" outlineLevel="1"/>
-    <col min="34" max="37" width="33.33203125" style="38" customWidth="1"/>
-    <col min="38" max="38" width="9" style="38" customWidth="1"/>
-    <col min="39" max="16384" width="9" style="38"/>
+    <col min="18" max="18" width="29" style="37" customWidth="1" outlineLevel="2"/>
+    <col min="19" max="20" width="18.33203125" style="37" customWidth="1" outlineLevel="2"/>
+    <col min="21" max="21" width="17.1640625" style="37" customWidth="1" outlineLevel="1"/>
+    <col min="22" max="24" width="9.1640625" style="37" customWidth="1" outlineLevel="2"/>
+    <col min="25" max="25" width="9.1640625" style="35" customWidth="1" outlineLevel="2"/>
+    <col min="26" max="31" width="9.1640625" style="38" customWidth="1" outlineLevel="2"/>
+    <col min="32" max="32" width="19.33203125" style="38" customWidth="1" outlineLevel="1"/>
+    <col min="33" max="36" width="33.33203125" style="38" customWidth="1"/>
+    <col min="37" max="37" width="9" style="38" customWidth="1"/>
+    <col min="38" max="16384" width="9" style="38"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:44">
+    <row r="1" spans="1:43">
       <c r="A1" s="34" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:44" ht="16" customHeight="1">
+    <row r="2" spans="1:43" ht="16" customHeight="1">
+      <c r="AG2" s="72" t="s">
+        <v>1</v>
+      </c>
       <c r="AH2" s="72" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI2" s="72" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AJ2" s="72" t="s">
-        <v>3</v>
-      </c>
-      <c r="AK2" s="72" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:44">
+    <row r="3" spans="1:43">
       <c r="A3" s="52"/>
-      <c r="AH3" s="32" t="str">
+      <c r="AG3" s="32" t="str">
         <f>IF(各種設定!$G$11=0,"",各種設定!$G$11)</f>
         <v>ja</v>
       </c>
+      <c r="AH3" s="32" t="str">
+        <f>IF(各種設定!$G$12=0,"",各種設定!$G$12)</f>
+        <v/>
+      </c>
       <c r="AI3" s="32" t="str">
-        <f>IF(各種設定!$G$12=0,"",各種設定!$G$12)</f>
+        <f>IF(各種設定!$G$13=0,"",各種設定!$G$13)</f>
         <v/>
       </c>
       <c r="AJ3" s="32" t="str">
-        <f>IF(各種設定!$G$13=0,"",各種設定!$G$13)</f>
-        <v/>
-      </c>
-      <c r="AK3" s="32" t="str">
         <f>IF(各種設定!$G$14=0,"",各種設定!$G$14)</f>
         <v/>
       </c>
     </row>
-    <row r="4" spans="1:44">
+    <row r="4" spans="1:43">
       <c r="A4" s="34"/>
     </row>
-    <row r="5" spans="1:44" s="40" customFormat="1" ht="45" customHeight="1">
+    <row r="5" spans="1:43" s="40" customFormat="1" ht="45" customHeight="1">
       <c r="A5" s="39" t="s">
         <v>5</v>
       </c>
@@ -7280,10 +7239,10 @@
       <c r="AF5" s="75" t="s">
         <v>36</v>
       </c>
-      <c r="AG5" s="75" t="s">
+      <c r="AG5" s="74" t="s">
         <v>37</v>
       </c>
-      <c r="AH5" s="74" t="s">
+      <c r="AH5" s="76" t="s">
         <v>38</v>
       </c>
       <c r="AI5" s="76" t="s">
@@ -7292,12 +7251,9 @@
       <c r="AJ5" s="76" t="s">
         <v>40</v>
       </c>
-      <c r="AK5" s="76" t="s">
-        <v>41</v>
-      </c>
-      <c r="AR5" s="41"/>
-    </row>
-    <row r="6" spans="1:44" s="40" customFormat="1" ht="14" customHeight="1">
+      <c r="AQ5" s="41"/>
+    </row>
+    <row r="6" spans="1:43" s="40" customFormat="1" ht="14" customHeight="1">
       <c r="A6" s="6"/>
       <c r="B6" s="6"/>
       <c r="C6" s="6"/>
@@ -7332,15 +7288,14 @@
       <c r="AC6" s="8"/>
       <c r="AD6" s="8"/>
       <c r="AE6" s="8"/>
-      <c r="AF6" s="8"/>
-      <c r="AG6" s="25"/>
-      <c r="AH6" s="42"/>
-      <c r="AI6" s="54"/>
-      <c r="AJ6" s="42"/>
-      <c r="AK6" s="39"/>
-      <c r="AR6" s="41"/>
-    </row>
-    <row r="7" spans="1:44" s="40" customFormat="1" ht="14" customHeight="1">
+      <c r="AF6" s="25"/>
+      <c r="AG6" s="42"/>
+      <c r="AH6" s="54"/>
+      <c r="AI6" s="42"/>
+      <c r="AJ6" s="39"/>
+      <c r="AQ6" s="41"/>
+    </row>
+    <row r="7" spans="1:43" s="40" customFormat="1" ht="14" customHeight="1">
       <c r="A7" s="6"/>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -7375,15 +7330,14 @@
       <c r="AC7" s="8"/>
       <c r="AD7" s="8"/>
       <c r="AE7" s="8"/>
-      <c r="AF7" s="8"/>
-      <c r="AG7" s="25"/>
+      <c r="AF7" s="25"/>
+      <c r="AG7" s="6"/>
       <c r="AH7" s="6"/>
-      <c r="AI7" s="6"/>
-      <c r="AJ7" s="42"/>
-      <c r="AK7" s="39"/>
-      <c r="AR7" s="41"/>
-    </row>
-    <row r="8" spans="1:44" s="40" customFormat="1" ht="14" customHeight="1">
+      <c r="AI7" s="42"/>
+      <c r="AJ7" s="39"/>
+      <c r="AQ7" s="41"/>
+    </row>
+    <row r="8" spans="1:43" s="40" customFormat="1" ht="14" customHeight="1">
       <c r="A8" s="6"/>
       <c r="B8" s="6"/>
       <c r="C8" s="6"/>
@@ -7418,15 +7372,14 @@
       <c r="AC8" s="8"/>
       <c r="AD8" s="8"/>
       <c r="AE8" s="8"/>
-      <c r="AF8" s="8"/>
-      <c r="AG8" s="25"/>
+      <c r="AF8" s="25"/>
+      <c r="AG8" s="6"/>
       <c r="AH8" s="6"/>
-      <c r="AI8" s="6"/>
-      <c r="AJ8" s="42"/>
-      <c r="AK8" s="39"/>
-      <c r="AR8" s="41"/>
-    </row>
-    <row r="9" spans="1:44" s="40" customFormat="1" ht="14" customHeight="1">
+      <c r="AI8" s="42"/>
+      <c r="AJ8" s="39"/>
+      <c r="AQ8" s="41"/>
+    </row>
+    <row r="9" spans="1:43" s="40" customFormat="1" ht="14" customHeight="1">
       <c r="A9" s="6"/>
       <c r="B9" s="6"/>
       <c r="C9" s="6"/>
@@ -7461,15 +7414,14 @@
       <c r="AC9" s="8"/>
       <c r="AD9" s="8"/>
       <c r="AE9" s="8"/>
-      <c r="AF9" s="8"/>
-      <c r="AG9" s="25"/>
+      <c r="AF9" s="25"/>
+      <c r="AG9" s="6"/>
       <c r="AH9" s="6"/>
-      <c r="AI9" s="6"/>
-      <c r="AJ9" s="42"/>
-      <c r="AK9" s="39"/>
-      <c r="AR9" s="41"/>
-    </row>
-    <row r="10" spans="1:44" s="40" customFormat="1" ht="14" customHeight="1">
+      <c r="AI9" s="42"/>
+      <c r="AJ9" s="39"/>
+      <c r="AQ9" s="41"/>
+    </row>
+    <row r="10" spans="1:43" s="40" customFormat="1" ht="14" customHeight="1">
       <c r="A10" s="42"/>
       <c r="B10" s="6"/>
       <c r="C10" s="6"/>
@@ -7493,8 +7445,8 @@
       <c r="R10" s="8"/>
       <c r="S10" s="8"/>
       <c r="T10" s="8"/>
-      <c r="U10" s="8"/>
-      <c r="V10" s="9"/>
+      <c r="U10" s="9"/>
+      <c r="V10" s="8"/>
       <c r="W10" s="8"/>
       <c r="X10" s="8"/>
       <c r="Y10" s="8"/>
@@ -7504,15 +7456,14 @@
       <c r="AC10" s="8"/>
       <c r="AD10" s="8"/>
       <c r="AE10" s="8"/>
-      <c r="AF10" s="8"/>
-      <c r="AG10" s="25"/>
+      <c r="AF10" s="25"/>
+      <c r="AG10" s="6"/>
       <c r="AH10" s="6"/>
-      <c r="AI10" s="6"/>
-      <c r="AJ10" s="42"/>
-      <c r="AK10" s="39"/>
-      <c r="AR10" s="41"/>
-    </row>
-    <row r="11" spans="1:44" s="40" customFormat="1" ht="14" customHeight="1">
+      <c r="AI10" s="42"/>
+      <c r="AJ10" s="39"/>
+      <c r="AQ10" s="41"/>
+    </row>
+    <row r="11" spans="1:43" s="40" customFormat="1" ht="14" customHeight="1">
       <c r="A11" s="42"/>
       <c r="B11" s="6"/>
       <c r="C11" s="6"/>
@@ -7536,8 +7487,8 @@
       <c r="R11" s="8"/>
       <c r="S11" s="8"/>
       <c r="T11" s="8"/>
-      <c r="U11" s="8"/>
-      <c r="V11" s="9"/>
+      <c r="U11" s="9"/>
+      <c r="V11" s="8"/>
       <c r="W11" s="8"/>
       <c r="X11" s="8"/>
       <c r="Y11" s="8"/>
@@ -7547,15 +7498,14 @@
       <c r="AC11" s="8"/>
       <c r="AD11" s="8"/>
       <c r="AE11" s="8"/>
-      <c r="AF11" s="8"/>
-      <c r="AG11" s="25"/>
+      <c r="AF11" s="25"/>
+      <c r="AG11" s="6"/>
       <c r="AH11" s="6"/>
-      <c r="AI11" s="6"/>
-      <c r="AJ11" s="42"/>
-      <c r="AK11" s="39"/>
-      <c r="AR11" s="41"/>
-    </row>
-    <row r="12" spans="1:44" s="40" customFormat="1" ht="14" customHeight="1">
+      <c r="AI11" s="42"/>
+      <c r="AJ11" s="39"/>
+      <c r="AQ11" s="41"/>
+    </row>
+    <row r="12" spans="1:43" s="40" customFormat="1" ht="14" customHeight="1">
       <c r="A12" s="6"/>
       <c r="B12" s="6"/>
       <c r="C12" s="6"/>
@@ -7590,15 +7540,14 @@
       <c r="AC12" s="8"/>
       <c r="AD12" s="8"/>
       <c r="AE12" s="8"/>
-      <c r="AF12" s="8"/>
-      <c r="AG12" s="25"/>
-      <c r="AH12" s="42"/>
-      <c r="AI12" s="54"/>
-      <c r="AJ12" s="42"/>
-      <c r="AK12" s="39"/>
-      <c r="AR12" s="41"/>
-    </row>
-    <row r="13" spans="1:44">
+      <c r="AF12" s="25"/>
+      <c r="AG12" s="42"/>
+      <c r="AH12" s="54"/>
+      <c r="AI12" s="42"/>
+      <c r="AJ12" s="39"/>
+      <c r="AQ12" s="41"/>
+    </row>
+    <row r="13" spans="1:43">
       <c r="A13" s="6"/>
       <c r="B13" s="42"/>
       <c r="C13" s="42"/>
@@ -7633,14 +7582,13 @@
       <c r="AC13" s="8"/>
       <c r="AD13" s="8"/>
       <c r="AE13" s="8"/>
-      <c r="AF13" s="8"/>
-      <c r="AG13" s="25"/>
-      <c r="AH13" s="6"/>
+      <c r="AF13" s="25"/>
+      <c r="AG13" s="6"/>
+      <c r="AH13" s="42"/>
       <c r="AI13" s="42"/>
-      <c r="AJ13" s="42"/>
-      <c r="AK13" s="39"/>
-    </row>
-    <row r="14" spans="1:44">
+      <c r="AJ13" s="39"/>
+    </row>
+    <row r="14" spans="1:43">
       <c r="A14" s="42"/>
       <c r="B14" s="42"/>
       <c r="C14" s="6"/>
@@ -7675,14 +7623,13 @@
       <c r="AC14" s="8"/>
       <c r="AD14" s="8"/>
       <c r="AE14" s="8"/>
-      <c r="AF14" s="8"/>
-      <c r="AG14" s="25"/>
+      <c r="AF14" s="25"/>
+      <c r="AG14" s="42"/>
       <c r="AH14" s="42"/>
       <c r="AI14" s="42"/>
-      <c r="AJ14" s="42"/>
-      <c r="AK14" s="39"/>
-    </row>
-    <row r="15" spans="1:44">
+      <c r="AJ14" s="39"/>
+    </row>
+    <row r="15" spans="1:43">
       <c r="A15" s="42"/>
       <c r="B15" s="42"/>
       <c r="C15" s="6"/>
@@ -7717,14 +7664,13 @@
       <c r="AC15" s="8"/>
       <c r="AD15" s="8"/>
       <c r="AE15" s="8"/>
-      <c r="AF15" s="8"/>
-      <c r="AG15" s="25"/>
+      <c r="AF15" s="25"/>
+      <c r="AG15" s="42"/>
       <c r="AH15" s="42"/>
       <c r="AI15" s="42"/>
-      <c r="AJ15" s="42"/>
-      <c r="AK15" s="39"/>
-    </row>
-    <row r="16" spans="1:44">
+      <c r="AJ15" s="39"/>
+    </row>
+    <row r="16" spans="1:43">
       <c r="A16" s="42"/>
       <c r="B16" s="42"/>
       <c r="C16" s="6"/>
@@ -7759,14 +7705,13 @@
       <c r="AC16" s="8"/>
       <c r="AD16" s="8"/>
       <c r="AE16" s="8"/>
-      <c r="AF16" s="8"/>
-      <c r="AG16" s="25"/>
-      <c r="AH16" s="42"/>
-      <c r="AI16" s="6"/>
-      <c r="AJ16" s="42"/>
-      <c r="AK16" s="39"/>
-    </row>
-    <row r="17" spans="1:44">
+      <c r="AF16" s="25"/>
+      <c r="AG16" s="42"/>
+      <c r="AH16" s="6"/>
+      <c r="AI16" s="42"/>
+      <c r="AJ16" s="39"/>
+    </row>
+    <row r="17" spans="1:43">
       <c r="A17" s="42"/>
       <c r="B17" s="42"/>
       <c r="C17" s="6"/>
@@ -7801,14 +7746,13 @@
       <c r="AC17" s="8"/>
       <c r="AD17" s="8"/>
       <c r="AE17" s="8"/>
-      <c r="AF17" s="8"/>
-      <c r="AG17" s="25"/>
-      <c r="AH17" s="42"/>
-      <c r="AI17" s="6"/>
-      <c r="AJ17" s="42"/>
-      <c r="AK17" s="39"/>
-    </row>
-    <row r="18" spans="1:44">
+      <c r="AF17" s="25"/>
+      <c r="AG17" s="42"/>
+      <c r="AH17" s="6"/>
+      <c r="AI17" s="42"/>
+      <c r="AJ17" s="39"/>
+    </row>
+    <row r="18" spans="1:43">
       <c r="A18" s="42"/>
       <c r="B18" s="42"/>
       <c r="C18" s="42"/>
@@ -7843,14 +7787,13 @@
       <c r="AC18" s="8"/>
       <c r="AD18" s="8"/>
       <c r="AE18" s="8"/>
-      <c r="AF18" s="8"/>
-      <c r="AG18" s="25"/>
-      <c r="AH18" s="42"/>
-      <c r="AI18" s="6"/>
-      <c r="AJ18" s="42"/>
-      <c r="AK18" s="39"/>
-    </row>
-    <row r="19" spans="1:44">
+      <c r="AF18" s="25"/>
+      <c r="AG18" s="42"/>
+      <c r="AH18" s="6"/>
+      <c r="AI18" s="42"/>
+      <c r="AJ18" s="39"/>
+    </row>
+    <row r="19" spans="1:43">
       <c r="A19" s="42"/>
       <c r="B19" s="6"/>
       <c r="C19" s="42"/>
@@ -7885,14 +7828,13 @@
       <c r="AC19" s="8"/>
       <c r="AD19" s="8"/>
       <c r="AE19" s="8"/>
-      <c r="AF19" s="8"/>
-      <c r="AG19" s="25"/>
+      <c r="AF19" s="25"/>
+      <c r="AG19" s="6"/>
       <c r="AH19" s="6"/>
-      <c r="AI19" s="6"/>
-      <c r="AJ19" s="42"/>
-      <c r="AK19" s="39"/>
-    </row>
-    <row r="20" spans="1:44">
+      <c r="AI19" s="42"/>
+      <c r="AJ19" s="39"/>
+    </row>
+    <row r="20" spans="1:43">
       <c r="A20" s="42"/>
       <c r="B20" s="6"/>
       <c r="C20" s="42"/>
@@ -7927,14 +7869,13 @@
       <c r="AC20" s="8"/>
       <c r="AD20" s="8"/>
       <c r="AE20" s="8"/>
-      <c r="AF20" s="8"/>
-      <c r="AG20" s="25"/>
-      <c r="AH20" s="42"/>
-      <c r="AI20" s="6"/>
-      <c r="AJ20" s="42"/>
-      <c r="AK20" s="39"/>
-    </row>
-    <row r="21" spans="1:44">
+      <c r="AF20" s="25"/>
+      <c r="AG20" s="42"/>
+      <c r="AH20" s="6"/>
+      <c r="AI20" s="42"/>
+      <c r="AJ20" s="39"/>
+    </row>
+    <row r="21" spans="1:43">
       <c r="A21" s="42"/>
       <c r="B21" s="6"/>
       <c r="C21" s="42"/>
@@ -7969,14 +7910,13 @@
       <c r="AC21" s="8"/>
       <c r="AD21" s="8"/>
       <c r="AE21" s="8"/>
-      <c r="AF21" s="8"/>
-      <c r="AG21" s="25"/>
-      <c r="AH21" s="42"/>
-      <c r="AI21" s="6"/>
-      <c r="AJ21" s="42"/>
-      <c r="AK21" s="39"/>
-    </row>
-    <row r="22" spans="1:44" s="40" customFormat="1" ht="14" customHeight="1">
+      <c r="AF21" s="25"/>
+      <c r="AG21" s="42"/>
+      <c r="AH21" s="6"/>
+      <c r="AI21" s="42"/>
+      <c r="AJ21" s="39"/>
+    </row>
+    <row r="22" spans="1:43" s="40" customFormat="1" ht="14" customHeight="1">
       <c r="A22" s="42"/>
       <c r="B22" s="42"/>
       <c r="C22" s="6"/>
@@ -8000,8 +7940,8 @@
       <c r="R22" s="8"/>
       <c r="S22" s="8"/>
       <c r="T22" s="8"/>
-      <c r="U22" s="8"/>
-      <c r="V22" s="9"/>
+      <c r="U22" s="9"/>
+      <c r="V22" s="8"/>
       <c r="W22" s="8"/>
       <c r="X22" s="8"/>
       <c r="Y22" s="8"/>
@@ -8011,15 +7951,14 @@
       <c r="AC22" s="8"/>
       <c r="AD22" s="8"/>
       <c r="AE22" s="8"/>
-      <c r="AF22" s="8"/>
-      <c r="AG22" s="25"/>
-      <c r="AH22" s="42"/>
-      <c r="AI22" s="51"/>
-      <c r="AJ22" s="42"/>
-      <c r="AK22" s="39"/>
-      <c r="AR22" s="41"/>
-    </row>
-    <row r="23" spans="1:44" s="40" customFormat="1" ht="14" customHeight="1">
+      <c r="AF22" s="25"/>
+      <c r="AG22" s="42"/>
+      <c r="AH22" s="51"/>
+      <c r="AI22" s="42"/>
+      <c r="AJ22" s="39"/>
+      <c r="AQ22" s="41"/>
+    </row>
+    <row r="23" spans="1:43" s="40" customFormat="1" ht="14" customHeight="1">
       <c r="A23" s="42"/>
       <c r="B23" s="42"/>
       <c r="C23" s="6"/>
@@ -8046,7 +7985,7 @@
       <c r="U23" s="8"/>
       <c r="V23" s="8"/>
       <c r="W23" s="8"/>
-      <c r="X23" s="8"/>
+      <c r="X23" s="44"/>
       <c r="Y23" s="44"/>
       <c r="Z23" s="44"/>
       <c r="AA23" s="44"/>
@@ -8054,15 +7993,14 @@
       <c r="AC23" s="44"/>
       <c r="AD23" s="44"/>
       <c r="AE23" s="44"/>
-      <c r="AF23" s="44"/>
-      <c r="AG23" s="60"/>
-      <c r="AH23" s="42"/>
-      <c r="AI23" s="51"/>
-      <c r="AJ23" s="42"/>
-      <c r="AK23" s="39"/>
-      <c r="AR23" s="41"/>
-    </row>
-    <row r="24" spans="1:44">
+      <c r="AF23" s="60"/>
+      <c r="AG23" s="42"/>
+      <c r="AH23" s="51"/>
+      <c r="AI23" s="42"/>
+      <c r="AJ23" s="39"/>
+      <c r="AQ23" s="41"/>
+    </row>
+    <row r="24" spans="1:43">
       <c r="A24" s="42"/>
       <c r="B24" s="6"/>
       <c r="C24" s="6"/>
@@ -8083,10 +8021,10 @@
       <c r="O24" s="8"/>
       <c r="P24" s="8"/>
       <c r="Q24" s="8"/>
-      <c r="R24" s="8"/>
+      <c r="R24" s="53"/>
       <c r="S24" s="53"/>
       <c r="T24" s="53"/>
-      <c r="U24" s="53"/>
+      <c r="U24" s="8"/>
       <c r="V24" s="8"/>
       <c r="W24" s="8"/>
       <c r="X24" s="8"/>
@@ -8097,12 +8035,11 @@
       <c r="AC24" s="8"/>
       <c r="AD24" s="8"/>
       <c r="AE24" s="8"/>
-      <c r="AF24" s="8"/>
-      <c r="AG24" s="25"/>
-      <c r="AH24" s="6"/>
-      <c r="AI24" s="63"/>
-    </row>
-    <row r="25" spans="1:44">
+      <c r="AF24" s="25"/>
+      <c r="AG24" s="6"/>
+      <c r="AH24" s="63"/>
+    </row>
+    <row r="25" spans="1:43">
       <c r="A25" s="42"/>
       <c r="B25" s="42"/>
       <c r="C25" s="6"/>
@@ -8137,14 +8074,13 @@
       <c r="AC25" s="8"/>
       <c r="AD25" s="8"/>
       <c r="AE25" s="8"/>
-      <c r="AF25" s="8"/>
-      <c r="AG25" s="25"/>
-      <c r="AH25" s="42"/>
-      <c r="AI25" s="6"/>
-      <c r="AJ25" s="42"/>
-      <c r="AK25" s="39"/>
-    </row>
-    <row r="26" spans="1:44" s="40" customFormat="1" ht="14" customHeight="1">
+      <c r="AF25" s="25"/>
+      <c r="AG25" s="42"/>
+      <c r="AH25" s="6"/>
+      <c r="AI25" s="42"/>
+      <c r="AJ25" s="39"/>
+    </row>
+    <row r="26" spans="1:43" s="40" customFormat="1" ht="14" customHeight="1">
       <c r="A26" s="42"/>
       <c r="B26" s="6"/>
       <c r="C26" s="6"/>
@@ -8171,7 +8107,7 @@
       <c r="U26" s="8"/>
       <c r="V26" s="8"/>
       <c r="W26" s="8"/>
-      <c r="X26" s="8"/>
+      <c r="X26" s="44"/>
       <c r="Y26" s="44"/>
       <c r="Z26" s="44"/>
       <c r="AA26" s="44"/>
@@ -8179,15 +8115,14 @@
       <c r="AC26" s="44"/>
       <c r="AD26" s="44"/>
       <c r="AE26" s="44"/>
-      <c r="AF26" s="44"/>
-      <c r="AG26" s="60"/>
-      <c r="AH26" s="42"/>
-      <c r="AI26" s="6"/>
-      <c r="AJ26" s="42"/>
-      <c r="AK26" s="39"/>
-      <c r="AR26" s="41"/>
-    </row>
-    <row r="27" spans="1:44" s="40" customFormat="1" ht="14" customHeight="1">
+      <c r="AF26" s="60"/>
+      <c r="AG26" s="42"/>
+      <c r="AH26" s="6"/>
+      <c r="AI26" s="42"/>
+      <c r="AJ26" s="39"/>
+      <c r="AQ26" s="41"/>
+    </row>
+    <row r="27" spans="1:43" s="40" customFormat="1" ht="14" customHeight="1">
       <c r="A27" s="42"/>
       <c r="B27" s="51"/>
       <c r="C27" s="6"/>
@@ -8214,7 +8149,7 @@
       <c r="U27" s="8"/>
       <c r="V27" s="8"/>
       <c r="W27" s="8"/>
-      <c r="X27" s="8"/>
+      <c r="X27" s="44"/>
       <c r="Y27" s="44"/>
       <c r="Z27" s="44"/>
       <c r="AA27" s="44"/>
@@ -8222,15 +8157,14 @@
       <c r="AC27" s="44"/>
       <c r="AD27" s="44"/>
       <c r="AE27" s="44"/>
-      <c r="AF27" s="44"/>
-      <c r="AG27" s="60"/>
-      <c r="AH27" s="51"/>
-      <c r="AI27" s="6"/>
-      <c r="AJ27" s="42"/>
-      <c r="AK27" s="39"/>
-      <c r="AR27" s="41"/>
-    </row>
-    <row r="28" spans="1:44" s="40" customFormat="1" ht="14" customHeight="1">
+      <c r="AF27" s="60"/>
+      <c r="AG27" s="51"/>
+      <c r="AH27" s="6"/>
+      <c r="AI27" s="42"/>
+      <c r="AJ27" s="39"/>
+      <c r="AQ27" s="41"/>
+    </row>
+    <row r="28" spans="1:43" s="40" customFormat="1" ht="14" customHeight="1">
       <c r="A28" s="6"/>
       <c r="B28" s="6"/>
       <c r="C28" s="6"/>
@@ -8257,7 +8191,7 @@
       <c r="U28" s="8"/>
       <c r="V28" s="8"/>
       <c r="W28" s="8"/>
-      <c r="X28" s="8"/>
+      <c r="X28" s="44"/>
       <c r="Y28" s="44"/>
       <c r="Z28" s="44"/>
       <c r="AA28" s="44"/>
@@ -8265,15 +8199,14 @@
       <c r="AC28" s="44"/>
       <c r="AD28" s="44"/>
       <c r="AE28" s="44"/>
-      <c r="AF28" s="44"/>
-      <c r="AG28" s="60"/>
+      <c r="AF28" s="60"/>
+      <c r="AG28" s="42"/>
       <c r="AH28" s="42"/>
       <c r="AI28" s="42"/>
-      <c r="AJ28" s="42"/>
-      <c r="AK28" s="39"/>
-      <c r="AR28" s="41"/>
-    </row>
-    <row r="29" spans="1:44" s="40" customFormat="1" ht="14" customHeight="1">
+      <c r="AJ28" s="39"/>
+      <c r="AQ28" s="41"/>
+    </row>
+    <row r="29" spans="1:43" s="40" customFormat="1" ht="14" customHeight="1">
       <c r="A29" s="6"/>
       <c r="B29" s="6"/>
       <c r="C29" s="6"/>
@@ -8294,13 +8227,13 @@
       <c r="O29" s="8"/>
       <c r="P29" s="8"/>
       <c r="Q29" s="8"/>
-      <c r="R29" s="8"/>
+      <c r="R29" s="53"/>
       <c r="S29" s="53"/>
-      <c r="T29" s="53"/>
+      <c r="T29" s="8"/>
       <c r="U29" s="8"/>
       <c r="V29" s="8"/>
       <c r="W29" s="8"/>
-      <c r="X29" s="8"/>
+      <c r="X29" s="44"/>
       <c r="Y29" s="44"/>
       <c r="Z29" s="44"/>
       <c r="AA29" s="44"/>
@@ -8308,15 +8241,14 @@
       <c r="AC29" s="44"/>
       <c r="AD29" s="44"/>
       <c r="AE29" s="44"/>
-      <c r="AF29" s="44"/>
-      <c r="AG29" s="60"/>
-      <c r="AH29" s="6"/>
-      <c r="AI29" s="63"/>
-      <c r="AJ29" s="42"/>
-      <c r="AK29" s="39"/>
-      <c r="AR29" s="41"/>
-    </row>
-    <row r="30" spans="1:44" s="40" customFormat="1" ht="14" customHeight="1">
+      <c r="AF29" s="60"/>
+      <c r="AG29" s="6"/>
+      <c r="AH29" s="63"/>
+      <c r="AI29" s="42"/>
+      <c r="AJ29" s="39"/>
+      <c r="AQ29" s="41"/>
+    </row>
+    <row r="30" spans="1:43" s="40" customFormat="1" ht="14" customHeight="1">
       <c r="A30" s="6"/>
       <c r="B30" s="51"/>
       <c r="C30" s="6"/>
@@ -8343,7 +8275,7 @@
       <c r="U30" s="8"/>
       <c r="V30" s="8"/>
       <c r="W30" s="8"/>
-      <c r="X30" s="8"/>
+      <c r="X30" s="44"/>
       <c r="Y30" s="44"/>
       <c r="Z30" s="44"/>
       <c r="AA30" s="44"/>
@@ -8351,15 +8283,14 @@
       <c r="AC30" s="44"/>
       <c r="AD30" s="44"/>
       <c r="AE30" s="44"/>
-      <c r="AF30" s="44"/>
-      <c r="AG30" s="60"/>
+      <c r="AF30" s="60"/>
+      <c r="AG30" s="51"/>
       <c r="AH30" s="51"/>
-      <c r="AI30" s="51"/>
-      <c r="AJ30" s="42"/>
-      <c r="AK30" s="39"/>
-      <c r="AR30" s="41"/>
-    </row>
-    <row r="31" spans="1:44" s="40" customFormat="1" ht="14" customHeight="1">
+      <c r="AI30" s="42"/>
+      <c r="AJ30" s="39"/>
+      <c r="AQ30" s="41"/>
+    </row>
+    <row r="31" spans="1:43" s="40" customFormat="1" ht="14" customHeight="1">
       <c r="A31" s="6"/>
       <c r="B31" s="51"/>
       <c r="C31" s="6"/>
@@ -8386,7 +8317,7 @@
       <c r="U31" s="8"/>
       <c r="V31" s="8"/>
       <c r="W31" s="8"/>
-      <c r="X31" s="8"/>
+      <c r="X31" s="44"/>
       <c r="Y31" s="44"/>
       <c r="Z31" s="44"/>
       <c r="AA31" s="44"/>
@@ -8394,15 +8325,14 @@
       <c r="AC31" s="44"/>
       <c r="AD31" s="44"/>
       <c r="AE31" s="44"/>
-      <c r="AF31" s="44"/>
-      <c r="AG31" s="60"/>
+      <c r="AF31" s="60"/>
+      <c r="AG31" s="51"/>
       <c r="AH31" s="51"/>
-      <c r="AI31" s="51"/>
-      <c r="AJ31" s="42"/>
-      <c r="AK31" s="39"/>
-      <c r="AR31" s="41"/>
-    </row>
-    <row r="32" spans="1:44">
+      <c r="AI31" s="42"/>
+      <c r="AJ31" s="39"/>
+      <c r="AQ31" s="41"/>
+    </row>
+    <row r="32" spans="1:43">
       <c r="A32" s="42"/>
       <c r="B32" s="6"/>
       <c r="C32" s="6"/>
@@ -8437,14 +8367,13 @@
       <c r="AC32" s="8"/>
       <c r="AD32" s="8"/>
       <c r="AE32" s="8"/>
-      <c r="AF32" s="8"/>
-      <c r="AG32" s="25"/>
-      <c r="AH32" s="42"/>
-      <c r="AI32" s="54"/>
-      <c r="AJ32" s="42"/>
-      <c r="AK32" s="39"/>
-    </row>
-    <row r="33" spans="1:44">
+      <c r="AF32" s="25"/>
+      <c r="AG32" s="42"/>
+      <c r="AH32" s="54"/>
+      <c r="AI32" s="42"/>
+      <c r="AJ32" s="39"/>
+    </row>
+    <row r="33" spans="1:43">
       <c r="A33" s="42"/>
       <c r="B33" s="6"/>
       <c r="C33" s="6"/>
@@ -8465,10 +8394,10 @@
       <c r="O33" s="8"/>
       <c r="P33" s="8"/>
       <c r="Q33" s="8"/>
-      <c r="R33" s="8"/>
+      <c r="R33" s="53"/>
       <c r="S33" s="53"/>
       <c r="T33" s="53"/>
-      <c r="U33" s="53"/>
+      <c r="U33" s="8"/>
       <c r="V33" s="8"/>
       <c r="W33" s="8"/>
       <c r="X33" s="8"/>
@@ -8479,14 +8408,13 @@
       <c r="AC33" s="8"/>
       <c r="AD33" s="8"/>
       <c r="AE33" s="8"/>
-      <c r="AF33" s="8"/>
-      <c r="AG33" s="25"/>
-      <c r="AH33" s="6"/>
-      <c r="AI33" s="63"/>
-      <c r="AJ33" s="42"/>
-      <c r="AK33" s="39"/>
-    </row>
-    <row r="34" spans="1:44" s="40" customFormat="1" ht="14" customHeight="1">
+      <c r="AF33" s="25"/>
+      <c r="AG33" s="6"/>
+      <c r="AH33" s="63"/>
+      <c r="AI33" s="42"/>
+      <c r="AJ33" s="39"/>
+    </row>
+    <row r="34" spans="1:43" s="40" customFormat="1" ht="14" customHeight="1">
       <c r="A34" s="42"/>
       <c r="B34" s="6"/>
       <c r="C34" s="6"/>
@@ -8521,15 +8449,14 @@
       <c r="AC34" s="8"/>
       <c r="AD34" s="8"/>
       <c r="AE34" s="8"/>
-      <c r="AF34" s="8"/>
-      <c r="AG34" s="25"/>
+      <c r="AF34" s="25"/>
+      <c r="AG34" s="6"/>
       <c r="AH34" s="6"/>
-      <c r="AI34" s="6"/>
-      <c r="AJ34" s="42"/>
-      <c r="AK34" s="39"/>
-      <c r="AR34" s="41"/>
-    </row>
-    <row r="35" spans="1:44" s="40" customFormat="1" ht="14" customHeight="1">
+      <c r="AI34" s="42"/>
+      <c r="AJ34" s="39"/>
+      <c r="AQ34" s="41"/>
+    </row>
+    <row r="35" spans="1:43" s="40" customFormat="1" ht="14" customHeight="1">
       <c r="A35" s="42"/>
       <c r="B35" s="6"/>
       <c r="C35" s="6"/>
@@ -8564,15 +8491,14 @@
       <c r="AC35" s="8"/>
       <c r="AD35" s="8"/>
       <c r="AE35" s="8"/>
-      <c r="AF35" s="8"/>
-      <c r="AG35" s="25"/>
+      <c r="AF35" s="25"/>
+      <c r="AG35" s="6"/>
       <c r="AH35" s="6"/>
-      <c r="AI35" s="6"/>
-      <c r="AJ35" s="42"/>
-      <c r="AK35" s="39"/>
-      <c r="AR35" s="41"/>
-    </row>
-    <row r="36" spans="1:44" s="40" customFormat="1" ht="14" customHeight="1">
+      <c r="AI35" s="42"/>
+      <c r="AJ35" s="39"/>
+      <c r="AQ35" s="41"/>
+    </row>
+    <row r="36" spans="1:43" s="40" customFormat="1" ht="14" customHeight="1">
       <c r="A36" s="42"/>
       <c r="B36" s="6"/>
       <c r="C36" s="6"/>
@@ -8607,15 +8533,14 @@
       <c r="AC36" s="8"/>
       <c r="AD36" s="8"/>
       <c r="AE36" s="8"/>
-      <c r="AF36" s="8"/>
-      <c r="AG36" s="25"/>
+      <c r="AF36" s="25"/>
+      <c r="AG36" s="6"/>
       <c r="AH36" s="6"/>
-      <c r="AI36" s="6"/>
-      <c r="AJ36" s="42"/>
-      <c r="AK36" s="39"/>
-      <c r="AR36" s="41"/>
-    </row>
-    <row r="37" spans="1:44" ht="160" customHeight="1">
+      <c r="AI36" s="42"/>
+      <c r="AJ36" s="39"/>
+      <c r="AQ36" s="41"/>
+    </row>
+    <row r="37" spans="1:43" ht="160" customHeight="1">
       <c r="A37" s="42"/>
       <c r="B37" s="6"/>
       <c r="C37" s="42"/>
@@ -8650,14 +8575,13 @@
       <c r="AC37" s="8"/>
       <c r="AD37" s="8"/>
       <c r="AE37" s="8"/>
-      <c r="AF37" s="8"/>
-      <c r="AG37" s="25"/>
+      <c r="AF37" s="25"/>
+      <c r="AG37" s="42"/>
       <c r="AH37" s="42"/>
       <c r="AI37" s="42"/>
-      <c r="AJ37" s="42"/>
-      <c r="AK37" s="39"/>
-    </row>
-    <row r="38" spans="1:44">
+      <c r="AJ37" s="39"/>
+    </row>
+    <row r="38" spans="1:43">
       <c r="A38" s="42"/>
       <c r="B38" s="6"/>
       <c r="C38" s="42"/>
@@ -8692,14 +8616,13 @@
       <c r="AC38" s="8"/>
       <c r="AD38" s="8"/>
       <c r="AE38" s="8"/>
-      <c r="AF38" s="8"/>
-      <c r="AG38" s="25"/>
+      <c r="AF38" s="25"/>
+      <c r="AG38" s="42"/>
       <c r="AH38" s="42"/>
       <c r="AI38" s="42"/>
-      <c r="AJ38" s="42"/>
-      <c r="AK38" s="39"/>
-    </row>
-    <row r="39" spans="1:44">
+      <c r="AJ38" s="39"/>
+    </row>
+    <row r="39" spans="1:43">
       <c r="A39" s="42"/>
       <c r="B39" s="6"/>
       <c r="C39" s="42"/>
@@ -8734,14 +8657,13 @@
       <c r="AC39" s="8"/>
       <c r="AD39" s="8"/>
       <c r="AE39" s="8"/>
-      <c r="AF39" s="8"/>
-      <c r="AG39" s="25"/>
-      <c r="AH39" s="42"/>
-      <c r="AI39" s="63"/>
-      <c r="AJ39" s="42"/>
-      <c r="AK39" s="39"/>
-    </row>
-    <row r="40" spans="1:44">
+      <c r="AF39" s="25"/>
+      <c r="AG39" s="42"/>
+      <c r="AH39" s="63"/>
+      <c r="AI39" s="42"/>
+      <c r="AJ39" s="39"/>
+    </row>
+    <row r="40" spans="1:43">
       <c r="A40" s="42"/>
       <c r="B40" s="6"/>
       <c r="C40" s="42"/>
@@ -8776,14 +8698,13 @@
       <c r="AC40" s="8"/>
       <c r="AD40" s="8"/>
       <c r="AE40" s="8"/>
-      <c r="AF40" s="8"/>
-      <c r="AG40" s="25"/>
-      <c r="AH40" s="42"/>
-      <c r="AI40" s="63"/>
-      <c r="AJ40" s="42"/>
-      <c r="AK40" s="39"/>
-    </row>
-    <row r="41" spans="1:44">
+      <c r="AF40" s="25"/>
+      <c r="AG40" s="42"/>
+      <c r="AH40" s="63"/>
+      <c r="AI40" s="42"/>
+      <c r="AJ40" s="39"/>
+    </row>
+    <row r="41" spans="1:43">
       <c r="A41" s="42"/>
       <c r="B41" s="6"/>
       <c r="C41" s="42"/>
@@ -8818,14 +8739,13 @@
       <c r="AC41" s="8"/>
       <c r="AD41" s="8"/>
       <c r="AE41" s="8"/>
-      <c r="AF41" s="8"/>
-      <c r="AG41" s="25"/>
-      <c r="AH41" s="42"/>
-      <c r="AI41" s="63"/>
-      <c r="AJ41" s="42"/>
-      <c r="AK41" s="39"/>
-    </row>
-    <row r="42" spans="1:44">
+      <c r="AF41" s="25"/>
+      <c r="AG41" s="42"/>
+      <c r="AH41" s="63"/>
+      <c r="AI41" s="42"/>
+      <c r="AJ41" s="39"/>
+    </row>
+    <row r="42" spans="1:43">
       <c r="A42" s="42"/>
       <c r="B42" s="6"/>
       <c r="C42" s="42"/>
@@ -8860,14 +8780,13 @@
       <c r="AC42" s="8"/>
       <c r="AD42" s="8"/>
       <c r="AE42" s="8"/>
-      <c r="AF42" s="8"/>
-      <c r="AG42" s="25"/>
-      <c r="AH42" s="42"/>
-      <c r="AI42" s="63"/>
-      <c r="AJ42" s="42"/>
-      <c r="AK42" s="39"/>
-    </row>
-    <row r="43" spans="1:44">
+      <c r="AF42" s="25"/>
+      <c r="AG42" s="42"/>
+      <c r="AH42" s="63"/>
+      <c r="AI42" s="42"/>
+      <c r="AJ42" s="39"/>
+    </row>
+    <row r="43" spans="1:43">
       <c r="A43" s="42"/>
       <c r="B43" s="6"/>
       <c r="C43" s="6"/>
@@ -8902,14 +8821,13 @@
       <c r="AC43" s="8"/>
       <c r="AD43" s="8"/>
       <c r="AE43" s="8"/>
-      <c r="AF43" s="8"/>
-      <c r="AG43" s="25"/>
-      <c r="AH43" s="42"/>
-      <c r="AI43" s="54"/>
-      <c r="AJ43" s="42"/>
-      <c r="AK43" s="39"/>
-    </row>
-    <row r="44" spans="1:44">
+      <c r="AF43" s="25"/>
+      <c r="AG43" s="42"/>
+      <c r="AH43" s="54"/>
+      <c r="AI43" s="42"/>
+      <c r="AJ43" s="39"/>
+    </row>
+    <row r="44" spans="1:43">
       <c r="A44" s="42"/>
       <c r="B44" s="6"/>
       <c r="C44" s="6"/>
@@ -8930,10 +8848,10 @@
       <c r="O44" s="8"/>
       <c r="P44" s="8"/>
       <c r="Q44" s="8"/>
-      <c r="R44" s="8"/>
-      <c r="S44" s="42"/>
+      <c r="R44" s="42"/>
+      <c r="S44" s="53"/>
       <c r="T44" s="53"/>
-      <c r="U44" s="53"/>
+      <c r="U44" s="8"/>
       <c r="V44" s="8"/>
       <c r="W44" s="8"/>
       <c r="X44" s="8"/>
@@ -8944,14 +8862,13 @@
       <c r="AC44" s="8"/>
       <c r="AD44" s="8"/>
       <c r="AE44" s="8"/>
-      <c r="AF44" s="8"/>
-      <c r="AG44" s="25"/>
-      <c r="AH44" s="6"/>
-      <c r="AI44" s="63"/>
-      <c r="AJ44" s="42"/>
-      <c r="AK44" s="39"/>
-    </row>
-    <row r="45" spans="1:44">
+      <c r="AF44" s="25"/>
+      <c r="AG44" s="6"/>
+      <c r="AH44" s="63"/>
+      <c r="AI44" s="42"/>
+      <c r="AJ44" s="39"/>
+    </row>
+    <row r="45" spans="1:43">
       <c r="A45" s="42"/>
       <c r="B45" s="6"/>
       <c r="C45" s="6"/>
@@ -8972,10 +8889,10 @@
       <c r="O45" s="8"/>
       <c r="P45" s="8"/>
       <c r="Q45" s="8"/>
-      <c r="R45" s="8"/>
+      <c r="R45" s="53"/>
       <c r="S45" s="53"/>
       <c r="T45" s="53"/>
-      <c r="U45" s="53"/>
+      <c r="U45" s="8"/>
       <c r="V45" s="8"/>
       <c r="W45" s="8"/>
       <c r="X45" s="8"/>
@@ -8986,14 +8903,13 @@
       <c r="AC45" s="8"/>
       <c r="AD45" s="8"/>
       <c r="AE45" s="8"/>
-      <c r="AF45" s="8"/>
-      <c r="AG45" s="25"/>
-      <c r="AH45" s="42"/>
-      <c r="AI45" s="63"/>
-      <c r="AJ45" s="42"/>
-      <c r="AK45" s="39"/>
-    </row>
-    <row r="46" spans="1:44">
+      <c r="AF45" s="25"/>
+      <c r="AG45" s="42"/>
+      <c r="AH45" s="63"/>
+      <c r="AI45" s="42"/>
+      <c r="AJ45" s="39"/>
+    </row>
+    <row r="46" spans="1:43">
       <c r="A46" s="42"/>
       <c r="B46" s="6"/>
       <c r="C46" s="6"/>
@@ -9028,14 +8944,13 @@
       <c r="AC46" s="8"/>
       <c r="AD46" s="8"/>
       <c r="AE46" s="8"/>
-      <c r="AF46" s="8"/>
-      <c r="AG46" s="25"/>
-      <c r="AH46" s="42"/>
-      <c r="AI46" s="63"/>
-      <c r="AJ46" s="42"/>
-      <c r="AK46" s="39"/>
-    </row>
-    <row r="47" spans="1:44">
+      <c r="AF46" s="25"/>
+      <c r="AG46" s="42"/>
+      <c r="AH46" s="63"/>
+      <c r="AI46" s="42"/>
+      <c r="AJ46" s="39"/>
+    </row>
+    <row r="47" spans="1:43">
       <c r="A47" s="42"/>
       <c r="B47" s="61"/>
       <c r="C47" s="42"/>
@@ -9070,14 +8985,13 @@
       <c r="AC47" s="8"/>
       <c r="AD47" s="8"/>
       <c r="AE47" s="8"/>
-      <c r="AF47" s="8"/>
-      <c r="AG47" s="25"/>
+      <c r="AF47" s="25"/>
+      <c r="AG47" s="61"/>
       <c r="AH47" s="61"/>
-      <c r="AI47" s="61"/>
-      <c r="AJ47" s="42"/>
-      <c r="AK47" s="39"/>
-    </row>
-    <row r="48" spans="1:44">
+      <c r="AI47" s="42"/>
+      <c r="AJ47" s="39"/>
+    </row>
+    <row r="48" spans="1:43">
       <c r="A48" s="42"/>
       <c r="B48" s="6"/>
       <c r="C48" s="6"/>
@@ -9112,14 +9026,13 @@
       <c r="AC48" s="8"/>
       <c r="AD48" s="8"/>
       <c r="AE48" s="8"/>
-      <c r="AF48" s="8"/>
-      <c r="AG48" s="25"/>
-      <c r="AH48" s="42"/>
-      <c r="AI48" s="54"/>
-      <c r="AJ48" s="42"/>
-      <c r="AK48" s="39"/>
-    </row>
-    <row r="49" spans="1:37">
+      <c r="AF48" s="25"/>
+      <c r="AG48" s="42"/>
+      <c r="AH48" s="54"/>
+      <c r="AI48" s="42"/>
+      <c r="AJ48" s="39"/>
+    </row>
+    <row r="49" spans="1:36">
       <c r="A49" s="42"/>
       <c r="B49" s="6"/>
       <c r="C49" s="6"/>
@@ -9140,10 +9053,10 @@
       <c r="O49" s="8"/>
       <c r="P49" s="8"/>
       <c r="Q49" s="8"/>
-      <c r="R49" s="8"/>
+      <c r="R49" s="53"/>
       <c r="S49" s="53"/>
       <c r="T49" s="53"/>
-      <c r="U49" s="53"/>
+      <c r="U49" s="8"/>
       <c r="V49" s="8"/>
       <c r="W49" s="8"/>
       <c r="X49" s="8"/>
@@ -9154,14 +9067,13 @@
       <c r="AC49" s="8"/>
       <c r="AD49" s="8"/>
       <c r="AE49" s="8"/>
-      <c r="AF49" s="8"/>
-      <c r="AG49" s="25"/>
-      <c r="AH49" s="6"/>
-      <c r="AI49" s="63"/>
-      <c r="AJ49" s="42"/>
-      <c r="AK49" s="39"/>
-    </row>
-    <row r="50" spans="1:37">
+      <c r="AF49" s="25"/>
+      <c r="AG49" s="6"/>
+      <c r="AH49" s="63"/>
+      <c r="AI49" s="42"/>
+      <c r="AJ49" s="39"/>
+    </row>
+    <row r="50" spans="1:36">
       <c r="A50" s="42"/>
       <c r="B50" s="6"/>
       <c r="C50" s="6"/>
@@ -9182,9 +9094,9 @@
       <c r="O50" s="8"/>
       <c r="P50" s="8"/>
       <c r="Q50" s="8"/>
-      <c r="R50" s="8"/>
+      <c r="R50" s="53"/>
       <c r="S50" s="53"/>
-      <c r="T50" s="53"/>
+      <c r="T50" s="8"/>
       <c r="U50" s="8"/>
       <c r="V50" s="8"/>
       <c r="W50" s="8"/>
@@ -9196,14 +9108,13 @@
       <c r="AC50" s="8"/>
       <c r="AD50" s="8"/>
       <c r="AE50" s="8"/>
-      <c r="AF50" s="8"/>
-      <c r="AG50" s="25"/>
-      <c r="AH50" s="42"/>
-      <c r="AI50" s="63"/>
-      <c r="AJ50" s="42"/>
-      <c r="AK50" s="39"/>
-    </row>
-    <row r="51" spans="1:37">
+      <c r="AF50" s="25"/>
+      <c r="AG50" s="42"/>
+      <c r="AH50" s="63"/>
+      <c r="AI50" s="42"/>
+      <c r="AJ50" s="39"/>
+    </row>
+    <row r="51" spans="1:36">
       <c r="A51" s="42"/>
       <c r="B51" s="6"/>
       <c r="C51" s="6"/>
@@ -9238,14 +9149,13 @@
       <c r="AC51" s="8"/>
       <c r="AD51" s="8"/>
       <c r="AE51" s="8"/>
-      <c r="AF51" s="8"/>
-      <c r="AG51" s="25"/>
-      <c r="AH51" s="6"/>
-      <c r="AI51" s="63"/>
-      <c r="AJ51" s="42"/>
-      <c r="AK51" s="39"/>
-    </row>
-    <row r="52" spans="1:37">
+      <c r="AF51" s="25"/>
+      <c r="AG51" s="6"/>
+      <c r="AH51" s="63"/>
+      <c r="AI51" s="42"/>
+      <c r="AJ51" s="39"/>
+    </row>
+    <row r="52" spans="1:36">
       <c r="A52" s="42"/>
       <c r="B52" s="6"/>
       <c r="C52" s="6"/>
@@ -9280,14 +9190,13 @@
       <c r="AC52" s="8"/>
       <c r="AD52" s="8"/>
       <c r="AE52" s="8"/>
-      <c r="AF52" s="8"/>
-      <c r="AG52" s="25"/>
-      <c r="AH52" s="6"/>
-      <c r="AI52" s="63"/>
-      <c r="AJ52" s="42"/>
-      <c r="AK52" s="39"/>
-    </row>
-    <row r="53" spans="1:37">
+      <c r="AF52" s="25"/>
+      <c r="AG52" s="6"/>
+      <c r="AH52" s="63"/>
+      <c r="AI52" s="42"/>
+      <c r="AJ52" s="39"/>
+    </row>
+    <row r="53" spans="1:36">
       <c r="A53" s="42"/>
       <c r="B53" s="6"/>
       <c r="C53" s="6"/>
@@ -9322,14 +9231,13 @@
       <c r="AC53" s="8"/>
       <c r="AD53" s="8"/>
       <c r="AE53" s="8"/>
-      <c r="AF53" s="8"/>
-      <c r="AG53" s="25"/>
-      <c r="AH53" s="42"/>
-      <c r="AI53" s="54"/>
-      <c r="AJ53" s="42"/>
-      <c r="AK53" s="39"/>
-    </row>
-    <row r="54" spans="1:37">
+      <c r="AF53" s="25"/>
+      <c r="AG53" s="42"/>
+      <c r="AH53" s="54"/>
+      <c r="AI53" s="42"/>
+      <c r="AJ53" s="39"/>
+    </row>
+    <row r="54" spans="1:36">
       <c r="A54" s="42"/>
       <c r="B54" s="6"/>
       <c r="C54" s="6"/>
@@ -9350,10 +9258,10 @@
       <c r="O54" s="8"/>
       <c r="P54" s="8"/>
       <c r="Q54" s="8"/>
-      <c r="R54" s="8"/>
+      <c r="R54" s="53"/>
       <c r="S54" s="53"/>
       <c r="T54" s="53"/>
-      <c r="U54" s="53"/>
+      <c r="U54" s="8"/>
       <c r="V54" s="8"/>
       <c r="W54" s="8"/>
       <c r="X54" s="8"/>
@@ -9364,14 +9272,13 @@
       <c r="AC54" s="8"/>
       <c r="AD54" s="8"/>
       <c r="AE54" s="8"/>
-      <c r="AF54" s="8"/>
-      <c r="AG54" s="25"/>
-      <c r="AH54" s="6"/>
-      <c r="AI54" s="63"/>
-      <c r="AJ54" s="42"/>
-      <c r="AK54" s="39"/>
-    </row>
-    <row r="55" spans="1:37">
+      <c r="AF54" s="25"/>
+      <c r="AG54" s="6"/>
+      <c r="AH54" s="63"/>
+      <c r="AI54" s="42"/>
+      <c r="AJ54" s="39"/>
+    </row>
+    <row r="55" spans="1:36">
       <c r="A55" s="42"/>
       <c r="B55" s="6"/>
       <c r="C55" s="42"/>
@@ -9406,14 +9313,13 @@
       <c r="AC55" s="8"/>
       <c r="AD55" s="8"/>
       <c r="AE55" s="8"/>
-      <c r="AF55" s="8"/>
-      <c r="AG55" s="25"/>
+      <c r="AF55" s="25"/>
+      <c r="AG55" s="42"/>
       <c r="AH55" s="42"/>
       <c r="AI55" s="42"/>
-      <c r="AJ55" s="42"/>
-      <c r="AK55" s="39"/>
-    </row>
-    <row r="56" spans="1:37">
+      <c r="AJ55" s="39"/>
+    </row>
+    <row r="56" spans="1:36">
       <c r="A56" s="42"/>
       <c r="B56" s="42"/>
       <c r="C56" s="42"/>
@@ -9434,10 +9340,10 @@
       <c r="O56" s="8"/>
       <c r="P56" s="8"/>
       <c r="Q56" s="8"/>
-      <c r="R56" s="8"/>
+      <c r="R56" s="53"/>
       <c r="S56" s="53"/>
       <c r="T56" s="53"/>
-      <c r="U56" s="53"/>
+      <c r="U56" s="8"/>
       <c r="V56" s="8"/>
       <c r="W56" s="8"/>
       <c r="X56" s="8"/>
@@ -9448,14 +9354,13 @@
       <c r="AC56" s="8"/>
       <c r="AD56" s="8"/>
       <c r="AE56" s="8"/>
-      <c r="AF56" s="8"/>
-      <c r="AG56" s="25"/>
+      <c r="AF56" s="25"/>
+      <c r="AG56" s="42"/>
       <c r="AH56" s="42"/>
       <c r="AI56" s="42"/>
-      <c r="AJ56" s="42"/>
-      <c r="AK56" s="39"/>
-    </row>
-    <row r="57" spans="1:37">
+      <c r="AJ56" s="39"/>
+    </row>
+    <row r="57" spans="1:36">
       <c r="A57" s="42"/>
       <c r="B57" s="6"/>
       <c r="C57" s="42"/>
@@ -9490,14 +9395,13 @@
       <c r="AC57" s="8"/>
       <c r="AD57" s="8"/>
       <c r="AE57" s="8"/>
-      <c r="AF57" s="8"/>
-      <c r="AG57" s="25"/>
+      <c r="AF57" s="25"/>
+      <c r="AG57" s="42"/>
       <c r="AH57" s="42"/>
       <c r="AI57" s="42"/>
-      <c r="AJ57" s="42"/>
-      <c r="AK57" s="39"/>
-    </row>
-    <row r="58" spans="1:37">
+      <c r="AJ57" s="39"/>
+    </row>
+    <row r="58" spans="1:36">
       <c r="A58" s="42"/>
       <c r="B58" s="6"/>
       <c r="C58" s="42"/>
@@ -9532,14 +9436,13 @@
       <c r="AC58" s="8"/>
       <c r="AD58" s="8"/>
       <c r="AE58" s="8"/>
-      <c r="AF58" s="8"/>
-      <c r="AG58" s="25"/>
-      <c r="AH58" s="42"/>
-      <c r="AI58" s="63"/>
-      <c r="AJ58" s="42"/>
-      <c r="AK58" s="39"/>
-    </row>
-    <row r="59" spans="1:37">
+      <c r="AF58" s="25"/>
+      <c r="AG58" s="42"/>
+      <c r="AH58" s="63"/>
+      <c r="AI58" s="42"/>
+      <c r="AJ58" s="39"/>
+    </row>
+    <row r="59" spans="1:36">
       <c r="A59" s="42"/>
       <c r="B59" s="6"/>
       <c r="C59" s="42"/>
@@ -9574,14 +9477,13 @@
       <c r="AC59" s="8"/>
       <c r="AD59" s="8"/>
       <c r="AE59" s="8"/>
-      <c r="AF59" s="8"/>
-      <c r="AG59" s="25"/>
-      <c r="AH59" s="42"/>
-      <c r="AI59" s="63"/>
-      <c r="AJ59" s="42"/>
-      <c r="AK59" s="39"/>
-    </row>
-    <row r="60" spans="1:37">
+      <c r="AF59" s="25"/>
+      <c r="AG59" s="42"/>
+      <c r="AH59" s="63"/>
+      <c r="AI59" s="42"/>
+      <c r="AJ59" s="39"/>
+    </row>
+    <row r="60" spans="1:36">
       <c r="A60" s="42"/>
       <c r="B60" s="6"/>
       <c r="C60" s="6"/>
@@ -9616,14 +9518,13 @@
       <c r="AC60" s="8"/>
       <c r="AD60" s="8"/>
       <c r="AE60" s="8"/>
-      <c r="AF60" s="8"/>
-      <c r="AG60" s="25"/>
-      <c r="AH60" s="42"/>
-      <c r="AI60" s="54"/>
-      <c r="AJ60" s="42"/>
-      <c r="AK60" s="39"/>
-    </row>
-    <row r="61" spans="1:37">
+      <c r="AF60" s="25"/>
+      <c r="AG60" s="42"/>
+      <c r="AH60" s="54"/>
+      <c r="AI60" s="42"/>
+      <c r="AJ60" s="39"/>
+    </row>
+    <row r="61" spans="1:36">
       <c r="A61" s="42"/>
       <c r="B61" s="6"/>
       <c r="C61" s="6"/>
@@ -9644,10 +9545,10 @@
       <c r="O61" s="8"/>
       <c r="P61" s="8"/>
       <c r="Q61" s="8"/>
-      <c r="R61" s="8"/>
+      <c r="R61" s="53"/>
       <c r="S61" s="53"/>
       <c r="T61" s="53"/>
-      <c r="U61" s="53"/>
+      <c r="U61" s="8"/>
       <c r="V61" s="8"/>
       <c r="W61" s="8"/>
       <c r="X61" s="8"/>
@@ -9658,14 +9559,13 @@
       <c r="AC61" s="8"/>
       <c r="AD61" s="8"/>
       <c r="AE61" s="8"/>
-      <c r="AF61" s="8"/>
-      <c r="AG61" s="25"/>
-      <c r="AH61" s="6"/>
-      <c r="AI61" s="63"/>
-      <c r="AJ61" s="42"/>
-      <c r="AK61" s="39"/>
-    </row>
-    <row r="62" spans="1:37">
+      <c r="AF61" s="25"/>
+      <c r="AG61" s="6"/>
+      <c r="AH61" s="63"/>
+      <c r="AI61" s="42"/>
+      <c r="AJ61" s="39"/>
+    </row>
+    <row r="62" spans="1:36">
       <c r="A62" s="42"/>
       <c r="B62" s="42"/>
       <c r="C62" s="42"/>
@@ -9686,10 +9586,10 @@
       <c r="O62" s="8"/>
       <c r="P62" s="8"/>
       <c r="Q62" s="8"/>
-      <c r="R62" s="8"/>
+      <c r="R62" s="53"/>
       <c r="S62" s="53"/>
       <c r="T62" s="53"/>
-      <c r="U62" s="53"/>
+      <c r="U62" s="8"/>
       <c r="V62" s="8"/>
       <c r="W62" s="8"/>
       <c r="X62" s="8"/>
@@ -9700,14 +9600,13 @@
       <c r="AC62" s="8"/>
       <c r="AD62" s="8"/>
       <c r="AE62" s="8"/>
-      <c r="AF62" s="8"/>
-      <c r="AG62" s="25"/>
+      <c r="AF62" s="25"/>
+      <c r="AG62" s="42"/>
       <c r="AH62" s="42"/>
       <c r="AI62" s="42"/>
-      <c r="AJ62" s="42"/>
-      <c r="AK62" s="39"/>
-    </row>
-    <row r="63" spans="1:37">
+      <c r="AJ62" s="39"/>
+    </row>
+    <row r="63" spans="1:36">
       <c r="A63" s="42"/>
       <c r="B63" s="42"/>
       <c r="C63" s="42"/>
@@ -9728,9 +9627,9 @@
       <c r="O63" s="8"/>
       <c r="P63" s="8"/>
       <c r="Q63" s="8"/>
-      <c r="R63" s="8"/>
+      <c r="R63" s="53"/>
       <c r="S63" s="53"/>
-      <c r="T63" s="53"/>
+      <c r="T63" s="8"/>
       <c r="U63" s="8"/>
       <c r="V63" s="8"/>
       <c r="W63" s="8"/>
@@ -9742,14 +9641,13 @@
       <c r="AC63" s="8"/>
       <c r="AD63" s="8"/>
       <c r="AE63" s="8"/>
-      <c r="AF63" s="8"/>
-      <c r="AG63" s="25"/>
+      <c r="AF63" s="25"/>
+      <c r="AG63" s="42"/>
       <c r="AH63" s="42"/>
       <c r="AI63" s="42"/>
-      <c r="AJ63" s="42"/>
-      <c r="AK63" s="39"/>
-    </row>
-    <row r="64" spans="1:37">
+      <c r="AJ63" s="39"/>
+    </row>
+    <row r="64" spans="1:36">
       <c r="A64" s="42"/>
       <c r="B64" s="42"/>
       <c r="C64" s="42"/>
@@ -9784,14 +9682,13 @@
       <c r="AC64" s="8"/>
       <c r="AD64" s="8"/>
       <c r="AE64" s="8"/>
-      <c r="AF64" s="8"/>
-      <c r="AG64" s="25"/>
+      <c r="AF64" s="25"/>
+      <c r="AG64" s="42"/>
       <c r="AH64" s="42"/>
       <c r="AI64" s="42"/>
-      <c r="AJ64" s="42"/>
-      <c r="AK64" s="39"/>
-    </row>
-    <row r="65" spans="1:37" ht="16" customHeight="1">
+      <c r="AJ64" s="39"/>
+    </row>
+    <row r="65" spans="1:36" ht="16" customHeight="1">
       <c r="A65" s="42"/>
       <c r="B65" s="42"/>
       <c r="C65" s="42"/>
@@ -9818,7 +9715,7 @@
       <c r="U65" s="8"/>
       <c r="V65" s="8"/>
       <c r="W65" s="8"/>
-      <c r="X65" s="8"/>
+      <c r="X65" s="39"/>
       <c r="Y65" s="39"/>
       <c r="Z65" s="39"/>
       <c r="AA65" s="39"/>
@@ -9826,14 +9723,13 @@
       <c r="AC65" s="39"/>
       <c r="AD65" s="39"/>
       <c r="AE65" s="39"/>
-      <c r="AF65" s="39"/>
-      <c r="AG65" s="48"/>
-      <c r="AH65" s="42"/>
-      <c r="AI65" s="6"/>
-      <c r="AJ65" s="42"/>
-      <c r="AK65" s="39"/>
-    </row>
-    <row r="66" spans="1:37">
+      <c r="AF65" s="48"/>
+      <c r="AG65" s="42"/>
+      <c r="AH65" s="6"/>
+      <c r="AI65" s="42"/>
+      <c r="AJ65" s="39"/>
+    </row>
+    <row r="66" spans="1:36">
       <c r="A66" s="42"/>
       <c r="B66" s="42"/>
       <c r="C66" s="42"/>
@@ -9860,7 +9756,7 @@
       <c r="U66" s="8"/>
       <c r="V66" s="8"/>
       <c r="W66" s="8"/>
-      <c r="X66" s="8"/>
+      <c r="X66" s="39"/>
       <c r="Y66" s="39"/>
       <c r="Z66" s="39"/>
       <c r="AA66" s="39"/>
@@ -9868,14 +9764,13 @@
       <c r="AC66" s="39"/>
       <c r="AD66" s="39"/>
       <c r="AE66" s="39"/>
-      <c r="AF66" s="39"/>
-      <c r="AG66" s="48"/>
-      <c r="AH66" s="42"/>
-      <c r="AI66" s="6"/>
-      <c r="AJ66" s="42"/>
-      <c r="AK66" s="39"/>
-    </row>
-    <row r="67" spans="1:37">
+      <c r="AF66" s="48"/>
+      <c r="AG66" s="42"/>
+      <c r="AH66" s="6"/>
+      <c r="AI66" s="42"/>
+      <c r="AJ66" s="39"/>
+    </row>
+    <row r="67" spans="1:36">
       <c r="A67" s="42"/>
       <c r="B67" s="42"/>
       <c r="C67" s="42"/>
@@ -9902,7 +9797,7 @@
       <c r="U67" s="8"/>
       <c r="V67" s="8"/>
       <c r="W67" s="8"/>
-      <c r="X67" s="8"/>
+      <c r="X67" s="39"/>
       <c r="Y67" s="39"/>
       <c r="Z67" s="39"/>
       <c r="AA67" s="39"/>
@@ -9910,14 +9805,13 @@
       <c r="AC67" s="39"/>
       <c r="AD67" s="39"/>
       <c r="AE67" s="39"/>
-      <c r="AF67" s="39"/>
-      <c r="AG67" s="48"/>
-      <c r="AH67" s="42"/>
-      <c r="AI67" s="6"/>
-      <c r="AJ67" s="42"/>
-      <c r="AK67" s="39"/>
-    </row>
-    <row r="68" spans="1:37" ht="48" customHeight="1">
+      <c r="AF67" s="48"/>
+      <c r="AG67" s="42"/>
+      <c r="AH67" s="6"/>
+      <c r="AI67" s="42"/>
+      <c r="AJ67" s="39"/>
+    </row>
+    <row r="68" spans="1:36" ht="48" customHeight="1">
       <c r="A68" s="42"/>
       <c r="B68" s="61"/>
       <c r="C68" s="61"/>
@@ -9938,10 +9832,10 @@
       <c r="O68" s="8"/>
       <c r="P68" s="8"/>
       <c r="Q68" s="8"/>
-      <c r="R68" s="8"/>
+      <c r="R68" s="53"/>
       <c r="S68" s="53"/>
       <c r="T68" s="53"/>
-      <c r="U68" s="53"/>
+      <c r="U68" s="8"/>
       <c r="V68" s="8"/>
       <c r="W68" s="8"/>
       <c r="X68" s="8"/>
@@ -9952,14 +9846,13 @@
       <c r="AC68" s="8"/>
       <c r="AD68" s="8"/>
       <c r="AE68" s="8"/>
-      <c r="AF68" s="8"/>
-      <c r="AG68" s="25"/>
-      <c r="AH68" s="61"/>
+      <c r="AF68" s="25"/>
+      <c r="AG68" s="61"/>
+      <c r="AH68" s="42"/>
       <c r="AI68" s="42"/>
-      <c r="AJ68" s="42"/>
-      <c r="AK68" s="39"/>
-    </row>
-    <row r="69" spans="1:37" ht="240" customHeight="1">
+      <c r="AJ68" s="39"/>
+    </row>
+    <row r="69" spans="1:36" ht="240" customHeight="1">
       <c r="A69" s="42"/>
       <c r="B69" s="42"/>
       <c r="C69" s="42"/>
@@ -9994,14 +9887,13 @@
       <c r="AC69" s="8"/>
       <c r="AD69" s="8"/>
       <c r="AE69" s="8"/>
-      <c r="AF69" s="8"/>
-      <c r="AG69" s="48"/>
+      <c r="AF69" s="48"/>
+      <c r="AG69" s="42"/>
       <c r="AH69" s="42"/>
       <c r="AI69" s="42"/>
-      <c r="AJ69" s="42"/>
-      <c r="AK69" s="39"/>
-    </row>
-    <row r="70" spans="1:37">
+      <c r="AJ69" s="39"/>
+    </row>
+    <row r="70" spans="1:36">
       <c r="A70" s="42"/>
       <c r="B70" s="42"/>
       <c r="C70" s="42"/>
@@ -10022,10 +9914,10 @@
       <c r="O70" s="8"/>
       <c r="P70" s="8"/>
       <c r="Q70" s="8"/>
-      <c r="R70" s="8"/>
+      <c r="R70" s="53"/>
       <c r="S70" s="53"/>
       <c r="T70" s="53"/>
-      <c r="U70" s="53"/>
+      <c r="U70" s="8"/>
       <c r="V70" s="8"/>
       <c r="W70" s="8"/>
       <c r="X70" s="8"/>
@@ -10036,14 +9928,13 @@
       <c r="AC70" s="8"/>
       <c r="AD70" s="8"/>
       <c r="AE70" s="8"/>
-      <c r="AF70" s="8"/>
-      <c r="AG70" s="25"/>
+      <c r="AF70" s="25"/>
+      <c r="AG70" s="42"/>
       <c r="AH70" s="42"/>
       <c r="AI70" s="42"/>
-      <c r="AJ70" s="42"/>
-      <c r="AK70" s="39"/>
-    </row>
-    <row r="71" spans="1:37">
+      <c r="AJ70" s="39"/>
+    </row>
+    <row r="71" spans="1:36">
       <c r="A71" s="42"/>
       <c r="B71" s="42"/>
       <c r="C71" s="42"/>
@@ -10078,14 +9969,13 @@
       <c r="AC71" s="8"/>
       <c r="AD71" s="8"/>
       <c r="AE71" s="8"/>
-      <c r="AF71" s="8"/>
-      <c r="AG71" s="25"/>
+      <c r="AF71" s="25"/>
+      <c r="AG71" s="42"/>
       <c r="AH71" s="42"/>
       <c r="AI71" s="42"/>
-      <c r="AJ71" s="42"/>
-      <c r="AK71" s="39"/>
-    </row>
-    <row r="72" spans="1:37">
+      <c r="AJ71" s="39"/>
+    </row>
+    <row r="72" spans="1:36">
       <c r="A72" s="42"/>
       <c r="B72" s="42"/>
       <c r="C72" s="42"/>
@@ -10107,10 +9997,10 @@
       <c r="P72" s="8"/>
       <c r="Q72" s="8"/>
       <c r="R72" s="8"/>
-      <c r="S72" s="8"/>
-      <c r="T72" s="6"/>
-      <c r="U72" s="8"/>
-      <c r="V72" s="65"/>
+      <c r="S72" s="6"/>
+      <c r="T72" s="8"/>
+      <c r="U72" s="65"/>
+      <c r="V72" s="8"/>
       <c r="W72" s="8"/>
       <c r="X72" s="8"/>
       <c r="Y72" s="8"/>
@@ -10120,14 +10010,13 @@
       <c r="AC72" s="8"/>
       <c r="AD72" s="8"/>
       <c r="AE72" s="8"/>
-      <c r="AF72" s="8"/>
-      <c r="AG72" s="25"/>
+      <c r="AF72" s="25"/>
+      <c r="AG72" s="42"/>
       <c r="AH72" s="42"/>
       <c r="AI72" s="42"/>
-      <c r="AJ72" s="42"/>
-      <c r="AK72" s="39"/>
-    </row>
-    <row r="73" spans="1:37">
+      <c r="AJ72" s="39"/>
+    </row>
+    <row r="73" spans="1:36">
       <c r="A73" s="42"/>
       <c r="B73" s="42"/>
       <c r="C73" s="42"/>
@@ -10148,11 +10037,11 @@
       <c r="O73" s="8"/>
       <c r="P73" s="8"/>
       <c r="Q73" s="8"/>
-      <c r="R73" s="8"/>
-      <c r="S73" s="42"/>
-      <c r="T73" s="6"/>
-      <c r="U73" s="8"/>
-      <c r="V73" s="65"/>
+      <c r="R73" s="42"/>
+      <c r="S73" s="6"/>
+      <c r="T73" s="8"/>
+      <c r="U73" s="65"/>
+      <c r="V73" s="8"/>
       <c r="W73" s="8"/>
       <c r="X73" s="8"/>
       <c r="Y73" s="8"/>
@@ -10162,14 +10051,13 @@
       <c r="AC73" s="8"/>
       <c r="AD73" s="8"/>
       <c r="AE73" s="8"/>
-      <c r="AF73" s="8"/>
-      <c r="AG73" s="25"/>
+      <c r="AF73" s="25"/>
+      <c r="AG73" s="42"/>
       <c r="AH73" s="42"/>
       <c r="AI73" s="42"/>
-      <c r="AJ73" s="42"/>
-      <c r="AK73" s="39"/>
-    </row>
-    <row r="74" spans="1:37">
+      <c r="AJ73" s="39"/>
+    </row>
+    <row r="74" spans="1:36">
       <c r="A74" s="61"/>
       <c r="B74" s="62"/>
       <c r="C74" s="62"/>
@@ -10204,14 +10092,13 @@
       <c r="AC74" s="65"/>
       <c r="AD74" s="65"/>
       <c r="AE74" s="65"/>
-      <c r="AF74" s="65"/>
-      <c r="AG74" s="59"/>
-      <c r="AH74" s="42"/>
-      <c r="AI74" s="66"/>
-      <c r="AJ74" s="42"/>
-      <c r="AK74" s="39"/>
-    </row>
-    <row r="75" spans="1:37">
+      <c r="AF74" s="59"/>
+      <c r="AG74" s="42"/>
+      <c r="AH74" s="66"/>
+      <c r="AI74" s="42"/>
+      <c r="AJ74" s="39"/>
+    </row>
+    <row r="75" spans="1:36">
       <c r="A75" s="61"/>
       <c r="B75" s="6"/>
       <c r="C75" s="6"/>
@@ -10232,10 +10119,10 @@
       <c r="O75" s="8"/>
       <c r="P75" s="8"/>
       <c r="Q75" s="8"/>
-      <c r="R75" s="8"/>
+      <c r="R75" s="53"/>
       <c r="S75" s="53"/>
       <c r="T75" s="53"/>
-      <c r="U75" s="53"/>
+      <c r="U75" s="8"/>
       <c r="V75" s="8"/>
       <c r="W75" s="8"/>
       <c r="X75" s="8"/>
@@ -10246,14 +10133,13 @@
       <c r="AC75" s="8"/>
       <c r="AD75" s="8"/>
       <c r="AE75" s="8"/>
-      <c r="AF75" s="8"/>
-      <c r="AG75" s="25"/>
-      <c r="AH75" s="6"/>
-      <c r="AI75" s="63"/>
-      <c r="AJ75" s="42"/>
-      <c r="AK75" s="39"/>
-    </row>
-    <row r="76" spans="1:37">
+      <c r="AF75" s="25"/>
+      <c r="AG75" s="6"/>
+      <c r="AH75" s="63"/>
+      <c r="AI75" s="42"/>
+      <c r="AJ75" s="39"/>
+    </row>
+    <row r="76" spans="1:36">
       <c r="A76" s="61"/>
       <c r="B76" s="61"/>
       <c r="C76" s="61"/>
@@ -10274,10 +10160,10 @@
       <c r="O76" s="8"/>
       <c r="P76" s="8"/>
       <c r="Q76" s="8"/>
-      <c r="R76" s="8"/>
+      <c r="R76" s="53"/>
       <c r="S76" s="53"/>
       <c r="T76" s="53"/>
-      <c r="U76" s="53"/>
+      <c r="U76" s="65"/>
       <c r="V76" s="65"/>
       <c r="W76" s="65"/>
       <c r="X76" s="65"/>
@@ -10288,14 +10174,13 @@
       <c r="AC76" s="65"/>
       <c r="AD76" s="65"/>
       <c r="AE76" s="65"/>
-      <c r="AF76" s="65"/>
-      <c r="AG76" s="59"/>
-      <c r="AH76" s="61"/>
-      <c r="AI76" s="66"/>
-      <c r="AJ76" s="42"/>
-      <c r="AK76" s="39"/>
-    </row>
-    <row r="77" spans="1:37" ht="48" customHeight="1">
+      <c r="AF76" s="59"/>
+      <c r="AG76" s="61"/>
+      <c r="AH76" s="66"/>
+      <c r="AI76" s="42"/>
+      <c r="AJ76" s="39"/>
+    </row>
+    <row r="77" spans="1:36" ht="48" customHeight="1">
       <c r="A77" s="61"/>
       <c r="B77" s="61"/>
       <c r="C77" s="61"/>
@@ -10316,10 +10201,10 @@
       <c r="O77" s="8"/>
       <c r="P77" s="8"/>
       <c r="Q77" s="8"/>
-      <c r="R77" s="8"/>
+      <c r="R77" s="53"/>
       <c r="S77" s="53"/>
       <c r="T77" s="53"/>
-      <c r="U77" s="53"/>
+      <c r="U77" s="8"/>
       <c r="V77" s="8"/>
       <c r="W77" s="8"/>
       <c r="X77" s="8"/>
@@ -10330,14 +10215,13 @@
       <c r="AC77" s="8"/>
       <c r="AD77" s="8"/>
       <c r="AE77" s="8"/>
-      <c r="AF77" s="8"/>
-      <c r="AG77" s="25"/>
-      <c r="AH77" s="61"/>
+      <c r="AF77" s="25"/>
+      <c r="AG77" s="61"/>
+      <c r="AH77" s="42"/>
       <c r="AI77" s="42"/>
-      <c r="AJ77" s="42"/>
-      <c r="AK77" s="39"/>
-    </row>
-    <row r="78" spans="1:37" ht="48" customHeight="1">
+      <c r="AJ77" s="39"/>
+    </row>
+    <row r="78" spans="1:36" ht="48" customHeight="1">
       <c r="A78" s="61"/>
       <c r="B78" s="42"/>
       <c r="C78" s="42"/>
@@ -10372,14 +10256,13 @@
       <c r="AC78" s="65"/>
       <c r="AD78" s="65"/>
       <c r="AE78" s="65"/>
-      <c r="AF78" s="65"/>
-      <c r="AG78" s="25"/>
+      <c r="AF78" s="25"/>
+      <c r="AG78" s="42"/>
       <c r="AH78" s="42"/>
       <c r="AI78" s="42"/>
-      <c r="AJ78" s="42"/>
-      <c r="AK78" s="39"/>
-    </row>
-    <row r="79" spans="1:37">
+      <c r="AJ78" s="39"/>
+    </row>
+    <row r="79" spans="1:36">
       <c r="A79" s="61"/>
       <c r="B79" s="42"/>
       <c r="C79" s="61"/>
@@ -10414,14 +10297,13 @@
       <c r="AC79" s="65"/>
       <c r="AD79" s="65"/>
       <c r="AE79" s="65"/>
-      <c r="AF79" s="65"/>
-      <c r="AG79" s="59"/>
+      <c r="AF79" s="59"/>
+      <c r="AG79" s="61"/>
       <c r="AH79" s="61"/>
-      <c r="AI79" s="61"/>
-      <c r="AJ79" s="42"/>
-      <c r="AK79" s="39"/>
-    </row>
-    <row r="80" spans="1:37">
+      <c r="AI79" s="42"/>
+      <c r="AJ79" s="39"/>
+    </row>
+    <row r="80" spans="1:36">
       <c r="A80" s="61"/>
       <c r="B80" s="62"/>
       <c r="C80" s="61"/>
@@ -10456,14 +10338,13 @@
       <c r="AC80" s="65"/>
       <c r="AD80" s="65"/>
       <c r="AE80" s="65"/>
-      <c r="AF80" s="65"/>
-      <c r="AG80" s="59"/>
-      <c r="AH80" s="62"/>
-      <c r="AI80" s="61"/>
-      <c r="AJ80" s="42"/>
-      <c r="AK80" s="39"/>
-    </row>
-    <row r="81" spans="1:37">
+      <c r="AF80" s="59"/>
+      <c r="AG80" s="62"/>
+      <c r="AH80" s="61"/>
+      <c r="AI80" s="42"/>
+      <c r="AJ80" s="39"/>
+    </row>
+    <row r="81" spans="1:36">
       <c r="A81" s="61"/>
       <c r="B81" s="61"/>
       <c r="C81" s="61"/>
@@ -10498,14 +10379,13 @@
       <c r="AC81" s="65"/>
       <c r="AD81" s="65"/>
       <c r="AE81" s="65"/>
-      <c r="AF81" s="65"/>
-      <c r="AG81" s="59"/>
+      <c r="AF81" s="59"/>
+      <c r="AG81" s="61"/>
       <c r="AH81" s="61"/>
-      <c r="AI81" s="61"/>
-      <c r="AJ81" s="42"/>
-      <c r="AK81" s="39"/>
-    </row>
-    <row r="82" spans="1:37">
+      <c r="AI81" s="42"/>
+      <c r="AJ81" s="39"/>
+    </row>
+    <row r="82" spans="1:36">
       <c r="A82" s="61"/>
       <c r="B82" s="61"/>
       <c r="C82" s="61"/>
@@ -10540,14 +10420,13 @@
       <c r="AC82" s="65"/>
       <c r="AD82" s="65"/>
       <c r="AE82" s="65"/>
-      <c r="AF82" s="65"/>
-      <c r="AG82" s="59"/>
+      <c r="AF82" s="59"/>
+      <c r="AG82" s="61"/>
       <c r="AH82" s="61"/>
-      <c r="AI82" s="61"/>
-      <c r="AJ82" s="42"/>
-      <c r="AK82" s="39"/>
-    </row>
-    <row r="83" spans="1:37">
+      <c r="AI82" s="42"/>
+      <c r="AJ82" s="39"/>
+    </row>
+    <row r="83" spans="1:36">
       <c r="A83" s="61"/>
       <c r="B83" s="61"/>
       <c r="C83" s="61"/>
@@ -10568,13 +10447,13 @@
       <c r="O83" s="8"/>
       <c r="P83" s="8"/>
       <c r="Q83" s="65"/>
-      <c r="R83" s="65"/>
+      <c r="R83" s="8"/>
       <c r="S83" s="8"/>
       <c r="T83" s="8"/>
       <c r="U83" s="8"/>
       <c r="V83" s="8"/>
       <c r="W83" s="8"/>
-      <c r="X83" s="8"/>
+      <c r="X83" s="65"/>
       <c r="Y83" s="65"/>
       <c r="Z83" s="65"/>
       <c r="AA83" s="65"/>
@@ -10582,14 +10461,13 @@
       <c r="AC83" s="65"/>
       <c r="AD83" s="65"/>
       <c r="AE83" s="65"/>
-      <c r="AF83" s="65"/>
-      <c r="AG83" s="59"/>
-      <c r="AH83" s="42"/>
-      <c r="AI83" s="66"/>
-      <c r="AJ83" s="42"/>
-      <c r="AK83" s="39"/>
-    </row>
-    <row r="84" spans="1:37">
+      <c r="AF83" s="59"/>
+      <c r="AG83" s="42"/>
+      <c r="AH83" s="66"/>
+      <c r="AI83" s="42"/>
+      <c r="AJ83" s="39"/>
+    </row>
+    <row r="84" spans="1:36">
       <c r="A84" s="61"/>
       <c r="B84" s="6"/>
       <c r="C84" s="6"/>
@@ -10610,10 +10488,10 @@
       <c r="O84" s="8"/>
       <c r="P84" s="8"/>
       <c r="Q84" s="8"/>
-      <c r="R84" s="8"/>
+      <c r="R84" s="53"/>
       <c r="S84" s="53"/>
       <c r="T84" s="53"/>
-      <c r="U84" s="53"/>
+      <c r="U84" s="8"/>
       <c r="V84" s="8"/>
       <c r="W84" s="8"/>
       <c r="X84" s="8"/>
@@ -10624,14 +10502,13 @@
       <c r="AC84" s="8"/>
       <c r="AD84" s="8"/>
       <c r="AE84" s="8"/>
-      <c r="AF84" s="8"/>
-      <c r="AG84" s="25"/>
-      <c r="AH84" s="6"/>
-      <c r="AI84" s="63"/>
-      <c r="AJ84" s="42"/>
-      <c r="AK84" s="39"/>
-    </row>
-    <row r="85" spans="1:37">
+      <c r="AF84" s="25"/>
+      <c r="AG84" s="6"/>
+      <c r="AH84" s="63"/>
+      <c r="AI84" s="42"/>
+      <c r="AJ84" s="39"/>
+    </row>
+    <row r="85" spans="1:36">
       <c r="A85" s="61"/>
       <c r="B85" s="61"/>
       <c r="C85" s="61"/>
@@ -10652,13 +10529,13 @@
       <c r="O85" s="8"/>
       <c r="P85" s="8"/>
       <c r="Q85" s="8"/>
-      <c r="R85" s="8"/>
+      <c r="R85" s="53"/>
       <c r="S85" s="53"/>
       <c r="T85" s="53"/>
-      <c r="U85" s="53"/>
+      <c r="U85" s="8"/>
       <c r="V85" s="8"/>
       <c r="W85" s="8"/>
-      <c r="X85" s="8"/>
+      <c r="X85" s="65"/>
       <c r="Y85" s="65"/>
       <c r="Z85" s="65"/>
       <c r="AA85" s="65"/>
@@ -10666,14 +10543,13 @@
       <c r="AC85" s="65"/>
       <c r="AD85" s="65"/>
       <c r="AE85" s="65"/>
-      <c r="AF85" s="65"/>
-      <c r="AG85" s="59"/>
+      <c r="AF85" s="59"/>
+      <c r="AG85" s="61"/>
       <c r="AH85" s="61"/>
-      <c r="AI85" s="61"/>
-      <c r="AJ85" s="42"/>
-      <c r="AK85" s="39"/>
-    </row>
-    <row r="86" spans="1:37">
+      <c r="AI85" s="42"/>
+      <c r="AJ85" s="39"/>
+    </row>
+    <row r="86" spans="1:36">
       <c r="A86" s="61"/>
       <c r="B86" s="61"/>
       <c r="C86" s="61"/>
@@ -10694,13 +10570,13 @@
       <c r="O86" s="8"/>
       <c r="P86" s="8"/>
       <c r="Q86" s="8"/>
-      <c r="R86" s="8"/>
+      <c r="R86" s="53"/>
       <c r="S86" s="53"/>
       <c r="T86" s="53"/>
-      <c r="U86" s="53"/>
+      <c r="U86" s="8"/>
       <c r="V86" s="8"/>
       <c r="W86" s="8"/>
-      <c r="X86" s="8"/>
+      <c r="X86" s="65"/>
       <c r="Y86" s="65"/>
       <c r="Z86" s="65"/>
       <c r="AA86" s="65"/>
@@ -10708,14 +10584,13 @@
       <c r="AC86" s="65"/>
       <c r="AD86" s="65"/>
       <c r="AE86" s="65"/>
-      <c r="AF86" s="65"/>
-      <c r="AG86" s="59"/>
+      <c r="AF86" s="59"/>
+      <c r="AG86" s="61"/>
       <c r="AH86" s="61"/>
-      <c r="AI86" s="61"/>
-      <c r="AJ86" s="42"/>
-      <c r="AK86" s="39"/>
-    </row>
-    <row r="87" spans="1:37">
+      <c r="AI86" s="42"/>
+      <c r="AJ86" s="39"/>
+    </row>
+    <row r="87" spans="1:36">
       <c r="A87" s="42"/>
       <c r="B87" s="61"/>
       <c r="C87" s="61"/>
@@ -10742,7 +10617,7 @@
       <c r="U87" s="8"/>
       <c r="V87" s="8"/>
       <c r="W87" s="8"/>
-      <c r="X87" s="8"/>
+      <c r="X87" s="65"/>
       <c r="Y87" s="65"/>
       <c r="Z87" s="65"/>
       <c r="AA87" s="65"/>
@@ -10750,14 +10625,13 @@
       <c r="AC87" s="65"/>
       <c r="AD87" s="65"/>
       <c r="AE87" s="65"/>
-      <c r="AF87" s="65"/>
-      <c r="AG87" s="59"/>
+      <c r="AF87" s="59"/>
+      <c r="AG87" s="61"/>
       <c r="AH87" s="61"/>
-      <c r="AI87" s="61"/>
-      <c r="AJ87" s="42"/>
-      <c r="AK87" s="39"/>
-    </row>
-    <row r="88" spans="1:37">
+      <c r="AI87" s="42"/>
+      <c r="AJ87" s="39"/>
+    </row>
+    <row r="88" spans="1:36">
       <c r="A88" s="42"/>
       <c r="B88" s="6"/>
       <c r="C88" s="6"/>
@@ -10778,10 +10652,10 @@
       <c r="O88" s="8"/>
       <c r="P88" s="8"/>
       <c r="Q88" s="8"/>
-      <c r="R88" s="8"/>
+      <c r="R88" s="53"/>
       <c r="S88" s="53"/>
       <c r="T88" s="53"/>
-      <c r="U88" s="53"/>
+      <c r="U88" s="8"/>
       <c r="V88" s="8"/>
       <c r="W88" s="8"/>
       <c r="X88" s="8"/>
@@ -10792,14 +10666,13 @@
       <c r="AC88" s="8"/>
       <c r="AD88" s="8"/>
       <c r="AE88" s="8"/>
-      <c r="AF88" s="8"/>
-      <c r="AG88" s="25"/>
-      <c r="AH88" s="6"/>
-      <c r="AI88" s="63"/>
-      <c r="AJ88" s="42"/>
-      <c r="AK88" s="39"/>
-    </row>
-    <row r="89" spans="1:37">
+      <c r="AF88" s="25"/>
+      <c r="AG88" s="6"/>
+      <c r="AH88" s="63"/>
+      <c r="AI88" s="42"/>
+      <c r="AJ88" s="39"/>
+    </row>
+    <row r="89" spans="1:36">
       <c r="A89" s="42"/>
       <c r="B89" s="42"/>
       <c r="C89" s="42"/>
@@ -10820,13 +10693,13 @@
       <c r="O89" s="8"/>
       <c r="P89" s="8"/>
       <c r="Q89" s="8"/>
-      <c r="R89" s="8"/>
+      <c r="R89" s="53"/>
       <c r="S89" s="53"/>
-      <c r="T89" s="53"/>
+      <c r="T89" s="8"/>
       <c r="U89" s="8"/>
       <c r="V89" s="8"/>
       <c r="W89" s="8"/>
-      <c r="X89" s="8"/>
+      <c r="X89" s="39"/>
       <c r="Y89" s="39"/>
       <c r="Z89" s="39"/>
       <c r="AA89" s="39"/>
@@ -10834,14 +10707,13 @@
       <c r="AC89" s="39"/>
       <c r="AD89" s="39"/>
       <c r="AE89" s="39"/>
-      <c r="AF89" s="39"/>
-      <c r="AG89" s="48"/>
-      <c r="AH89" s="42"/>
-      <c r="AI89" s="6"/>
-      <c r="AJ89" s="42"/>
-      <c r="AK89" s="39"/>
-    </row>
-    <row r="90" spans="1:37">
+      <c r="AF89" s="48"/>
+      <c r="AG89" s="42"/>
+      <c r="AH89" s="6"/>
+      <c r="AI89" s="42"/>
+      <c r="AJ89" s="39"/>
+    </row>
+    <row r="90" spans="1:36">
       <c r="A90" s="42"/>
       <c r="B90" s="42"/>
       <c r="C90" s="6"/>
@@ -10862,10 +10734,10 @@
       <c r="O90" s="8"/>
       <c r="P90" s="8"/>
       <c r="Q90" s="8"/>
-      <c r="R90" s="8"/>
-      <c r="S90" s="42"/>
-      <c r="T90" s="53"/>
-      <c r="U90" s="42"/>
+      <c r="R90" s="42"/>
+      <c r="S90" s="53"/>
+      <c r="T90" s="42"/>
+      <c r="U90" s="8"/>
       <c r="V90" s="8"/>
       <c r="W90" s="8"/>
       <c r="X90" s="8"/>
@@ -10876,14 +10748,13 @@
       <c r="AC90" s="8"/>
       <c r="AD90" s="8"/>
       <c r="AE90" s="8"/>
-      <c r="AF90" s="8"/>
-      <c r="AG90" s="25"/>
+      <c r="AF90" s="25"/>
+      <c r="AG90" s="42"/>
       <c r="AH90" s="42"/>
       <c r="AI90" s="42"/>
-      <c r="AJ90" s="42"/>
-      <c r="AK90" s="39"/>
-    </row>
-    <row r="91" spans="1:37">
+      <c r="AJ90" s="39"/>
+    </row>
+    <row r="91" spans="1:36">
       <c r="A91" s="42"/>
       <c r="B91" s="42"/>
       <c r="C91" s="6"/>
@@ -10904,13 +10775,13 @@
       <c r="O91" s="8"/>
       <c r="P91" s="8"/>
       <c r="Q91" s="39"/>
-      <c r="R91" s="39"/>
+      <c r="R91" s="8"/>
       <c r="S91" s="8"/>
-      <c r="T91" s="8"/>
-      <c r="U91" s="39"/>
+      <c r="T91" s="39"/>
+      <c r="U91" s="8"/>
       <c r="V91" s="8"/>
       <c r="W91" s="8"/>
-      <c r="X91" s="8"/>
+      <c r="X91" s="39"/>
       <c r="Y91" s="39"/>
       <c r="Z91" s="39"/>
       <c r="AA91" s="39"/>
@@ -10918,14 +10789,13 @@
       <c r="AC91" s="39"/>
       <c r="AD91" s="39"/>
       <c r="AE91" s="39"/>
-      <c r="AF91" s="39"/>
-      <c r="AG91" s="48"/>
+      <c r="AF91" s="48"/>
+      <c r="AG91" s="42"/>
       <c r="AH91" s="42"/>
       <c r="AI91" s="42"/>
-      <c r="AJ91" s="42"/>
-      <c r="AK91" s="39"/>
-    </row>
-    <row r="92" spans="1:37">
+      <c r="AJ91" s="39"/>
+    </row>
+    <row r="92" spans="1:36">
       <c r="A92" s="42"/>
       <c r="B92" s="6"/>
       <c r="C92" s="6"/>
@@ -10946,13 +10816,13 @@
       <c r="O92" s="8"/>
       <c r="P92" s="8"/>
       <c r="Q92" s="8"/>
-      <c r="R92" s="8"/>
+      <c r="R92" s="53"/>
       <c r="S92" s="53"/>
-      <c r="T92" s="53"/>
-      <c r="U92" s="39"/>
+      <c r="T92" s="39"/>
+      <c r="U92" s="8"/>
       <c r="V92" s="8"/>
       <c r="W92" s="8"/>
-      <c r="X92" s="8"/>
+      <c r="X92" s="39"/>
       <c r="Y92" s="39"/>
       <c r="Z92" s="39"/>
       <c r="AA92" s="39"/>
@@ -10960,14 +10830,13 @@
       <c r="AC92" s="39"/>
       <c r="AD92" s="39"/>
       <c r="AE92" s="39"/>
-      <c r="AF92" s="39"/>
-      <c r="AG92" s="48"/>
-      <c r="AH92" s="6"/>
-      <c r="AI92" s="63"/>
-      <c r="AJ92" s="6"/>
-      <c r="AK92" s="39"/>
-    </row>
-    <row r="93" spans="1:37">
+      <c r="AF92" s="48"/>
+      <c r="AG92" s="6"/>
+      <c r="AH92" s="63"/>
+      <c r="AI92" s="6"/>
+      <c r="AJ92" s="39"/>
+    </row>
+    <row r="93" spans="1:36">
       <c r="A93" s="42"/>
       <c r="B93" s="6"/>
       <c r="C93" s="6"/>
@@ -10988,13 +10857,13 @@
       <c r="O93" s="8"/>
       <c r="P93" s="8"/>
       <c r="Q93" s="8"/>
-      <c r="R93" s="8"/>
+      <c r="R93" s="53"/>
       <c r="S93" s="53"/>
-      <c r="T93" s="53"/>
-      <c r="U93" s="39"/>
+      <c r="T93" s="39"/>
+      <c r="U93" s="8"/>
       <c r="V93" s="8"/>
       <c r="W93" s="8"/>
-      <c r="X93" s="8"/>
+      <c r="X93" s="39"/>
       <c r="Y93" s="39"/>
       <c r="Z93" s="39"/>
       <c r="AA93" s="39"/>
@@ -11002,14 +10871,13 @@
       <c r="AC93" s="39"/>
       <c r="AD93" s="39"/>
       <c r="AE93" s="39"/>
-      <c r="AF93" s="39"/>
-      <c r="AG93" s="48"/>
+      <c r="AF93" s="48"/>
+      <c r="AG93" s="6"/>
       <c r="AH93" s="6"/>
       <c r="AI93" s="6"/>
-      <c r="AJ93" s="6"/>
-      <c r="AK93" s="39"/>
-    </row>
-    <row r="94" spans="1:37">
+      <c r="AJ93" s="39"/>
+    </row>
+    <row r="94" spans="1:36">
       <c r="A94" s="42"/>
       <c r="B94" s="42"/>
       <c r="C94" s="6"/>
@@ -11032,11 +10900,11 @@
       <c r="Q94" s="8"/>
       <c r="R94" s="8"/>
       <c r="S94" s="8"/>
-      <c r="T94" s="8"/>
-      <c r="U94" s="39"/>
+      <c r="T94" s="39"/>
+      <c r="U94" s="8"/>
       <c r="V94" s="8"/>
       <c r="W94" s="8"/>
-      <c r="X94" s="8"/>
+      <c r="X94" s="39"/>
       <c r="Y94" s="39"/>
       <c r="Z94" s="39"/>
       <c r="AA94" s="39"/>
@@ -11044,14 +10912,13 @@
       <c r="AC94" s="39"/>
       <c r="AD94" s="39"/>
       <c r="AE94" s="39"/>
-      <c r="AF94" s="39"/>
-      <c r="AG94" s="48"/>
+      <c r="AF94" s="48"/>
+      <c r="AG94" s="42"/>
       <c r="AH94" s="42"/>
       <c r="AI94" s="42"/>
-      <c r="AJ94" s="42"/>
-      <c r="AK94" s="39"/>
-    </row>
-    <row r="95" spans="1:37">
+      <c r="AJ94" s="39"/>
+    </row>
+    <row r="95" spans="1:36">
       <c r="A95" s="42"/>
       <c r="B95" s="42"/>
       <c r="C95" s="6"/>
@@ -11074,11 +10941,11 @@
       <c r="Q95" s="8"/>
       <c r="R95" s="8"/>
       <c r="S95" s="8"/>
-      <c r="T95" s="8"/>
-      <c r="U95" s="39"/>
+      <c r="T95" s="39"/>
+      <c r="U95" s="8"/>
       <c r="V95" s="8"/>
       <c r="W95" s="8"/>
-      <c r="X95" s="8"/>
+      <c r="X95" s="39"/>
       <c r="Y95" s="39"/>
       <c r="Z95" s="39"/>
       <c r="AA95" s="39"/>
@@ -11086,14 +10953,13 @@
       <c r="AC95" s="39"/>
       <c r="AD95" s="39"/>
       <c r="AE95" s="39"/>
-      <c r="AF95" s="39"/>
-      <c r="AG95" s="48"/>
+      <c r="AF95" s="48"/>
+      <c r="AG95" s="42"/>
       <c r="AH95" s="42"/>
       <c r="AI95" s="42"/>
-      <c r="AJ95" s="42"/>
-      <c r="AK95" s="39"/>
-    </row>
-    <row r="96" spans="1:37">
+      <c r="AJ95" s="39"/>
+    </row>
+    <row r="96" spans="1:36">
       <c r="A96" s="42"/>
       <c r="B96" s="42"/>
       <c r="C96" s="42"/>
@@ -11128,14 +10994,13 @@
       <c r="AC96" s="8"/>
       <c r="AD96" s="8"/>
       <c r="AE96" s="8"/>
-      <c r="AF96" s="8"/>
-      <c r="AG96" s="25"/>
+      <c r="AF96" s="25"/>
+      <c r="AG96" s="42"/>
       <c r="AH96" s="42"/>
       <c r="AI96" s="42"/>
-      <c r="AJ96" s="42"/>
-      <c r="AK96" s="39"/>
-    </row>
-    <row r="97" spans="1:37" ht="112" customHeight="1">
+      <c r="AJ96" s="39"/>
+    </row>
+    <row r="97" spans="1:36" ht="112" customHeight="1">
       <c r="A97" s="42"/>
       <c r="B97" s="42"/>
       <c r="C97" s="42"/>
@@ -11162,7 +11027,7 @@
       <c r="U97" s="8"/>
       <c r="V97" s="8"/>
       <c r="W97" s="8"/>
-      <c r="X97" s="8"/>
+      <c r="X97" s="39"/>
       <c r="Y97" s="39"/>
       <c r="Z97" s="39"/>
       <c r="AA97" s="39"/>
@@ -11170,14 +11035,13 @@
       <c r="AC97" s="39"/>
       <c r="AD97" s="39"/>
       <c r="AE97" s="39"/>
-      <c r="AF97" s="39"/>
-      <c r="AG97" s="48"/>
-      <c r="AH97" s="42"/>
-      <c r="AI97" s="6"/>
-      <c r="AJ97" s="42"/>
-      <c r="AK97" s="39"/>
-    </row>
-    <row r="98" spans="1:37">
+      <c r="AF97" s="48"/>
+      <c r="AG97" s="42"/>
+      <c r="AH97" s="6"/>
+      <c r="AI97" s="42"/>
+      <c r="AJ97" s="39"/>
+    </row>
+    <row r="98" spans="1:36">
       <c r="A98" s="42"/>
       <c r="B98" s="42"/>
       <c r="C98" s="42"/>
@@ -11212,14 +11076,13 @@
       <c r="AC98" s="8"/>
       <c r="AD98" s="8"/>
       <c r="AE98" s="8"/>
-      <c r="AF98" s="8"/>
-      <c r="AG98" s="25"/>
-      <c r="AH98" s="42"/>
-      <c r="AI98" s="6"/>
-      <c r="AJ98" s="42"/>
-      <c r="AK98" s="39"/>
-    </row>
-    <row r="99" spans="1:37">
+      <c r="AF98" s="25"/>
+      <c r="AG98" s="42"/>
+      <c r="AH98" s="6"/>
+      <c r="AI98" s="42"/>
+      <c r="AJ98" s="39"/>
+    </row>
+    <row r="99" spans="1:36">
       <c r="A99" s="42"/>
       <c r="B99" s="42"/>
       <c r="C99" s="42"/>
@@ -11240,13 +11103,13 @@
       <c r="O99" s="8"/>
       <c r="P99" s="8"/>
       <c r="Q99" s="39"/>
-      <c r="R99" s="39"/>
+      <c r="R99" s="8"/>
       <c r="S99" s="8"/>
-      <c r="T99" s="8"/>
-      <c r="U99" s="39"/>
+      <c r="T99" s="39"/>
+      <c r="U99" s="8"/>
       <c r="V99" s="8"/>
       <c r="W99" s="8"/>
-      <c r="X99" s="8"/>
+      <c r="X99" s="39"/>
       <c r="Y99" s="39"/>
       <c r="Z99" s="39"/>
       <c r="AA99" s="39"/>
@@ -11254,14 +11117,13 @@
       <c r="AC99" s="39"/>
       <c r="AD99" s="39"/>
       <c r="AE99" s="39"/>
-      <c r="AF99" s="39"/>
-      <c r="AG99" s="48"/>
+      <c r="AF99" s="48"/>
+      <c r="AG99" s="42"/>
       <c r="AH99" s="42"/>
       <c r="AI99" s="42"/>
-      <c r="AJ99" s="42"/>
-      <c r="AK99" s="39"/>
-    </row>
-    <row r="100" spans="1:37">
+      <c r="AJ99" s="39"/>
+    </row>
+    <row r="100" spans="1:36">
       <c r="A100" s="42"/>
       <c r="B100" s="42"/>
       <c r="C100" s="42"/>
@@ -11282,13 +11144,13 @@
       <c r="O100" s="8"/>
       <c r="P100" s="8"/>
       <c r="Q100" s="39"/>
-      <c r="R100" s="39"/>
+      <c r="R100" s="8"/>
       <c r="S100" s="8"/>
-      <c r="T100" s="8"/>
-      <c r="U100" s="39"/>
+      <c r="T100" s="39"/>
+      <c r="U100" s="8"/>
       <c r="V100" s="8"/>
       <c r="W100" s="8"/>
-      <c r="X100" s="8"/>
+      <c r="X100" s="39"/>
       <c r="Y100" s="39"/>
       <c r="Z100" s="39"/>
       <c r="AA100" s="39"/>
@@ -11296,14 +11158,13 @@
       <c r="AC100" s="39"/>
       <c r="AD100" s="39"/>
       <c r="AE100" s="39"/>
-      <c r="AF100" s="39"/>
-      <c r="AG100" s="48"/>
+      <c r="AF100" s="48"/>
+      <c r="AG100" s="42"/>
       <c r="AH100" s="42"/>
       <c r="AI100" s="42"/>
-      <c r="AJ100" s="42"/>
-      <c r="AK100" s="39"/>
-    </row>
-    <row r="101" spans="1:37">
+      <c r="AJ100" s="39"/>
+    </row>
+    <row r="101" spans="1:36">
       <c r="A101" s="42"/>
       <c r="B101" s="42"/>
       <c r="C101" s="42"/>
@@ -11324,13 +11185,13 @@
       <c r="O101" s="8"/>
       <c r="P101" s="8"/>
       <c r="Q101" s="39"/>
-      <c r="R101" s="39"/>
+      <c r="R101" s="8"/>
       <c r="S101" s="8"/>
-      <c r="T101" s="8"/>
-      <c r="U101" s="39"/>
+      <c r="T101" s="39"/>
+      <c r="U101" s="8"/>
       <c r="V101" s="8"/>
       <c r="W101" s="8"/>
-      <c r="X101" s="8"/>
+      <c r="X101" s="39"/>
       <c r="Y101" s="39"/>
       <c r="Z101" s="39"/>
       <c r="AA101" s="39"/>
@@ -11338,14 +11199,13 @@
       <c r="AC101" s="39"/>
       <c r="AD101" s="39"/>
       <c r="AE101" s="39"/>
-      <c r="AF101" s="39"/>
-      <c r="AG101" s="48"/>
+      <c r="AF101" s="48"/>
+      <c r="AG101" s="42"/>
       <c r="AH101" s="42"/>
       <c r="AI101" s="42"/>
-      <c r="AJ101" s="42"/>
-      <c r="AK101" s="39"/>
-    </row>
-    <row r="102" spans="1:37">
+      <c r="AJ101" s="39"/>
+    </row>
+    <row r="102" spans="1:36">
       <c r="A102" s="42"/>
       <c r="B102" s="42"/>
       <c r="C102" s="42"/>
@@ -11366,13 +11226,13 @@
       <c r="O102" s="8"/>
       <c r="P102" s="8"/>
       <c r="Q102" s="39"/>
-      <c r="R102" s="39"/>
+      <c r="R102" s="8"/>
       <c r="S102" s="8"/>
-      <c r="T102" s="8"/>
-      <c r="U102" s="39"/>
+      <c r="T102" s="39"/>
+      <c r="U102" s="8"/>
       <c r="V102" s="8"/>
       <c r="W102" s="8"/>
-      <c r="X102" s="8"/>
+      <c r="X102" s="39"/>
       <c r="Y102" s="39"/>
       <c r="Z102" s="39"/>
       <c r="AA102" s="39"/>
@@ -11380,14 +11240,13 @@
       <c r="AC102" s="39"/>
       <c r="AD102" s="39"/>
       <c r="AE102" s="39"/>
-      <c r="AF102" s="39"/>
-      <c r="AG102" s="48"/>
+      <c r="AF102" s="48"/>
+      <c r="AG102" s="42"/>
       <c r="AH102" s="42"/>
       <c r="AI102" s="42"/>
-      <c r="AJ102" s="42"/>
-      <c r="AK102" s="39"/>
-    </row>
-    <row r="103" spans="1:37">
+      <c r="AJ102" s="39"/>
+    </row>
+    <row r="103" spans="1:36">
       <c r="A103" s="42"/>
       <c r="B103" s="42"/>
       <c r="C103" s="42"/>
@@ -11408,13 +11267,13 @@
       <c r="O103" s="8"/>
       <c r="P103" s="8"/>
       <c r="Q103" s="39"/>
-      <c r="R103" s="39"/>
+      <c r="R103" s="8"/>
       <c r="S103" s="8"/>
-      <c r="T103" s="8"/>
-      <c r="U103" s="39"/>
+      <c r="T103" s="39"/>
+      <c r="U103" s="8"/>
       <c r="V103" s="8"/>
       <c r="W103" s="8"/>
-      <c r="X103" s="8"/>
+      <c r="X103" s="39"/>
       <c r="Y103" s="39"/>
       <c r="Z103" s="39"/>
       <c r="AA103" s="39"/>
@@ -11422,14 +11281,13 @@
       <c r="AC103" s="39"/>
       <c r="AD103" s="39"/>
       <c r="AE103" s="39"/>
-      <c r="AF103" s="39"/>
-      <c r="AG103" s="48"/>
+      <c r="AF103" s="48"/>
+      <c r="AG103" s="42"/>
       <c r="AH103" s="42"/>
       <c r="AI103" s="42"/>
-      <c r="AJ103" s="42"/>
-      <c r="AK103" s="39"/>
-    </row>
-    <row r="104" spans="1:37">
+      <c r="AJ103" s="39"/>
+    </row>
+    <row r="104" spans="1:36">
       <c r="A104" s="42"/>
       <c r="B104" s="42"/>
       <c r="C104" s="6"/>
@@ -11450,13 +11308,13 @@
       <c r="O104" s="8"/>
       <c r="P104" s="8"/>
       <c r="Q104" s="39"/>
-      <c r="R104" s="39"/>
+      <c r="R104" s="8"/>
       <c r="S104" s="8"/>
-      <c r="T104" s="8"/>
-      <c r="U104" s="39"/>
+      <c r="T104" s="39"/>
+      <c r="U104" s="8"/>
       <c r="V104" s="8"/>
       <c r="W104" s="8"/>
-      <c r="X104" s="8"/>
+      <c r="X104" s="39"/>
       <c r="Y104" s="39"/>
       <c r="Z104" s="39"/>
       <c r="AA104" s="39"/>
@@ -11464,14 +11322,13 @@
       <c r="AC104" s="39"/>
       <c r="AD104" s="39"/>
       <c r="AE104" s="39"/>
-      <c r="AF104" s="39"/>
-      <c r="AG104" s="48"/>
+      <c r="AF104" s="48"/>
+      <c r="AG104" s="42"/>
       <c r="AH104" s="42"/>
       <c r="AI104" s="42"/>
-      <c r="AJ104" s="42"/>
-      <c r="AK104" s="39"/>
-    </row>
-    <row r="105" spans="1:37">
+      <c r="AJ104" s="39"/>
+    </row>
+    <row r="105" spans="1:36">
       <c r="A105" s="42"/>
       <c r="B105" s="42"/>
       <c r="C105" s="6"/>
@@ -11492,13 +11349,13 @@
       <c r="O105" s="8"/>
       <c r="P105" s="8"/>
       <c r="Q105" s="39"/>
-      <c r="R105" s="39"/>
+      <c r="R105" s="8"/>
       <c r="S105" s="8"/>
-      <c r="T105" s="8"/>
-      <c r="U105" s="39"/>
+      <c r="T105" s="39"/>
+      <c r="U105" s="8"/>
       <c r="V105" s="8"/>
       <c r="W105" s="8"/>
-      <c r="X105" s="8"/>
+      <c r="X105" s="39"/>
       <c r="Y105" s="39"/>
       <c r="Z105" s="39"/>
       <c r="AA105" s="39"/>
@@ -11506,14 +11363,13 @@
       <c r="AC105" s="39"/>
       <c r="AD105" s="39"/>
       <c r="AE105" s="39"/>
-      <c r="AF105" s="39"/>
-      <c r="AG105" s="48"/>
-      <c r="AH105" s="42"/>
-      <c r="AI105" s="6"/>
-      <c r="AJ105" s="42"/>
-      <c r="AK105" s="39"/>
-    </row>
-    <row r="106" spans="1:37">
+      <c r="AF105" s="48"/>
+      <c r="AG105" s="42"/>
+      <c r="AH105" s="6"/>
+      <c r="AI105" s="42"/>
+      <c r="AJ105" s="39"/>
+    </row>
+    <row r="106" spans="1:36">
       <c r="A106" s="42"/>
       <c r="B106" s="42"/>
       <c r="C106" s="42"/>
@@ -11534,13 +11390,13 @@
       <c r="O106" s="8"/>
       <c r="P106" s="8"/>
       <c r="Q106" s="39"/>
-      <c r="R106" s="39"/>
+      <c r="R106" s="8"/>
       <c r="S106" s="8"/>
-      <c r="T106" s="8"/>
-      <c r="U106" s="39"/>
+      <c r="T106" s="39"/>
+      <c r="U106" s="8"/>
       <c r="V106" s="8"/>
       <c r="W106" s="8"/>
-      <c r="X106" s="8"/>
+      <c r="X106" s="39"/>
       <c r="Y106" s="39"/>
       <c r="Z106" s="39"/>
       <c r="AA106" s="39"/>
@@ -11548,14 +11404,13 @@
       <c r="AC106" s="39"/>
       <c r="AD106" s="39"/>
       <c r="AE106" s="39"/>
-      <c r="AF106" s="39"/>
-      <c r="AG106" s="48"/>
+      <c r="AF106" s="48"/>
+      <c r="AG106" s="42"/>
       <c r="AH106" s="42"/>
       <c r="AI106" s="42"/>
-      <c r="AJ106" s="42"/>
-      <c r="AK106" s="39"/>
-    </row>
-    <row r="107" spans="1:37">
+      <c r="AJ106" s="39"/>
+    </row>
+    <row r="107" spans="1:36">
       <c r="A107" s="42"/>
       <c r="B107" s="42"/>
       <c r="C107" s="42"/>
@@ -11576,13 +11431,13 @@
       <c r="O107" s="8"/>
       <c r="P107" s="8"/>
       <c r="Q107" s="39"/>
-      <c r="R107" s="39"/>
+      <c r="R107" s="8"/>
       <c r="S107" s="8"/>
-      <c r="T107" s="8"/>
-      <c r="U107" s="39"/>
+      <c r="T107" s="39"/>
+      <c r="U107" s="8"/>
       <c r="V107" s="8"/>
       <c r="W107" s="8"/>
-      <c r="X107" s="8"/>
+      <c r="X107" s="39"/>
       <c r="Y107" s="39"/>
       <c r="Z107" s="39"/>
       <c r="AA107" s="39"/>
@@ -11590,14 +11445,13 @@
       <c r="AC107" s="39"/>
       <c r="AD107" s="39"/>
       <c r="AE107" s="39"/>
-      <c r="AF107" s="39"/>
-      <c r="AG107" s="48"/>
+      <c r="AF107" s="48"/>
+      <c r="AG107" s="42"/>
       <c r="AH107" s="42"/>
       <c r="AI107" s="42"/>
-      <c r="AJ107" s="42"/>
-      <c r="AK107" s="39"/>
-    </row>
-    <row r="108" spans="1:37">
+      <c r="AJ107" s="39"/>
+    </row>
+    <row r="108" spans="1:36">
       <c r="A108" s="42"/>
       <c r="B108" s="42"/>
       <c r="C108" s="42"/>
@@ -11618,13 +11472,13 @@
       <c r="O108" s="8"/>
       <c r="P108" s="8"/>
       <c r="Q108" s="39"/>
-      <c r="R108" s="39"/>
+      <c r="R108" s="8"/>
       <c r="S108" s="8"/>
-      <c r="T108" s="8"/>
-      <c r="U108" s="39"/>
+      <c r="T108" s="39"/>
+      <c r="U108" s="8"/>
       <c r="V108" s="8"/>
       <c r="W108" s="8"/>
-      <c r="X108" s="8"/>
+      <c r="X108" s="39"/>
       <c r="Y108" s="39"/>
       <c r="Z108" s="39"/>
       <c r="AA108" s="39"/>
@@ -11632,14 +11486,13 @@
       <c r="AC108" s="39"/>
       <c r="AD108" s="39"/>
       <c r="AE108" s="39"/>
-      <c r="AF108" s="39"/>
-      <c r="AG108" s="48"/>
+      <c r="AF108" s="48"/>
+      <c r="AG108" s="42"/>
       <c r="AH108" s="42"/>
       <c r="AI108" s="42"/>
-      <c r="AJ108" s="42"/>
-      <c r="AK108" s="39"/>
-    </row>
-    <row r="109" spans="1:37">
+      <c r="AJ108" s="39"/>
+    </row>
+    <row r="109" spans="1:36">
       <c r="A109" s="42"/>
       <c r="B109" s="42"/>
       <c r="C109" s="42"/>
@@ -11660,13 +11513,13 @@
       <c r="O109" s="8"/>
       <c r="P109" s="8"/>
       <c r="Q109" s="39"/>
-      <c r="R109" s="39"/>
+      <c r="R109" s="8"/>
       <c r="S109" s="8"/>
-      <c r="T109" s="8"/>
-      <c r="U109" s="39"/>
+      <c r="T109" s="39"/>
+      <c r="U109" s="8"/>
       <c r="V109" s="8"/>
       <c r="W109" s="8"/>
-      <c r="X109" s="8"/>
+      <c r="X109" s="39"/>
       <c r="Y109" s="39"/>
       <c r="Z109" s="39"/>
       <c r="AA109" s="39"/>
@@ -11674,14 +11527,13 @@
       <c r="AC109" s="39"/>
       <c r="AD109" s="39"/>
       <c r="AE109" s="39"/>
-      <c r="AF109" s="39"/>
-      <c r="AG109" s="48"/>
+      <c r="AF109" s="48"/>
+      <c r="AG109" s="42"/>
       <c r="AH109" s="42"/>
       <c r="AI109" s="42"/>
-      <c r="AJ109" s="42"/>
-      <c r="AK109" s="39"/>
-    </row>
-    <row r="110" spans="1:37">
+      <c r="AJ109" s="39"/>
+    </row>
+    <row r="110" spans="1:36">
       <c r="A110" s="42"/>
       <c r="B110" s="42"/>
       <c r="C110" s="42"/>
@@ -11702,13 +11554,13 @@
       <c r="O110" s="8"/>
       <c r="P110" s="8"/>
       <c r="Q110" s="39"/>
-      <c r="R110" s="39"/>
+      <c r="R110" s="8"/>
       <c r="S110" s="8"/>
-      <c r="T110" s="8"/>
-      <c r="U110" s="39"/>
+      <c r="T110" s="39"/>
+      <c r="U110" s="8"/>
       <c r="V110" s="8"/>
       <c r="W110" s="8"/>
-      <c r="X110" s="8"/>
+      <c r="X110" s="39"/>
       <c r="Y110" s="39"/>
       <c r="Z110" s="39"/>
       <c r="AA110" s="39"/>
@@ -11716,14 +11568,13 @@
       <c r="AC110" s="39"/>
       <c r="AD110" s="39"/>
       <c r="AE110" s="39"/>
-      <c r="AF110" s="39"/>
-      <c r="AG110" s="48"/>
+      <c r="AF110" s="48"/>
+      <c r="AG110" s="42"/>
       <c r="AH110" s="42"/>
       <c r="AI110" s="42"/>
-      <c r="AJ110" s="42"/>
-      <c r="AK110" s="39"/>
-    </row>
-    <row r="111" spans="1:37">
+      <c r="AJ110" s="39"/>
+    </row>
+    <row r="111" spans="1:36">
       <c r="A111" s="42"/>
       <c r="B111" s="42"/>
       <c r="C111" s="6"/>
@@ -11744,13 +11595,13 @@
       <c r="O111" s="8"/>
       <c r="P111" s="8"/>
       <c r="Q111" s="39"/>
-      <c r="R111" s="39"/>
+      <c r="R111" s="8"/>
       <c r="S111" s="8"/>
-      <c r="T111" s="8"/>
-      <c r="U111" s="39"/>
+      <c r="T111" s="39"/>
+      <c r="U111" s="8"/>
       <c r="V111" s="8"/>
       <c r="W111" s="8"/>
-      <c r="X111" s="8"/>
+      <c r="X111" s="39"/>
       <c r="Y111" s="39"/>
       <c r="Z111" s="39"/>
       <c r="AA111" s="39"/>
@@ -11758,14 +11609,13 @@
       <c r="AC111" s="39"/>
       <c r="AD111" s="39"/>
       <c r="AE111" s="39"/>
-      <c r="AF111" s="39"/>
-      <c r="AG111" s="48"/>
+      <c r="AF111" s="48"/>
+      <c r="AG111" s="42"/>
       <c r="AH111" s="42"/>
       <c r="AI111" s="42"/>
-      <c r="AJ111" s="42"/>
-      <c r="AK111" s="39"/>
-    </row>
-    <row r="112" spans="1:37">
+      <c r="AJ111" s="39"/>
+    </row>
+    <row r="112" spans="1:36">
       <c r="A112" s="42"/>
       <c r="B112" s="42"/>
       <c r="C112" s="6"/>
@@ -11786,13 +11636,13 @@
       <c r="O112" s="8"/>
       <c r="P112" s="8"/>
       <c r="Q112" s="39"/>
-      <c r="R112" s="39"/>
+      <c r="R112" s="8"/>
       <c r="S112" s="8"/>
-      <c r="T112" s="8"/>
-      <c r="U112" s="39"/>
+      <c r="T112" s="39"/>
+      <c r="U112" s="8"/>
       <c r="V112" s="8"/>
       <c r="W112" s="8"/>
-      <c r="X112" s="8"/>
+      <c r="X112" s="39"/>
       <c r="Y112" s="39"/>
       <c r="Z112" s="39"/>
       <c r="AA112" s="39"/>
@@ -11800,14 +11650,13 @@
       <c r="AC112" s="39"/>
       <c r="AD112" s="39"/>
       <c r="AE112" s="39"/>
-      <c r="AF112" s="39"/>
-      <c r="AG112" s="48"/>
+      <c r="AF112" s="48"/>
+      <c r="AG112" s="42"/>
       <c r="AH112" s="42"/>
       <c r="AI112" s="42"/>
-      <c r="AJ112" s="42"/>
-      <c r="AK112" s="39"/>
-    </row>
-    <row r="113" spans="1:37">
+      <c r="AJ112" s="39"/>
+    </row>
+    <row r="113" spans="1:36">
       <c r="A113" s="42"/>
       <c r="B113" s="42"/>
       <c r="C113" s="42"/>
@@ -11828,13 +11677,13 @@
       <c r="O113" s="8"/>
       <c r="P113" s="8"/>
       <c r="Q113" s="39"/>
-      <c r="R113" s="39"/>
+      <c r="R113" s="8"/>
       <c r="S113" s="8"/>
-      <c r="T113" s="8"/>
-      <c r="U113" s="39"/>
+      <c r="T113" s="39"/>
+      <c r="U113" s="8"/>
       <c r="V113" s="8"/>
       <c r="W113" s="8"/>
-      <c r="X113" s="8"/>
+      <c r="X113" s="39"/>
       <c r="Y113" s="39"/>
       <c r="Z113" s="39"/>
       <c r="AA113" s="39"/>
@@ -11842,14 +11691,13 @@
       <c r="AC113" s="39"/>
       <c r="AD113" s="39"/>
       <c r="AE113" s="39"/>
-      <c r="AF113" s="39"/>
-      <c r="AG113" s="48"/>
+      <c r="AF113" s="48"/>
+      <c r="AG113" s="42"/>
       <c r="AH113" s="42"/>
       <c r="AI113" s="42"/>
-      <c r="AJ113" s="42"/>
-      <c r="AK113" s="39"/>
-    </row>
-    <row r="114" spans="1:37">
+      <c r="AJ113" s="39"/>
+    </row>
+    <row r="114" spans="1:36">
       <c r="A114" s="42"/>
       <c r="B114" s="42"/>
       <c r="C114" s="42"/>
@@ -11870,13 +11718,13 @@
       <c r="O114" s="8"/>
       <c r="P114" s="8"/>
       <c r="Q114" s="39"/>
-      <c r="R114" s="39"/>
+      <c r="R114" s="8"/>
       <c r="S114" s="8"/>
-      <c r="T114" s="8"/>
-      <c r="U114" s="39"/>
+      <c r="T114" s="39"/>
+      <c r="U114" s="8"/>
       <c r="V114" s="8"/>
       <c r="W114" s="8"/>
-      <c r="X114" s="8"/>
+      <c r="X114" s="39"/>
       <c r="Y114" s="39"/>
       <c r="Z114" s="39"/>
       <c r="AA114" s="39"/>
@@ -11884,14 +11732,13 @@
       <c r="AC114" s="39"/>
       <c r="AD114" s="39"/>
       <c r="AE114" s="39"/>
-      <c r="AF114" s="39"/>
-      <c r="AG114" s="48"/>
+      <c r="AF114" s="48"/>
+      <c r="AG114" s="42"/>
       <c r="AH114" s="42"/>
       <c r="AI114" s="42"/>
-      <c r="AJ114" s="42"/>
-      <c r="AK114" s="39"/>
-    </row>
-    <row r="115" spans="1:37">
+      <c r="AJ114" s="39"/>
+    </row>
+    <row r="115" spans="1:36">
       <c r="A115" s="42"/>
       <c r="B115" s="42"/>
       <c r="C115" s="42"/>
@@ -11912,13 +11759,13 @@
       <c r="O115" s="8"/>
       <c r="P115" s="8"/>
       <c r="Q115" s="39"/>
-      <c r="R115" s="39"/>
+      <c r="R115" s="8"/>
       <c r="S115" s="8"/>
-      <c r="T115" s="8"/>
-      <c r="U115" s="39"/>
+      <c r="T115" s="39"/>
+      <c r="U115" s="8"/>
       <c r="V115" s="8"/>
       <c r="W115" s="8"/>
-      <c r="X115" s="8"/>
+      <c r="X115" s="39"/>
       <c r="Y115" s="39"/>
       <c r="Z115" s="39"/>
       <c r="AA115" s="39"/>
@@ -11926,14 +11773,13 @@
       <c r="AC115" s="39"/>
       <c r="AD115" s="39"/>
       <c r="AE115" s="39"/>
-      <c r="AF115" s="39"/>
-      <c r="AG115" s="48"/>
+      <c r="AF115" s="48"/>
+      <c r="AG115" s="42"/>
       <c r="AH115" s="42"/>
       <c r="AI115" s="42"/>
-      <c r="AJ115" s="42"/>
-      <c r="AK115" s="39"/>
-    </row>
-    <row r="116" spans="1:37">
+      <c r="AJ115" s="39"/>
+    </row>
+    <row r="116" spans="1:36">
       <c r="A116" s="42"/>
       <c r="B116" s="42"/>
       <c r="C116" s="42"/>
@@ -11954,13 +11800,13 @@
       <c r="O116" s="8"/>
       <c r="P116" s="8"/>
       <c r="Q116" s="39"/>
-      <c r="R116" s="39"/>
+      <c r="R116" s="8"/>
       <c r="S116" s="8"/>
-      <c r="T116" s="8"/>
-      <c r="U116" s="39"/>
+      <c r="T116" s="39"/>
+      <c r="U116" s="8"/>
       <c r="V116" s="8"/>
       <c r="W116" s="8"/>
-      <c r="X116" s="8"/>
+      <c r="X116" s="39"/>
       <c r="Y116" s="39"/>
       <c r="Z116" s="39"/>
       <c r="AA116" s="39"/>
@@ -11968,14 +11814,13 @@
       <c r="AC116" s="39"/>
       <c r="AD116" s="39"/>
       <c r="AE116" s="39"/>
-      <c r="AF116" s="39"/>
-      <c r="AG116" s="48"/>
+      <c r="AF116" s="48"/>
+      <c r="AG116" s="42"/>
       <c r="AH116" s="42"/>
       <c r="AI116" s="42"/>
-      <c r="AJ116" s="42"/>
-      <c r="AK116" s="39"/>
-    </row>
-    <row r="117" spans="1:37">
+      <c r="AJ116" s="39"/>
+    </row>
+    <row r="117" spans="1:36">
       <c r="A117" s="42"/>
       <c r="B117" s="42"/>
       <c r="C117" s="42"/>
@@ -11996,13 +11841,13 @@
       <c r="O117" s="8"/>
       <c r="P117" s="8"/>
       <c r="Q117" s="39"/>
-      <c r="R117" s="39"/>
+      <c r="R117" s="8"/>
       <c r="S117" s="8"/>
-      <c r="T117" s="8"/>
-      <c r="U117" s="39"/>
+      <c r="T117" s="39"/>
+      <c r="U117" s="8"/>
       <c r="V117" s="8"/>
       <c r="W117" s="8"/>
-      <c r="X117" s="8"/>
+      <c r="X117" s="39"/>
       <c r="Y117" s="39"/>
       <c r="Z117" s="39"/>
       <c r="AA117" s="39"/>
@@ -12010,14 +11855,13 @@
       <c r="AC117" s="39"/>
       <c r="AD117" s="39"/>
       <c r="AE117" s="39"/>
-      <c r="AF117" s="39"/>
-      <c r="AG117" s="48"/>
+      <c r="AF117" s="48"/>
+      <c r="AG117" s="42"/>
       <c r="AH117" s="42"/>
       <c r="AI117" s="42"/>
-      <c r="AJ117" s="42"/>
-      <c r="AK117" s="39"/>
-    </row>
-    <row r="118" spans="1:37">
+      <c r="AJ117" s="39"/>
+    </row>
+    <row r="118" spans="1:36">
       <c r="A118" s="42"/>
       <c r="B118" s="42"/>
       <c r="C118" s="42"/>
@@ -12038,13 +11882,13 @@
       <c r="O118" s="8"/>
       <c r="P118" s="8"/>
       <c r="Q118" s="39"/>
-      <c r="R118" s="39"/>
+      <c r="R118" s="8"/>
       <c r="S118" s="8"/>
-      <c r="T118" s="8"/>
-      <c r="U118" s="39"/>
+      <c r="T118" s="39"/>
+      <c r="U118" s="8"/>
       <c r="V118" s="8"/>
       <c r="W118" s="8"/>
-      <c r="X118" s="8"/>
+      <c r="X118" s="39"/>
       <c r="Y118" s="39"/>
       <c r="Z118" s="39"/>
       <c r="AA118" s="39"/>
@@ -12052,14 +11896,13 @@
       <c r="AC118" s="39"/>
       <c r="AD118" s="39"/>
       <c r="AE118" s="39"/>
-      <c r="AF118" s="39"/>
-      <c r="AG118" s="48"/>
-      <c r="AH118" s="42"/>
-      <c r="AI118" s="6"/>
-      <c r="AJ118" s="42"/>
-      <c r="AK118" s="39"/>
-    </row>
-    <row r="119" spans="1:37">
+      <c r="AF118" s="48"/>
+      <c r="AG118" s="42"/>
+      <c r="AH118" s="6"/>
+      <c r="AI118" s="42"/>
+      <c r="AJ118" s="39"/>
+    </row>
+    <row r="119" spans="1:36">
       <c r="A119" s="42"/>
       <c r="B119" s="42"/>
       <c r="C119" s="42"/>
@@ -12080,13 +11923,13 @@
       <c r="O119" s="8"/>
       <c r="P119" s="8"/>
       <c r="Q119" s="39"/>
-      <c r="R119" s="39"/>
+      <c r="R119" s="8"/>
       <c r="S119" s="8"/>
-      <c r="T119" s="8"/>
-      <c r="U119" s="39"/>
+      <c r="T119" s="39"/>
+      <c r="U119" s="8"/>
       <c r="V119" s="8"/>
       <c r="W119" s="8"/>
-      <c r="X119" s="8"/>
+      <c r="X119" s="39"/>
       <c r="Y119" s="39"/>
       <c r="Z119" s="39"/>
       <c r="AA119" s="39"/>
@@ -12094,12 +11937,11 @@
       <c r="AC119" s="39"/>
       <c r="AD119" s="39"/>
       <c r="AE119" s="39"/>
-      <c r="AF119" s="39"/>
-      <c r="AG119" s="48"/>
+      <c r="AF119" s="48"/>
+      <c r="AG119" s="42"/>
       <c r="AH119" s="42"/>
       <c r="AI119" s="42"/>
-      <c r="AJ119" s="42"/>
-      <c r="AK119" s="39"/>
+      <c r="AJ119" s="39"/>
     </row>
   </sheetData>
   <dataValidations count="4">
@@ -12109,7 +11951,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P6:P119" xr:uid="{00000000-0002-0000-0700-000001000000}">
       <formula1>"unidirectional,bidirectional"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E6:M119 V6:V119" xr:uid="{00000000-0002-0000-0700-000002000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E6:M119 U6:U119" xr:uid="{00000000-0002-0000-0700-000002000000}">
       <formula1>"○"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N6:N119" xr:uid="{00000000-0002-0000-0700-000003000000}">
@@ -12126,7 +11968,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:AK13"/>
+  <dimension ref="A1:AJ13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="39.1640625" style="35" bestFit="1" customWidth="1"/>
@@ -12143,60 +11985,59 @@
     <col min="14" max="14" width="8.5" style="37" customWidth="1" outlineLevel="1"/>
     <col min="15" max="16" width="18.33203125" style="37" customWidth="1" outlineLevel="2"/>
     <col min="17" max="17" width="29.5" style="37" customWidth="1" outlineLevel="2"/>
-    <col min="18" max="18" width="24.33203125" style="37" customWidth="1" outlineLevel="2"/>
-    <col min="19" max="19" width="29" style="37" customWidth="1" outlineLevel="2"/>
-    <col min="20" max="21" width="18.33203125" style="37" customWidth="1" outlineLevel="2"/>
-    <col min="22" max="22" width="17.1640625" style="37" bestFit="1" customWidth="1" outlineLevel="1"/>
-    <col min="23" max="24" width="9.1640625" style="37" hidden="1" customWidth="1" outlineLevel="2"/>
-    <col min="25" max="25" width="9.33203125" style="37" hidden="1" customWidth="1" outlineLevel="2"/>
-    <col min="26" max="26" width="37.5" style="35" hidden="1" customWidth="1" outlineLevel="2"/>
-    <col min="27" max="32" width="19.33203125" style="38" hidden="1" customWidth="1" outlineLevel="2"/>
-    <col min="33" max="33" width="19.33203125" style="38" customWidth="1" outlineLevel="1" collapsed="1"/>
-    <col min="34" max="37" width="19.33203125" style="38" customWidth="1"/>
+    <col min="18" max="18" width="29" style="37" customWidth="1" outlineLevel="2"/>
+    <col min="19" max="20" width="18.33203125" style="37" customWidth="1" outlineLevel="2"/>
+    <col min="21" max="21" width="17.1640625" style="37" bestFit="1" customWidth="1" outlineLevel="1"/>
+    <col min="22" max="23" width="9.1640625" style="37" hidden="1" customWidth="1" outlineLevel="2"/>
+    <col min="24" max="24" width="9.33203125" style="37" hidden="1" customWidth="1" outlineLevel="2"/>
+    <col min="25" max="25" width="37.5" style="35" hidden="1" customWidth="1" outlineLevel="2"/>
+    <col min="26" max="31" width="19.33203125" style="38" hidden="1" customWidth="1" outlineLevel="2"/>
+    <col min="32" max="32" width="19.33203125" style="38" customWidth="1" outlineLevel="1" collapsed="1"/>
+    <col min="33" max="36" width="19.33203125" style="38" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37">
+    <row r="1" spans="1:36">
       <c r="A1" s="7" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="2" spans="1:37" ht="16" customHeight="1">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="2" spans="1:36" ht="16" customHeight="1">
+      <c r="AG2" s="72" t="s">
+        <v>1</v>
+      </c>
       <c r="AH2" s="72" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI2" s="72" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AJ2" s="72" t="s">
-        <v>3</v>
-      </c>
-      <c r="AK2" s="72" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:37">
+    <row r="3" spans="1:36">
       <c r="A3" s="52"/>
-      <c r="AH3" s="32" t="str">
+      <c r="AG3" s="32" t="str">
         <f>IF(各種設定!$G$11=0,"",各種設定!$G$11)</f>
         <v>ja</v>
       </c>
+      <c r="AH3" s="32" t="str">
+        <f>IF(各種設定!$G$12=0,"",各種設定!$G$12)</f>
+        <v/>
+      </c>
       <c r="AI3" s="32" t="str">
-        <f>IF(各種設定!$G$12=0,"",各種設定!$G$12)</f>
+        <f>IF(各種設定!$G$13=0,"",各種設定!$G$13)</f>
         <v/>
       </c>
       <c r="AJ3" s="32" t="str">
-        <f>IF(各種設定!$G$13=0,"",各種設定!$G$13)</f>
-        <v/>
-      </c>
-      <c r="AK3" s="32" t="str">
         <f>IF(各種設定!$G$14=0,"",各種設定!$G$14)</f>
         <v/>
       </c>
     </row>
-    <row r="4" spans="1:37">
+    <row r="4" spans="1:36">
       <c r="A4" s="34"/>
     </row>
-    <row r="5" spans="1:37" s="1" customFormat="1" ht="43" customHeight="1">
+    <row r="5" spans="1:36" s="1" customFormat="1" ht="43" customHeight="1">
       <c r="A5" s="103" t="s">
         <v>5</v>
       </c>
@@ -12260,7 +12101,7 @@
       <c r="U5" s="75" t="s">
         <v>25</v>
       </c>
-      <c r="V5" s="75" t="s">
+      <c r="V5" s="109" t="s">
         <v>26</v>
       </c>
       <c r="W5" s="109" t="s">
@@ -12290,13 +12131,13 @@
       <c r="AE5" s="109" t="s">
         <v>35</v>
       </c>
-      <c r="AF5" s="109" t="s">
+      <c r="AF5" s="75" t="s">
         <v>36</v>
       </c>
-      <c r="AG5" s="75" t="s">
+      <c r="AG5" s="74" t="s">
         <v>37</v>
       </c>
-      <c r="AH5" s="74" t="s">
+      <c r="AH5" s="76" t="s">
         <v>38</v>
       </c>
       <c r="AI5" s="76" t="s">
@@ -12305,11 +12146,8 @@
       <c r="AJ5" s="76" t="s">
         <v>40</v>
       </c>
-      <c r="AK5" s="76" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="6" spans="1:37" s="1" customFormat="1">
+    </row>
+    <row r="6" spans="1:36" s="1" customFormat="1">
       <c r="A6" s="80"/>
       <c r="B6" s="82"/>
       <c r="C6" s="81"/>
@@ -12330,11 +12168,11 @@
       <c r="O6" s="88"/>
       <c r="P6" s="88"/>
       <c r="Q6" s="88"/>
-      <c r="R6" s="88"/>
+      <c r="R6" s="86"/>
       <c r="S6" s="86"/>
-      <c r="T6" s="86"/>
-      <c r="U6" s="57"/>
-      <c r="V6" s="92"/>
+      <c r="T6" s="57"/>
+      <c r="U6" s="92"/>
+      <c r="V6" s="91"/>
       <c r="W6" s="91"/>
       <c r="X6" s="91"/>
       <c r="Y6" s="91"/>
@@ -12344,14 +12182,13 @@
       <c r="AC6" s="91"/>
       <c r="AD6" s="91"/>
       <c r="AE6" s="91"/>
-      <c r="AF6" s="91"/>
-      <c r="AG6" s="104"/>
-      <c r="AH6" s="81"/>
-      <c r="AI6" s="54"/>
-      <c r="AJ6" s="42"/>
-      <c r="AK6" s="39"/>
-    </row>
-    <row r="7" spans="1:37" s="1" customFormat="1">
+      <c r="AF6" s="104"/>
+      <c r="AG6" s="81"/>
+      <c r="AH6" s="54"/>
+      <c r="AI6" s="42"/>
+      <c r="AJ6" s="39"/>
+    </row>
+    <row r="7" spans="1:36" s="1" customFormat="1">
       <c r="A7" s="89"/>
       <c r="B7" s="91"/>
       <c r="C7" s="90"/>
@@ -12372,11 +12209,11 @@
       <c r="O7" s="47"/>
       <c r="P7" s="47"/>
       <c r="Q7" s="47"/>
-      <c r="R7" s="47"/>
+      <c r="R7" s="57"/>
       <c r="S7" s="57"/>
       <c r="T7" s="57"/>
-      <c r="U7" s="57"/>
-      <c r="V7" s="92"/>
+      <c r="U7" s="92"/>
+      <c r="V7" s="57"/>
       <c r="W7" s="57"/>
       <c r="X7" s="57"/>
       <c r="Y7" s="57"/>
@@ -12386,14 +12223,13 @@
       <c r="AC7" s="57"/>
       <c r="AD7" s="57"/>
       <c r="AE7" s="57"/>
-      <c r="AF7" s="57"/>
-      <c r="AG7" s="105"/>
-      <c r="AH7" s="90"/>
-      <c r="AI7" s="54"/>
-      <c r="AJ7" s="42"/>
-      <c r="AK7" s="39"/>
-    </row>
-    <row r="8" spans="1:37" s="1" customFormat="1">
+      <c r="AF7" s="105"/>
+      <c r="AG7" s="90"/>
+      <c r="AH7" s="54"/>
+      <c r="AI7" s="42"/>
+      <c r="AJ7" s="39"/>
+    </row>
+    <row r="8" spans="1:36" s="1" customFormat="1">
       <c r="A8" s="80"/>
       <c r="B8" s="82"/>
       <c r="C8" s="95"/>
@@ -12414,11 +12250,11 @@
       <c r="O8" s="88"/>
       <c r="P8" s="88"/>
       <c r="Q8" s="88"/>
-      <c r="R8" s="88"/>
+      <c r="R8" s="96"/>
       <c r="S8" s="96"/>
-      <c r="T8" s="96"/>
-      <c r="U8" s="106"/>
-      <c r="V8" s="92"/>
+      <c r="T8" s="106"/>
+      <c r="U8" s="92"/>
+      <c r="V8" s="101"/>
       <c r="W8" s="101"/>
       <c r="X8" s="101"/>
       <c r="Y8" s="101"/>
@@ -12428,14 +12264,13 @@
       <c r="AC8" s="101"/>
       <c r="AD8" s="101"/>
       <c r="AE8" s="101"/>
-      <c r="AF8" s="101"/>
-      <c r="AG8" s="107"/>
-      <c r="AH8" s="81"/>
-      <c r="AI8" s="54"/>
-      <c r="AJ8" s="42"/>
-      <c r="AK8" s="39"/>
-    </row>
-    <row r="9" spans="1:37">
+      <c r="AF8" s="107"/>
+      <c r="AG8" s="81"/>
+      <c r="AH8" s="54"/>
+      <c r="AI8" s="42"/>
+      <c r="AJ8" s="39"/>
+    </row>
+    <row r="9" spans="1:36">
       <c r="A9" s="89"/>
       <c r="B9" s="99"/>
       <c r="C9" s="90"/>
@@ -12459,8 +12294,8 @@
       <c r="R9" s="47"/>
       <c r="S9" s="47"/>
       <c r="T9" s="47"/>
-      <c r="U9" s="47"/>
-      <c r="V9" s="92"/>
+      <c r="U9" s="92"/>
+      <c r="V9" s="47"/>
       <c r="W9" s="47"/>
       <c r="X9" s="47"/>
       <c r="Y9" s="47"/>
@@ -12470,14 +12305,13 @@
       <c r="AC9" s="47"/>
       <c r="AD9" s="47"/>
       <c r="AE9" s="47"/>
-      <c r="AF9" s="47"/>
-      <c r="AG9" s="108"/>
-      <c r="AH9" s="98"/>
-      <c r="AI9" s="122"/>
-      <c r="AJ9" s="42"/>
-      <c r="AK9" s="39"/>
-    </row>
-    <row r="10" spans="1:37">
+      <c r="AF9" s="108"/>
+      <c r="AG9" s="98"/>
+      <c r="AH9" s="122"/>
+      <c r="AI9" s="42"/>
+      <c r="AJ9" s="39"/>
+    </row>
+    <row r="10" spans="1:36">
       <c r="A10" s="80"/>
       <c r="B10" s="102"/>
       <c r="C10" s="81"/>
@@ -12500,9 +12334,9 @@
       <c r="Q10" s="88"/>
       <c r="R10" s="88"/>
       <c r="S10" s="88"/>
-      <c r="T10" s="88"/>
-      <c r="U10" s="47"/>
-      <c r="V10" s="92"/>
+      <c r="T10" s="47"/>
+      <c r="U10" s="92"/>
+      <c r="V10" s="47"/>
       <c r="W10" s="47"/>
       <c r="X10" s="47"/>
       <c r="Y10" s="47"/>
@@ -12512,14 +12346,13 @@
       <c r="AC10" s="47"/>
       <c r="AD10" s="47"/>
       <c r="AE10" s="47"/>
-      <c r="AF10" s="47"/>
-      <c r="AG10" s="108"/>
-      <c r="AH10" s="95"/>
-      <c r="AI10" s="122"/>
-      <c r="AJ10" s="42"/>
-      <c r="AK10" s="39"/>
-    </row>
-    <row r="11" spans="1:37">
+      <c r="AF10" s="108"/>
+      <c r="AG10" s="95"/>
+      <c r="AH10" s="122"/>
+      <c r="AI10" s="42"/>
+      <c r="AJ10" s="39"/>
+    </row>
+    <row r="11" spans="1:36">
       <c r="A11" s="89"/>
       <c r="B11" s="98"/>
       <c r="C11" s="98"/>
@@ -12543,8 +12376,8 @@
       <c r="R11" s="47"/>
       <c r="S11" s="47"/>
       <c r="T11" s="47"/>
-      <c r="U11" s="47"/>
-      <c r="V11" s="92"/>
+      <c r="U11" s="92"/>
+      <c r="V11" s="47"/>
       <c r="W11" s="47"/>
       <c r="X11" s="47"/>
       <c r="Y11" s="47"/>
@@ -12554,14 +12387,13 @@
       <c r="AC11" s="47"/>
       <c r="AD11" s="47"/>
       <c r="AE11" s="47"/>
-      <c r="AF11" s="47"/>
-      <c r="AG11" s="108"/>
-      <c r="AH11" s="98"/>
-      <c r="AI11" s="122"/>
-      <c r="AJ11" s="42"/>
-      <c r="AK11" s="39"/>
-    </row>
-    <row r="12" spans="1:37">
+      <c r="AF11" s="108"/>
+      <c r="AG11" s="98"/>
+      <c r="AH11" s="122"/>
+      <c r="AI11" s="42"/>
+      <c r="AJ11" s="39"/>
+    </row>
+    <row r="12" spans="1:36">
       <c r="A12" s="80"/>
       <c r="B12" s="95"/>
       <c r="C12" s="95"/>
@@ -12584,9 +12416,9 @@
       <c r="Q12" s="88"/>
       <c r="R12" s="88"/>
       <c r="S12" s="88"/>
-      <c r="T12" s="88"/>
-      <c r="U12" s="47"/>
-      <c r="V12" s="92"/>
+      <c r="T12" s="47"/>
+      <c r="U12" s="92"/>
+      <c r="V12" s="47"/>
       <c r="W12" s="47"/>
       <c r="X12" s="47"/>
       <c r="Y12" s="47"/>
@@ -12596,14 +12428,13 @@
       <c r="AC12" s="47"/>
       <c r="AD12" s="47"/>
       <c r="AE12" s="47"/>
-      <c r="AF12" s="47"/>
-      <c r="AG12" s="108"/>
-      <c r="AH12" s="95"/>
-      <c r="AI12" s="122"/>
-      <c r="AJ12" s="42"/>
-      <c r="AK12" s="39"/>
-    </row>
-    <row r="13" spans="1:37">
+      <c r="AF12" s="108"/>
+      <c r="AG12" s="95"/>
+      <c r="AH12" s="122"/>
+      <c r="AI12" s="42"/>
+      <c r="AJ12" s="39"/>
+    </row>
+    <row r="13" spans="1:36">
       <c r="A13" s="89"/>
       <c r="B13" s="98"/>
       <c r="C13" s="98"/>
@@ -12627,8 +12458,8 @@
       <c r="R13" s="47"/>
       <c r="S13" s="47"/>
       <c r="T13" s="47"/>
-      <c r="U13" s="47"/>
-      <c r="V13" s="92"/>
+      <c r="U13" s="92"/>
+      <c r="V13" s="47"/>
       <c r="W13" s="47"/>
       <c r="X13" s="47"/>
       <c r="Y13" s="47"/>
@@ -12638,16 +12469,15 @@
       <c r="AC13" s="47"/>
       <c r="AD13" s="47"/>
       <c r="AE13" s="47"/>
-      <c r="AF13" s="47"/>
-      <c r="AG13" s="108"/>
-      <c r="AH13" s="98"/>
-      <c r="AI13" s="51"/>
-      <c r="AJ13" s="42"/>
-      <c r="AK13" s="39"/>
+      <c r="AF13" s="108"/>
+      <c r="AG13" s="98"/>
+      <c r="AH13" s="51"/>
+      <c r="AI13" s="42"/>
+      <c r="AJ13" s="39"/>
     </row>
   </sheetData>
   <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V6:V13 E6:M13" xr:uid="{00000000-0002-0000-0800-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U6:U13 E6:M13" xr:uid="{00000000-0002-0000-0800-000000000000}">
       <formula1>"○"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N6:N13" xr:uid="{00000000-0002-0000-0800-000001000000}">

--- a/excel-format/db-column-definitions_fmt-v5.0.0-ja_my-app.xlsx
+++ b/excel-format/db-column-definitions_fmt-v5.0.0-ja_my-app.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yosuke.tanaka/Desktop/development/git/ecuacion-tool-code-generator/excel-format/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EF66E71-AFB0-444B-94E5-7499C2C1C498}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D3E0B60-5500-904B-944B-94D86AFE5ACF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2280" windowWidth="28800" windowHeight="14820" tabRatio="853" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="2280" windowWidth="28800" windowHeight="14820" tabRatio="853" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="dataTypeプルダウン項目" sheetId="1" state="hidden" r:id="rId1"/>
@@ -25,7 +25,7 @@
     <sheet name="テーブル一覧" sheetId="10" r:id="rId10"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="7">DB項目定義!$A$1:$Y$5</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="7">DB項目定義!$A$1:$AA$5</definedName>
     <definedName name="一般">dataTypeプルダウン項目!$A$3:$A$16</definedName>
     <definedName name="固定フォーマット">dataTypeプルダウン項目!#REF!</definedName>
     <definedName name="日時">dataTypeプルダウン項目!#REF!</definedName>
@@ -124,7 +124,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="469" uniqueCount="284">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="473" uniqueCount="286">
   <si>
     <t>DB項目定義</t>
   </si>
@@ -1140,6 +1140,12 @@
     <t>ja</t>
   </si>
   <si>
+    <t>関連：参照元変数itemNameKeyClass</t>
+  </si>
+  <si>
+    <t>関連：参照先変数itemNameKeyClass</t>
+  </si>
+  <si>
     <t>■バージョン情報
 ・対応code-generator version: 15.0.0-beta.3 以降
 ・前minorバージョンからのformat移行が必要な場合：必須
@@ -1149,7 +1155,8 @@
 ・ファイル名の形式変更
 ▼「DB項目定義」・「DB共通項目定義」シート
 　・「PK・UK」列を、「Surrogate key」と「natural key (unique key)」 の2つの列に分割。
-　　また、もともと「S・U」で記載していたのを、「○」で記載するよう変更</t>
+　　また、もともと「S・U」で記載していたのを、「○」で記載するよう変更
+　・「関連：参照元変数itemNameKeyClass」、「関連：参照先変数itemNameKeyClass」列の追加</t>
   </si>
 </sst>
 </file>
@@ -1924,7 +1931,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="標準 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
-  <dxfs count="122">
+  <dxfs count="126">
     <dxf>
       <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="center" vertical="center"/>
@@ -2232,6 +2239,22 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
       <fill>
         <patternFill>
           <fgColor indexed="64"/>
@@ -2308,6 +2331,22 @@
         <horizontal/>
       </border>
       <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
     </dxf>
     <dxf>
       <numFmt numFmtId="30" formatCode="@"/>
@@ -2594,6 +2633,277 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="left" vertical="center"/>
+      <border outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="6" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="6" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="center" vertical="bottom"/>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="general" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="center" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="center" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="general" vertical="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="general" vertical="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="general" vertical="center" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="general" vertical="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="general" vertical="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="general" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.34998626667073579"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </dxf>
@@ -2816,6 +3126,27 @@
       <protection locked="0" hidden="0"/>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0" hidden="0"/>
@@ -2854,6 +3185,27 @@
       </font>
       <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <protection locked="0" hidden="0"/>
     </dxf>
     <dxf>
@@ -3049,277 +3401,6 @@
       <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="center" vertical="center"/>
     </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="left" vertical="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="left" vertical="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="left" vertical="center"/>
-      <border outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="6" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="6" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="left" vertical="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="center" vertical="bottom"/>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="left" vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="ＭＳ Ｐゴシック"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="general" vertical="center"/>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="general" vertical="center" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="general" vertical="center" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="general" vertical="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="general" vertical="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="general" vertical="center" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="general" vertical="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="general" vertical="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="general" vertical="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="general" vertical="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="general" vertical="center"/>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="right" vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.34998626667073579"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center"/>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
   <extLst>
@@ -3415,114 +3496,114 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="テーブル5" displayName="テーブル5" ref="A3:D39" totalsRowShown="0" headerRowDxfId="112" dataDxfId="111">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="テーブル5" displayName="テーブル5" ref="A3:D39" totalsRowShown="0" headerRowDxfId="85" dataDxfId="84">
   <autoFilter ref="A3:D39" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="日付" dataDxfId="110"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="バージョン" dataDxfId="109"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="修正事項" dataDxfId="108"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="修正者" dataDxfId="107"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="日付" dataDxfId="83"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="バージョン" dataDxfId="82"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="修正事項" dataDxfId="81"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="修正者" dataDxfId="80"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="テーブル50" displayName="テーブル50" ref="A5:H28" totalsRowShown="0" dataDxfId="121">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="テーブル50" displayName="テーブル50" ref="A5:H28" totalsRowShown="0" dataDxfId="79">
   <autoFilter ref="A5:H28" xr:uid="{00000000-0009-0000-0100-000004000000}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="#" dataDxfId="120">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="#" dataDxfId="78">
       <calculatedColumnFormula>ROW()-5</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0300-000008000000}" name="分類" dataDxfId="119"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="分類名" dataDxfId="118"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="項目" dataDxfId="117"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="説明" dataDxfId="116"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0300-000009000000}" name="必須" dataDxfId="115"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0300-000005000000}" name="値" dataDxfId="114"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0300-000006000000}" name="備考" dataDxfId="113"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0300-000008000000}" name="分類" dataDxfId="77"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="分類名" dataDxfId="76"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="項目" dataDxfId="75"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="説明" dataDxfId="74"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0300-000009000000}" name="必須" dataDxfId="73"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0300-000005000000}" name="値" dataDxfId="72"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0300-000006000000}" name="備考" dataDxfId="71"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="テーブル2" displayName="テーブル2" ref="A7:S37" tableType="xml" totalsRowShown="0" headerRowDxfId="106" dataDxfId="105">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="テーブル2" displayName="テーブル2" ref="A7:S37" tableType="xml" totalsRowShown="0" headerRowDxfId="70" dataDxfId="69">
   <tableColumns count="19">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" uniqueName="name" name="DataType名" dataDxfId="104">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" uniqueName="name" name="DataType名" dataDxfId="68">
       <xmlColumnPr mapId="191" xpath="/root/datatype/@name" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" uniqueName="kata" name="型" dataDxfId="103">
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" uniqueName="kata" name="型" dataDxfId="67">
       <xmlColumnPr mapId="191" xpath="/root/datatype/kata" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0400-000004000000}" uniqueName="minLength" name="長さ最小" dataDxfId="102">
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0400-000004000000}" uniqueName="minLength" name="長さ最小" dataDxfId="66">
       <xmlColumnPr mapId="191" xpath="/root/datatype/minLength" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0400-00000B000000}" uniqueName="maxLength" name="長さ最大" dataDxfId="101">
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0400-00000B000000}" uniqueName="maxLength" name="長さ最大" dataDxfId="65">
       <xmlColumnPr mapId="191" xpath="/root/datatype/maxLength" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0400-00000F000000}" uniqueName="numScale" name="データパターン（日本語）" dataDxfId="100"/>
-    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0400-000018000000}" uniqueName="stringDataPtn" name="データパターン" dataDxfId="99">
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0400-00000F000000}" uniqueName="numScale" name="データパターン（日本語）" dataDxfId="64"/>
+    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0400-000018000000}" uniqueName="stringDataPtn" name="データパターン" dataDxfId="63">
       <calculatedColumnFormula>IF(テーブル2[[#This Row],[データパターン（日本語）]]="", "", VLOOKUP(テーブル2[[#This Row],[データパターン（日本語）]],dataType・データパターン一覧!A:B,2,FALSE))</calculatedColumnFormula>
       <xmlColumnPr mapId="191" xpath="/root/datatype/stringDataPtn" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0400-000012000000}" uniqueName="18" name="禁則文字チェック除外" dataDxfId="98"/>
-    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0400-000019000000}" uniqueName="stringRegEx" name="正規表現" dataDxfId="97">
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0400-000012000000}" uniqueName="18" name="禁則文字チェック除外" dataDxfId="62"/>
+    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0400-000019000000}" uniqueName="stringRegEx" name="正規表現" dataDxfId="61">
       <xmlColumnPr mapId="191" xpath="/root/datatype/stringRegEx" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0400-000009000000}" uniqueName="numMinVal" name="最小値" dataDxfId="96">
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0400-000009000000}" uniqueName="numMinVal" name="最小値" dataDxfId="60">
       <xmlColumnPr mapId="191" xpath="/root/datatype/numMinVal" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0400-00000A000000}" uniqueName="numMaxVal" name="最大値" dataDxfId="95">
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0400-00000A000000}" uniqueName="numMaxVal" name="最大値" dataDxfId="59">
       <xmlColumnPr mapId="191" xpath="/root/datatype/numMaxVal" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0400-00000C000000}" uniqueName="numDigitInteger" name="整数部桁数" dataDxfId="94">
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0400-00000C000000}" uniqueName="numDigitInteger" name="整数部桁数" dataDxfId="58">
       <xmlColumnPr mapId="191" xpath="/root/datatype/numDigitInteger" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0400-00000D000000}" uniqueName="numDigitFraction" name="小数部桁数" dataDxfId="93">
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0400-00000D000000}" uniqueName="numDigitFraction" name="小数部桁数" dataDxfId="57">
       <xmlColumnPr mapId="191" xpath="/root/datatype/numDigitFraction" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0400-000005000000}" uniqueName="enumCodeLength" name="コードの長さ" dataDxfId="92">
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0400-000005000000}" uniqueName="enumCodeLength" name="コードの長さ" dataDxfId="56">
       <xmlColumnPr mapId="191" xpath="/root/datatype/enumCodeLength" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0400-00000E000000}" uniqueName="notNeedsTimezone" name="timezoneなし" dataDxfId="91">
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0400-00000E000000}" uniqueName="notNeedsTimezone" name="timezoneなし" dataDxfId="55">
       <xmlColumnPr mapId="191" xpath="/root/datatype/notNeedsTimezone" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0400-000010000000}" uniqueName="javadoc" name="備考" dataDxfId="90">
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0400-000010000000}" uniqueName="javadoc" name="備考" dataDxfId="54">
       <xmlColumnPr mapId="191" xpath="/root/datatype/javadoc" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" uniqueName="2" name="パターン説明（デフォルト言語）" dataDxfId="89"/>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0400-000013000000}" uniqueName="19" name="パターン説明（追加言語1）" dataDxfId="88"/>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0400-000014000000}" uniqueName="20" name="パターン説明（追加言語2）" dataDxfId="87"/>
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0400-000015000000}" uniqueName="21" name="パターン説明（追加言語）" dataDxfId="86"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" uniqueName="2" name="パターン説明（デフォルト言語）" dataDxfId="53"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0400-000013000000}" uniqueName="19" name="パターン説明（追加言語1）" dataDxfId="52"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0400-000014000000}" uniqueName="20" name="パターン説明（追加言語2）" dataDxfId="51"/>
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0400-000015000000}" uniqueName="21" name="パターン説明（追加言語）" dataDxfId="50"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{00000000-000C-0000-FFFF-FFFF05000000}" name="テーブル4" displayName="テーブル4" ref="A6:I33" tableType="xml" totalsRowShown="0" headerRowDxfId="85" dataDxfId="84">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{00000000-000C-0000-FFFF-FFFF05000000}" name="テーブル4" displayName="テーブル4" ref="A6:I33" tableType="xml" totalsRowShown="0" headerRowDxfId="49" dataDxfId="48">
   <autoFilter ref="A6:I33" xr:uid="{00000000-0009-0000-0100-000006000000}"/>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0500-000001000000}" uniqueName="dataTypeName" name="DataType名" dataDxfId="83">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0500-000001000000}" uniqueName="dataTypeName" name="DataType名" dataDxfId="47">
       <xmlColumnPr mapId="132" xpath="/root/enum/dataTypeName" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0500-000008000000}" uniqueName="8" name="code" dataDxfId="82"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0500-000005000000}" uniqueName="varName" name="varName" dataDxfId="81">
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0500-000008000000}" uniqueName="8" name="code" dataDxfId="46"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0500-000005000000}" uniqueName="varName" name="varName" dataDxfId="45">
       <xmlColumnPr mapId="132" xpath="/root/enum/varName" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0500-00000A000000}" uniqueName="10" name="javaのみ" dataDxfId="80"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0500-00000C000000}" uniqueName="javadoc-value" name="備考" dataDxfId="79">
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0500-00000A000000}" uniqueName="10" name="javaのみ" dataDxfId="44"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0500-00000C000000}" uniqueName="javadoc-value" name="備考" dataDxfId="43">
       <xmlColumnPr mapId="132" xpath="/root/enum/javadoc-value" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0500-000009000000}" uniqueName="9" name="表示名（デフォルト言語）" dataDxfId="78"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0500-000004000000}" uniqueName="dispNameAddLang1" name="表示名（追加言語1）" dataDxfId="77">
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0500-000009000000}" uniqueName="9" name="表示名（デフォルト言語）" dataDxfId="42"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0500-000004000000}" uniqueName="dispNameAddLang1" name="表示名（追加言語1）" dataDxfId="41">
       <xmlColumnPr mapId="132" xpath="/root/enum/dispNameAddLang1" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0500-000006000000}" uniqueName="dispNameAddLang2" name="表示名（追加言語2）" dataDxfId="76">
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0500-000006000000}" uniqueName="dispNameAddLang2" name="表示名（追加言語2）" dataDxfId="40">
       <xmlColumnPr mapId="132" xpath="/root/enum/dispNameAddLang2" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0500-000007000000}" uniqueName="dispNameAddLang3" name="表示名（追加言語3）" dataDxfId="75">
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0500-000007000000}" uniqueName="dispNameAddLang3" name="表示名（追加言語3）" dataDxfId="39">
       <xmlColumnPr mapId="132" xpath="/root/enum/dispNameAddLang3" xmlDataType="string"/>
     </tableColumn>
   </tableColumns>
@@ -3531,81 +3612,83 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{00000000-000C-0000-FFFF-FFFF06000000}" name="テーブル7" displayName="テーブル7" ref="A5:AJ119" tableType="xml" totalsRowShown="0" headerRowDxfId="74" dataDxfId="73">
-  <autoFilter ref="A5:AJ119" xr:uid="{00000000-0009-0000-0100-000007000000}"/>
-  <tableColumns count="36">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0600-000001000000}" uniqueName="table" name="テーブル名" dataDxfId="72">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{00000000-000C-0000-FFFF-FFFF06000000}" name="テーブル7" displayName="テーブル7" ref="A5:AL119" tableType="xml" totalsRowShown="0" headerRowDxfId="125" dataDxfId="124">
+  <autoFilter ref="A5:AL119" xr:uid="{00000000-0009-0000-0100-000007000000}"/>
+  <tableColumns count="38">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0600-000001000000}" uniqueName="table" name="テーブル名" dataDxfId="123">
       <xmlColumnPr mapId="161" xpath="/root/column/table" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0600-000002000000}" uniqueName="name" name="カラム名" dataDxfId="71">
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0600-000002000000}" uniqueName="name" name="カラム名" dataDxfId="122">
       <xmlColumnPr mapId="161" xpath="/root/column/@name" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0600-00000F000000}" uniqueName="dataType" name="dataType" dataDxfId="70">
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0600-00000F000000}" uniqueName="dataType" name="dataType" dataDxfId="121">
       <xmlColumnPr mapId="161" xpath="/root/column/dataType" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0600-000010000000}" uniqueName="16" name="dataType存在確認" dataDxfId="69">
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0600-000010000000}" uniqueName="16" name="dataType存在確認" dataDxfId="120">
       <calculatedColumnFormula>IF(テーブル7[[#This Row],[dataType]]="","",IF(NOT(ISNA(VLOOKUP(テーブル7[[#This Row],[dataType]], dataType定義!A:A, 1,FALSE))), "○", "×"))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0600-00001C000000}" uniqueName="28" name="javaのみ" dataDxfId="68"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0600-000006000000}" uniqueName="pk" name="Surrogate key " dataDxfId="67">
+    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0600-00001C000000}" uniqueName="28" name="javaのみ" dataDxfId="119"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0600-000006000000}" uniqueName="pk" name="Surrogate key " dataDxfId="118">
       <xmlColumnPr mapId="161" xpath="/root/column/pk" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="29" xr3:uid="{00000000-0010-0000-0600-00001D000000}" uniqueName="29" name="natural key (unique key)" dataDxfId="66"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0600-000008000000}" uniqueName="nullable" name="nullable" dataDxfId="65">
+    <tableColumn id="29" xr3:uid="{00000000-0010-0000-0600-00001D000000}" uniqueName="29" name="natural key (unique key)" dataDxfId="117"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0600-000008000000}" uniqueName="nullable" name="nullable" dataDxfId="116">
       <xmlColumnPr mapId="161" xpath="/root/column/nullable" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0600-00000A000000}" uniqueName="autoIncrement" name="自動採番" dataDxfId="64">
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0600-00000A000000}" uniqueName="autoIncrement" name="自動採番" dataDxfId="115">
       <xmlColumnPr mapId="161" xpath="/root/column/autoIncrement" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0600-000015000000}" uniqueName="forcedIncrement" name="強制採番" dataDxfId="63">
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0600-000015000000}" uniqueName="forcedIncrement" name="強制採番" dataDxfId="114">
       <xmlColumnPr mapId="161" xpath="/root/column/forcedIncrement" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0600-00000B000000}" uniqueName="autoUpdate" name="自動更新" dataDxfId="62">
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0600-00000B000000}" uniqueName="autoUpdate" name="自動更新" dataDxfId="113">
       <xmlColumnPr mapId="161" xpath="/root/column/autoUpdate" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0600-000014000000}" uniqueName="forcedUpdate" name="強制更新" dataDxfId="61">
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0600-000014000000}" uniqueName="forcedUpdate" name="強制更新" dataDxfId="112">
       <xmlColumnPr mapId="161" xpath="/root/column/forcedUpdate" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0600-00000C000000}" uniqueName="valueChangeMethod" name="グループ識別項目" dataDxfId="60">
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0600-00000C000000}" uniqueName="valueChangeMethod" name="グループ識別項目" dataDxfId="111">
       <xmlColumnPr mapId="161" xpath="/root/column/valueChangeMethod" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0600-000012000000}" uniqueName="updatedValue" name="SPRING監査" dataDxfId="59">
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0600-000012000000}" uniqueName="updatedValue" name="SPRING監査" dataDxfId="110">
       <xmlColumnPr mapId="161" xpath="/root/column/updatedValue" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0600-000013000000}" uniqueName="optLock" name="関連：種類" dataDxfId="58">
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0600-000013000000}" uniqueName="optLock" name="関連：種類" dataDxfId="109">
       <xmlColumnPr mapId="161" xpath="/root/column/optLock" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0600-000016000000}" uniqueName="22" name="関連：direction" dataDxfId="57"/>
-    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0600-00001A000000}" uniqueName="26" name="関連：参照元変数名" dataDxfId="56"/>
-    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0600-000017000000}" uniqueName="23" name="関連：参照先テーブル" dataDxfId="55"/>
-    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0600-000018000000}" uniqueName="24" name="関連：参照先カラム" dataDxfId="54"/>
-    <tableColumn id="27" xr3:uid="{00000000-0010-0000-0600-00001B000000}" uniqueName="27" name="関連：参照先変数名" dataDxfId="53"/>
-    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0600-000019000000}" uniqueName="25" name="関連：eager" dataDxfId="52"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0600-000011000000}" uniqueName="index1" name="index1" dataDxfId="51">
+    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0600-000016000000}" uniqueName="22" name="関連：direction" dataDxfId="108"/>
+    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0600-00001A000000}" uniqueName="26" name="関連：参照元変数名" dataDxfId="107"/>
+    <tableColumn id="30" xr3:uid="{5A9AA2EE-4621-8F41-8558-DC101287E367}" uniqueName="30" name="関連：参照元変数itemNameKeyClass" dataDxfId="106"/>
+    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0600-000017000000}" uniqueName="23" name="関連：参照先テーブル" dataDxfId="105"/>
+    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0600-000018000000}" uniqueName="24" name="関連：参照先カラム" dataDxfId="104"/>
+    <tableColumn id="27" xr3:uid="{00000000-0010-0000-0600-00001B000000}" uniqueName="27" name="関連：参照先変数名" dataDxfId="103"/>
+    <tableColumn id="31" xr3:uid="{E81A02AD-8596-4D46-814C-6DF696078275}" uniqueName="31" name="関連：参照先変数itemNameKeyClass" dataDxfId="102"/>
+    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0600-000019000000}" uniqueName="25" name="関連：eager" dataDxfId="101"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0600-000011000000}" uniqueName="index1" name="index1" dataDxfId="100">
       <xmlColumnPr mapId="161" xpath="/root/column/index1" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0600-00000E000000}" uniqueName="index2" name="index2" dataDxfId="50">
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0600-00000E000000}" uniqueName="index2" name="index2" dataDxfId="99">
       <xmlColumnPr mapId="161" xpath="/root/column/index2" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0600-00000D000000}" uniqueName="index3" name="index3" dataDxfId="49">
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0600-00000D000000}" uniqueName="index3" name="index3" dataDxfId="98">
       <xmlColumnPr mapId="161" xpath="/root/column/index3" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="34" xr3:uid="{00000000-0010-0000-0600-000022000000}" uniqueName="34" name="index4" dataDxfId="48"/>
-    <tableColumn id="35" xr3:uid="{00000000-0010-0000-0600-000023000000}" uniqueName="35" name="index5" dataDxfId="47"/>
-    <tableColumn id="36" xr3:uid="{00000000-0010-0000-0600-000024000000}" uniqueName="36" name="index6" dataDxfId="46"/>
-    <tableColumn id="37" xr3:uid="{00000000-0010-0000-0600-000025000000}" uniqueName="37" name="index7" dataDxfId="45"/>
-    <tableColumn id="38" xr3:uid="{00000000-0010-0000-0600-000026000000}" uniqueName="38" name="index8" dataDxfId="44"/>
-    <tableColumn id="39" xr3:uid="{00000000-0010-0000-0600-000027000000}" uniqueName="39" name="index9" dataDxfId="43"/>
-    <tableColumn id="40" xr3:uid="{00000000-0010-0000-0600-000028000000}" uniqueName="40" name="index10" dataDxfId="42"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0600-000005000000}" uniqueName="dispNameAddLang1" name="備考" dataDxfId="41"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0600-000009000000}" uniqueName="9" name="カラム表示名（デフォルト言語）" dataDxfId="40"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0600-000003000000}" uniqueName="dispNameAddLang1" name="カラム表示名（追加言語1）" dataDxfId="39">
+    <tableColumn id="34" xr3:uid="{00000000-0010-0000-0600-000022000000}" uniqueName="34" name="index4" dataDxfId="97"/>
+    <tableColumn id="35" xr3:uid="{00000000-0010-0000-0600-000023000000}" uniqueName="35" name="index5" dataDxfId="96"/>
+    <tableColumn id="36" xr3:uid="{00000000-0010-0000-0600-000024000000}" uniqueName="36" name="index6" dataDxfId="95"/>
+    <tableColumn id="37" xr3:uid="{00000000-0010-0000-0600-000025000000}" uniqueName="37" name="index7" dataDxfId="94"/>
+    <tableColumn id="38" xr3:uid="{00000000-0010-0000-0600-000026000000}" uniqueName="38" name="index8" dataDxfId="93"/>
+    <tableColumn id="39" xr3:uid="{00000000-0010-0000-0600-000027000000}" uniqueName="39" name="index9" dataDxfId="92"/>
+    <tableColumn id="40" xr3:uid="{00000000-0010-0000-0600-000028000000}" uniqueName="40" name="index10" dataDxfId="91"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0600-000005000000}" uniqueName="dispNameAddLang1" name="備考" dataDxfId="90"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0600-000009000000}" uniqueName="9" name="カラム表示名（デフォルト言語）" dataDxfId="89"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0600-000003000000}" uniqueName="dispNameAddLang1" name="カラム表示名（追加言語1）" dataDxfId="88">
       <xmlColumnPr mapId="161" xpath="/root/column/dispNameAddLang1" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0600-000004000000}" uniqueName="dispNameAddLang2" name="カラム表示名（追加言語2）" dataDxfId="38">
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0600-000004000000}" uniqueName="dispNameAddLang2" name="カラム表示名（追加言語2）" dataDxfId="87">
       <xmlColumnPr mapId="161" xpath="/root/column/dispNameAddLang2" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0600-000007000000}" uniqueName="dispNameAddLang3" name="カラム表示名（追加言語3）" dataDxfId="37">
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0600-000007000000}" uniqueName="dispNameAddLang3" name="カラム表示名（追加言語3）" dataDxfId="86">
       <xmlColumnPr mapId="161" xpath="/root/column/dispNameAddLang3" xmlDataType="string"/>
     </tableColumn>
   </tableColumns>
@@ -3614,31 +3697,33 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{00000000-000C-0000-FFFF-FFFF07000000}" name="テーブル74" displayName="テーブル74" ref="A5:AJ13" totalsRowShown="0" headerRowDxfId="36" dataDxfId="35">
-  <autoFilter ref="A5:AJ13" xr:uid="{00000000-0009-0000-0100-000008000000}"/>
-  <tableColumns count="36">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0700-000001000000}" name="テーブル名" dataDxfId="34"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0700-000002000000}" name="カラム名" dataDxfId="33"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0700-00000F000000}" name="dataType" dataDxfId="32"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0700-000010000000}" name="dataType存在確認" dataDxfId="31">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{00000000-000C-0000-FFFF-FFFF07000000}" name="テーブル74" displayName="テーブル74" ref="A5:AL13" totalsRowShown="0" headerRowDxfId="38" dataDxfId="37">
+  <autoFilter ref="A5:AL13" xr:uid="{00000000-0009-0000-0100-000008000000}"/>
+  <tableColumns count="38">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0700-000001000000}" name="テーブル名" dataDxfId="36"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0700-000002000000}" name="カラム名" dataDxfId="35"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0700-00000F000000}" name="dataType" dataDxfId="34"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0700-000010000000}" name="dataType存在確認" dataDxfId="33">
       <calculatedColumnFormula>IF(C6="","",IF(テーブル74[[#This Row],[dataType]]="","",IF(NOT(ISNA(VLOOKUP(テーブル74[[#This Row],[dataType]], dataType定義!A:A, 1,FALSE))), "○", "×")))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0700-00001C000000}" name="javaのみ" dataDxfId="30"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0700-000006000000}" name="Surrogate key " dataDxfId="29"/>
+    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0700-00001C000000}" name="javaのみ" dataDxfId="32"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0700-000006000000}" name="Surrogate key " dataDxfId="31"/>
     <tableColumn id="9" xr3:uid="{00000000-0010-0000-0700-000009000000}" name="natural key (unique key)"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0700-000008000000}" name="nullable" dataDxfId="28"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0700-00000A000000}" name="自動採番" dataDxfId="27"/>
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0700-000015000000}" name="強制採番" dataDxfId="26"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0700-00000B000000}" name="自動更新" dataDxfId="25"/>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0700-000014000000}" name="強制更新" dataDxfId="24"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0700-00000C000000}" name="グループ識別項目" dataDxfId="23"/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0700-000012000000}" name="SPRING監査" dataDxfId="22"/>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0700-000013000000}" name="関連：種類" dataDxfId="21"/>
-    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0700-000016000000}" name="関連：direction" dataDxfId="20"/>
-    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0700-00001A000000}" name="関連：参照元変数名" dataDxfId="19"/>
-    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0700-000017000000}" name="関連：参照先テーブル" dataDxfId="18"/>
-    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0700-000018000000}" name="関連：参照先カラム" dataDxfId="17"/>
-    <tableColumn id="27" xr3:uid="{00000000-0010-0000-0700-00001B000000}" name="関連：参照先変数名" dataDxfId="16"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0700-000008000000}" name="nullable" dataDxfId="30"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0700-00000A000000}" name="自動採番" dataDxfId="29"/>
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0700-000015000000}" name="強制採番" dataDxfId="28"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0700-00000B000000}" name="自動更新" dataDxfId="27"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0700-000014000000}" name="強制更新" dataDxfId="26"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0700-00000C000000}" name="グループ識別項目" dataDxfId="25"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0700-000012000000}" name="SPRING監査" dataDxfId="24"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0700-000013000000}" name="関連：種類" dataDxfId="23"/>
+    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0700-000016000000}" name="関連：direction" dataDxfId="22"/>
+    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0700-00001A000000}" name="関連：参照元変数名" dataDxfId="21"/>
+    <tableColumn id="29" xr3:uid="{8F9BEFCA-73D4-F641-A356-ABA79D5CBDF7}" name="関連：参照元変数itemNameKeyClass" dataDxfId="20"/>
+    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0700-000017000000}" name="関連：参照先テーブル" dataDxfId="19"/>
+    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0700-000018000000}" name="関連：参照先カラム" dataDxfId="18"/>
+    <tableColumn id="27" xr3:uid="{00000000-0010-0000-0700-00001B000000}" name="関連：参照先変数名" dataDxfId="17"/>
+    <tableColumn id="30" xr3:uid="{9B4BCFDB-122E-A545-94F1-44AB69834AD9}" name="関連：参照先変数itemNameKeyClass" dataDxfId="16"/>
     <tableColumn id="25" xr3:uid="{00000000-0010-0000-0700-000019000000}" name="関連：eager" dataDxfId="15"/>
     <tableColumn id="17" xr3:uid="{00000000-0010-0000-0700-000011000000}" name="index1" dataDxfId="14"/>
     <tableColumn id="14" xr3:uid="{00000000-0010-0000-0700-00000E000000}" name="index2" dataDxfId="13"/>
@@ -5119,7 +5204,7 @@
         <v>183</v>
       </c>
       <c r="C39" s="15" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="D39" s="4" t="s">
         <v>114</v>
@@ -7072,7 +7157,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AQ119"/>
+  <dimension ref="A1:AS119"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="39.1640625" style="35" bestFit="1" customWidth="1"/>
@@ -7089,60 +7174,61 @@
     <col min="14" max="14" width="8.5" style="37" customWidth="1" outlineLevel="1"/>
     <col min="15" max="16" width="18.33203125" style="37" customWidth="1" outlineLevel="2"/>
     <col min="17" max="17" width="29.5" style="37" customWidth="1" outlineLevel="2"/>
-    <col min="18" max="18" width="29" style="37" customWidth="1" outlineLevel="2"/>
-    <col min="19" max="20" width="18.33203125" style="37" customWidth="1" outlineLevel="2"/>
-    <col min="21" max="21" width="17.1640625" style="37" customWidth="1" outlineLevel="1"/>
-    <col min="22" max="24" width="9.1640625" style="37" customWidth="1" outlineLevel="2"/>
-    <col min="25" max="25" width="9.1640625" style="35" customWidth="1" outlineLevel="2"/>
-    <col min="26" max="31" width="9.1640625" style="38" customWidth="1" outlineLevel="2"/>
-    <col min="32" max="32" width="19.33203125" style="38" customWidth="1" outlineLevel="1"/>
-    <col min="33" max="36" width="33.33203125" style="38" customWidth="1"/>
-    <col min="37" max="37" width="9" style="38" customWidth="1"/>
-    <col min="38" max="16384" width="9" style="38"/>
+    <col min="18" max="18" width="18.1640625" style="37" customWidth="1" outlineLevel="2"/>
+    <col min="19" max="19" width="29" style="37" customWidth="1" outlineLevel="2"/>
+    <col min="20" max="22" width="18.33203125" style="37" customWidth="1" outlineLevel="2"/>
+    <col min="23" max="23" width="17.1640625" style="37" customWidth="1" outlineLevel="1"/>
+    <col min="24" max="26" width="9.1640625" style="37" customWidth="1" outlineLevel="2"/>
+    <col min="27" max="27" width="9.1640625" style="35" customWidth="1" outlineLevel="2"/>
+    <col min="28" max="33" width="9.1640625" style="38" customWidth="1" outlineLevel="2"/>
+    <col min="34" max="34" width="19.33203125" style="38" customWidth="1" outlineLevel="1"/>
+    <col min="35" max="38" width="33.33203125" style="38" customWidth="1"/>
+    <col min="39" max="39" width="9" style="38" customWidth="1"/>
+    <col min="40" max="16384" width="9" style="38"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:43">
+    <row r="1" spans="1:45">
       <c r="A1" s="34" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:43" ht="16" customHeight="1">
-      <c r="AG2" s="72" t="s">
+    <row r="2" spans="1:45" ht="16" customHeight="1">
+      <c r="AI2" s="72" t="s">
         <v>1</v>
       </c>
-      <c r="AH2" s="72" t="s">
+      <c r="AJ2" s="72" t="s">
         <v>2</v>
       </c>
-      <c r="AI2" s="72" t="s">
+      <c r="AK2" s="72" t="s">
         <v>3</v>
       </c>
-      <c r="AJ2" s="72" t="s">
+      <c r="AL2" s="72" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:43">
+    <row r="3" spans="1:45">
       <c r="A3" s="52"/>
-      <c r="AG3" s="32" t="str">
+      <c r="AI3" s="32" t="str">
         <f>IF(各種設定!$G$11=0,"",各種設定!$G$11)</f>
         <v>ja</v>
       </c>
-      <c r="AH3" s="32" t="str">
+      <c r="AJ3" s="32" t="str">
         <f>IF(各種設定!$G$12=0,"",各種設定!$G$12)</f>
         <v/>
       </c>
-      <c r="AI3" s="32" t="str">
+      <c r="AK3" s="32" t="str">
         <f>IF(各種設定!$G$13=0,"",各種設定!$G$13)</f>
         <v/>
       </c>
-      <c r="AJ3" s="32" t="str">
+      <c r="AL3" s="32" t="str">
         <f>IF(各種設定!$G$14=0,"",各種設定!$G$14)</f>
         <v/>
       </c>
     </row>
-    <row r="4" spans="1:43">
+    <row r="4" spans="1:45">
       <c r="A4" s="34"/>
     </row>
-    <row r="5" spans="1:43" s="40" customFormat="1" ht="45" customHeight="1">
+    <row r="5" spans="1:45" s="40" customFormat="1" ht="45" customHeight="1">
       <c r="A5" s="39" t="s">
         <v>5</v>
       </c>
@@ -7195,65 +7281,71 @@
         <v>21</v>
       </c>
       <c r="R5" s="75" t="s">
+        <v>283</v>
+      </c>
+      <c r="S5" s="75" t="s">
         <v>22</v>
       </c>
-      <c r="S5" s="75" t="s">
+      <c r="T5" s="75" t="s">
         <v>23</v>
       </c>
-      <c r="T5" s="75" t="s">
+      <c r="U5" s="75" t="s">
         <v>24</v>
       </c>
-      <c r="U5" s="75" t="s">
+      <c r="V5" s="75" t="s">
+        <v>284</v>
+      </c>
+      <c r="W5" s="75" t="s">
         <v>25</v>
       </c>
-      <c r="V5" s="75" t="s">
+      <c r="X5" s="75" t="s">
         <v>26</v>
       </c>
-      <c r="W5" s="75" t="s">
+      <c r="Y5" s="75" t="s">
         <v>27</v>
       </c>
-      <c r="X5" s="75" t="s">
+      <c r="Z5" s="75" t="s">
         <v>28</v>
       </c>
-      <c r="Y5" s="75" t="s">
+      <c r="AA5" s="75" t="s">
         <v>29</v>
       </c>
-      <c r="Z5" s="75" t="s">
+      <c r="AB5" s="75" t="s">
         <v>30</v>
       </c>
-      <c r="AA5" s="75" t="s">
+      <c r="AC5" s="75" t="s">
         <v>31</v>
       </c>
-      <c r="AB5" s="75" t="s">
+      <c r="AD5" s="75" t="s">
         <v>32</v>
       </c>
-      <c r="AC5" s="75" t="s">
+      <c r="AE5" s="75" t="s">
         <v>33</v>
       </c>
-      <c r="AD5" s="75" t="s">
+      <c r="AF5" s="75" t="s">
         <v>34</v>
       </c>
-      <c r="AE5" s="75" t="s">
+      <c r="AG5" s="75" t="s">
         <v>35</v>
       </c>
-      <c r="AF5" s="75" t="s">
+      <c r="AH5" s="75" t="s">
         <v>36</v>
       </c>
-      <c r="AG5" s="74" t="s">
+      <c r="AI5" s="74" t="s">
         <v>37</v>
       </c>
-      <c r="AH5" s="76" t="s">
+      <c r="AJ5" s="76" t="s">
         <v>38</v>
       </c>
-      <c r="AI5" s="76" t="s">
+      <c r="AK5" s="76" t="s">
         <v>39</v>
       </c>
-      <c r="AJ5" s="76" t="s">
+      <c r="AL5" s="76" t="s">
         <v>40</v>
       </c>
-      <c r="AQ5" s="41"/>
-    </row>
-    <row r="6" spans="1:43" s="40" customFormat="1" ht="14" customHeight="1">
+      <c r="AS5" s="41"/>
+    </row>
+    <row r="6" spans="1:45" s="40" customFormat="1" ht="14" customHeight="1">
       <c r="A6" s="6"/>
       <c r="B6" s="6"/>
       <c r="C6" s="6"/>
@@ -7288,14 +7380,16 @@
       <c r="AC6" s="8"/>
       <c r="AD6" s="8"/>
       <c r="AE6" s="8"/>
-      <c r="AF6" s="25"/>
-      <c r="AG6" s="42"/>
-      <c r="AH6" s="54"/>
+      <c r="AF6" s="8"/>
+      <c r="AG6" s="8"/>
+      <c r="AH6" s="25"/>
       <c r="AI6" s="42"/>
-      <c r="AJ6" s="39"/>
-      <c r="AQ6" s="41"/>
-    </row>
-    <row r="7" spans="1:43" s="40" customFormat="1" ht="14" customHeight="1">
+      <c r="AJ6" s="54"/>
+      <c r="AK6" s="42"/>
+      <c r="AL6" s="39"/>
+      <c r="AS6" s="41"/>
+    </row>
+    <row r="7" spans="1:45" s="40" customFormat="1" ht="14" customHeight="1">
       <c r="A7" s="6"/>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -7330,14 +7424,16 @@
       <c r="AC7" s="8"/>
       <c r="AD7" s="8"/>
       <c r="AE7" s="8"/>
-      <c r="AF7" s="25"/>
-      <c r="AG7" s="6"/>
-      <c r="AH7" s="6"/>
-      <c r="AI7" s="42"/>
-      <c r="AJ7" s="39"/>
-      <c r="AQ7" s="41"/>
-    </row>
-    <row r="8" spans="1:43" s="40" customFormat="1" ht="14" customHeight="1">
+      <c r="AF7" s="8"/>
+      <c r="AG7" s="8"/>
+      <c r="AH7" s="25"/>
+      <c r="AI7" s="6"/>
+      <c r="AJ7" s="6"/>
+      <c r="AK7" s="42"/>
+      <c r="AL7" s="39"/>
+      <c r="AS7" s="41"/>
+    </row>
+    <row r="8" spans="1:45" s="40" customFormat="1" ht="14" customHeight="1">
       <c r="A8" s="6"/>
       <c r="B8" s="6"/>
       <c r="C8" s="6"/>
@@ -7372,14 +7468,16 @@
       <c r="AC8" s="8"/>
       <c r="AD8" s="8"/>
       <c r="AE8" s="8"/>
-      <c r="AF8" s="25"/>
-      <c r="AG8" s="6"/>
-      <c r="AH8" s="6"/>
-      <c r="AI8" s="42"/>
-      <c r="AJ8" s="39"/>
-      <c r="AQ8" s="41"/>
-    </row>
-    <row r="9" spans="1:43" s="40" customFormat="1" ht="14" customHeight="1">
+      <c r="AF8" s="8"/>
+      <c r="AG8" s="8"/>
+      <c r="AH8" s="25"/>
+      <c r="AI8" s="6"/>
+      <c r="AJ8" s="6"/>
+      <c r="AK8" s="42"/>
+      <c r="AL8" s="39"/>
+      <c r="AS8" s="41"/>
+    </row>
+    <row r="9" spans="1:45" s="40" customFormat="1" ht="14" customHeight="1">
       <c r="A9" s="6"/>
       <c r="B9" s="6"/>
       <c r="C9" s="6"/>
@@ -7414,14 +7512,16 @@
       <c r="AC9" s="8"/>
       <c r="AD9" s="8"/>
       <c r="AE9" s="8"/>
-      <c r="AF9" s="25"/>
-      <c r="AG9" s="6"/>
-      <c r="AH9" s="6"/>
-      <c r="AI9" s="42"/>
-      <c r="AJ9" s="39"/>
-      <c r="AQ9" s="41"/>
-    </row>
-    <row r="10" spans="1:43" s="40" customFormat="1" ht="14" customHeight="1">
+      <c r="AF9" s="8"/>
+      <c r="AG9" s="8"/>
+      <c r="AH9" s="25"/>
+      <c r="AI9" s="6"/>
+      <c r="AJ9" s="6"/>
+      <c r="AK9" s="42"/>
+      <c r="AL9" s="39"/>
+      <c r="AS9" s="41"/>
+    </row>
+    <row r="10" spans="1:45" s="40" customFormat="1" ht="14" customHeight="1">
       <c r="A10" s="42"/>
       <c r="B10" s="6"/>
       <c r="C10" s="6"/>
@@ -7445,9 +7545,9 @@
       <c r="R10" s="8"/>
       <c r="S10" s="8"/>
       <c r="T10" s="8"/>
-      <c r="U10" s="9"/>
+      <c r="U10" s="8"/>
       <c r="V10" s="8"/>
-      <c r="W10" s="8"/>
+      <c r="W10" s="9"/>
       <c r="X10" s="8"/>
       <c r="Y10" s="8"/>
       <c r="Z10" s="8"/>
@@ -7456,14 +7556,16 @@
       <c r="AC10" s="8"/>
       <c r="AD10" s="8"/>
       <c r="AE10" s="8"/>
-      <c r="AF10" s="25"/>
-      <c r="AG10" s="6"/>
-      <c r="AH10" s="6"/>
-      <c r="AI10" s="42"/>
-      <c r="AJ10" s="39"/>
-      <c r="AQ10" s="41"/>
-    </row>
-    <row r="11" spans="1:43" s="40" customFormat="1" ht="14" customHeight="1">
+      <c r="AF10" s="8"/>
+      <c r="AG10" s="8"/>
+      <c r="AH10" s="25"/>
+      <c r="AI10" s="6"/>
+      <c r="AJ10" s="6"/>
+      <c r="AK10" s="42"/>
+      <c r="AL10" s="39"/>
+      <c r="AS10" s="41"/>
+    </row>
+    <row r="11" spans="1:45" s="40" customFormat="1" ht="14" customHeight="1">
       <c r="A11" s="42"/>
       <c r="B11" s="6"/>
       <c r="C11" s="6"/>
@@ -7487,9 +7589,9 @@
       <c r="R11" s="8"/>
       <c r="S11" s="8"/>
       <c r="T11" s="8"/>
-      <c r="U11" s="9"/>
+      <c r="U11" s="8"/>
       <c r="V11" s="8"/>
-      <c r="W11" s="8"/>
+      <c r="W11" s="9"/>
       <c r="X11" s="8"/>
       <c r="Y11" s="8"/>
       <c r="Z11" s="8"/>
@@ -7498,14 +7600,16 @@
       <c r="AC11" s="8"/>
       <c r="AD11" s="8"/>
       <c r="AE11" s="8"/>
-      <c r="AF11" s="25"/>
-      <c r="AG11" s="6"/>
-      <c r="AH11" s="6"/>
-      <c r="AI11" s="42"/>
-      <c r="AJ11" s="39"/>
-      <c r="AQ11" s="41"/>
-    </row>
-    <row r="12" spans="1:43" s="40" customFormat="1" ht="14" customHeight="1">
+      <c r="AF11" s="8"/>
+      <c r="AG11" s="8"/>
+      <c r="AH11" s="25"/>
+      <c r="AI11" s="6"/>
+      <c r="AJ11" s="6"/>
+      <c r="AK11" s="42"/>
+      <c r="AL11" s="39"/>
+      <c r="AS11" s="41"/>
+    </row>
+    <row r="12" spans="1:45" s="40" customFormat="1" ht="14" customHeight="1">
       <c r="A12" s="6"/>
       <c r="B12" s="6"/>
       <c r="C12" s="6"/>
@@ -7540,14 +7644,16 @@
       <c r="AC12" s="8"/>
       <c r="AD12" s="8"/>
       <c r="AE12" s="8"/>
-      <c r="AF12" s="25"/>
-      <c r="AG12" s="42"/>
-      <c r="AH12" s="54"/>
+      <c r="AF12" s="8"/>
+      <c r="AG12" s="8"/>
+      <c r="AH12" s="25"/>
       <c r="AI12" s="42"/>
-      <c r="AJ12" s="39"/>
-      <c r="AQ12" s="41"/>
-    </row>
-    <row r="13" spans="1:43">
+      <c r="AJ12" s="54"/>
+      <c r="AK12" s="42"/>
+      <c r="AL12" s="39"/>
+      <c r="AS12" s="41"/>
+    </row>
+    <row r="13" spans="1:45">
       <c r="A13" s="6"/>
       <c r="B13" s="42"/>
       <c r="C13" s="42"/>
@@ -7582,13 +7688,15 @@
       <c r="AC13" s="8"/>
       <c r="AD13" s="8"/>
       <c r="AE13" s="8"/>
-      <c r="AF13" s="25"/>
-      <c r="AG13" s="6"/>
-      <c r="AH13" s="42"/>
-      <c r="AI13" s="42"/>
-      <c r="AJ13" s="39"/>
-    </row>
-    <row r="14" spans="1:43">
+      <c r="AF13" s="8"/>
+      <c r="AG13" s="8"/>
+      <c r="AH13" s="25"/>
+      <c r="AI13" s="6"/>
+      <c r="AJ13" s="42"/>
+      <c r="AK13" s="42"/>
+      <c r="AL13" s="39"/>
+    </row>
+    <row r="14" spans="1:45">
       <c r="A14" s="42"/>
       <c r="B14" s="42"/>
       <c r="C14" s="6"/>
@@ -7623,13 +7731,15 @@
       <c r="AC14" s="8"/>
       <c r="AD14" s="8"/>
       <c r="AE14" s="8"/>
-      <c r="AF14" s="25"/>
-      <c r="AG14" s="42"/>
-      <c r="AH14" s="42"/>
+      <c r="AF14" s="8"/>
+      <c r="AG14" s="8"/>
+      <c r="AH14" s="25"/>
       <c r="AI14" s="42"/>
-      <c r="AJ14" s="39"/>
-    </row>
-    <row r="15" spans="1:43">
+      <c r="AJ14" s="42"/>
+      <c r="AK14" s="42"/>
+      <c r="AL14" s="39"/>
+    </row>
+    <row r="15" spans="1:45">
       <c r="A15" s="42"/>
       <c r="B15" s="42"/>
       <c r="C15" s="6"/>
@@ -7664,13 +7774,15 @@
       <c r="AC15" s="8"/>
       <c r="AD15" s="8"/>
       <c r="AE15" s="8"/>
-      <c r="AF15" s="25"/>
-      <c r="AG15" s="42"/>
-      <c r="AH15" s="42"/>
+      <c r="AF15" s="8"/>
+      <c r="AG15" s="8"/>
+      <c r="AH15" s="25"/>
       <c r="AI15" s="42"/>
-      <c r="AJ15" s="39"/>
-    </row>
-    <row r="16" spans="1:43">
+      <c r="AJ15" s="42"/>
+      <c r="AK15" s="42"/>
+      <c r="AL15" s="39"/>
+    </row>
+    <row r="16" spans="1:45">
       <c r="A16" s="42"/>
       <c r="B16" s="42"/>
       <c r="C16" s="6"/>
@@ -7705,13 +7817,15 @@
       <c r="AC16" s="8"/>
       <c r="AD16" s="8"/>
       <c r="AE16" s="8"/>
-      <c r="AF16" s="25"/>
-      <c r="AG16" s="42"/>
-      <c r="AH16" s="6"/>
+      <c r="AF16" s="8"/>
+      <c r="AG16" s="8"/>
+      <c r="AH16" s="25"/>
       <c r="AI16" s="42"/>
-      <c r="AJ16" s="39"/>
-    </row>
-    <row r="17" spans="1:43">
+      <c r="AJ16" s="6"/>
+      <c r="AK16" s="42"/>
+      <c r="AL16" s="39"/>
+    </row>
+    <row r="17" spans="1:45">
       <c r="A17" s="42"/>
       <c r="B17" s="42"/>
       <c r="C17" s="6"/>
@@ -7746,13 +7860,15 @@
       <c r="AC17" s="8"/>
       <c r="AD17" s="8"/>
       <c r="AE17" s="8"/>
-      <c r="AF17" s="25"/>
-      <c r="AG17" s="42"/>
-      <c r="AH17" s="6"/>
+      <c r="AF17" s="8"/>
+      <c r="AG17" s="8"/>
+      <c r="AH17" s="25"/>
       <c r="AI17" s="42"/>
-      <c r="AJ17" s="39"/>
-    </row>
-    <row r="18" spans="1:43">
+      <c r="AJ17" s="6"/>
+      <c r="AK17" s="42"/>
+      <c r="AL17" s="39"/>
+    </row>
+    <row r="18" spans="1:45">
       <c r="A18" s="42"/>
       <c r="B18" s="42"/>
       <c r="C18" s="42"/>
@@ -7787,13 +7903,15 @@
       <c r="AC18" s="8"/>
       <c r="AD18" s="8"/>
       <c r="AE18" s="8"/>
-      <c r="AF18" s="25"/>
-      <c r="AG18" s="42"/>
-      <c r="AH18" s="6"/>
+      <c r="AF18" s="8"/>
+      <c r="AG18" s="8"/>
+      <c r="AH18" s="25"/>
       <c r="AI18" s="42"/>
-      <c r="AJ18" s="39"/>
-    </row>
-    <row r="19" spans="1:43">
+      <c r="AJ18" s="6"/>
+      <c r="AK18" s="42"/>
+      <c r="AL18" s="39"/>
+    </row>
+    <row r="19" spans="1:45">
       <c r="A19" s="42"/>
       <c r="B19" s="6"/>
       <c r="C19" s="42"/>
@@ -7828,13 +7946,15 @@
       <c r="AC19" s="8"/>
       <c r="AD19" s="8"/>
       <c r="AE19" s="8"/>
-      <c r="AF19" s="25"/>
-      <c r="AG19" s="6"/>
-      <c r="AH19" s="6"/>
-      <c r="AI19" s="42"/>
-      <c r="AJ19" s="39"/>
-    </row>
-    <row r="20" spans="1:43">
+      <c r="AF19" s="8"/>
+      <c r="AG19" s="8"/>
+      <c r="AH19" s="25"/>
+      <c r="AI19" s="6"/>
+      <c r="AJ19" s="6"/>
+      <c r="AK19" s="42"/>
+      <c r="AL19" s="39"/>
+    </row>
+    <row r="20" spans="1:45">
       <c r="A20" s="42"/>
       <c r="B20" s="6"/>
       <c r="C20" s="42"/>
@@ -7869,13 +7989,15 @@
       <c r="AC20" s="8"/>
       <c r="AD20" s="8"/>
       <c r="AE20" s="8"/>
-      <c r="AF20" s="25"/>
-      <c r="AG20" s="42"/>
-      <c r="AH20" s="6"/>
+      <c r="AF20" s="8"/>
+      <c r="AG20" s="8"/>
+      <c r="AH20" s="25"/>
       <c r="AI20" s="42"/>
-      <c r="AJ20" s="39"/>
-    </row>
-    <row r="21" spans="1:43">
+      <c r="AJ20" s="6"/>
+      <c r="AK20" s="42"/>
+      <c r="AL20" s="39"/>
+    </row>
+    <row r="21" spans="1:45">
       <c r="A21" s="42"/>
       <c r="B21" s="6"/>
       <c r="C21" s="42"/>
@@ -7910,13 +8032,15 @@
       <c r="AC21" s="8"/>
       <c r="AD21" s="8"/>
       <c r="AE21" s="8"/>
-      <c r="AF21" s="25"/>
-      <c r="AG21" s="42"/>
-      <c r="AH21" s="6"/>
+      <c r="AF21" s="8"/>
+      <c r="AG21" s="8"/>
+      <c r="AH21" s="25"/>
       <c r="AI21" s="42"/>
-      <c r="AJ21" s="39"/>
-    </row>
-    <row r="22" spans="1:43" s="40" customFormat="1" ht="14" customHeight="1">
+      <c r="AJ21" s="6"/>
+      <c r="AK21" s="42"/>
+      <c r="AL21" s="39"/>
+    </row>
+    <row r="22" spans="1:45" s="40" customFormat="1" ht="14" customHeight="1">
       <c r="A22" s="42"/>
       <c r="B22" s="42"/>
       <c r="C22" s="6"/>
@@ -7940,9 +8064,9 @@
       <c r="R22" s="8"/>
       <c r="S22" s="8"/>
       <c r="T22" s="8"/>
-      <c r="U22" s="9"/>
+      <c r="U22" s="8"/>
       <c r="V22" s="8"/>
-      <c r="W22" s="8"/>
+      <c r="W22" s="9"/>
       <c r="X22" s="8"/>
       <c r="Y22" s="8"/>
       <c r="Z22" s="8"/>
@@ -7951,14 +8075,16 @@
       <c r="AC22" s="8"/>
       <c r="AD22" s="8"/>
       <c r="AE22" s="8"/>
-      <c r="AF22" s="25"/>
-      <c r="AG22" s="42"/>
-      <c r="AH22" s="51"/>
+      <c r="AF22" s="8"/>
+      <c r="AG22" s="8"/>
+      <c r="AH22" s="25"/>
       <c r="AI22" s="42"/>
-      <c r="AJ22" s="39"/>
-      <c r="AQ22" s="41"/>
-    </row>
-    <row r="23" spans="1:43" s="40" customFormat="1" ht="14" customHeight="1">
+      <c r="AJ22" s="51"/>
+      <c r="AK22" s="42"/>
+      <c r="AL22" s="39"/>
+      <c r="AS22" s="41"/>
+    </row>
+    <row r="23" spans="1:45" s="40" customFormat="1" ht="14" customHeight="1">
       <c r="A23" s="42"/>
       <c r="B23" s="42"/>
       <c r="C23" s="6"/>
@@ -7985,22 +8111,24 @@
       <c r="U23" s="8"/>
       <c r="V23" s="8"/>
       <c r="W23" s="8"/>
-      <c r="X23" s="44"/>
-      <c r="Y23" s="44"/>
+      <c r="X23" s="8"/>
+      <c r="Y23" s="8"/>
       <c r="Z23" s="44"/>
       <c r="AA23" s="44"/>
       <c r="AB23" s="44"/>
       <c r="AC23" s="44"/>
       <c r="AD23" s="44"/>
       <c r="AE23" s="44"/>
-      <c r="AF23" s="60"/>
-      <c r="AG23" s="42"/>
-      <c r="AH23" s="51"/>
+      <c r="AF23" s="44"/>
+      <c r="AG23" s="44"/>
+      <c r="AH23" s="60"/>
       <c r="AI23" s="42"/>
-      <c r="AJ23" s="39"/>
-      <c r="AQ23" s="41"/>
-    </row>
-    <row r="24" spans="1:43">
+      <c r="AJ23" s="51"/>
+      <c r="AK23" s="42"/>
+      <c r="AL23" s="39"/>
+      <c r="AS23" s="41"/>
+    </row>
+    <row r="24" spans="1:45">
       <c r="A24" s="42"/>
       <c r="B24" s="6"/>
       <c r="C24" s="6"/>
@@ -8021,11 +8149,11 @@
       <c r="O24" s="8"/>
       <c r="P24" s="8"/>
       <c r="Q24" s="8"/>
-      <c r="R24" s="53"/>
+      <c r="R24" s="8"/>
       <c r="S24" s="53"/>
       <c r="T24" s="53"/>
-      <c r="U24" s="8"/>
-      <c r="V24" s="8"/>
+      <c r="U24" s="53"/>
+      <c r="V24" s="53"/>
       <c r="W24" s="8"/>
       <c r="X24" s="8"/>
       <c r="Y24" s="8"/>
@@ -8035,11 +8163,13 @@
       <c r="AC24" s="8"/>
       <c r="AD24" s="8"/>
       <c r="AE24" s="8"/>
-      <c r="AF24" s="25"/>
-      <c r="AG24" s="6"/>
-      <c r="AH24" s="63"/>
-    </row>
-    <row r="25" spans="1:43">
+      <c r="AF24" s="8"/>
+      <c r="AG24" s="8"/>
+      <c r="AH24" s="25"/>
+      <c r="AI24" s="6"/>
+      <c r="AJ24" s="63"/>
+    </row>
+    <row r="25" spans="1:45">
       <c r="A25" s="42"/>
       <c r="B25" s="42"/>
       <c r="C25" s="6"/>
@@ -8074,13 +8204,15 @@
       <c r="AC25" s="8"/>
       <c r="AD25" s="8"/>
       <c r="AE25" s="8"/>
-      <c r="AF25" s="25"/>
-      <c r="AG25" s="42"/>
-      <c r="AH25" s="6"/>
+      <c r="AF25" s="8"/>
+      <c r="AG25" s="8"/>
+      <c r="AH25" s="25"/>
       <c r="AI25" s="42"/>
-      <c r="AJ25" s="39"/>
-    </row>
-    <row r="26" spans="1:43" s="40" customFormat="1" ht="14" customHeight="1">
+      <c r="AJ25" s="6"/>
+      <c r="AK25" s="42"/>
+      <c r="AL25" s="39"/>
+    </row>
+    <row r="26" spans="1:45" s="40" customFormat="1" ht="14" customHeight="1">
       <c r="A26" s="42"/>
       <c r="B26" s="6"/>
       <c r="C26" s="6"/>
@@ -8107,22 +8239,24 @@
       <c r="U26" s="8"/>
       <c r="V26" s="8"/>
       <c r="W26" s="8"/>
-      <c r="X26" s="44"/>
-      <c r="Y26" s="44"/>
+      <c r="X26" s="8"/>
+      <c r="Y26" s="8"/>
       <c r="Z26" s="44"/>
       <c r="AA26" s="44"/>
       <c r="AB26" s="44"/>
       <c r="AC26" s="44"/>
       <c r="AD26" s="44"/>
       <c r="AE26" s="44"/>
-      <c r="AF26" s="60"/>
-      <c r="AG26" s="42"/>
-      <c r="AH26" s="6"/>
+      <c r="AF26" s="44"/>
+      <c r="AG26" s="44"/>
+      <c r="AH26" s="60"/>
       <c r="AI26" s="42"/>
-      <c r="AJ26" s="39"/>
-      <c r="AQ26" s="41"/>
-    </row>
-    <row r="27" spans="1:43" s="40" customFormat="1" ht="14" customHeight="1">
+      <c r="AJ26" s="6"/>
+      <c r="AK26" s="42"/>
+      <c r="AL26" s="39"/>
+      <c r="AS26" s="41"/>
+    </row>
+    <row r="27" spans="1:45" s="40" customFormat="1" ht="14" customHeight="1">
       <c r="A27" s="42"/>
       <c r="B27" s="51"/>
       <c r="C27" s="6"/>
@@ -8149,22 +8283,24 @@
       <c r="U27" s="8"/>
       <c r="V27" s="8"/>
       <c r="W27" s="8"/>
-      <c r="X27" s="44"/>
-      <c r="Y27" s="44"/>
+      <c r="X27" s="8"/>
+      <c r="Y27" s="8"/>
       <c r="Z27" s="44"/>
       <c r="AA27" s="44"/>
       <c r="AB27" s="44"/>
       <c r="AC27" s="44"/>
       <c r="AD27" s="44"/>
       <c r="AE27" s="44"/>
-      <c r="AF27" s="60"/>
-      <c r="AG27" s="51"/>
-      <c r="AH27" s="6"/>
-      <c r="AI27" s="42"/>
-      <c r="AJ27" s="39"/>
-      <c r="AQ27" s="41"/>
-    </row>
-    <row r="28" spans="1:43" s="40" customFormat="1" ht="14" customHeight="1">
+      <c r="AF27" s="44"/>
+      <c r="AG27" s="44"/>
+      <c r="AH27" s="60"/>
+      <c r="AI27" s="51"/>
+      <c r="AJ27" s="6"/>
+      <c r="AK27" s="42"/>
+      <c r="AL27" s="39"/>
+      <c r="AS27" s="41"/>
+    </row>
+    <row r="28" spans="1:45" s="40" customFormat="1" ht="14" customHeight="1">
       <c r="A28" s="6"/>
       <c r="B28" s="6"/>
       <c r="C28" s="6"/>
@@ -8191,22 +8327,24 @@
       <c r="U28" s="8"/>
       <c r="V28" s="8"/>
       <c r="W28" s="8"/>
-      <c r="X28" s="44"/>
-      <c r="Y28" s="44"/>
+      <c r="X28" s="8"/>
+      <c r="Y28" s="8"/>
       <c r="Z28" s="44"/>
       <c r="AA28" s="44"/>
       <c r="AB28" s="44"/>
       <c r="AC28" s="44"/>
       <c r="AD28" s="44"/>
       <c r="AE28" s="44"/>
-      <c r="AF28" s="60"/>
-      <c r="AG28" s="42"/>
-      <c r="AH28" s="42"/>
+      <c r="AF28" s="44"/>
+      <c r="AG28" s="44"/>
+      <c r="AH28" s="60"/>
       <c r="AI28" s="42"/>
-      <c r="AJ28" s="39"/>
-      <c r="AQ28" s="41"/>
-    </row>
-    <row r="29" spans="1:43" s="40" customFormat="1" ht="14" customHeight="1">
+      <c r="AJ28" s="42"/>
+      <c r="AK28" s="42"/>
+      <c r="AL28" s="39"/>
+      <c r="AS28" s="41"/>
+    </row>
+    <row r="29" spans="1:45" s="40" customFormat="1" ht="14" customHeight="1">
       <c r="A29" s="6"/>
       <c r="B29" s="6"/>
       <c r="C29" s="6"/>
@@ -8227,28 +8365,30 @@
       <c r="O29" s="8"/>
       <c r="P29" s="8"/>
       <c r="Q29" s="8"/>
-      <c r="R29" s="53"/>
+      <c r="R29" s="8"/>
       <c r="S29" s="53"/>
-      <c r="T29" s="8"/>
+      <c r="T29" s="53"/>
       <c r="U29" s="8"/>
       <c r="V29" s="8"/>
       <c r="W29" s="8"/>
-      <c r="X29" s="44"/>
-      <c r="Y29" s="44"/>
+      <c r="X29" s="8"/>
+      <c r="Y29" s="8"/>
       <c r="Z29" s="44"/>
       <c r="AA29" s="44"/>
       <c r="AB29" s="44"/>
       <c r="AC29" s="44"/>
       <c r="AD29" s="44"/>
       <c r="AE29" s="44"/>
-      <c r="AF29" s="60"/>
-      <c r="AG29" s="6"/>
-      <c r="AH29" s="63"/>
-      <c r="AI29" s="42"/>
-      <c r="AJ29" s="39"/>
-      <c r="AQ29" s="41"/>
-    </row>
-    <row r="30" spans="1:43" s="40" customFormat="1" ht="14" customHeight="1">
+      <c r="AF29" s="44"/>
+      <c r="AG29" s="44"/>
+      <c r="AH29" s="60"/>
+      <c r="AI29" s="6"/>
+      <c r="AJ29" s="63"/>
+      <c r="AK29" s="42"/>
+      <c r="AL29" s="39"/>
+      <c r="AS29" s="41"/>
+    </row>
+    <row r="30" spans="1:45" s="40" customFormat="1" ht="14" customHeight="1">
       <c r="A30" s="6"/>
       <c r="B30" s="51"/>
       <c r="C30" s="6"/>
@@ -8275,22 +8415,24 @@
       <c r="U30" s="8"/>
       <c r="V30" s="8"/>
       <c r="W30" s="8"/>
-      <c r="X30" s="44"/>
-      <c r="Y30" s="44"/>
+      <c r="X30" s="8"/>
+      <c r="Y30" s="8"/>
       <c r="Z30" s="44"/>
       <c r="AA30" s="44"/>
       <c r="AB30" s="44"/>
       <c r="AC30" s="44"/>
       <c r="AD30" s="44"/>
       <c r="AE30" s="44"/>
-      <c r="AF30" s="60"/>
-      <c r="AG30" s="51"/>
-      <c r="AH30" s="51"/>
-      <c r="AI30" s="42"/>
-      <c r="AJ30" s="39"/>
-      <c r="AQ30" s="41"/>
-    </row>
-    <row r="31" spans="1:43" s="40" customFormat="1" ht="14" customHeight="1">
+      <c r="AF30" s="44"/>
+      <c r="AG30" s="44"/>
+      <c r="AH30" s="60"/>
+      <c r="AI30" s="51"/>
+      <c r="AJ30" s="51"/>
+      <c r="AK30" s="42"/>
+      <c r="AL30" s="39"/>
+      <c r="AS30" s="41"/>
+    </row>
+    <row r="31" spans="1:45" s="40" customFormat="1" ht="14" customHeight="1">
       <c r="A31" s="6"/>
       <c r="B31" s="51"/>
       <c r="C31" s="6"/>
@@ -8317,22 +8459,24 @@
       <c r="U31" s="8"/>
       <c r="V31" s="8"/>
       <c r="W31" s="8"/>
-      <c r="X31" s="44"/>
-      <c r="Y31" s="44"/>
+      <c r="X31" s="8"/>
+      <c r="Y31" s="8"/>
       <c r="Z31" s="44"/>
       <c r="AA31" s="44"/>
       <c r="AB31" s="44"/>
       <c r="AC31" s="44"/>
       <c r="AD31" s="44"/>
       <c r="AE31" s="44"/>
-      <c r="AF31" s="60"/>
-      <c r="AG31" s="51"/>
-      <c r="AH31" s="51"/>
-      <c r="AI31" s="42"/>
-      <c r="AJ31" s="39"/>
-      <c r="AQ31" s="41"/>
-    </row>
-    <row r="32" spans="1:43">
+      <c r="AF31" s="44"/>
+      <c r="AG31" s="44"/>
+      <c r="AH31" s="60"/>
+      <c r="AI31" s="51"/>
+      <c r="AJ31" s="51"/>
+      <c r="AK31" s="42"/>
+      <c r="AL31" s="39"/>
+      <c r="AS31" s="41"/>
+    </row>
+    <row r="32" spans="1:45">
       <c r="A32" s="42"/>
       <c r="B32" s="6"/>
       <c r="C32" s="6"/>
@@ -8367,13 +8511,15 @@
       <c r="AC32" s="8"/>
       <c r="AD32" s="8"/>
       <c r="AE32" s="8"/>
-      <c r="AF32" s="25"/>
-      <c r="AG32" s="42"/>
-      <c r="AH32" s="54"/>
+      <c r="AF32" s="8"/>
+      <c r="AG32" s="8"/>
+      <c r="AH32" s="25"/>
       <c r="AI32" s="42"/>
-      <c r="AJ32" s="39"/>
-    </row>
-    <row r="33" spans="1:43">
+      <c r="AJ32" s="54"/>
+      <c r="AK32" s="42"/>
+      <c r="AL32" s="39"/>
+    </row>
+    <row r="33" spans="1:45">
       <c r="A33" s="42"/>
       <c r="B33" s="6"/>
       <c r="C33" s="6"/>
@@ -8394,11 +8540,11 @@
       <c r="O33" s="8"/>
       <c r="P33" s="8"/>
       <c r="Q33" s="8"/>
-      <c r="R33" s="53"/>
+      <c r="R33" s="8"/>
       <c r="S33" s="53"/>
       <c r="T33" s="53"/>
-      <c r="U33" s="8"/>
-      <c r="V33" s="8"/>
+      <c r="U33" s="53"/>
+      <c r="V33" s="53"/>
       <c r="W33" s="8"/>
       <c r="X33" s="8"/>
       <c r="Y33" s="8"/>
@@ -8408,13 +8554,15 @@
       <c r="AC33" s="8"/>
       <c r="AD33" s="8"/>
       <c r="AE33" s="8"/>
-      <c r="AF33" s="25"/>
-      <c r="AG33" s="6"/>
-      <c r="AH33" s="63"/>
-      <c r="AI33" s="42"/>
-      <c r="AJ33" s="39"/>
-    </row>
-    <row r="34" spans="1:43" s="40" customFormat="1" ht="14" customHeight="1">
+      <c r="AF33" s="8"/>
+      <c r="AG33" s="8"/>
+      <c r="AH33" s="25"/>
+      <c r="AI33" s="6"/>
+      <c r="AJ33" s="63"/>
+      <c r="AK33" s="42"/>
+      <c r="AL33" s="39"/>
+    </row>
+    <row r="34" spans="1:45" s="40" customFormat="1" ht="14" customHeight="1">
       <c r="A34" s="42"/>
       <c r="B34" s="6"/>
       <c r="C34" s="6"/>
@@ -8449,14 +8597,16 @@
       <c r="AC34" s="8"/>
       <c r="AD34" s="8"/>
       <c r="AE34" s="8"/>
-      <c r="AF34" s="25"/>
-      <c r="AG34" s="6"/>
-      <c r="AH34" s="6"/>
-      <c r="AI34" s="42"/>
-      <c r="AJ34" s="39"/>
-      <c r="AQ34" s="41"/>
-    </row>
-    <row r="35" spans="1:43" s="40" customFormat="1" ht="14" customHeight="1">
+      <c r="AF34" s="8"/>
+      <c r="AG34" s="8"/>
+      <c r="AH34" s="25"/>
+      <c r="AI34" s="6"/>
+      <c r="AJ34" s="6"/>
+      <c r="AK34" s="42"/>
+      <c r="AL34" s="39"/>
+      <c r="AS34" s="41"/>
+    </row>
+    <row r="35" spans="1:45" s="40" customFormat="1" ht="14" customHeight="1">
       <c r="A35" s="42"/>
       <c r="B35" s="6"/>
       <c r="C35" s="6"/>
@@ -8491,14 +8641,16 @@
       <c r="AC35" s="8"/>
       <c r="AD35" s="8"/>
       <c r="AE35" s="8"/>
-      <c r="AF35" s="25"/>
-      <c r="AG35" s="6"/>
-      <c r="AH35" s="6"/>
-      <c r="AI35" s="42"/>
-      <c r="AJ35" s="39"/>
-      <c r="AQ35" s="41"/>
-    </row>
-    <row r="36" spans="1:43" s="40" customFormat="1" ht="14" customHeight="1">
+      <c r="AF35" s="8"/>
+      <c r="AG35" s="8"/>
+      <c r="AH35" s="25"/>
+      <c r="AI35" s="6"/>
+      <c r="AJ35" s="6"/>
+      <c r="AK35" s="42"/>
+      <c r="AL35" s="39"/>
+      <c r="AS35" s="41"/>
+    </row>
+    <row r="36" spans="1:45" s="40" customFormat="1" ht="14" customHeight="1">
       <c r="A36" s="42"/>
       <c r="B36" s="6"/>
       <c r="C36" s="6"/>
@@ -8533,14 +8685,16 @@
       <c r="AC36" s="8"/>
       <c r="AD36" s="8"/>
       <c r="AE36" s="8"/>
-      <c r="AF36" s="25"/>
-      <c r="AG36" s="6"/>
-      <c r="AH36" s="6"/>
-      <c r="AI36" s="42"/>
-      <c r="AJ36" s="39"/>
-      <c r="AQ36" s="41"/>
-    </row>
-    <row r="37" spans="1:43" ht="160" customHeight="1">
+      <c r="AF36" s="8"/>
+      <c r="AG36" s="8"/>
+      <c r="AH36" s="25"/>
+      <c r="AI36" s="6"/>
+      <c r="AJ36" s="6"/>
+      <c r="AK36" s="42"/>
+      <c r="AL36" s="39"/>
+      <c r="AS36" s="41"/>
+    </row>
+    <row r="37" spans="1:45" ht="160" customHeight="1">
       <c r="A37" s="42"/>
       <c r="B37" s="6"/>
       <c r="C37" s="42"/>
@@ -8575,13 +8729,15 @@
       <c r="AC37" s="8"/>
       <c r="AD37" s="8"/>
       <c r="AE37" s="8"/>
-      <c r="AF37" s="25"/>
-      <c r="AG37" s="42"/>
-      <c r="AH37" s="42"/>
+      <c r="AF37" s="8"/>
+      <c r="AG37" s="8"/>
+      <c r="AH37" s="25"/>
       <c r="AI37" s="42"/>
-      <c r="AJ37" s="39"/>
-    </row>
-    <row r="38" spans="1:43">
+      <c r="AJ37" s="42"/>
+      <c r="AK37" s="42"/>
+      <c r="AL37" s="39"/>
+    </row>
+    <row r="38" spans="1:45">
       <c r="A38" s="42"/>
       <c r="B38" s="6"/>
       <c r="C38" s="42"/>
@@ -8616,13 +8772,15 @@
       <c r="AC38" s="8"/>
       <c r="AD38" s="8"/>
       <c r="AE38" s="8"/>
-      <c r="AF38" s="25"/>
-      <c r="AG38" s="42"/>
-      <c r="AH38" s="42"/>
+      <c r="AF38" s="8"/>
+      <c r="AG38" s="8"/>
+      <c r="AH38" s="25"/>
       <c r="AI38" s="42"/>
-      <c r="AJ38" s="39"/>
-    </row>
-    <row r="39" spans="1:43">
+      <c r="AJ38" s="42"/>
+      <c r="AK38" s="42"/>
+      <c r="AL38" s="39"/>
+    </row>
+    <row r="39" spans="1:45">
       <c r="A39" s="42"/>
       <c r="B39" s="6"/>
       <c r="C39" s="42"/>
@@ -8657,13 +8815,15 @@
       <c r="AC39" s="8"/>
       <c r="AD39" s="8"/>
       <c r="AE39" s="8"/>
-      <c r="AF39" s="25"/>
-      <c r="AG39" s="42"/>
-      <c r="AH39" s="63"/>
+      <c r="AF39" s="8"/>
+      <c r="AG39" s="8"/>
+      <c r="AH39" s="25"/>
       <c r="AI39" s="42"/>
-      <c r="AJ39" s="39"/>
-    </row>
-    <row r="40" spans="1:43">
+      <c r="AJ39" s="63"/>
+      <c r="AK39" s="42"/>
+      <c r="AL39" s="39"/>
+    </row>
+    <row r="40" spans="1:45">
       <c r="A40" s="42"/>
       <c r="B40" s="6"/>
       <c r="C40" s="42"/>
@@ -8698,13 +8858,15 @@
       <c r="AC40" s="8"/>
       <c r="AD40" s="8"/>
       <c r="AE40" s="8"/>
-      <c r="AF40" s="25"/>
-      <c r="AG40" s="42"/>
-      <c r="AH40" s="63"/>
+      <c r="AF40" s="8"/>
+      <c r="AG40" s="8"/>
+      <c r="AH40" s="25"/>
       <c r="AI40" s="42"/>
-      <c r="AJ40" s="39"/>
-    </row>
-    <row r="41" spans="1:43">
+      <c r="AJ40" s="63"/>
+      <c r="AK40" s="42"/>
+      <c r="AL40" s="39"/>
+    </row>
+    <row r="41" spans="1:45">
       <c r="A41" s="42"/>
       <c r="B41" s="6"/>
       <c r="C41" s="42"/>
@@ -8739,13 +8901,15 @@
       <c r="AC41" s="8"/>
       <c r="AD41" s="8"/>
       <c r="AE41" s="8"/>
-      <c r="AF41" s="25"/>
-      <c r="AG41" s="42"/>
-      <c r="AH41" s="63"/>
+      <c r="AF41" s="8"/>
+      <c r="AG41" s="8"/>
+      <c r="AH41" s="25"/>
       <c r="AI41" s="42"/>
-      <c r="AJ41" s="39"/>
-    </row>
-    <row r="42" spans="1:43">
+      <c r="AJ41" s="63"/>
+      <c r="AK41" s="42"/>
+      <c r="AL41" s="39"/>
+    </row>
+    <row r="42" spans="1:45">
       <c r="A42" s="42"/>
       <c r="B42" s="6"/>
       <c r="C42" s="42"/>
@@ -8780,13 +8944,15 @@
       <c r="AC42" s="8"/>
       <c r="AD42" s="8"/>
       <c r="AE42" s="8"/>
-      <c r="AF42" s="25"/>
-      <c r="AG42" s="42"/>
-      <c r="AH42" s="63"/>
+      <c r="AF42" s="8"/>
+      <c r="AG42" s="8"/>
+      <c r="AH42" s="25"/>
       <c r="AI42" s="42"/>
-      <c r="AJ42" s="39"/>
-    </row>
-    <row r="43" spans="1:43">
+      <c r="AJ42" s="63"/>
+      <c r="AK42" s="42"/>
+      <c r="AL42" s="39"/>
+    </row>
+    <row r="43" spans="1:45">
       <c r="A43" s="42"/>
       <c r="B43" s="6"/>
       <c r="C43" s="6"/>
@@ -8821,13 +8987,15 @@
       <c r="AC43" s="8"/>
       <c r="AD43" s="8"/>
       <c r="AE43" s="8"/>
-      <c r="AF43" s="25"/>
-      <c r="AG43" s="42"/>
-      <c r="AH43" s="54"/>
+      <c r="AF43" s="8"/>
+      <c r="AG43" s="8"/>
+      <c r="AH43" s="25"/>
       <c r="AI43" s="42"/>
-      <c r="AJ43" s="39"/>
-    </row>
-    <row r="44" spans="1:43">
+      <c r="AJ43" s="54"/>
+      <c r="AK43" s="42"/>
+      <c r="AL43" s="39"/>
+    </row>
+    <row r="44" spans="1:45">
       <c r="A44" s="42"/>
       <c r="B44" s="6"/>
       <c r="C44" s="6"/>
@@ -8848,11 +9016,11 @@
       <c r="O44" s="8"/>
       <c r="P44" s="8"/>
       <c r="Q44" s="8"/>
-      <c r="R44" s="42"/>
-      <c r="S44" s="53"/>
+      <c r="R44" s="8"/>
+      <c r="S44" s="42"/>
       <c r="T44" s="53"/>
-      <c r="U44" s="8"/>
-      <c r="V44" s="8"/>
+      <c r="U44" s="53"/>
+      <c r="V44" s="53"/>
       <c r="W44" s="8"/>
       <c r="X44" s="8"/>
       <c r="Y44" s="8"/>
@@ -8862,13 +9030,15 @@
       <c r="AC44" s="8"/>
       <c r="AD44" s="8"/>
       <c r="AE44" s="8"/>
-      <c r="AF44" s="25"/>
-      <c r="AG44" s="6"/>
-      <c r="AH44" s="63"/>
-      <c r="AI44" s="42"/>
-      <c r="AJ44" s="39"/>
-    </row>
-    <row r="45" spans="1:43">
+      <c r="AF44" s="8"/>
+      <c r="AG44" s="8"/>
+      <c r="AH44" s="25"/>
+      <c r="AI44" s="6"/>
+      <c r="AJ44" s="63"/>
+      <c r="AK44" s="42"/>
+      <c r="AL44" s="39"/>
+    </row>
+    <row r="45" spans="1:45">
       <c r="A45" s="42"/>
       <c r="B45" s="6"/>
       <c r="C45" s="6"/>
@@ -8889,11 +9059,11 @@
       <c r="O45" s="8"/>
       <c r="P45" s="8"/>
       <c r="Q45" s="8"/>
-      <c r="R45" s="53"/>
+      <c r="R45" s="8"/>
       <c r="S45" s="53"/>
       <c r="T45" s="53"/>
-      <c r="U45" s="8"/>
-      <c r="V45" s="8"/>
+      <c r="U45" s="53"/>
+      <c r="V45" s="53"/>
       <c r="W45" s="8"/>
       <c r="X45" s="8"/>
       <c r="Y45" s="8"/>
@@ -8903,13 +9073,15 @@
       <c r="AC45" s="8"/>
       <c r="AD45" s="8"/>
       <c r="AE45" s="8"/>
-      <c r="AF45" s="25"/>
-      <c r="AG45" s="42"/>
-      <c r="AH45" s="63"/>
+      <c r="AF45" s="8"/>
+      <c r="AG45" s="8"/>
+      <c r="AH45" s="25"/>
       <c r="AI45" s="42"/>
-      <c r="AJ45" s="39"/>
-    </row>
-    <row r="46" spans="1:43">
+      <c r="AJ45" s="63"/>
+      <c r="AK45" s="42"/>
+      <c r="AL45" s="39"/>
+    </row>
+    <row r="46" spans="1:45">
       <c r="A46" s="42"/>
       <c r="B46" s="6"/>
       <c r="C46" s="6"/>
@@ -8944,13 +9116,15 @@
       <c r="AC46" s="8"/>
       <c r="AD46" s="8"/>
       <c r="AE46" s="8"/>
-      <c r="AF46" s="25"/>
-      <c r="AG46" s="42"/>
-      <c r="AH46" s="63"/>
+      <c r="AF46" s="8"/>
+      <c r="AG46" s="8"/>
+      <c r="AH46" s="25"/>
       <c r="AI46" s="42"/>
-      <c r="AJ46" s="39"/>
-    </row>
-    <row r="47" spans="1:43">
+      <c r="AJ46" s="63"/>
+      <c r="AK46" s="42"/>
+      <c r="AL46" s="39"/>
+    </row>
+    <row r="47" spans="1:45">
       <c r="A47" s="42"/>
       <c r="B47" s="61"/>
       <c r="C47" s="42"/>
@@ -8985,13 +9159,15 @@
       <c r="AC47" s="8"/>
       <c r="AD47" s="8"/>
       <c r="AE47" s="8"/>
-      <c r="AF47" s="25"/>
-      <c r="AG47" s="61"/>
-      <c r="AH47" s="61"/>
-      <c r="AI47" s="42"/>
-      <c r="AJ47" s="39"/>
-    </row>
-    <row r="48" spans="1:43">
+      <c r="AF47" s="8"/>
+      <c r="AG47" s="8"/>
+      <c r="AH47" s="25"/>
+      <c r="AI47" s="61"/>
+      <c r="AJ47" s="61"/>
+      <c r="AK47" s="42"/>
+      <c r="AL47" s="39"/>
+    </row>
+    <row r="48" spans="1:45">
       <c r="A48" s="42"/>
       <c r="B48" s="6"/>
       <c r="C48" s="6"/>
@@ -9026,13 +9202,15 @@
       <c r="AC48" s="8"/>
       <c r="AD48" s="8"/>
       <c r="AE48" s="8"/>
-      <c r="AF48" s="25"/>
-      <c r="AG48" s="42"/>
-      <c r="AH48" s="54"/>
+      <c r="AF48" s="8"/>
+      <c r="AG48" s="8"/>
+      <c r="AH48" s="25"/>
       <c r="AI48" s="42"/>
-      <c r="AJ48" s="39"/>
-    </row>
-    <row r="49" spans="1:36">
+      <c r="AJ48" s="54"/>
+      <c r="AK48" s="42"/>
+      <c r="AL48" s="39"/>
+    </row>
+    <row r="49" spans="1:38">
       <c r="A49" s="42"/>
       <c r="B49" s="6"/>
       <c r="C49" s="6"/>
@@ -9053,11 +9231,11 @@
       <c r="O49" s="8"/>
       <c r="P49" s="8"/>
       <c r="Q49" s="8"/>
-      <c r="R49" s="53"/>
+      <c r="R49" s="8"/>
       <c r="S49" s="53"/>
       <c r="T49" s="53"/>
-      <c r="U49" s="8"/>
-      <c r="V49" s="8"/>
+      <c r="U49" s="53"/>
+      <c r="V49" s="53"/>
       <c r="W49" s="8"/>
       <c r="X49" s="8"/>
       <c r="Y49" s="8"/>
@@ -9067,13 +9245,15 @@
       <c r="AC49" s="8"/>
       <c r="AD49" s="8"/>
       <c r="AE49" s="8"/>
-      <c r="AF49" s="25"/>
-      <c r="AG49" s="6"/>
-      <c r="AH49" s="63"/>
-      <c r="AI49" s="42"/>
-      <c r="AJ49" s="39"/>
-    </row>
-    <row r="50" spans="1:36">
+      <c r="AF49" s="8"/>
+      <c r="AG49" s="8"/>
+      <c r="AH49" s="25"/>
+      <c r="AI49" s="6"/>
+      <c r="AJ49" s="63"/>
+      <c r="AK49" s="42"/>
+      <c r="AL49" s="39"/>
+    </row>
+    <row r="50" spans="1:38">
       <c r="A50" s="42"/>
       <c r="B50" s="6"/>
       <c r="C50" s="6"/>
@@ -9094,9 +9274,9 @@
       <c r="O50" s="8"/>
       <c r="P50" s="8"/>
       <c r="Q50" s="8"/>
-      <c r="R50" s="53"/>
+      <c r="R50" s="8"/>
       <c r="S50" s="53"/>
-      <c r="T50" s="8"/>
+      <c r="T50" s="53"/>
       <c r="U50" s="8"/>
       <c r="V50" s="8"/>
       <c r="W50" s="8"/>
@@ -9108,13 +9288,15 @@
       <c r="AC50" s="8"/>
       <c r="AD50" s="8"/>
       <c r="AE50" s="8"/>
-      <c r="AF50" s="25"/>
-      <c r="AG50" s="42"/>
-      <c r="AH50" s="63"/>
+      <c r="AF50" s="8"/>
+      <c r="AG50" s="8"/>
+      <c r="AH50" s="25"/>
       <c r="AI50" s="42"/>
-      <c r="AJ50" s="39"/>
-    </row>
-    <row r="51" spans="1:36">
+      <c r="AJ50" s="63"/>
+      <c r="AK50" s="42"/>
+      <c r="AL50" s="39"/>
+    </row>
+    <row r="51" spans="1:38">
       <c r="A51" s="42"/>
       <c r="B51" s="6"/>
       <c r="C51" s="6"/>
@@ -9149,13 +9331,15 @@
       <c r="AC51" s="8"/>
       <c r="AD51" s="8"/>
       <c r="AE51" s="8"/>
-      <c r="AF51" s="25"/>
-      <c r="AG51" s="6"/>
-      <c r="AH51" s="63"/>
-      <c r="AI51" s="42"/>
-      <c r="AJ51" s="39"/>
-    </row>
-    <row r="52" spans="1:36">
+      <c r="AF51" s="8"/>
+      <c r="AG51" s="8"/>
+      <c r="AH51" s="25"/>
+      <c r="AI51" s="6"/>
+      <c r="AJ51" s="63"/>
+      <c r="AK51" s="42"/>
+      <c r="AL51" s="39"/>
+    </row>
+    <row r="52" spans="1:38">
       <c r="A52" s="42"/>
       <c r="B52" s="6"/>
       <c r="C52" s="6"/>
@@ -9190,13 +9374,15 @@
       <c r="AC52" s="8"/>
       <c r="AD52" s="8"/>
       <c r="AE52" s="8"/>
-      <c r="AF52" s="25"/>
-      <c r="AG52" s="6"/>
-      <c r="AH52" s="63"/>
-      <c r="AI52" s="42"/>
-      <c r="AJ52" s="39"/>
-    </row>
-    <row r="53" spans="1:36">
+      <c r="AF52" s="8"/>
+      <c r="AG52" s="8"/>
+      <c r="AH52" s="25"/>
+      <c r="AI52" s="6"/>
+      <c r="AJ52" s="63"/>
+      <c r="AK52" s="42"/>
+      <c r="AL52" s="39"/>
+    </row>
+    <row r="53" spans="1:38">
       <c r="A53" s="42"/>
       <c r="B53" s="6"/>
       <c r="C53" s="6"/>
@@ -9231,13 +9417,15 @@
       <c r="AC53" s="8"/>
       <c r="AD53" s="8"/>
       <c r="AE53" s="8"/>
-      <c r="AF53" s="25"/>
-      <c r="AG53" s="42"/>
-      <c r="AH53" s="54"/>
+      <c r="AF53" s="8"/>
+      <c r="AG53" s="8"/>
+      <c r="AH53" s="25"/>
       <c r="AI53" s="42"/>
-      <c r="AJ53" s="39"/>
-    </row>
-    <row r="54" spans="1:36">
+      <c r="AJ53" s="54"/>
+      <c r="AK53" s="42"/>
+      <c r="AL53" s="39"/>
+    </row>
+    <row r="54" spans="1:38">
       <c r="A54" s="42"/>
       <c r="B54" s="6"/>
       <c r="C54" s="6"/>
@@ -9258,11 +9446,11 @@
       <c r="O54" s="8"/>
       <c r="P54" s="8"/>
       <c r="Q54" s="8"/>
-      <c r="R54" s="53"/>
+      <c r="R54" s="8"/>
       <c r="S54" s="53"/>
       <c r="T54" s="53"/>
-      <c r="U54" s="8"/>
-      <c r="V54" s="8"/>
+      <c r="U54" s="53"/>
+      <c r="V54" s="53"/>
       <c r="W54" s="8"/>
       <c r="X54" s="8"/>
       <c r="Y54" s="8"/>
@@ -9272,13 +9460,15 @@
       <c r="AC54" s="8"/>
       <c r="AD54" s="8"/>
       <c r="AE54" s="8"/>
-      <c r="AF54" s="25"/>
-      <c r="AG54" s="6"/>
-      <c r="AH54" s="63"/>
-      <c r="AI54" s="42"/>
-      <c r="AJ54" s="39"/>
-    </row>
-    <row r="55" spans="1:36">
+      <c r="AF54" s="8"/>
+      <c r="AG54" s="8"/>
+      <c r="AH54" s="25"/>
+      <c r="AI54" s="6"/>
+      <c r="AJ54" s="63"/>
+      <c r="AK54" s="42"/>
+      <c r="AL54" s="39"/>
+    </row>
+    <row r="55" spans="1:38">
       <c r="A55" s="42"/>
       <c r="B55" s="6"/>
       <c r="C55" s="42"/>
@@ -9313,13 +9503,15 @@
       <c r="AC55" s="8"/>
       <c r="AD55" s="8"/>
       <c r="AE55" s="8"/>
-      <c r="AF55" s="25"/>
-      <c r="AG55" s="42"/>
-      <c r="AH55" s="42"/>
+      <c r="AF55" s="8"/>
+      <c r="AG55" s="8"/>
+      <c r="AH55" s="25"/>
       <c r="AI55" s="42"/>
-      <c r="AJ55" s="39"/>
-    </row>
-    <row r="56" spans="1:36">
+      <c r="AJ55" s="42"/>
+      <c r="AK55" s="42"/>
+      <c r="AL55" s="39"/>
+    </row>
+    <row r="56" spans="1:38">
       <c r="A56" s="42"/>
       <c r="B56" s="42"/>
       <c r="C56" s="42"/>
@@ -9340,11 +9532,11 @@
       <c r="O56" s="8"/>
       <c r="P56" s="8"/>
       <c r="Q56" s="8"/>
-      <c r="R56" s="53"/>
+      <c r="R56" s="8"/>
       <c r="S56" s="53"/>
       <c r="T56" s="53"/>
-      <c r="U56" s="8"/>
-      <c r="V56" s="8"/>
+      <c r="U56" s="53"/>
+      <c r="V56" s="53"/>
       <c r="W56" s="8"/>
       <c r="X56" s="8"/>
       <c r="Y56" s="8"/>
@@ -9354,13 +9546,15 @@
       <c r="AC56" s="8"/>
       <c r="AD56" s="8"/>
       <c r="AE56" s="8"/>
-      <c r="AF56" s="25"/>
-      <c r="AG56" s="42"/>
-      <c r="AH56" s="42"/>
+      <c r="AF56" s="8"/>
+      <c r="AG56" s="8"/>
+      <c r="AH56" s="25"/>
       <c r="AI56" s="42"/>
-      <c r="AJ56" s="39"/>
-    </row>
-    <row r="57" spans="1:36">
+      <c r="AJ56" s="42"/>
+      <c r="AK56" s="42"/>
+      <c r="AL56" s="39"/>
+    </row>
+    <row r="57" spans="1:38">
       <c r="A57" s="42"/>
       <c r="B57" s="6"/>
       <c r="C57" s="42"/>
@@ -9395,13 +9589,15 @@
       <c r="AC57" s="8"/>
       <c r="AD57" s="8"/>
       <c r="AE57" s="8"/>
-      <c r="AF57" s="25"/>
-      <c r="AG57" s="42"/>
-      <c r="AH57" s="42"/>
+      <c r="AF57" s="8"/>
+      <c r="AG57" s="8"/>
+      <c r="AH57" s="25"/>
       <c r="AI57" s="42"/>
-      <c r="AJ57" s="39"/>
-    </row>
-    <row r="58" spans="1:36">
+      <c r="AJ57" s="42"/>
+      <c r="AK57" s="42"/>
+      <c r="AL57" s="39"/>
+    </row>
+    <row r="58" spans="1:38">
       <c r="A58" s="42"/>
       <c r="B58" s="6"/>
       <c r="C58" s="42"/>
@@ -9436,13 +9632,15 @@
       <c r="AC58" s="8"/>
       <c r="AD58" s="8"/>
       <c r="AE58" s="8"/>
-      <c r="AF58" s="25"/>
-      <c r="AG58" s="42"/>
-      <c r="AH58" s="63"/>
+      <c r="AF58" s="8"/>
+      <c r="AG58" s="8"/>
+      <c r="AH58" s="25"/>
       <c r="AI58" s="42"/>
-      <c r="AJ58" s="39"/>
-    </row>
-    <row r="59" spans="1:36">
+      <c r="AJ58" s="63"/>
+      <c r="AK58" s="42"/>
+      <c r="AL58" s="39"/>
+    </row>
+    <row r="59" spans="1:38">
       <c r="A59" s="42"/>
       <c r="B59" s="6"/>
       <c r="C59" s="42"/>
@@ -9477,13 +9675,15 @@
       <c r="AC59" s="8"/>
       <c r="AD59" s="8"/>
       <c r="AE59" s="8"/>
-      <c r="AF59" s="25"/>
-      <c r="AG59" s="42"/>
-      <c r="AH59" s="63"/>
+      <c r="AF59" s="8"/>
+      <c r="AG59" s="8"/>
+      <c r="AH59" s="25"/>
       <c r="AI59" s="42"/>
-      <c r="AJ59" s="39"/>
-    </row>
-    <row r="60" spans="1:36">
+      <c r="AJ59" s="63"/>
+      <c r="AK59" s="42"/>
+      <c r="AL59" s="39"/>
+    </row>
+    <row r="60" spans="1:38">
       <c r="A60" s="42"/>
       <c r="B60" s="6"/>
       <c r="C60" s="6"/>
@@ -9518,13 +9718,15 @@
       <c r="AC60" s="8"/>
       <c r="AD60" s="8"/>
       <c r="AE60" s="8"/>
-      <c r="AF60" s="25"/>
-      <c r="AG60" s="42"/>
-      <c r="AH60" s="54"/>
+      <c r="AF60" s="8"/>
+      <c r="AG60" s="8"/>
+      <c r="AH60" s="25"/>
       <c r="AI60" s="42"/>
-      <c r="AJ60" s="39"/>
-    </row>
-    <row r="61" spans="1:36">
+      <c r="AJ60" s="54"/>
+      <c r="AK60" s="42"/>
+      <c r="AL60" s="39"/>
+    </row>
+    <row r="61" spans="1:38">
       <c r="A61" s="42"/>
       <c r="B61" s="6"/>
       <c r="C61" s="6"/>
@@ -9545,11 +9747,11 @@
       <c r="O61" s="8"/>
       <c r="P61" s="8"/>
       <c r="Q61" s="8"/>
-      <c r="R61" s="53"/>
+      <c r="R61" s="8"/>
       <c r="S61" s="53"/>
       <c r="T61" s="53"/>
-      <c r="U61" s="8"/>
-      <c r="V61" s="8"/>
+      <c r="U61" s="53"/>
+      <c r="V61" s="53"/>
       <c r="W61" s="8"/>
       <c r="X61" s="8"/>
       <c r="Y61" s="8"/>
@@ -9559,13 +9761,15 @@
       <c r="AC61" s="8"/>
       <c r="AD61" s="8"/>
       <c r="AE61" s="8"/>
-      <c r="AF61" s="25"/>
-      <c r="AG61" s="6"/>
-      <c r="AH61" s="63"/>
-      <c r="AI61" s="42"/>
-      <c r="AJ61" s="39"/>
-    </row>
-    <row r="62" spans="1:36">
+      <c r="AF61" s="8"/>
+      <c r="AG61" s="8"/>
+      <c r="AH61" s="25"/>
+      <c r="AI61" s="6"/>
+      <c r="AJ61" s="63"/>
+      <c r="AK61" s="42"/>
+      <c r="AL61" s="39"/>
+    </row>
+    <row r="62" spans="1:38">
       <c r="A62" s="42"/>
       <c r="B62" s="42"/>
       <c r="C62" s="42"/>
@@ -9586,11 +9790,11 @@
       <c r="O62" s="8"/>
       <c r="P62" s="8"/>
       <c r="Q62" s="8"/>
-      <c r="R62" s="53"/>
+      <c r="R62" s="8"/>
       <c r="S62" s="53"/>
       <c r="T62" s="53"/>
-      <c r="U62" s="8"/>
-      <c r="V62" s="8"/>
+      <c r="U62" s="53"/>
+      <c r="V62" s="53"/>
       <c r="W62" s="8"/>
       <c r="X62" s="8"/>
       <c r="Y62" s="8"/>
@@ -9600,13 +9804,15 @@
       <c r="AC62" s="8"/>
       <c r="AD62" s="8"/>
       <c r="AE62" s="8"/>
-      <c r="AF62" s="25"/>
-      <c r="AG62" s="42"/>
-      <c r="AH62" s="42"/>
+      <c r="AF62" s="8"/>
+      <c r="AG62" s="8"/>
+      <c r="AH62" s="25"/>
       <c r="AI62" s="42"/>
-      <c r="AJ62" s="39"/>
-    </row>
-    <row r="63" spans="1:36">
+      <c r="AJ62" s="42"/>
+      <c r="AK62" s="42"/>
+      <c r="AL62" s="39"/>
+    </row>
+    <row r="63" spans="1:38">
       <c r="A63" s="42"/>
       <c r="B63" s="42"/>
       <c r="C63" s="42"/>
@@ -9627,9 +9833,9 @@
       <c r="O63" s="8"/>
       <c r="P63" s="8"/>
       <c r="Q63" s="8"/>
-      <c r="R63" s="53"/>
+      <c r="R63" s="8"/>
       <c r="S63" s="53"/>
-      <c r="T63" s="8"/>
+      <c r="T63" s="53"/>
       <c r="U63" s="8"/>
       <c r="V63" s="8"/>
       <c r="W63" s="8"/>
@@ -9641,13 +9847,15 @@
       <c r="AC63" s="8"/>
       <c r="AD63" s="8"/>
       <c r="AE63" s="8"/>
-      <c r="AF63" s="25"/>
-      <c r="AG63" s="42"/>
-      <c r="AH63" s="42"/>
+      <c r="AF63" s="8"/>
+      <c r="AG63" s="8"/>
+      <c r="AH63" s="25"/>
       <c r="AI63" s="42"/>
-      <c r="AJ63" s="39"/>
-    </row>
-    <row r="64" spans="1:36">
+      <c r="AJ63" s="42"/>
+      <c r="AK63" s="42"/>
+      <c r="AL63" s="39"/>
+    </row>
+    <row r="64" spans="1:38">
       <c r="A64" s="42"/>
       <c r="B64" s="42"/>
       <c r="C64" s="42"/>
@@ -9682,13 +9890,15 @@
       <c r="AC64" s="8"/>
       <c r="AD64" s="8"/>
       <c r="AE64" s="8"/>
-      <c r="AF64" s="25"/>
-      <c r="AG64" s="42"/>
-      <c r="AH64" s="42"/>
+      <c r="AF64" s="8"/>
+      <c r="AG64" s="8"/>
+      <c r="AH64" s="25"/>
       <c r="AI64" s="42"/>
-      <c r="AJ64" s="39"/>
-    </row>
-    <row r="65" spans="1:36" ht="16" customHeight="1">
+      <c r="AJ64" s="42"/>
+      <c r="AK64" s="42"/>
+      <c r="AL64" s="39"/>
+    </row>
+    <row r="65" spans="1:38" ht="16" customHeight="1">
       <c r="A65" s="42"/>
       <c r="B65" s="42"/>
       <c r="C65" s="42"/>
@@ -9715,21 +9925,23 @@
       <c r="U65" s="8"/>
       <c r="V65" s="8"/>
       <c r="W65" s="8"/>
-      <c r="X65" s="39"/>
-      <c r="Y65" s="39"/>
+      <c r="X65" s="8"/>
+      <c r="Y65" s="8"/>
       <c r="Z65" s="39"/>
       <c r="AA65" s="39"/>
       <c r="AB65" s="39"/>
       <c r="AC65" s="39"/>
       <c r="AD65" s="39"/>
       <c r="AE65" s="39"/>
-      <c r="AF65" s="48"/>
-      <c r="AG65" s="42"/>
-      <c r="AH65" s="6"/>
+      <c r="AF65" s="39"/>
+      <c r="AG65" s="39"/>
+      <c r="AH65" s="48"/>
       <c r="AI65" s="42"/>
-      <c r="AJ65" s="39"/>
-    </row>
-    <row r="66" spans="1:36">
+      <c r="AJ65" s="6"/>
+      <c r="AK65" s="42"/>
+      <c r="AL65" s="39"/>
+    </row>
+    <row r="66" spans="1:38">
       <c r="A66" s="42"/>
       <c r="B66" s="42"/>
       <c r="C66" s="42"/>
@@ -9756,21 +9968,23 @@
       <c r="U66" s="8"/>
       <c r="V66" s="8"/>
       <c r="W66" s="8"/>
-      <c r="X66" s="39"/>
-      <c r="Y66" s="39"/>
+      <c r="X66" s="8"/>
+      <c r="Y66" s="8"/>
       <c r="Z66" s="39"/>
       <c r="AA66" s="39"/>
       <c r="AB66" s="39"/>
       <c r="AC66" s="39"/>
       <c r="AD66" s="39"/>
       <c r="AE66" s="39"/>
-      <c r="AF66" s="48"/>
-      <c r="AG66" s="42"/>
-      <c r="AH66" s="6"/>
+      <c r="AF66" s="39"/>
+      <c r="AG66" s="39"/>
+      <c r="AH66" s="48"/>
       <c r="AI66" s="42"/>
-      <c r="AJ66" s="39"/>
-    </row>
-    <row r="67" spans="1:36">
+      <c r="AJ66" s="6"/>
+      <c r="AK66" s="42"/>
+      <c r="AL66" s="39"/>
+    </row>
+    <row r="67" spans="1:38">
       <c r="A67" s="42"/>
       <c r="B67" s="42"/>
       <c r="C67" s="42"/>
@@ -9797,21 +10011,23 @@
       <c r="U67" s="8"/>
       <c r="V67" s="8"/>
       <c r="W67" s="8"/>
-      <c r="X67" s="39"/>
-      <c r="Y67" s="39"/>
+      <c r="X67" s="8"/>
+      <c r="Y67" s="8"/>
       <c r="Z67" s="39"/>
       <c r="AA67" s="39"/>
       <c r="AB67" s="39"/>
       <c r="AC67" s="39"/>
       <c r="AD67" s="39"/>
       <c r="AE67" s="39"/>
-      <c r="AF67" s="48"/>
-      <c r="AG67" s="42"/>
-      <c r="AH67" s="6"/>
+      <c r="AF67" s="39"/>
+      <c r="AG67" s="39"/>
+      <c r="AH67" s="48"/>
       <c r="AI67" s="42"/>
-      <c r="AJ67" s="39"/>
-    </row>
-    <row r="68" spans="1:36" ht="48" customHeight="1">
+      <c r="AJ67" s="6"/>
+      <c r="AK67" s="42"/>
+      <c r="AL67" s="39"/>
+    </row>
+    <row r="68" spans="1:38" ht="48" customHeight="1">
       <c r="A68" s="42"/>
       <c r="B68" s="61"/>
       <c r="C68" s="61"/>
@@ -9832,11 +10048,11 @@
       <c r="O68" s="8"/>
       <c r="P68" s="8"/>
       <c r="Q68" s="8"/>
-      <c r="R68" s="53"/>
+      <c r="R68" s="8"/>
       <c r="S68" s="53"/>
       <c r="T68" s="53"/>
-      <c r="U68" s="8"/>
-      <c r="V68" s="8"/>
+      <c r="U68" s="53"/>
+      <c r="V68" s="53"/>
       <c r="W68" s="8"/>
       <c r="X68" s="8"/>
       <c r="Y68" s="8"/>
@@ -9846,13 +10062,15 @@
       <c r="AC68" s="8"/>
       <c r="AD68" s="8"/>
       <c r="AE68" s="8"/>
-      <c r="AF68" s="25"/>
-      <c r="AG68" s="61"/>
-      <c r="AH68" s="42"/>
-      <c r="AI68" s="42"/>
-      <c r="AJ68" s="39"/>
-    </row>
-    <row r="69" spans="1:36" ht="240" customHeight="1">
+      <c r="AF68" s="8"/>
+      <c r="AG68" s="8"/>
+      <c r="AH68" s="25"/>
+      <c r="AI68" s="61"/>
+      <c r="AJ68" s="42"/>
+      <c r="AK68" s="42"/>
+      <c r="AL68" s="39"/>
+    </row>
+    <row r="69" spans="1:38" ht="240" customHeight="1">
       <c r="A69" s="42"/>
       <c r="B69" s="42"/>
       <c r="C69" s="42"/>
@@ -9887,13 +10105,15 @@
       <c r="AC69" s="8"/>
       <c r="AD69" s="8"/>
       <c r="AE69" s="8"/>
-      <c r="AF69" s="48"/>
-      <c r="AG69" s="42"/>
-      <c r="AH69" s="42"/>
+      <c r="AF69" s="8"/>
+      <c r="AG69" s="8"/>
+      <c r="AH69" s="48"/>
       <c r="AI69" s="42"/>
-      <c r="AJ69" s="39"/>
-    </row>
-    <row r="70" spans="1:36">
+      <c r="AJ69" s="42"/>
+      <c r="AK69" s="42"/>
+      <c r="AL69" s="39"/>
+    </row>
+    <row r="70" spans="1:38">
       <c r="A70" s="42"/>
       <c r="B70" s="42"/>
       <c r="C70" s="42"/>
@@ -9914,11 +10134,11 @@
       <c r="O70" s="8"/>
       <c r="P70" s="8"/>
       <c r="Q70" s="8"/>
-      <c r="R70" s="53"/>
+      <c r="R70" s="8"/>
       <c r="S70" s="53"/>
       <c r="T70" s="53"/>
-      <c r="U70" s="8"/>
-      <c r="V70" s="8"/>
+      <c r="U70" s="53"/>
+      <c r="V70" s="53"/>
       <c r="W70" s="8"/>
       <c r="X70" s="8"/>
       <c r="Y70" s="8"/>
@@ -9928,13 +10148,15 @@
       <c r="AC70" s="8"/>
       <c r="AD70" s="8"/>
       <c r="AE70" s="8"/>
-      <c r="AF70" s="25"/>
-      <c r="AG70" s="42"/>
-      <c r="AH70" s="42"/>
+      <c r="AF70" s="8"/>
+      <c r="AG70" s="8"/>
+      <c r="AH70" s="25"/>
       <c r="AI70" s="42"/>
-      <c r="AJ70" s="39"/>
-    </row>
-    <row r="71" spans="1:36">
+      <c r="AJ70" s="42"/>
+      <c r="AK70" s="42"/>
+      <c r="AL70" s="39"/>
+    </row>
+    <row r="71" spans="1:38">
       <c r="A71" s="42"/>
       <c r="B71" s="42"/>
       <c r="C71" s="42"/>
@@ -9969,13 +10191,15 @@
       <c r="AC71" s="8"/>
       <c r="AD71" s="8"/>
       <c r="AE71" s="8"/>
-      <c r="AF71" s="25"/>
-      <c r="AG71" s="42"/>
-      <c r="AH71" s="42"/>
+      <c r="AF71" s="8"/>
+      <c r="AG71" s="8"/>
+      <c r="AH71" s="25"/>
       <c r="AI71" s="42"/>
-      <c r="AJ71" s="39"/>
-    </row>
-    <row r="72" spans="1:36">
+      <c r="AJ71" s="42"/>
+      <c r="AK71" s="42"/>
+      <c r="AL71" s="39"/>
+    </row>
+    <row r="72" spans="1:38">
       <c r="A72" s="42"/>
       <c r="B72" s="42"/>
       <c r="C72" s="42"/>
@@ -9997,11 +10221,11 @@
       <c r="P72" s="8"/>
       <c r="Q72" s="8"/>
       <c r="R72" s="8"/>
-      <c r="S72" s="6"/>
-      <c r="T72" s="8"/>
-      <c r="U72" s="65"/>
+      <c r="S72" s="8"/>
+      <c r="T72" s="6"/>
+      <c r="U72" s="8"/>
       <c r="V72" s="8"/>
-      <c r="W72" s="8"/>
+      <c r="W72" s="65"/>
       <c r="X72" s="8"/>
       <c r="Y72" s="8"/>
       <c r="Z72" s="8"/>
@@ -10010,13 +10234,15 @@
       <c r="AC72" s="8"/>
       <c r="AD72" s="8"/>
       <c r="AE72" s="8"/>
-      <c r="AF72" s="25"/>
-      <c r="AG72" s="42"/>
-      <c r="AH72" s="42"/>
+      <c r="AF72" s="8"/>
+      <c r="AG72" s="8"/>
+      <c r="AH72" s="25"/>
       <c r="AI72" s="42"/>
-      <c r="AJ72" s="39"/>
-    </row>
-    <row r="73" spans="1:36">
+      <c r="AJ72" s="42"/>
+      <c r="AK72" s="42"/>
+      <c r="AL72" s="39"/>
+    </row>
+    <row r="73" spans="1:38">
       <c r="A73" s="42"/>
       <c r="B73" s="42"/>
       <c r="C73" s="42"/>
@@ -10037,12 +10263,12 @@
       <c r="O73" s="8"/>
       <c r="P73" s="8"/>
       <c r="Q73" s="8"/>
-      <c r="R73" s="42"/>
-      <c r="S73" s="6"/>
-      <c r="T73" s="8"/>
-      <c r="U73" s="65"/>
+      <c r="R73" s="8"/>
+      <c r="S73" s="42"/>
+      <c r="T73" s="6"/>
+      <c r="U73" s="8"/>
       <c r="V73" s="8"/>
-      <c r="W73" s="8"/>
+      <c r="W73" s="65"/>
       <c r="X73" s="8"/>
       <c r="Y73" s="8"/>
       <c r="Z73" s="8"/>
@@ -10051,13 +10277,15 @@
       <c r="AC73" s="8"/>
       <c r="AD73" s="8"/>
       <c r="AE73" s="8"/>
-      <c r="AF73" s="25"/>
-      <c r="AG73" s="42"/>
-      <c r="AH73" s="42"/>
+      <c r="AF73" s="8"/>
+      <c r="AG73" s="8"/>
+      <c r="AH73" s="25"/>
       <c r="AI73" s="42"/>
-      <c r="AJ73" s="39"/>
-    </row>
-    <row r="74" spans="1:36">
+      <c r="AJ73" s="42"/>
+      <c r="AK73" s="42"/>
+      <c r="AL73" s="39"/>
+    </row>
+    <row r="74" spans="1:38">
       <c r="A74" s="61"/>
       <c r="B74" s="62"/>
       <c r="C74" s="62"/>
@@ -10092,13 +10320,15 @@
       <c r="AC74" s="65"/>
       <c r="AD74" s="65"/>
       <c r="AE74" s="65"/>
-      <c r="AF74" s="59"/>
-      <c r="AG74" s="42"/>
-      <c r="AH74" s="66"/>
+      <c r="AF74" s="65"/>
+      <c r="AG74" s="65"/>
+      <c r="AH74" s="59"/>
       <c r="AI74" s="42"/>
-      <c r="AJ74" s="39"/>
-    </row>
-    <row r="75" spans="1:36">
+      <c r="AJ74" s="66"/>
+      <c r="AK74" s="42"/>
+      <c r="AL74" s="39"/>
+    </row>
+    <row r="75" spans="1:38">
       <c r="A75" s="61"/>
       <c r="B75" s="6"/>
       <c r="C75" s="6"/>
@@ -10119,11 +10349,11 @@
       <c r="O75" s="8"/>
       <c r="P75" s="8"/>
       <c r="Q75" s="8"/>
-      <c r="R75" s="53"/>
+      <c r="R75" s="8"/>
       <c r="S75" s="53"/>
       <c r="T75" s="53"/>
-      <c r="U75" s="8"/>
-      <c r="V75" s="8"/>
+      <c r="U75" s="53"/>
+      <c r="V75" s="53"/>
       <c r="W75" s="8"/>
       <c r="X75" s="8"/>
       <c r="Y75" s="8"/>
@@ -10133,13 +10363,15 @@
       <c r="AC75" s="8"/>
       <c r="AD75" s="8"/>
       <c r="AE75" s="8"/>
-      <c r="AF75" s="25"/>
-      <c r="AG75" s="6"/>
-      <c r="AH75" s="63"/>
-      <c r="AI75" s="42"/>
-      <c r="AJ75" s="39"/>
-    </row>
-    <row r="76" spans="1:36">
+      <c r="AF75" s="8"/>
+      <c r="AG75" s="8"/>
+      <c r="AH75" s="25"/>
+      <c r="AI75" s="6"/>
+      <c r="AJ75" s="63"/>
+      <c r="AK75" s="42"/>
+      <c r="AL75" s="39"/>
+    </row>
+    <row r="76" spans="1:38">
       <c r="A76" s="61"/>
       <c r="B76" s="61"/>
       <c r="C76" s="61"/>
@@ -10160,11 +10392,11 @@
       <c r="O76" s="8"/>
       <c r="P76" s="8"/>
       <c r="Q76" s="8"/>
-      <c r="R76" s="53"/>
+      <c r="R76" s="8"/>
       <c r="S76" s="53"/>
       <c r="T76" s="53"/>
-      <c r="U76" s="65"/>
-      <c r="V76" s="65"/>
+      <c r="U76" s="53"/>
+      <c r="V76" s="53"/>
       <c r="W76" s="65"/>
       <c r="X76" s="65"/>
       <c r="Y76" s="65"/>
@@ -10174,13 +10406,15 @@
       <c r="AC76" s="65"/>
       <c r="AD76" s="65"/>
       <c r="AE76" s="65"/>
-      <c r="AF76" s="59"/>
-      <c r="AG76" s="61"/>
-      <c r="AH76" s="66"/>
-      <c r="AI76" s="42"/>
-      <c r="AJ76" s="39"/>
-    </row>
-    <row r="77" spans="1:36" ht="48" customHeight="1">
+      <c r="AF76" s="65"/>
+      <c r="AG76" s="65"/>
+      <c r="AH76" s="59"/>
+      <c r="AI76" s="61"/>
+      <c r="AJ76" s="66"/>
+      <c r="AK76" s="42"/>
+      <c r="AL76" s="39"/>
+    </row>
+    <row r="77" spans="1:38" ht="48" customHeight="1">
       <c r="A77" s="61"/>
       <c r="B77" s="61"/>
       <c r="C77" s="61"/>
@@ -10201,11 +10435,11 @@
       <c r="O77" s="8"/>
       <c r="P77" s="8"/>
       <c r="Q77" s="8"/>
-      <c r="R77" s="53"/>
+      <c r="R77" s="8"/>
       <c r="S77" s="53"/>
       <c r="T77" s="53"/>
-      <c r="U77" s="8"/>
-      <c r="V77" s="8"/>
+      <c r="U77" s="53"/>
+      <c r="V77" s="53"/>
       <c r="W77" s="8"/>
       <c r="X77" s="8"/>
       <c r="Y77" s="8"/>
@@ -10215,13 +10449,15 @@
       <c r="AC77" s="8"/>
       <c r="AD77" s="8"/>
       <c r="AE77" s="8"/>
-      <c r="AF77" s="25"/>
-      <c r="AG77" s="61"/>
-      <c r="AH77" s="42"/>
-      <c r="AI77" s="42"/>
-      <c r="AJ77" s="39"/>
-    </row>
-    <row r="78" spans="1:36" ht="48" customHeight="1">
+      <c r="AF77" s="8"/>
+      <c r="AG77" s="8"/>
+      <c r="AH77" s="25"/>
+      <c r="AI77" s="61"/>
+      <c r="AJ77" s="42"/>
+      <c r="AK77" s="42"/>
+      <c r="AL77" s="39"/>
+    </row>
+    <row r="78" spans="1:38" ht="48" customHeight="1">
       <c r="A78" s="61"/>
       <c r="B78" s="42"/>
       <c r="C78" s="42"/>
@@ -10256,13 +10492,15 @@
       <c r="AC78" s="65"/>
       <c r="AD78" s="65"/>
       <c r="AE78" s="65"/>
-      <c r="AF78" s="25"/>
-      <c r="AG78" s="42"/>
-      <c r="AH78" s="42"/>
+      <c r="AF78" s="65"/>
+      <c r="AG78" s="65"/>
+      <c r="AH78" s="25"/>
       <c r="AI78" s="42"/>
-      <c r="AJ78" s="39"/>
-    </row>
-    <row r="79" spans="1:36">
+      <c r="AJ78" s="42"/>
+      <c r="AK78" s="42"/>
+      <c r="AL78" s="39"/>
+    </row>
+    <row r="79" spans="1:38">
       <c r="A79" s="61"/>
       <c r="B79" s="42"/>
       <c r="C79" s="61"/>
@@ -10297,13 +10535,15 @@
       <c r="AC79" s="65"/>
       <c r="AD79" s="65"/>
       <c r="AE79" s="65"/>
-      <c r="AF79" s="59"/>
-      <c r="AG79" s="61"/>
-      <c r="AH79" s="61"/>
-      <c r="AI79" s="42"/>
-      <c r="AJ79" s="39"/>
-    </row>
-    <row r="80" spans="1:36">
+      <c r="AF79" s="65"/>
+      <c r="AG79" s="65"/>
+      <c r="AH79" s="59"/>
+      <c r="AI79" s="61"/>
+      <c r="AJ79" s="61"/>
+      <c r="AK79" s="42"/>
+      <c r="AL79" s="39"/>
+    </row>
+    <row r="80" spans="1:38">
       <c r="A80" s="61"/>
       <c r="B80" s="62"/>
       <c r="C80" s="61"/>
@@ -10338,13 +10578,15 @@
       <c r="AC80" s="65"/>
       <c r="AD80" s="65"/>
       <c r="AE80" s="65"/>
-      <c r="AF80" s="59"/>
-      <c r="AG80" s="62"/>
-      <c r="AH80" s="61"/>
-      <c r="AI80" s="42"/>
-      <c r="AJ80" s="39"/>
-    </row>
-    <row r="81" spans="1:36">
+      <c r="AF80" s="65"/>
+      <c r="AG80" s="65"/>
+      <c r="AH80" s="59"/>
+      <c r="AI80" s="62"/>
+      <c r="AJ80" s="61"/>
+      <c r="AK80" s="42"/>
+      <c r="AL80" s="39"/>
+    </row>
+    <row r="81" spans="1:38">
       <c r="A81" s="61"/>
       <c r="B81" s="61"/>
       <c r="C81" s="61"/>
@@ -10379,13 +10621,15 @@
       <c r="AC81" s="65"/>
       <c r="AD81" s="65"/>
       <c r="AE81" s="65"/>
-      <c r="AF81" s="59"/>
-      <c r="AG81" s="61"/>
-      <c r="AH81" s="61"/>
-      <c r="AI81" s="42"/>
-      <c r="AJ81" s="39"/>
-    </row>
-    <row r="82" spans="1:36">
+      <c r="AF81" s="65"/>
+      <c r="AG81" s="65"/>
+      <c r="AH81" s="59"/>
+      <c r="AI81" s="61"/>
+      <c r="AJ81" s="61"/>
+      <c r="AK81" s="42"/>
+      <c r="AL81" s="39"/>
+    </row>
+    <row r="82" spans="1:38">
       <c r="A82" s="61"/>
       <c r="B82" s="61"/>
       <c r="C82" s="61"/>
@@ -10420,13 +10664,15 @@
       <c r="AC82" s="65"/>
       <c r="AD82" s="65"/>
       <c r="AE82" s="65"/>
-      <c r="AF82" s="59"/>
-      <c r="AG82" s="61"/>
-      <c r="AH82" s="61"/>
-      <c r="AI82" s="42"/>
-      <c r="AJ82" s="39"/>
-    </row>
-    <row r="83" spans="1:36">
+      <c r="AF82" s="65"/>
+      <c r="AG82" s="65"/>
+      <c r="AH82" s="59"/>
+      <c r="AI82" s="61"/>
+      <c r="AJ82" s="61"/>
+      <c r="AK82" s="42"/>
+      <c r="AL82" s="39"/>
+    </row>
+    <row r="83" spans="1:38">
       <c r="A83" s="61"/>
       <c r="B83" s="61"/>
       <c r="C83" s="61"/>
@@ -10447,27 +10693,29 @@
       <c r="O83" s="8"/>
       <c r="P83" s="8"/>
       <c r="Q83" s="65"/>
-      <c r="R83" s="8"/>
+      <c r="R83" s="65"/>
       <c r="S83" s="8"/>
       <c r="T83" s="8"/>
       <c r="U83" s="8"/>
       <c r="V83" s="8"/>
       <c r="W83" s="8"/>
-      <c r="X83" s="65"/>
-      <c r="Y83" s="65"/>
+      <c r="X83" s="8"/>
+      <c r="Y83" s="8"/>
       <c r="Z83" s="65"/>
       <c r="AA83" s="65"/>
       <c r="AB83" s="65"/>
       <c r="AC83" s="65"/>
       <c r="AD83" s="65"/>
       <c r="AE83" s="65"/>
-      <c r="AF83" s="59"/>
-      <c r="AG83" s="42"/>
-      <c r="AH83" s="66"/>
+      <c r="AF83" s="65"/>
+      <c r="AG83" s="65"/>
+      <c r="AH83" s="59"/>
       <c r="AI83" s="42"/>
-      <c r="AJ83" s="39"/>
-    </row>
-    <row r="84" spans="1:36">
+      <c r="AJ83" s="66"/>
+      <c r="AK83" s="42"/>
+      <c r="AL83" s="39"/>
+    </row>
+    <row r="84" spans="1:38">
       <c r="A84" s="61"/>
       <c r="B84" s="6"/>
       <c r="C84" s="6"/>
@@ -10488,11 +10736,11 @@
       <c r="O84" s="8"/>
       <c r="P84" s="8"/>
       <c r="Q84" s="8"/>
-      <c r="R84" s="53"/>
+      <c r="R84" s="8"/>
       <c r="S84" s="53"/>
       <c r="T84" s="53"/>
-      <c r="U84" s="8"/>
-      <c r="V84" s="8"/>
+      <c r="U84" s="53"/>
+      <c r="V84" s="53"/>
       <c r="W84" s="8"/>
       <c r="X84" s="8"/>
       <c r="Y84" s="8"/>
@@ -10502,13 +10750,15 @@
       <c r="AC84" s="8"/>
       <c r="AD84" s="8"/>
       <c r="AE84" s="8"/>
-      <c r="AF84" s="25"/>
-      <c r="AG84" s="6"/>
-      <c r="AH84" s="63"/>
-      <c r="AI84" s="42"/>
-      <c r="AJ84" s="39"/>
-    </row>
-    <row r="85" spans="1:36">
+      <c r="AF84" s="8"/>
+      <c r="AG84" s="8"/>
+      <c r="AH84" s="25"/>
+      <c r="AI84" s="6"/>
+      <c r="AJ84" s="63"/>
+      <c r="AK84" s="42"/>
+      <c r="AL84" s="39"/>
+    </row>
+    <row r="85" spans="1:38">
       <c r="A85" s="61"/>
       <c r="B85" s="61"/>
       <c r="C85" s="61"/>
@@ -10529,27 +10779,29 @@
       <c r="O85" s="8"/>
       <c r="P85" s="8"/>
       <c r="Q85" s="8"/>
-      <c r="R85" s="53"/>
+      <c r="R85" s="8"/>
       <c r="S85" s="53"/>
       <c r="T85" s="53"/>
-      <c r="U85" s="8"/>
-      <c r="V85" s="8"/>
+      <c r="U85" s="53"/>
+      <c r="V85" s="53"/>
       <c r="W85" s="8"/>
-      <c r="X85" s="65"/>
-      <c r="Y85" s="65"/>
+      <c r="X85" s="8"/>
+      <c r="Y85" s="8"/>
       <c r="Z85" s="65"/>
       <c r="AA85" s="65"/>
       <c r="AB85" s="65"/>
       <c r="AC85" s="65"/>
       <c r="AD85" s="65"/>
       <c r="AE85" s="65"/>
-      <c r="AF85" s="59"/>
-      <c r="AG85" s="61"/>
-      <c r="AH85" s="61"/>
-      <c r="AI85" s="42"/>
-      <c r="AJ85" s="39"/>
-    </row>
-    <row r="86" spans="1:36">
+      <c r="AF85" s="65"/>
+      <c r="AG85" s="65"/>
+      <c r="AH85" s="59"/>
+      <c r="AI85" s="61"/>
+      <c r="AJ85" s="61"/>
+      <c r="AK85" s="42"/>
+      <c r="AL85" s="39"/>
+    </row>
+    <row r="86" spans="1:38">
       <c r="A86" s="61"/>
       <c r="B86" s="61"/>
       <c r="C86" s="61"/>
@@ -10570,27 +10822,29 @@
       <c r="O86" s="8"/>
       <c r="P86" s="8"/>
       <c r="Q86" s="8"/>
-      <c r="R86" s="53"/>
+      <c r="R86" s="8"/>
       <c r="S86" s="53"/>
       <c r="T86" s="53"/>
-      <c r="U86" s="8"/>
-      <c r="V86" s="8"/>
+      <c r="U86" s="53"/>
+      <c r="V86" s="53"/>
       <c r="W86" s="8"/>
-      <c r="X86" s="65"/>
-      <c r="Y86" s="65"/>
+      <c r="X86" s="8"/>
+      <c r="Y86" s="8"/>
       <c r="Z86" s="65"/>
       <c r="AA86" s="65"/>
       <c r="AB86" s="65"/>
       <c r="AC86" s="65"/>
       <c r="AD86" s="65"/>
       <c r="AE86" s="65"/>
-      <c r="AF86" s="59"/>
-      <c r="AG86" s="61"/>
-      <c r="AH86" s="61"/>
-      <c r="AI86" s="42"/>
-      <c r="AJ86" s="39"/>
-    </row>
-    <row r="87" spans="1:36">
+      <c r="AF86" s="65"/>
+      <c r="AG86" s="65"/>
+      <c r="AH86" s="59"/>
+      <c r="AI86" s="61"/>
+      <c r="AJ86" s="61"/>
+      <c r="AK86" s="42"/>
+      <c r="AL86" s="39"/>
+    </row>
+    <row r="87" spans="1:38">
       <c r="A87" s="42"/>
       <c r="B87" s="61"/>
       <c r="C87" s="61"/>
@@ -10617,21 +10871,23 @@
       <c r="U87" s="8"/>
       <c r="V87" s="8"/>
       <c r="W87" s="8"/>
-      <c r="X87" s="65"/>
-      <c r="Y87" s="65"/>
+      <c r="X87" s="8"/>
+      <c r="Y87" s="8"/>
       <c r="Z87" s="65"/>
       <c r="AA87" s="65"/>
       <c r="AB87" s="65"/>
       <c r="AC87" s="65"/>
       <c r="AD87" s="65"/>
       <c r="AE87" s="65"/>
-      <c r="AF87" s="59"/>
-      <c r="AG87" s="61"/>
-      <c r="AH87" s="61"/>
-      <c r="AI87" s="42"/>
-      <c r="AJ87" s="39"/>
-    </row>
-    <row r="88" spans="1:36">
+      <c r="AF87" s="65"/>
+      <c r="AG87" s="65"/>
+      <c r="AH87" s="59"/>
+      <c r="AI87" s="61"/>
+      <c r="AJ87" s="61"/>
+      <c r="AK87" s="42"/>
+      <c r="AL87" s="39"/>
+    </row>
+    <row r="88" spans="1:38">
       <c r="A88" s="42"/>
       <c r="B88" s="6"/>
       <c r="C88" s="6"/>
@@ -10652,11 +10908,11 @@
       <c r="O88" s="8"/>
       <c r="P88" s="8"/>
       <c r="Q88" s="8"/>
-      <c r="R88" s="53"/>
+      <c r="R88" s="8"/>
       <c r="S88" s="53"/>
       <c r="T88" s="53"/>
-      <c r="U88" s="8"/>
-      <c r="V88" s="8"/>
+      <c r="U88" s="53"/>
+      <c r="V88" s="53"/>
       <c r="W88" s="8"/>
       <c r="X88" s="8"/>
       <c r="Y88" s="8"/>
@@ -10666,13 +10922,15 @@
       <c r="AC88" s="8"/>
       <c r="AD88" s="8"/>
       <c r="AE88" s="8"/>
-      <c r="AF88" s="25"/>
-      <c r="AG88" s="6"/>
-      <c r="AH88" s="63"/>
-      <c r="AI88" s="42"/>
-      <c r="AJ88" s="39"/>
-    </row>
-    <row r="89" spans="1:36">
+      <c r="AF88" s="8"/>
+      <c r="AG88" s="8"/>
+      <c r="AH88" s="25"/>
+      <c r="AI88" s="6"/>
+      <c r="AJ88" s="63"/>
+      <c r="AK88" s="42"/>
+      <c r="AL88" s="39"/>
+    </row>
+    <row r="89" spans="1:38">
       <c r="A89" s="42"/>
       <c r="B89" s="42"/>
       <c r="C89" s="42"/>
@@ -10693,27 +10951,29 @@
       <c r="O89" s="8"/>
       <c r="P89" s="8"/>
       <c r="Q89" s="8"/>
-      <c r="R89" s="53"/>
+      <c r="R89" s="8"/>
       <c r="S89" s="53"/>
-      <c r="T89" s="8"/>
+      <c r="T89" s="53"/>
       <c r="U89" s="8"/>
       <c r="V89" s="8"/>
       <c r="W89" s="8"/>
-      <c r="X89" s="39"/>
-      <c r="Y89" s="39"/>
+      <c r="X89" s="8"/>
+      <c r="Y89" s="8"/>
       <c r="Z89" s="39"/>
       <c r="AA89" s="39"/>
       <c r="AB89" s="39"/>
       <c r="AC89" s="39"/>
       <c r="AD89" s="39"/>
       <c r="AE89" s="39"/>
-      <c r="AF89" s="48"/>
-      <c r="AG89" s="42"/>
-      <c r="AH89" s="6"/>
+      <c r="AF89" s="39"/>
+      <c r="AG89" s="39"/>
+      <c r="AH89" s="48"/>
       <c r="AI89" s="42"/>
-      <c r="AJ89" s="39"/>
-    </row>
-    <row r="90" spans="1:36">
+      <c r="AJ89" s="6"/>
+      <c r="AK89" s="42"/>
+      <c r="AL89" s="39"/>
+    </row>
+    <row r="90" spans="1:38">
       <c r="A90" s="42"/>
       <c r="B90" s="42"/>
       <c r="C90" s="6"/>
@@ -10734,11 +10994,11 @@
       <c r="O90" s="8"/>
       <c r="P90" s="8"/>
       <c r="Q90" s="8"/>
-      <c r="R90" s="42"/>
-      <c r="S90" s="53"/>
-      <c r="T90" s="42"/>
-      <c r="U90" s="8"/>
-      <c r="V90" s="8"/>
+      <c r="R90" s="8"/>
+      <c r="S90" s="42"/>
+      <c r="T90" s="53"/>
+      <c r="U90" s="42"/>
+      <c r="V90" s="42"/>
       <c r="W90" s="8"/>
       <c r="X90" s="8"/>
       <c r="Y90" s="8"/>
@@ -10748,13 +11008,15 @@
       <c r="AC90" s="8"/>
       <c r="AD90" s="8"/>
       <c r="AE90" s="8"/>
-      <c r="AF90" s="25"/>
-      <c r="AG90" s="42"/>
-      <c r="AH90" s="42"/>
+      <c r="AF90" s="8"/>
+      <c r="AG90" s="8"/>
+      <c r="AH90" s="25"/>
       <c r="AI90" s="42"/>
-      <c r="AJ90" s="39"/>
-    </row>
-    <row r="91" spans="1:36">
+      <c r="AJ90" s="42"/>
+      <c r="AK90" s="42"/>
+      <c r="AL90" s="39"/>
+    </row>
+    <row r="91" spans="1:38">
       <c r="A91" s="42"/>
       <c r="B91" s="42"/>
       <c r="C91" s="6"/>
@@ -10775,27 +11037,29 @@
       <c r="O91" s="8"/>
       <c r="P91" s="8"/>
       <c r="Q91" s="39"/>
-      <c r="R91" s="8"/>
+      <c r="R91" s="39"/>
       <c r="S91" s="8"/>
-      <c r="T91" s="39"/>
-      <c r="U91" s="8"/>
-      <c r="V91" s="8"/>
+      <c r="T91" s="8"/>
+      <c r="U91" s="39"/>
+      <c r="V91" s="39"/>
       <c r="W91" s="8"/>
-      <c r="X91" s="39"/>
-      <c r="Y91" s="39"/>
+      <c r="X91" s="8"/>
+      <c r="Y91" s="8"/>
       <c r="Z91" s="39"/>
       <c r="AA91" s="39"/>
       <c r="AB91" s="39"/>
       <c r="AC91" s="39"/>
       <c r="AD91" s="39"/>
       <c r="AE91" s="39"/>
-      <c r="AF91" s="48"/>
-      <c r="AG91" s="42"/>
-      <c r="AH91" s="42"/>
+      <c r="AF91" s="39"/>
+      <c r="AG91" s="39"/>
+      <c r="AH91" s="48"/>
       <c r="AI91" s="42"/>
-      <c r="AJ91" s="39"/>
-    </row>
-    <row r="92" spans="1:36">
+      <c r="AJ91" s="42"/>
+      <c r="AK91" s="42"/>
+      <c r="AL91" s="39"/>
+    </row>
+    <row r="92" spans="1:38">
       <c r="A92" s="42"/>
       <c r="B92" s="6"/>
       <c r="C92" s="6"/>
@@ -10816,27 +11080,29 @@
       <c r="O92" s="8"/>
       <c r="P92" s="8"/>
       <c r="Q92" s="8"/>
-      <c r="R92" s="53"/>
+      <c r="R92" s="8"/>
       <c r="S92" s="53"/>
-      <c r="T92" s="39"/>
-      <c r="U92" s="8"/>
-      <c r="V92" s="8"/>
+      <c r="T92" s="53"/>
+      <c r="U92" s="39"/>
+      <c r="V92" s="39"/>
       <c r="W92" s="8"/>
-      <c r="X92" s="39"/>
-      <c r="Y92" s="39"/>
+      <c r="X92" s="8"/>
+      <c r="Y92" s="8"/>
       <c r="Z92" s="39"/>
       <c r="AA92" s="39"/>
       <c r="AB92" s="39"/>
       <c r="AC92" s="39"/>
       <c r="AD92" s="39"/>
       <c r="AE92" s="39"/>
-      <c r="AF92" s="48"/>
-      <c r="AG92" s="6"/>
-      <c r="AH92" s="63"/>
+      <c r="AF92" s="39"/>
+      <c r="AG92" s="39"/>
+      <c r="AH92" s="48"/>
       <c r="AI92" s="6"/>
-      <c r="AJ92" s="39"/>
-    </row>
-    <row r="93" spans="1:36">
+      <c r="AJ92" s="63"/>
+      <c r="AK92" s="6"/>
+      <c r="AL92" s="39"/>
+    </row>
+    <row r="93" spans="1:38">
       <c r="A93" s="42"/>
       <c r="B93" s="6"/>
       <c r="C93" s="6"/>
@@ -10857,27 +11123,29 @@
       <c r="O93" s="8"/>
       <c r="P93" s="8"/>
       <c r="Q93" s="8"/>
-      <c r="R93" s="53"/>
+      <c r="R93" s="8"/>
       <c r="S93" s="53"/>
-      <c r="T93" s="39"/>
-      <c r="U93" s="8"/>
-      <c r="V93" s="8"/>
+      <c r="T93" s="53"/>
+      <c r="U93" s="39"/>
+      <c r="V93" s="39"/>
       <c r="W93" s="8"/>
-      <c r="X93" s="39"/>
-      <c r="Y93" s="39"/>
+      <c r="X93" s="8"/>
+      <c r="Y93" s="8"/>
       <c r="Z93" s="39"/>
       <c r="AA93" s="39"/>
       <c r="AB93" s="39"/>
       <c r="AC93" s="39"/>
       <c r="AD93" s="39"/>
       <c r="AE93" s="39"/>
-      <c r="AF93" s="48"/>
-      <c r="AG93" s="6"/>
-      <c r="AH93" s="6"/>
+      <c r="AF93" s="39"/>
+      <c r="AG93" s="39"/>
+      <c r="AH93" s="48"/>
       <c r="AI93" s="6"/>
-      <c r="AJ93" s="39"/>
-    </row>
-    <row r="94" spans="1:36">
+      <c r="AJ93" s="6"/>
+      <c r="AK93" s="6"/>
+      <c r="AL93" s="39"/>
+    </row>
+    <row r="94" spans="1:38">
       <c r="A94" s="42"/>
       <c r="B94" s="42"/>
       <c r="C94" s="6"/>
@@ -10900,25 +11168,27 @@
       <c r="Q94" s="8"/>
       <c r="R94" s="8"/>
       <c r="S94" s="8"/>
-      <c r="T94" s="39"/>
-      <c r="U94" s="8"/>
-      <c r="V94" s="8"/>
+      <c r="T94" s="8"/>
+      <c r="U94" s="39"/>
+      <c r="V94" s="39"/>
       <c r="W94" s="8"/>
-      <c r="X94" s="39"/>
-      <c r="Y94" s="39"/>
+      <c r="X94" s="8"/>
+      <c r="Y94" s="8"/>
       <c r="Z94" s="39"/>
       <c r="AA94" s="39"/>
       <c r="AB94" s="39"/>
       <c r="AC94" s="39"/>
       <c r="AD94" s="39"/>
       <c r="AE94" s="39"/>
-      <c r="AF94" s="48"/>
-      <c r="AG94" s="42"/>
-      <c r="AH94" s="42"/>
+      <c r="AF94" s="39"/>
+      <c r="AG94" s="39"/>
+      <c r="AH94" s="48"/>
       <c r="AI94" s="42"/>
-      <c r="AJ94" s="39"/>
-    </row>
-    <row r="95" spans="1:36">
+      <c r="AJ94" s="42"/>
+      <c r="AK94" s="42"/>
+      <c r="AL94" s="39"/>
+    </row>
+    <row r="95" spans="1:38">
       <c r="A95" s="42"/>
       <c r="B95" s="42"/>
       <c r="C95" s="6"/>
@@ -10941,25 +11211,27 @@
       <c r="Q95" s="8"/>
       <c r="R95" s="8"/>
       <c r="S95" s="8"/>
-      <c r="T95" s="39"/>
-      <c r="U95" s="8"/>
-      <c r="V95" s="8"/>
+      <c r="T95" s="8"/>
+      <c r="U95" s="39"/>
+      <c r="V95" s="39"/>
       <c r="W95" s="8"/>
-      <c r="X95" s="39"/>
-      <c r="Y95" s="39"/>
+      <c r="X95" s="8"/>
+      <c r="Y95" s="8"/>
       <c r="Z95" s="39"/>
       <c r="AA95" s="39"/>
       <c r="AB95" s="39"/>
       <c r="AC95" s="39"/>
       <c r="AD95" s="39"/>
       <c r="AE95" s="39"/>
-      <c r="AF95" s="48"/>
-      <c r="AG95" s="42"/>
-      <c r="AH95" s="42"/>
+      <c r="AF95" s="39"/>
+      <c r="AG95" s="39"/>
+      <c r="AH95" s="48"/>
       <c r="AI95" s="42"/>
-      <c r="AJ95" s="39"/>
-    </row>
-    <row r="96" spans="1:36">
+      <c r="AJ95" s="42"/>
+      <c r="AK95" s="42"/>
+      <c r="AL95" s="39"/>
+    </row>
+    <row r="96" spans="1:38">
       <c r="A96" s="42"/>
       <c r="B96" s="42"/>
       <c r="C96" s="42"/>
@@ -10994,13 +11266,15 @@
       <c r="AC96" s="8"/>
       <c r="AD96" s="8"/>
       <c r="AE96" s="8"/>
-      <c r="AF96" s="25"/>
-      <c r="AG96" s="42"/>
-      <c r="AH96" s="42"/>
+      <c r="AF96" s="8"/>
+      <c r="AG96" s="8"/>
+      <c r="AH96" s="25"/>
       <c r="AI96" s="42"/>
-      <c r="AJ96" s="39"/>
-    </row>
-    <row r="97" spans="1:36" ht="112" customHeight="1">
+      <c r="AJ96" s="42"/>
+      <c r="AK96" s="42"/>
+      <c r="AL96" s="39"/>
+    </row>
+    <row r="97" spans="1:38" ht="112" customHeight="1">
       <c r="A97" s="42"/>
       <c r="B97" s="42"/>
       <c r="C97" s="42"/>
@@ -11027,21 +11301,23 @@
       <c r="U97" s="8"/>
       <c r="V97" s="8"/>
       <c r="W97" s="8"/>
-      <c r="X97" s="39"/>
-      <c r="Y97" s="39"/>
+      <c r="X97" s="8"/>
+      <c r="Y97" s="8"/>
       <c r="Z97" s="39"/>
       <c r="AA97" s="39"/>
       <c r="AB97" s="39"/>
       <c r="AC97" s="39"/>
       <c r="AD97" s="39"/>
       <c r="AE97" s="39"/>
-      <c r="AF97" s="48"/>
-      <c r="AG97" s="42"/>
-      <c r="AH97" s="6"/>
+      <c r="AF97" s="39"/>
+      <c r="AG97" s="39"/>
+      <c r="AH97" s="48"/>
       <c r="AI97" s="42"/>
-      <c r="AJ97" s="39"/>
-    </row>
-    <row r="98" spans="1:36">
+      <c r="AJ97" s="6"/>
+      <c r="AK97" s="42"/>
+      <c r="AL97" s="39"/>
+    </row>
+    <row r="98" spans="1:38">
       <c r="A98" s="42"/>
       <c r="B98" s="42"/>
       <c r="C98" s="42"/>
@@ -11076,13 +11352,15 @@
       <c r="AC98" s="8"/>
       <c r="AD98" s="8"/>
       <c r="AE98" s="8"/>
-      <c r="AF98" s="25"/>
-      <c r="AG98" s="42"/>
-      <c r="AH98" s="6"/>
+      <c r="AF98" s="8"/>
+      <c r="AG98" s="8"/>
+      <c r="AH98" s="25"/>
       <c r="AI98" s="42"/>
-      <c r="AJ98" s="39"/>
-    </row>
-    <row r="99" spans="1:36">
+      <c r="AJ98" s="6"/>
+      <c r="AK98" s="42"/>
+      <c r="AL98" s="39"/>
+    </row>
+    <row r="99" spans="1:38">
       <c r="A99" s="42"/>
       <c r="B99" s="42"/>
       <c r="C99" s="42"/>
@@ -11103,27 +11381,29 @@
       <c r="O99" s="8"/>
       <c r="P99" s="8"/>
       <c r="Q99" s="39"/>
-      <c r="R99" s="8"/>
+      <c r="R99" s="39"/>
       <c r="S99" s="8"/>
-      <c r="T99" s="39"/>
-      <c r="U99" s="8"/>
-      <c r="V99" s="8"/>
+      <c r="T99" s="8"/>
+      <c r="U99" s="39"/>
+      <c r="V99" s="39"/>
       <c r="W99" s="8"/>
-      <c r="X99" s="39"/>
-      <c r="Y99" s="39"/>
+      <c r="X99" s="8"/>
+      <c r="Y99" s="8"/>
       <c r="Z99" s="39"/>
       <c r="AA99" s="39"/>
       <c r="AB99" s="39"/>
       <c r="AC99" s="39"/>
       <c r="AD99" s="39"/>
       <c r="AE99" s="39"/>
-      <c r="AF99" s="48"/>
-      <c r="AG99" s="42"/>
-      <c r="AH99" s="42"/>
+      <c r="AF99" s="39"/>
+      <c r="AG99" s="39"/>
+      <c r="AH99" s="48"/>
       <c r="AI99" s="42"/>
-      <c r="AJ99" s="39"/>
-    </row>
-    <row r="100" spans="1:36">
+      <c r="AJ99" s="42"/>
+      <c r="AK99" s="42"/>
+      <c r="AL99" s="39"/>
+    </row>
+    <row r="100" spans="1:38">
       <c r="A100" s="42"/>
       <c r="B100" s="42"/>
       <c r="C100" s="42"/>
@@ -11144,27 +11424,29 @@
       <c r="O100" s="8"/>
       <c r="P100" s="8"/>
       <c r="Q100" s="39"/>
-      <c r="R100" s="8"/>
+      <c r="R100" s="39"/>
       <c r="S100" s="8"/>
-      <c r="T100" s="39"/>
-      <c r="U100" s="8"/>
-      <c r="V100" s="8"/>
+      <c r="T100" s="8"/>
+      <c r="U100" s="39"/>
+      <c r="V100" s="39"/>
       <c r="W100" s="8"/>
-      <c r="X100" s="39"/>
-      <c r="Y100" s="39"/>
+      <c r="X100" s="8"/>
+      <c r="Y100" s="8"/>
       <c r="Z100" s="39"/>
       <c r="AA100" s="39"/>
       <c r="AB100" s="39"/>
       <c r="AC100" s="39"/>
       <c r="AD100" s="39"/>
       <c r="AE100" s="39"/>
-      <c r="AF100" s="48"/>
-      <c r="AG100" s="42"/>
-      <c r="AH100" s="42"/>
+      <c r="AF100" s="39"/>
+      <c r="AG100" s="39"/>
+      <c r="AH100" s="48"/>
       <c r="AI100" s="42"/>
-      <c r="AJ100" s="39"/>
-    </row>
-    <row r="101" spans="1:36">
+      <c r="AJ100" s="42"/>
+      <c r="AK100" s="42"/>
+      <c r="AL100" s="39"/>
+    </row>
+    <row r="101" spans="1:38">
       <c r="A101" s="42"/>
       <c r="B101" s="42"/>
       <c r="C101" s="42"/>
@@ -11185,27 +11467,29 @@
       <c r="O101" s="8"/>
       <c r="P101" s="8"/>
       <c r="Q101" s="39"/>
-      <c r="R101" s="8"/>
+      <c r="R101" s="39"/>
       <c r="S101" s="8"/>
-      <c r="T101" s="39"/>
-      <c r="U101" s="8"/>
-      <c r="V101" s="8"/>
+      <c r="T101" s="8"/>
+      <c r="U101" s="39"/>
+      <c r="V101" s="39"/>
       <c r="W101" s="8"/>
-      <c r="X101" s="39"/>
-      <c r="Y101" s="39"/>
+      <c r="X101" s="8"/>
+      <c r="Y101" s="8"/>
       <c r="Z101" s="39"/>
       <c r="AA101" s="39"/>
       <c r="AB101" s="39"/>
       <c r="AC101" s="39"/>
       <c r="AD101" s="39"/>
       <c r="AE101" s="39"/>
-      <c r="AF101" s="48"/>
-      <c r="AG101" s="42"/>
-      <c r="AH101" s="42"/>
+      <c r="AF101" s="39"/>
+      <c r="AG101" s="39"/>
+      <c r="AH101" s="48"/>
       <c r="AI101" s="42"/>
-      <c r="AJ101" s="39"/>
-    </row>
-    <row r="102" spans="1:36">
+      <c r="AJ101" s="42"/>
+      <c r="AK101" s="42"/>
+      <c r="AL101" s="39"/>
+    </row>
+    <row r="102" spans="1:38">
       <c r="A102" s="42"/>
       <c r="B102" s="42"/>
       <c r="C102" s="42"/>
@@ -11226,27 +11510,29 @@
       <c r="O102" s="8"/>
       <c r="P102" s="8"/>
       <c r="Q102" s="39"/>
-      <c r="R102" s="8"/>
+      <c r="R102" s="39"/>
       <c r="S102" s="8"/>
-      <c r="T102" s="39"/>
-      <c r="U102" s="8"/>
-      <c r="V102" s="8"/>
+      <c r="T102" s="8"/>
+      <c r="U102" s="39"/>
+      <c r="V102" s="39"/>
       <c r="W102" s="8"/>
-      <c r="X102" s="39"/>
-      <c r="Y102" s="39"/>
+      <c r="X102" s="8"/>
+      <c r="Y102" s="8"/>
       <c r="Z102" s="39"/>
       <c r="AA102" s="39"/>
       <c r="AB102" s="39"/>
       <c r="AC102" s="39"/>
       <c r="AD102" s="39"/>
       <c r="AE102" s="39"/>
-      <c r="AF102" s="48"/>
-      <c r="AG102" s="42"/>
-      <c r="AH102" s="42"/>
+      <c r="AF102" s="39"/>
+      <c r="AG102" s="39"/>
+      <c r="AH102" s="48"/>
       <c r="AI102" s="42"/>
-      <c r="AJ102" s="39"/>
-    </row>
-    <row r="103" spans="1:36">
+      <c r="AJ102" s="42"/>
+      <c r="AK102" s="42"/>
+      <c r="AL102" s="39"/>
+    </row>
+    <row r="103" spans="1:38">
       <c r="A103" s="42"/>
       <c r="B103" s="42"/>
       <c r="C103" s="42"/>
@@ -11267,27 +11553,29 @@
       <c r="O103" s="8"/>
       <c r="P103" s="8"/>
       <c r="Q103" s="39"/>
-      <c r="R103" s="8"/>
+      <c r="R103" s="39"/>
       <c r="S103" s="8"/>
-      <c r="T103" s="39"/>
-      <c r="U103" s="8"/>
-      <c r="V103" s="8"/>
+      <c r="T103" s="8"/>
+      <c r="U103" s="39"/>
+      <c r="V103" s="39"/>
       <c r="W103" s="8"/>
-      <c r="X103" s="39"/>
-      <c r="Y103" s="39"/>
+      <c r="X103" s="8"/>
+      <c r="Y103" s="8"/>
       <c r="Z103" s="39"/>
       <c r="AA103" s="39"/>
       <c r="AB103" s="39"/>
       <c r="AC103" s="39"/>
       <c r="AD103" s="39"/>
       <c r="AE103" s="39"/>
-      <c r="AF103" s="48"/>
-      <c r="AG103" s="42"/>
-      <c r="AH103" s="42"/>
+      <c r="AF103" s="39"/>
+      <c r="AG103" s="39"/>
+      <c r="AH103" s="48"/>
       <c r="AI103" s="42"/>
-      <c r="AJ103" s="39"/>
-    </row>
-    <row r="104" spans="1:36">
+      <c r="AJ103" s="42"/>
+      <c r="AK103" s="42"/>
+      <c r="AL103" s="39"/>
+    </row>
+    <row r="104" spans="1:38">
       <c r="A104" s="42"/>
       <c r="B104" s="42"/>
       <c r="C104" s="6"/>
@@ -11308,27 +11596,29 @@
       <c r="O104" s="8"/>
       <c r="P104" s="8"/>
       <c r="Q104" s="39"/>
-      <c r="R104" s="8"/>
+      <c r="R104" s="39"/>
       <c r="S104" s="8"/>
-      <c r="T104" s="39"/>
-      <c r="U104" s="8"/>
-      <c r="V104" s="8"/>
+      <c r="T104" s="8"/>
+      <c r="U104" s="39"/>
+      <c r="V104" s="39"/>
       <c r="W104" s="8"/>
-      <c r="X104" s="39"/>
-      <c r="Y104" s="39"/>
+      <c r="X104" s="8"/>
+      <c r="Y104" s="8"/>
       <c r="Z104" s="39"/>
       <c r="AA104" s="39"/>
       <c r="AB104" s="39"/>
       <c r="AC104" s="39"/>
       <c r="AD104" s="39"/>
       <c r="AE104" s="39"/>
-      <c r="AF104" s="48"/>
-      <c r="AG104" s="42"/>
-      <c r="AH104" s="42"/>
+      <c r="AF104" s="39"/>
+      <c r="AG104" s="39"/>
+      <c r="AH104" s="48"/>
       <c r="AI104" s="42"/>
-      <c r="AJ104" s="39"/>
-    </row>
-    <row r="105" spans="1:36">
+      <c r="AJ104" s="42"/>
+      <c r="AK104" s="42"/>
+      <c r="AL104" s="39"/>
+    </row>
+    <row r="105" spans="1:38">
       <c r="A105" s="42"/>
       <c r="B105" s="42"/>
       <c r="C105" s="6"/>
@@ -11349,27 +11639,29 @@
       <c r="O105" s="8"/>
       <c r="P105" s="8"/>
       <c r="Q105" s="39"/>
-      <c r="R105" s="8"/>
+      <c r="R105" s="39"/>
       <c r="S105" s="8"/>
-      <c r="T105" s="39"/>
-      <c r="U105" s="8"/>
-      <c r="V105" s="8"/>
+      <c r="T105" s="8"/>
+      <c r="U105" s="39"/>
+      <c r="V105" s="39"/>
       <c r="W105" s="8"/>
-      <c r="X105" s="39"/>
-      <c r="Y105" s="39"/>
+      <c r="X105" s="8"/>
+      <c r="Y105" s="8"/>
       <c r="Z105" s="39"/>
       <c r="AA105" s="39"/>
       <c r="AB105" s="39"/>
       <c r="AC105" s="39"/>
       <c r="AD105" s="39"/>
       <c r="AE105" s="39"/>
-      <c r="AF105" s="48"/>
-      <c r="AG105" s="42"/>
-      <c r="AH105" s="6"/>
+      <c r="AF105" s="39"/>
+      <c r="AG105" s="39"/>
+      <c r="AH105" s="48"/>
       <c r="AI105" s="42"/>
-      <c r="AJ105" s="39"/>
-    </row>
-    <row r="106" spans="1:36">
+      <c r="AJ105" s="6"/>
+      <c r="AK105" s="42"/>
+      <c r="AL105" s="39"/>
+    </row>
+    <row r="106" spans="1:38">
       <c r="A106" s="42"/>
       <c r="B106" s="42"/>
       <c r="C106" s="42"/>
@@ -11390,27 +11682,29 @@
       <c r="O106" s="8"/>
       <c r="P106" s="8"/>
       <c r="Q106" s="39"/>
-      <c r="R106" s="8"/>
+      <c r="R106" s="39"/>
       <c r="S106" s="8"/>
-      <c r="T106" s="39"/>
-      <c r="U106" s="8"/>
-      <c r="V106" s="8"/>
+      <c r="T106" s="8"/>
+      <c r="U106" s="39"/>
+      <c r="V106" s="39"/>
       <c r="W106" s="8"/>
-      <c r="X106" s="39"/>
-      <c r="Y106" s="39"/>
+      <c r="X106" s="8"/>
+      <c r="Y106" s="8"/>
       <c r="Z106" s="39"/>
       <c r="AA106" s="39"/>
       <c r="AB106" s="39"/>
       <c r="AC106" s="39"/>
       <c r="AD106" s="39"/>
       <c r="AE106" s="39"/>
-      <c r="AF106" s="48"/>
-      <c r="AG106" s="42"/>
-      <c r="AH106" s="42"/>
+      <c r="AF106" s="39"/>
+      <c r="AG106" s="39"/>
+      <c r="AH106" s="48"/>
       <c r="AI106" s="42"/>
-      <c r="AJ106" s="39"/>
-    </row>
-    <row r="107" spans="1:36">
+      <c r="AJ106" s="42"/>
+      <c r="AK106" s="42"/>
+      <c r="AL106" s="39"/>
+    </row>
+    <row r="107" spans="1:38">
       <c r="A107" s="42"/>
       <c r="B107" s="42"/>
       <c r="C107" s="42"/>
@@ -11431,27 +11725,29 @@
       <c r="O107" s="8"/>
       <c r="P107" s="8"/>
       <c r="Q107" s="39"/>
-      <c r="R107" s="8"/>
+      <c r="R107" s="39"/>
       <c r="S107" s="8"/>
-      <c r="T107" s="39"/>
-      <c r="U107" s="8"/>
-      <c r="V107" s="8"/>
+      <c r="T107" s="8"/>
+      <c r="U107" s="39"/>
+      <c r="V107" s="39"/>
       <c r="W107" s="8"/>
-      <c r="X107" s="39"/>
-      <c r="Y107" s="39"/>
+      <c r="X107" s="8"/>
+      <c r="Y107" s="8"/>
       <c r="Z107" s="39"/>
       <c r="AA107" s="39"/>
       <c r="AB107" s="39"/>
       <c r="AC107" s="39"/>
       <c r="AD107" s="39"/>
       <c r="AE107" s="39"/>
-      <c r="AF107" s="48"/>
-      <c r="AG107" s="42"/>
-      <c r="AH107" s="42"/>
+      <c r="AF107" s="39"/>
+      <c r="AG107" s="39"/>
+      <c r="AH107" s="48"/>
       <c r="AI107" s="42"/>
-      <c r="AJ107" s="39"/>
-    </row>
-    <row r="108" spans="1:36">
+      <c r="AJ107" s="42"/>
+      <c r="AK107" s="42"/>
+      <c r="AL107" s="39"/>
+    </row>
+    <row r="108" spans="1:38">
       <c r="A108" s="42"/>
       <c r="B108" s="42"/>
       <c r="C108" s="42"/>
@@ -11472,27 +11768,29 @@
       <c r="O108" s="8"/>
       <c r="P108" s="8"/>
       <c r="Q108" s="39"/>
-      <c r="R108" s="8"/>
+      <c r="R108" s="39"/>
       <c r="S108" s="8"/>
-      <c r="T108" s="39"/>
-      <c r="U108" s="8"/>
-      <c r="V108" s="8"/>
+      <c r="T108" s="8"/>
+      <c r="U108" s="39"/>
+      <c r="V108" s="39"/>
       <c r="W108" s="8"/>
-      <c r="X108" s="39"/>
-      <c r="Y108" s="39"/>
+      <c r="X108" s="8"/>
+      <c r="Y108" s="8"/>
       <c r="Z108" s="39"/>
       <c r="AA108" s="39"/>
       <c r="AB108" s="39"/>
       <c r="AC108" s="39"/>
       <c r="AD108" s="39"/>
       <c r="AE108" s="39"/>
-      <c r="AF108" s="48"/>
-      <c r="AG108" s="42"/>
-      <c r="AH108" s="42"/>
+      <c r="AF108" s="39"/>
+      <c r="AG108" s="39"/>
+      <c r="AH108" s="48"/>
       <c r="AI108" s="42"/>
-      <c r="AJ108" s="39"/>
-    </row>
-    <row r="109" spans="1:36">
+      <c r="AJ108" s="42"/>
+      <c r="AK108" s="42"/>
+      <c r="AL108" s="39"/>
+    </row>
+    <row r="109" spans="1:38">
       <c r="A109" s="42"/>
       <c r="B109" s="42"/>
       <c r="C109" s="42"/>
@@ -11513,27 +11811,29 @@
       <c r="O109" s="8"/>
       <c r="P109" s="8"/>
       <c r="Q109" s="39"/>
-      <c r="R109" s="8"/>
+      <c r="R109" s="39"/>
       <c r="S109" s="8"/>
-      <c r="T109" s="39"/>
-      <c r="U109" s="8"/>
-      <c r="V109" s="8"/>
+      <c r="T109" s="8"/>
+      <c r="U109" s="39"/>
+      <c r="V109" s="39"/>
       <c r="W109" s="8"/>
-      <c r="X109" s="39"/>
-      <c r="Y109" s="39"/>
+      <c r="X109" s="8"/>
+      <c r="Y109" s="8"/>
       <c r="Z109" s="39"/>
       <c r="AA109" s="39"/>
       <c r="AB109" s="39"/>
       <c r="AC109" s="39"/>
       <c r="AD109" s="39"/>
       <c r="AE109" s="39"/>
-      <c r="AF109" s="48"/>
-      <c r="AG109" s="42"/>
-      <c r="AH109" s="42"/>
+      <c r="AF109" s="39"/>
+      <c r="AG109" s="39"/>
+      <c r="AH109" s="48"/>
       <c r="AI109" s="42"/>
-      <c r="AJ109" s="39"/>
-    </row>
-    <row r="110" spans="1:36">
+      <c r="AJ109" s="42"/>
+      <c r="AK109" s="42"/>
+      <c r="AL109" s="39"/>
+    </row>
+    <row r="110" spans="1:38">
       <c r="A110" s="42"/>
       <c r="B110" s="42"/>
       <c r="C110" s="42"/>
@@ -11554,27 +11854,29 @@
       <c r="O110" s="8"/>
       <c r="P110" s="8"/>
       <c r="Q110" s="39"/>
-      <c r="R110" s="8"/>
+      <c r="R110" s="39"/>
       <c r="S110" s="8"/>
-      <c r="T110" s="39"/>
-      <c r="U110" s="8"/>
-      <c r="V110" s="8"/>
+      <c r="T110" s="8"/>
+      <c r="U110" s="39"/>
+      <c r="V110" s="39"/>
       <c r="W110" s="8"/>
-      <c r="X110" s="39"/>
-      <c r="Y110" s="39"/>
+      <c r="X110" s="8"/>
+      <c r="Y110" s="8"/>
       <c r="Z110" s="39"/>
       <c r="AA110" s="39"/>
       <c r="AB110" s="39"/>
       <c r="AC110" s="39"/>
       <c r="AD110" s="39"/>
       <c r="AE110" s="39"/>
-      <c r="AF110" s="48"/>
-      <c r="AG110" s="42"/>
-      <c r="AH110" s="42"/>
+      <c r="AF110" s="39"/>
+      <c r="AG110" s="39"/>
+      <c r="AH110" s="48"/>
       <c r="AI110" s="42"/>
-      <c r="AJ110" s="39"/>
-    </row>
-    <row r="111" spans="1:36">
+      <c r="AJ110" s="42"/>
+      <c r="AK110" s="42"/>
+      <c r="AL110" s="39"/>
+    </row>
+    <row r="111" spans="1:38">
       <c r="A111" s="42"/>
       <c r="B111" s="42"/>
       <c r="C111" s="6"/>
@@ -11595,27 +11897,29 @@
       <c r="O111" s="8"/>
       <c r="P111" s="8"/>
       <c r="Q111" s="39"/>
-      <c r="R111" s="8"/>
+      <c r="R111" s="39"/>
       <c r="S111" s="8"/>
-      <c r="T111" s="39"/>
-      <c r="U111" s="8"/>
-      <c r="V111" s="8"/>
+      <c r="T111" s="8"/>
+      <c r="U111" s="39"/>
+      <c r="V111" s="39"/>
       <c r="W111" s="8"/>
-      <c r="X111" s="39"/>
-      <c r="Y111" s="39"/>
+      <c r="X111" s="8"/>
+      <c r="Y111" s="8"/>
       <c r="Z111" s="39"/>
       <c r="AA111" s="39"/>
       <c r="AB111" s="39"/>
       <c r="AC111" s="39"/>
       <c r="AD111" s="39"/>
       <c r="AE111" s="39"/>
-      <c r="AF111" s="48"/>
-      <c r="AG111" s="42"/>
-      <c r="AH111" s="42"/>
+      <c r="AF111" s="39"/>
+      <c r="AG111" s="39"/>
+      <c r="AH111" s="48"/>
       <c r="AI111" s="42"/>
-      <c r="AJ111" s="39"/>
-    </row>
-    <row r="112" spans="1:36">
+      <c r="AJ111" s="42"/>
+      <c r="AK111" s="42"/>
+      <c r="AL111" s="39"/>
+    </row>
+    <row r="112" spans="1:38">
       <c r="A112" s="42"/>
       <c r="B112" s="42"/>
       <c r="C112" s="6"/>
@@ -11636,27 +11940,29 @@
       <c r="O112" s="8"/>
       <c r="P112" s="8"/>
       <c r="Q112" s="39"/>
-      <c r="R112" s="8"/>
+      <c r="R112" s="39"/>
       <c r="S112" s="8"/>
-      <c r="T112" s="39"/>
-      <c r="U112" s="8"/>
-      <c r="V112" s="8"/>
+      <c r="T112" s="8"/>
+      <c r="U112" s="39"/>
+      <c r="V112" s="39"/>
       <c r="W112" s="8"/>
-      <c r="X112" s="39"/>
-      <c r="Y112" s="39"/>
+      <c r="X112" s="8"/>
+      <c r="Y112" s="8"/>
       <c r="Z112" s="39"/>
       <c r="AA112" s="39"/>
       <c r="AB112" s="39"/>
       <c r="AC112" s="39"/>
       <c r="AD112" s="39"/>
       <c r="AE112" s="39"/>
-      <c r="AF112" s="48"/>
-      <c r="AG112" s="42"/>
-      <c r="AH112" s="42"/>
+      <c r="AF112" s="39"/>
+      <c r="AG112" s="39"/>
+      <c r="AH112" s="48"/>
       <c r="AI112" s="42"/>
-      <c r="AJ112" s="39"/>
-    </row>
-    <row r="113" spans="1:36">
+      <c r="AJ112" s="42"/>
+      <c r="AK112" s="42"/>
+      <c r="AL112" s="39"/>
+    </row>
+    <row r="113" spans="1:38">
       <c r="A113" s="42"/>
       <c r="B113" s="42"/>
       <c r="C113" s="42"/>
@@ -11677,27 +11983,29 @@
       <c r="O113" s="8"/>
       <c r="P113" s="8"/>
       <c r="Q113" s="39"/>
-      <c r="R113" s="8"/>
+      <c r="R113" s="39"/>
       <c r="S113" s="8"/>
-      <c r="T113" s="39"/>
-      <c r="U113" s="8"/>
-      <c r="V113" s="8"/>
+      <c r="T113" s="8"/>
+      <c r="U113" s="39"/>
+      <c r="V113" s="39"/>
       <c r="W113" s="8"/>
-      <c r="X113" s="39"/>
-      <c r="Y113" s="39"/>
+      <c r="X113" s="8"/>
+      <c r="Y113" s="8"/>
       <c r="Z113" s="39"/>
       <c r="AA113" s="39"/>
       <c r="AB113" s="39"/>
       <c r="AC113" s="39"/>
       <c r="AD113" s="39"/>
       <c r="AE113" s="39"/>
-      <c r="AF113" s="48"/>
-      <c r="AG113" s="42"/>
-      <c r="AH113" s="42"/>
+      <c r="AF113" s="39"/>
+      <c r="AG113" s="39"/>
+      <c r="AH113" s="48"/>
       <c r="AI113" s="42"/>
-      <c r="AJ113" s="39"/>
-    </row>
-    <row r="114" spans="1:36">
+      <c r="AJ113" s="42"/>
+      <c r="AK113" s="42"/>
+      <c r="AL113" s="39"/>
+    </row>
+    <row r="114" spans="1:38">
       <c r="A114" s="42"/>
       <c r="B114" s="42"/>
       <c r="C114" s="42"/>
@@ -11718,27 +12026,29 @@
       <c r="O114" s="8"/>
       <c r="P114" s="8"/>
       <c r="Q114" s="39"/>
-      <c r="R114" s="8"/>
+      <c r="R114" s="39"/>
       <c r="S114" s="8"/>
-      <c r="T114" s="39"/>
-      <c r="U114" s="8"/>
-      <c r="V114" s="8"/>
+      <c r="T114" s="8"/>
+      <c r="U114" s="39"/>
+      <c r="V114" s="39"/>
       <c r="W114" s="8"/>
-      <c r="X114" s="39"/>
-      <c r="Y114" s="39"/>
+      <c r="X114" s="8"/>
+      <c r="Y114" s="8"/>
       <c r="Z114" s="39"/>
       <c r="AA114" s="39"/>
       <c r="AB114" s="39"/>
       <c r="AC114" s="39"/>
       <c r="AD114" s="39"/>
       <c r="AE114" s="39"/>
-      <c r="AF114" s="48"/>
-      <c r="AG114" s="42"/>
-      <c r="AH114" s="42"/>
+      <c r="AF114" s="39"/>
+      <c r="AG114" s="39"/>
+      <c r="AH114" s="48"/>
       <c r="AI114" s="42"/>
-      <c r="AJ114" s="39"/>
-    </row>
-    <row r="115" spans="1:36">
+      <c r="AJ114" s="42"/>
+      <c r="AK114" s="42"/>
+      <c r="AL114" s="39"/>
+    </row>
+    <row r="115" spans="1:38">
       <c r="A115" s="42"/>
       <c r="B115" s="42"/>
       <c r="C115" s="42"/>
@@ -11759,27 +12069,29 @@
       <c r="O115" s="8"/>
       <c r="P115" s="8"/>
       <c r="Q115" s="39"/>
-      <c r="R115" s="8"/>
+      <c r="R115" s="39"/>
       <c r="S115" s="8"/>
-      <c r="T115" s="39"/>
-      <c r="U115" s="8"/>
-      <c r="V115" s="8"/>
+      <c r="T115" s="8"/>
+      <c r="U115" s="39"/>
+      <c r="V115" s="39"/>
       <c r="W115" s="8"/>
-      <c r="X115" s="39"/>
-      <c r="Y115" s="39"/>
+      <c r="X115" s="8"/>
+      <c r="Y115" s="8"/>
       <c r="Z115" s="39"/>
       <c r="AA115" s="39"/>
       <c r="AB115" s="39"/>
       <c r="AC115" s="39"/>
       <c r="AD115" s="39"/>
       <c r="AE115" s="39"/>
-      <c r="AF115" s="48"/>
-      <c r="AG115" s="42"/>
-      <c r="AH115" s="42"/>
+      <c r="AF115" s="39"/>
+      <c r="AG115" s="39"/>
+      <c r="AH115" s="48"/>
       <c r="AI115" s="42"/>
-      <c r="AJ115" s="39"/>
-    </row>
-    <row r="116" spans="1:36">
+      <c r="AJ115" s="42"/>
+      <c r="AK115" s="42"/>
+      <c r="AL115" s="39"/>
+    </row>
+    <row r="116" spans="1:38">
       <c r="A116" s="42"/>
       <c r="B116" s="42"/>
       <c r="C116" s="42"/>
@@ -11800,27 +12112,29 @@
       <c r="O116" s="8"/>
       <c r="P116" s="8"/>
       <c r="Q116" s="39"/>
-      <c r="R116" s="8"/>
+      <c r="R116" s="39"/>
       <c r="S116" s="8"/>
-      <c r="T116" s="39"/>
-      <c r="U116" s="8"/>
-      <c r="V116" s="8"/>
+      <c r="T116" s="8"/>
+      <c r="U116" s="39"/>
+      <c r="V116" s="39"/>
       <c r="W116" s="8"/>
-      <c r="X116" s="39"/>
-      <c r="Y116" s="39"/>
+      <c r="X116" s="8"/>
+      <c r="Y116" s="8"/>
       <c r="Z116" s="39"/>
       <c r="AA116" s="39"/>
       <c r="AB116" s="39"/>
       <c r="AC116" s="39"/>
       <c r="AD116" s="39"/>
       <c r="AE116" s="39"/>
-      <c r="AF116" s="48"/>
-      <c r="AG116" s="42"/>
-      <c r="AH116" s="42"/>
+      <c r="AF116" s="39"/>
+      <c r="AG116" s="39"/>
+      <c r="AH116" s="48"/>
       <c r="AI116" s="42"/>
-      <c r="AJ116" s="39"/>
-    </row>
-    <row r="117" spans="1:36">
+      <c r="AJ116" s="42"/>
+      <c r="AK116" s="42"/>
+      <c r="AL116" s="39"/>
+    </row>
+    <row r="117" spans="1:38">
       <c r="A117" s="42"/>
       <c r="B117" s="42"/>
       <c r="C117" s="42"/>
@@ -11841,27 +12155,29 @@
       <c r="O117" s="8"/>
       <c r="P117" s="8"/>
       <c r="Q117" s="39"/>
-      <c r="R117" s="8"/>
+      <c r="R117" s="39"/>
       <c r="S117" s="8"/>
-      <c r="T117" s="39"/>
-      <c r="U117" s="8"/>
-      <c r="V117" s="8"/>
+      <c r="T117" s="8"/>
+      <c r="U117" s="39"/>
+      <c r="V117" s="39"/>
       <c r="W117" s="8"/>
-      <c r="X117" s="39"/>
-      <c r="Y117" s="39"/>
+      <c r="X117" s="8"/>
+      <c r="Y117" s="8"/>
       <c r="Z117" s="39"/>
       <c r="AA117" s="39"/>
       <c r="AB117" s="39"/>
       <c r="AC117" s="39"/>
       <c r="AD117" s="39"/>
       <c r="AE117" s="39"/>
-      <c r="AF117" s="48"/>
-      <c r="AG117" s="42"/>
-      <c r="AH117" s="42"/>
+      <c r="AF117" s="39"/>
+      <c r="AG117" s="39"/>
+      <c r="AH117" s="48"/>
       <c r="AI117" s="42"/>
-      <c r="AJ117" s="39"/>
-    </row>
-    <row r="118" spans="1:36">
+      <c r="AJ117" s="42"/>
+      <c r="AK117" s="42"/>
+      <c r="AL117" s="39"/>
+    </row>
+    <row r="118" spans="1:38">
       <c r="A118" s="42"/>
       <c r="B118" s="42"/>
       <c r="C118" s="42"/>
@@ -11882,27 +12198,29 @@
       <c r="O118" s="8"/>
       <c r="P118" s="8"/>
       <c r="Q118" s="39"/>
-      <c r="R118" s="8"/>
+      <c r="R118" s="39"/>
       <c r="S118" s="8"/>
-      <c r="T118" s="39"/>
-      <c r="U118" s="8"/>
-      <c r="V118" s="8"/>
+      <c r="T118" s="8"/>
+      <c r="U118" s="39"/>
+      <c r="V118" s="39"/>
       <c r="W118" s="8"/>
-      <c r="X118" s="39"/>
-      <c r="Y118" s="39"/>
+      <c r="X118" s="8"/>
+      <c r="Y118" s="8"/>
       <c r="Z118" s="39"/>
       <c r="AA118" s="39"/>
       <c r="AB118" s="39"/>
       <c r="AC118" s="39"/>
       <c r="AD118" s="39"/>
       <c r="AE118" s="39"/>
-      <c r="AF118" s="48"/>
-      <c r="AG118" s="42"/>
-      <c r="AH118" s="6"/>
+      <c r="AF118" s="39"/>
+      <c r="AG118" s="39"/>
+      <c r="AH118" s="48"/>
       <c r="AI118" s="42"/>
-      <c r="AJ118" s="39"/>
-    </row>
-    <row r="119" spans="1:36">
+      <c r="AJ118" s="6"/>
+      <c r="AK118" s="42"/>
+      <c r="AL118" s="39"/>
+    </row>
+    <row r="119" spans="1:38">
       <c r="A119" s="42"/>
       <c r="B119" s="42"/>
       <c r="C119" s="42"/>
@@ -11923,25 +12241,27 @@
       <c r="O119" s="8"/>
       <c r="P119" s="8"/>
       <c r="Q119" s="39"/>
-      <c r="R119" s="8"/>
+      <c r="R119" s="39"/>
       <c r="S119" s="8"/>
-      <c r="T119" s="39"/>
-      <c r="U119" s="8"/>
-      <c r="V119" s="8"/>
+      <c r="T119" s="8"/>
+      <c r="U119" s="39"/>
+      <c r="V119" s="39"/>
       <c r="W119" s="8"/>
-      <c r="X119" s="39"/>
-      <c r="Y119" s="39"/>
+      <c r="X119" s="8"/>
+      <c r="Y119" s="8"/>
       <c r="Z119" s="39"/>
       <c r="AA119" s="39"/>
       <c r="AB119" s="39"/>
       <c r="AC119" s="39"/>
       <c r="AD119" s="39"/>
       <c r="AE119" s="39"/>
-      <c r="AF119" s="48"/>
-      <c r="AG119" s="42"/>
-      <c r="AH119" s="42"/>
+      <c r="AF119" s="39"/>
+      <c r="AG119" s="39"/>
+      <c r="AH119" s="48"/>
       <c r="AI119" s="42"/>
-      <c r="AJ119" s="39"/>
+      <c r="AJ119" s="42"/>
+      <c r="AK119" s="42"/>
+      <c r="AL119" s="39"/>
     </row>
   </sheetData>
   <dataValidations count="4">
@@ -11951,7 +12271,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P6:P119" xr:uid="{00000000-0002-0000-0700-000001000000}">
       <formula1>"unidirectional,bidirectional"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E6:M119 U6:U119" xr:uid="{00000000-0002-0000-0700-000002000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E6:M119 W6:W119" xr:uid="{00000000-0002-0000-0700-000002000000}">
       <formula1>"○"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N6:N119" xr:uid="{00000000-0002-0000-0700-000003000000}">
@@ -11968,7 +12288,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:AJ13"/>
+  <dimension ref="A1:AL13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="39.1640625" style="35" bestFit="1" customWidth="1"/>
@@ -11985,59 +12305,60 @@
     <col min="14" max="14" width="8.5" style="37" customWidth="1" outlineLevel="1"/>
     <col min="15" max="16" width="18.33203125" style="37" customWidth="1" outlineLevel="2"/>
     <col min="17" max="17" width="29.5" style="37" customWidth="1" outlineLevel="2"/>
-    <col min="18" max="18" width="29" style="37" customWidth="1" outlineLevel="2"/>
-    <col min="19" max="20" width="18.33203125" style="37" customWidth="1" outlineLevel="2"/>
-    <col min="21" max="21" width="17.1640625" style="37" bestFit="1" customWidth="1" outlineLevel="1"/>
-    <col min="22" max="23" width="9.1640625" style="37" hidden="1" customWidth="1" outlineLevel="2"/>
-    <col min="24" max="24" width="9.33203125" style="37" hidden="1" customWidth="1" outlineLevel="2"/>
-    <col min="25" max="25" width="37.5" style="35" hidden="1" customWidth="1" outlineLevel="2"/>
-    <col min="26" max="31" width="19.33203125" style="38" hidden="1" customWidth="1" outlineLevel="2"/>
-    <col min="32" max="32" width="19.33203125" style="38" customWidth="1" outlineLevel="1" collapsed="1"/>
-    <col min="33" max="36" width="19.33203125" style="38" customWidth="1"/>
+    <col min="18" max="18" width="20.1640625" style="37" customWidth="1" outlineLevel="2"/>
+    <col min="19" max="19" width="29" style="37" customWidth="1" outlineLevel="2"/>
+    <col min="20" max="22" width="18.33203125" style="37" customWidth="1" outlineLevel="2"/>
+    <col min="23" max="23" width="17.1640625" style="37" bestFit="1" customWidth="1" outlineLevel="1"/>
+    <col min="24" max="25" width="9.1640625" style="37" hidden="1" customWidth="1" outlineLevel="2"/>
+    <col min="26" max="26" width="9.33203125" style="37" hidden="1" customWidth="1" outlineLevel="2"/>
+    <col min="27" max="27" width="37.5" style="35" hidden="1" customWidth="1" outlineLevel="2"/>
+    <col min="28" max="33" width="19.33203125" style="38" hidden="1" customWidth="1" outlineLevel="2"/>
+    <col min="34" max="34" width="19.33203125" style="38" customWidth="1" outlineLevel="1" collapsed="1"/>
+    <col min="35" max="38" width="19.33203125" style="38" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36">
+    <row r="1" spans="1:38">
       <c r="A1" s="7" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="2" spans="1:36" ht="16" customHeight="1">
-      <c r="AG2" s="72" t="s">
+    <row r="2" spans="1:38" ht="16" customHeight="1">
+      <c r="AI2" s="72" t="s">
         <v>1</v>
       </c>
-      <c r="AH2" s="72" t="s">
+      <c r="AJ2" s="72" t="s">
         <v>2</v>
       </c>
-      <c r="AI2" s="72" t="s">
+      <c r="AK2" s="72" t="s">
         <v>3</v>
       </c>
-      <c r="AJ2" s="72" t="s">
+      <c r="AL2" s="72" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:36">
+    <row r="3" spans="1:38">
       <c r="A3" s="52"/>
-      <c r="AG3" s="32" t="str">
+      <c r="AI3" s="32" t="str">
         <f>IF(各種設定!$G$11=0,"",各種設定!$G$11)</f>
         <v>ja</v>
       </c>
-      <c r="AH3" s="32" t="str">
+      <c r="AJ3" s="32" t="str">
         <f>IF(各種設定!$G$12=0,"",各種設定!$G$12)</f>
         <v/>
       </c>
-      <c r="AI3" s="32" t="str">
+      <c r="AK3" s="32" t="str">
         <f>IF(各種設定!$G$13=0,"",各種設定!$G$13)</f>
         <v/>
       </c>
-      <c r="AJ3" s="32" t="str">
+      <c r="AL3" s="32" t="str">
         <f>IF(各種設定!$G$14=0,"",各種設定!$G$14)</f>
         <v/>
       </c>
     </row>
-    <row r="4" spans="1:36">
+    <row r="4" spans="1:38">
       <c r="A4" s="34"/>
     </row>
-    <row r="5" spans="1:36" s="1" customFormat="1" ht="43" customHeight="1">
+    <row r="5" spans="1:38" s="1" customFormat="1" ht="43" customHeight="1">
       <c r="A5" s="103" t="s">
         <v>5</v>
       </c>
@@ -12090,64 +12411,70 @@
         <v>21</v>
       </c>
       <c r="R5" s="75" t="s">
+        <v>283</v>
+      </c>
+      <c r="S5" s="75" t="s">
         <v>22</v>
       </c>
-      <c r="S5" s="75" t="s">
+      <c r="T5" s="75" t="s">
         <v>23</v>
       </c>
-      <c r="T5" s="75" t="s">
+      <c r="U5" s="75" t="s">
         <v>24</v>
       </c>
-      <c r="U5" s="75" t="s">
+      <c r="V5" s="75" t="s">
+        <v>284</v>
+      </c>
+      <c r="W5" s="75" t="s">
         <v>25</v>
       </c>
-      <c r="V5" s="109" t="s">
+      <c r="X5" s="109" t="s">
         <v>26</v>
       </c>
-      <c r="W5" s="109" t="s">
+      <c r="Y5" s="109" t="s">
         <v>27</v>
       </c>
-      <c r="X5" s="109" t="s">
+      <c r="Z5" s="109" t="s">
         <v>28</v>
       </c>
-      <c r="Y5" s="109" t="s">
+      <c r="AA5" s="109" t="s">
         <v>29</v>
       </c>
-      <c r="Z5" s="109" t="s">
+      <c r="AB5" s="109" t="s">
         <v>30</v>
       </c>
-      <c r="AA5" s="109" t="s">
+      <c r="AC5" s="109" t="s">
         <v>31</v>
       </c>
-      <c r="AB5" s="109" t="s">
+      <c r="AD5" s="109" t="s">
         <v>32</v>
       </c>
-      <c r="AC5" s="109" t="s">
+      <c r="AE5" s="109" t="s">
         <v>33</v>
       </c>
-      <c r="AD5" s="109" t="s">
+      <c r="AF5" s="109" t="s">
         <v>34</v>
       </c>
-      <c r="AE5" s="109" t="s">
+      <c r="AG5" s="109" t="s">
         <v>35</v>
       </c>
-      <c r="AF5" s="75" t="s">
+      <c r="AH5" s="75" t="s">
         <v>36</v>
       </c>
-      <c r="AG5" s="74" t="s">
+      <c r="AI5" s="74" t="s">
         <v>37</v>
       </c>
-      <c r="AH5" s="76" t="s">
+      <c r="AJ5" s="76" t="s">
         <v>38</v>
       </c>
-      <c r="AI5" s="76" t="s">
+      <c r="AK5" s="76" t="s">
         <v>39</v>
       </c>
-      <c r="AJ5" s="76" t="s">
+      <c r="AL5" s="76" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="6" spans="1:36" s="1" customFormat="1">
+    <row r="6" spans="1:38" s="1" customFormat="1">
       <c r="A6" s="80"/>
       <c r="B6" s="82"/>
       <c r="C6" s="81"/>
@@ -12168,12 +12495,12 @@
       <c r="O6" s="88"/>
       <c r="P6" s="88"/>
       <c r="Q6" s="88"/>
-      <c r="R6" s="86"/>
+      <c r="R6" s="88"/>
       <c r="S6" s="86"/>
-      <c r="T6" s="57"/>
-      <c r="U6" s="92"/>
-      <c r="V6" s="91"/>
-      <c r="W6" s="91"/>
+      <c r="T6" s="86"/>
+      <c r="U6" s="57"/>
+      <c r="V6" s="57"/>
+      <c r="W6" s="92"/>
       <c r="X6" s="91"/>
       <c r="Y6" s="91"/>
       <c r="Z6" s="91"/>
@@ -12182,13 +12509,15 @@
       <c r="AC6" s="91"/>
       <c r="AD6" s="91"/>
       <c r="AE6" s="91"/>
-      <c r="AF6" s="104"/>
-      <c r="AG6" s="81"/>
-      <c r="AH6" s="54"/>
-      <c r="AI6" s="42"/>
-      <c r="AJ6" s="39"/>
-    </row>
-    <row r="7" spans="1:36" s="1" customFormat="1">
+      <c r="AF6" s="91"/>
+      <c r="AG6" s="91"/>
+      <c r="AH6" s="104"/>
+      <c r="AI6" s="81"/>
+      <c r="AJ6" s="54"/>
+      <c r="AK6" s="42"/>
+      <c r="AL6" s="39"/>
+    </row>
+    <row r="7" spans="1:38" s="1" customFormat="1">
       <c r="A7" s="89"/>
       <c r="B7" s="91"/>
       <c r="C7" s="90"/>
@@ -12209,12 +12538,12 @@
       <c r="O7" s="47"/>
       <c r="P7" s="47"/>
       <c r="Q7" s="47"/>
-      <c r="R7" s="57"/>
+      <c r="R7" s="47"/>
       <c r="S7" s="57"/>
       <c r="T7" s="57"/>
-      <c r="U7" s="92"/>
+      <c r="U7" s="57"/>
       <c r="V7" s="57"/>
-      <c r="W7" s="57"/>
+      <c r="W7" s="92"/>
       <c r="X7" s="57"/>
       <c r="Y7" s="57"/>
       <c r="Z7" s="57"/>
@@ -12223,13 +12552,15 @@
       <c r="AC7" s="57"/>
       <c r="AD7" s="57"/>
       <c r="AE7" s="57"/>
-      <c r="AF7" s="105"/>
-      <c r="AG7" s="90"/>
-      <c r="AH7" s="54"/>
-      <c r="AI7" s="42"/>
-      <c r="AJ7" s="39"/>
-    </row>
-    <row r="8" spans="1:36" s="1" customFormat="1">
+      <c r="AF7" s="57"/>
+      <c r="AG7" s="57"/>
+      <c r="AH7" s="105"/>
+      <c r="AI7" s="90"/>
+      <c r="AJ7" s="54"/>
+      <c r="AK7" s="42"/>
+      <c r="AL7" s="39"/>
+    </row>
+    <row r="8" spans="1:38" s="1" customFormat="1">
       <c r="A8" s="80"/>
       <c r="B8" s="82"/>
       <c r="C8" s="95"/>
@@ -12250,12 +12581,12 @@
       <c r="O8" s="88"/>
       <c r="P8" s="88"/>
       <c r="Q8" s="88"/>
-      <c r="R8" s="96"/>
+      <c r="R8" s="88"/>
       <c r="S8" s="96"/>
-      <c r="T8" s="106"/>
-      <c r="U8" s="92"/>
-      <c r="V8" s="101"/>
-      <c r="W8" s="101"/>
+      <c r="T8" s="96"/>
+      <c r="U8" s="106"/>
+      <c r="V8" s="106"/>
+      <c r="W8" s="92"/>
       <c r="X8" s="101"/>
       <c r="Y8" s="101"/>
       <c r="Z8" s="101"/>
@@ -12264,13 +12595,15 @@
       <c r="AC8" s="101"/>
       <c r="AD8" s="101"/>
       <c r="AE8" s="101"/>
-      <c r="AF8" s="107"/>
-      <c r="AG8" s="81"/>
-      <c r="AH8" s="54"/>
-      <c r="AI8" s="42"/>
-      <c r="AJ8" s="39"/>
-    </row>
-    <row r="9" spans="1:36">
+      <c r="AF8" s="101"/>
+      <c r="AG8" s="101"/>
+      <c r="AH8" s="107"/>
+      <c r="AI8" s="81"/>
+      <c r="AJ8" s="54"/>
+      <c r="AK8" s="42"/>
+      <c r="AL8" s="39"/>
+    </row>
+    <row r="9" spans="1:38">
       <c r="A9" s="89"/>
       <c r="B9" s="99"/>
       <c r="C9" s="90"/>
@@ -12294,9 +12627,9 @@
       <c r="R9" s="47"/>
       <c r="S9" s="47"/>
       <c r="T9" s="47"/>
-      <c r="U9" s="92"/>
+      <c r="U9" s="47"/>
       <c r="V9" s="47"/>
-      <c r="W9" s="47"/>
+      <c r="W9" s="92"/>
       <c r="X9" s="47"/>
       <c r="Y9" s="47"/>
       <c r="Z9" s="47"/>
@@ -12305,13 +12638,15 @@
       <c r="AC9" s="47"/>
       <c r="AD9" s="47"/>
       <c r="AE9" s="47"/>
-      <c r="AF9" s="108"/>
-      <c r="AG9" s="98"/>
-      <c r="AH9" s="122"/>
-      <c r="AI9" s="42"/>
-      <c r="AJ9" s="39"/>
-    </row>
-    <row r="10" spans="1:36">
+      <c r="AF9" s="47"/>
+      <c r="AG9" s="47"/>
+      <c r="AH9" s="108"/>
+      <c r="AI9" s="98"/>
+      <c r="AJ9" s="122"/>
+      <c r="AK9" s="42"/>
+      <c r="AL9" s="39"/>
+    </row>
+    <row r="10" spans="1:38">
       <c r="A10" s="80"/>
       <c r="B10" s="102"/>
       <c r="C10" s="81"/>
@@ -12334,10 +12669,10 @@
       <c r="Q10" s="88"/>
       <c r="R10" s="88"/>
       <c r="S10" s="88"/>
-      <c r="T10" s="47"/>
-      <c r="U10" s="92"/>
+      <c r="T10" s="88"/>
+      <c r="U10" s="47"/>
       <c r="V10" s="47"/>
-      <c r="W10" s="47"/>
+      <c r="W10" s="92"/>
       <c r="X10" s="47"/>
       <c r="Y10" s="47"/>
       <c r="Z10" s="47"/>
@@ -12346,13 +12681,15 @@
       <c r="AC10" s="47"/>
       <c r="AD10" s="47"/>
       <c r="AE10" s="47"/>
-      <c r="AF10" s="108"/>
-      <c r="AG10" s="95"/>
-      <c r="AH10" s="122"/>
-      <c r="AI10" s="42"/>
-      <c r="AJ10" s="39"/>
-    </row>
-    <row r="11" spans="1:36">
+      <c r="AF10" s="47"/>
+      <c r="AG10" s="47"/>
+      <c r="AH10" s="108"/>
+      <c r="AI10" s="95"/>
+      <c r="AJ10" s="122"/>
+      <c r="AK10" s="42"/>
+      <c r="AL10" s="39"/>
+    </row>
+    <row r="11" spans="1:38">
       <c r="A11" s="89"/>
       <c r="B11" s="98"/>
       <c r="C11" s="98"/>
@@ -12376,9 +12713,9 @@
       <c r="R11" s="47"/>
       <c r="S11" s="47"/>
       <c r="T11" s="47"/>
-      <c r="U11" s="92"/>
+      <c r="U11" s="47"/>
       <c r="V11" s="47"/>
-      <c r="W11" s="47"/>
+      <c r="W11" s="92"/>
       <c r="X11" s="47"/>
       <c r="Y11" s="47"/>
       <c r="Z11" s="47"/>
@@ -12387,13 +12724,15 @@
       <c r="AC11" s="47"/>
       <c r="AD11" s="47"/>
       <c r="AE11" s="47"/>
-      <c r="AF11" s="108"/>
-      <c r="AG11" s="98"/>
-      <c r="AH11" s="122"/>
-      <c r="AI11" s="42"/>
-      <c r="AJ11" s="39"/>
-    </row>
-    <row r="12" spans="1:36">
+      <c r="AF11" s="47"/>
+      <c r="AG11" s="47"/>
+      <c r="AH11" s="108"/>
+      <c r="AI11" s="98"/>
+      <c r="AJ11" s="122"/>
+      <c r="AK11" s="42"/>
+      <c r="AL11" s="39"/>
+    </row>
+    <row r="12" spans="1:38">
       <c r="A12" s="80"/>
       <c r="B12" s="95"/>
       <c r="C12" s="95"/>
@@ -12416,10 +12755,10 @@
       <c r="Q12" s="88"/>
       <c r="R12" s="88"/>
       <c r="S12" s="88"/>
-      <c r="T12" s="47"/>
-      <c r="U12" s="92"/>
+      <c r="T12" s="88"/>
+      <c r="U12" s="47"/>
       <c r="V12" s="47"/>
-      <c r="W12" s="47"/>
+      <c r="W12" s="92"/>
       <c r="X12" s="47"/>
       <c r="Y12" s="47"/>
       <c r="Z12" s="47"/>
@@ -12428,13 +12767,15 @@
       <c r="AC12" s="47"/>
       <c r="AD12" s="47"/>
       <c r="AE12" s="47"/>
-      <c r="AF12" s="108"/>
-      <c r="AG12" s="95"/>
-      <c r="AH12" s="122"/>
-      <c r="AI12" s="42"/>
-      <c r="AJ12" s="39"/>
-    </row>
-    <row r="13" spans="1:36">
+      <c r="AF12" s="47"/>
+      <c r="AG12" s="47"/>
+      <c r="AH12" s="108"/>
+      <c r="AI12" s="95"/>
+      <c r="AJ12" s="122"/>
+      <c r="AK12" s="42"/>
+      <c r="AL12" s="39"/>
+    </row>
+    <row r="13" spans="1:38">
       <c r="A13" s="89"/>
       <c r="B13" s="98"/>
       <c r="C13" s="98"/>
@@ -12458,9 +12799,9 @@
       <c r="R13" s="47"/>
       <c r="S13" s="47"/>
       <c r="T13" s="47"/>
-      <c r="U13" s="92"/>
+      <c r="U13" s="47"/>
       <c r="V13" s="47"/>
-      <c r="W13" s="47"/>
+      <c r="W13" s="92"/>
       <c r="X13" s="47"/>
       <c r="Y13" s="47"/>
       <c r="Z13" s="47"/>
@@ -12469,15 +12810,17 @@
       <c r="AC13" s="47"/>
       <c r="AD13" s="47"/>
       <c r="AE13" s="47"/>
-      <c r="AF13" s="108"/>
-      <c r="AG13" s="98"/>
-      <c r="AH13" s="51"/>
-      <c r="AI13" s="42"/>
-      <c r="AJ13" s="39"/>
+      <c r="AF13" s="47"/>
+      <c r="AG13" s="47"/>
+      <c r="AH13" s="108"/>
+      <c r="AI13" s="98"/>
+      <c r="AJ13" s="51"/>
+      <c r="AK13" s="42"/>
+      <c r="AL13" s="39"/>
     </row>
   </sheetData>
   <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U6:U13 E6:M13" xr:uid="{00000000-0002-0000-0800-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W6:W13 E6:M13" xr:uid="{00000000-0002-0000-0800-000000000000}">
       <formula1>"○"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N6:N13" xr:uid="{00000000-0002-0000-0800-000001000000}">
